--- a/assets/archivos/TRANSPARENCIA/ART 63 COMUNES 2024/2DO_TRIMESTRE/FRACCIONES XI-XX/FRACC XIX/LTAIPT_A63F19.xlsx
+++ b/assets/archivos/TRANSPARENCIA/ART 63 COMUNES 2024/2DO_TRIMESTRE/FRACCIONES XI-XX/FRACC XIX/LTAIPT_A63F19.xlsx
@@ -1,10 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <fileVersion appName="xl" lastEdited="5" lowestEdited="5" rupBuild="9303"/>
-  <workbookPr defaultThemeVersion="124226"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="26327"/>
+  <workbookPr defaultThemeVersion="166925"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\COBAT\Downloads\SEGUNDO TRIMESTRE ABRIL-JUNIO 2024\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{124F38E8-C8BB-49A6-BAF6-775D3259B3F8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="330" yWindow="555" windowWidth="19815" windowHeight="8385"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Informacion" sheetId="1" r:id="rId1"/>
@@ -39,7 +45,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1408" uniqueCount="389">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2059" uniqueCount="435">
   <si>
     <t>48968</t>
   </si>
@@ -168,9 +174,6 @@
   </si>
   <si>
     <t>436110</t>
-  </si>
-  <si>
-    <t>436100</t>
   </si>
   <si>
     <t>436105</t>
@@ -266,241 +269,277 @@
 Tabla_436104</t>
   </si>
   <si>
-    <t>Hipervínculo al Catálogo Nacional de Regulaciones, Tramites y Servicios o al sistema homólogo</t>
+    <t>Hipervínculo al Catálogo Nacional de Regulaciones, Trámites y Servicios o al sistema homólogo</t>
   </si>
   <si>
     <t>Área(s) responsable(s) que genera(n), posee(n), publica(n) y actualizan la información</t>
   </si>
   <si>
-    <t>Fecha de validación</t>
-  </si>
-  <si>
     <t>Fecha de actualización</t>
   </si>
   <si>
     <t>Nota</t>
   </si>
   <si>
-    <t>2023</t>
+    <t>2024</t>
+  </si>
+  <si>
+    <t>Ficha de Examen de Selección</t>
+  </si>
+  <si>
+    <t>Directo</t>
+  </si>
+  <si>
+    <t>Aspirantes a ingresar a planteles del Colegio de Bachilleres del Estado de Tlaxcala</t>
+  </si>
+  <si>
+    <t>Documento que permite participar en el proceso de selección para ingresar a un plantel del Colegio de Bachilleres del Estado de Tlaxcala</t>
+  </si>
+  <si>
+    <t>Presencial</t>
+  </si>
+  <si>
+    <t>Pago de Derechos, Productos y Aprovechamientos</t>
+  </si>
+  <si>
+    <t>Solicitud de aspirante, copia de Acta de Nacimiento, dos fotografías tamaño infantil (blanco y negro) fondo blanco, frente y oídos descubiertos, hombres sin bigote y sin barba, mujeres sin aretes y sin maquillaje, copia de Certificado de Secundaria o constancia de que cursa el tercer año, copias de boletas de primero y segundo año de Secundaria</t>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t>Un día hábil</t>
+  </si>
+  <si>
+    <t>Inmediato</t>
+  </si>
+  <si>
+    <t>16344185</t>
+  </si>
+  <si>
+    <t>Supervisar el registro y control escolar del estudiantado en los planteles</t>
+  </si>
+  <si>
+    <t>Ley que Crea el Colegio de Bachilleres del Estado de Tlaxcala Capítulo III El Gobierno del Colegio de Bachilleres del Estado de Tlaxcala Artículo 12 Fracción II</t>
+  </si>
+  <si>
+    <t>Instituciones bancarias (Bancomer, Santander, HSBC, Scotiabank, Banorte, Citibanamex) Pago de Servicios Banca Electrónica Clientes Bancomer / HSBC, Transferencia electrónica de otros bancos (Bancomer, HSBC), Tiendas ANTAD (Chedraui, Farmacias del Ahorro, Soriana, Multired Global, Extra, Transfer, Bodega Aurrera, Walmart, SAM´S Club, Superama, Elektra, Banco Azteca) Receptoras de pago con cobro de comisión (Telecomm, HSBC RAP 2900, Oxxo)</t>
+  </si>
+  <si>
+    <t>Constitución Política de los Estados Unidos Mexicanos Título Primero Capítulo I de los Derechos Humanos y sus Garantías Artículo 3. Ley que Crea el Colegio de Bachilleres del Estado de Tlaxcala Capítulo I personalidad y objetivos Artículo 2 Fracción II. Reglamento Interior del Organismo Público Desconcentrado Colegio de Bachilleres del Estado de Tlaxcala Artículo 26 Fracción VI</t>
+  </si>
+  <si>
+    <t>Queja ante el Órgano de Control Interno del Sujeto Obligado</t>
+  </si>
+  <si>
+    <t>Solicitud de aspirante, Pago de Derechos, Productos y Aprovechamientos</t>
+  </si>
+  <si>
+    <t>https://www.tlaxcaladigital.gob.mx/Inicio</t>
+  </si>
+  <si>
+    <t>Dirección Académica</t>
+  </si>
+  <si>
+    <t>Inscripción a Ciclo Escolar</t>
+  </si>
+  <si>
+    <t>Aspirantes seleccionados y seleccionadas para ingresar a planteles del Colegio de Bachilleres del Estado de Tlaxcala</t>
+  </si>
+  <si>
+    <t>Proceso mediante el cual, se formaliza el acceso de los y las estudiantes, al primer periodo escolar</t>
+  </si>
+  <si>
+    <t>Acta de Nacimiento (original y copia), seis fotografías tamaño infantil (blanco y negro) fondo blanco, frente y oídos descubiertos, hombres sin bigote y sin barba, mujeres sin aretes y sin maquillaje, Certificado de Secundaria (original y copia), Clave Única de Registro de Población (original y copia), Certificado Médico expedido por el Sector Salud Secretaría de Salud, Instituto de Seguridad y Servicios Sociales de los Trabajadores del Estado o Instituto Mexicano del Seguro Social, con biometría hemática, copia de comprobante de domicilio</t>
+  </si>
+  <si>
+    <t>Un semestre</t>
+  </si>
+  <si>
+    <t>16344186</t>
+  </si>
+  <si>
+    <t>Constitución Política de los Estados Unidos Mexicanos Título Primero Capítulo I de los Derechos Humanos y sus Garantías Artículo 3. Ley que Crea el Colegio de Bachilleres del Estado de Tlaxcala Capítulo I personalidad y objetivos Artículo 2 Fracción II. Reglamento General de la Ley que Crea el Colegio de Bachilleres del Estado de Tlaxcala Capítulo Décimo de los alumnos Artículo 50. Reglamento Interior del Organismo Público Desconcentrado Colegio de Bachilleres del Estado de Tlaxcala Artículo 26 Fracción II</t>
+  </si>
+  <si>
+    <t>Acta de Nacimiento (copia), seis fotografías tamaño infantil (blanco y negro) fondo blanco, frente y oídos descubiertos, hombres sin bigote y sin barba, mujeres sin aretes y sin maquillaje, Certificado de Secundaria (copia), Clave Única de Registro de Población (copia), Certificado Médico expedido por el Sector Salud Secretaría de Salud, Instituto de Seguridad y Servicios Sociales de los Trabajadores del Estado o Instituto Mexicano del Seguro Social, con biometría hemática, copia de comprobante de domicilio; Pago de Derechos, Productos y Aprovechamientos</t>
+  </si>
+  <si>
+    <t>Derecho a Laboratorio</t>
+  </si>
+  <si>
+    <t>Estudiantes del Colegio de Bachilleres del Estado de Tlaxcala</t>
+  </si>
+  <si>
+    <t>Uso de las instalaciones de los laboratorios en los planteles del Colegio de Bachilleres del Estado de Tlaxcala</t>
+  </si>
+  <si>
+    <t>Ficha de Pago</t>
+  </si>
+  <si>
+    <t>16341253</t>
+  </si>
+  <si>
+    <t>Reglamento General de la Ley que Crea el Colegio de Bachilleres del Estado de Tlaxcala Capítulo Décimo de los alumnos Artículo 55 Fracción VIII. Reglamento Interior del Organismo Público Desconcentrado Colegio de Bachilleres del Estado de Tlaxcala Artículo 24 Fracción I, Fracción VII</t>
+  </si>
+  <si>
+    <t>Reinscripción por Semestre</t>
+  </si>
+  <si>
+    <t>Estudiantes regulares del Colegio de Bachilleres del Estado de Tlaxcala</t>
+  </si>
+  <si>
+    <t>Servicio que permite formalizar la reinscripción de segundo a sexto semestre a los planteles del Colegio de Bachilleres del Estado de Tlaxcala</t>
+  </si>
+  <si>
+    <t>Ser estudiante regular, no adeudar más de tres Unidades de Aprendizaje Curricular del Plan de Estudios del Colegio de Bachilleres del Estado de Tlaxcala, boleta de estudios del último semestre concluido</t>
+  </si>
+  <si>
+    <t>http://cobatlaxcala.edu.mx/transparencia/TRANSPARENCIA%202022/Subdireccion%20Servicios%20Educativos/1er_Trimestre/REINSCRIPCION%20POR%20SEMESTRE.pdf</t>
+  </si>
+  <si>
+    <t>09/05/2022</t>
+  </si>
+  <si>
+    <t>16341252</t>
+  </si>
+  <si>
+    <t>Boleta de estudios del último semestre concluido, Pago de Derechos, Productos y Aprovechamientos</t>
+  </si>
+  <si>
+    <t>Examen Extraordinario</t>
+  </si>
+  <si>
+    <t>Instrumento aplicado a los y las estudiantes que han reprobado la evaluación ordinaria, solo comprenderá los periodos parciales no acreditados y el instrumento será elaborado por el/la docente del campo disciplinar</t>
+  </si>
+  <si>
+    <t>Solicitud de examen en su plantel</t>
+  </si>
+  <si>
+    <t>Diez días hábiles</t>
+  </si>
+  <si>
+    <t>16344184</t>
+  </si>
+  <si>
+    <t>Supervisar que la documentación de evaluaciones semestrales y de regularización, emitida por los planteles, se encuentre correcta</t>
+  </si>
+  <si>
+    <t>Reglamento General de la Ley que Crea el Colegio de Bachilleres del Estado de Tlaxcala Capítulo Décimo de los alumnos Artículo 55 Fracción II. Reglamento Interior del Organismo Público Desconcentrado Colegio de Bachilleres del Estado de Tlaxcala Artículo 26 Fracción V</t>
+  </si>
+  <si>
+    <t>Solicitud de examen en su plantel, Pago de Derechos, Productos y Aprovechamientos</t>
   </si>
   <si>
     <t>Examen a Título de Suficiencia</t>
   </si>
   <si>
-    <t>Directo</t>
-  </si>
-  <si>
-    <t>Estudiantes del Colegio de Bachilleres del Estado de Tlaxcala</t>
-  </si>
-  <si>
-    <t>Documento que permite participar en el proceso de selección para ingresar a un plantel del Colegio de Bachilleres del Estado de Tlaxcala</t>
-  </si>
-  <si>
-    <t>Presencial</t>
-  </si>
-  <si>
-    <t>Pago de Derechos, Productos y Aprovechamientos</t>
-  </si>
-  <si>
-    <t>Solicitud de examen en su plantel</t>
+    <t>Instrumento aplicado a los y las estudiantes que han reprobado la evaluación extraordinaria, comprenderá todo el programa y el instrumento será elaborado por el/la docente del campo disciplinar</t>
+  </si>
+  <si>
+    <t>16344183</t>
+  </si>
+  <si>
+    <t>16341250</t>
+  </si>
+  <si>
+    <t>16341249</t>
+  </si>
+  <si>
+    <t>16341251</t>
+  </si>
+  <si>
+    <t>16341248</t>
+  </si>
+  <si>
+    <t>16344188</t>
+  </si>
+  <si>
+    <t>16344187</t>
+  </si>
+  <si>
+    <t>15986461</t>
+  </si>
+  <si>
+    <t>150</t>
+  </si>
+  <si>
+    <t>15986464</t>
+  </si>
+  <si>
+    <t>15986463</t>
+  </si>
+  <si>
+    <t>614</t>
+  </si>
+  <si>
+    <t>15986462</t>
+  </si>
+  <si>
+    <t>15986459</t>
+  </si>
+  <si>
+    <t>103</t>
+  </si>
+  <si>
+    <t>15986460</t>
+  </si>
+  <si>
+    <t>94</t>
+  </si>
+  <si>
+    <t>81AF4ED8525E9393A103B52E382C1119</t>
+  </si>
+  <si>
+    <t>01/04/2024</t>
+  </si>
+  <si>
+    <t>30/06/2024</t>
   </si>
   <si>
     <t>http://cobatlaxcala.edu.mx/transparencia/TRANSPARENCIA%202022/Subdireccion%20Servicios%20Educativos/1er_Trimestre/EXAMEN%20A%20TITULO%20DE%20SUFICIENCIA.pdf</t>
   </si>
   <si>
-    <t>09/05/2022</t>
-  </si>
-  <si>
-    <t>Diez días hábiles</t>
-  </si>
-  <si>
-    <t/>
-  </si>
-  <si>
-    <t>Inmediato</t>
-  </si>
-  <si>
-    <t>8125218</t>
-  </si>
-  <si>
-    <t>Supervisar que la documentación de evaluaciones semestrales y de regularización, emitida por los planteles, se encuentre correcta</t>
-  </si>
-  <si>
-    <t>103</t>
-  </si>
-  <si>
-    <t>Ley que Crea el Colegio de Bachilleres del Estado de Tlaxcala Capítulo III El Gobierno del Colegio de Bachilleres del Estado de Tlaxcala Artículo 12 Fracción II</t>
-  </si>
-  <si>
-    <t>Instituciones bancarias (Bancomer, Santander, HSBC, Scotiabank, Banorte, Citibanamex) Pago de Servicios Banca Electrónica Clientes Bancomer / HSBC, Transferencia electrónica de otros bancos (Bancomer, HSBC), Tiendas ANTAD (Chedraui, Farmacias del Ahorro, Soriana, Multired Global, Extra, Transfer, Bodega Aurrera, Walmart, SAM´S Club, Superama, Elektra, Banco Azteca) Receptoras de pago con cobro de comisión (Telecomm, HSBC RAP 2900, Oxxo)</t>
-  </si>
-  <si>
-    <t>Reglamento General de la Ley que Crea el Colegio de Bachilleres del Estado de Tlaxcala Capítulo Décimo de los alumnos Artículo 55 Fracción II. Reglamento Interior del Organismo Público Desconcentrado Colegio de Bachilleres del Estado de Tlaxcala Artículo 26 Fracción V</t>
-  </si>
-  <si>
-    <t>Queja ante el Órgano de Control Interno del Sujeto Obligado</t>
-  </si>
-  <si>
-    <t>Solicitud de examen en su plantel, Pago de Derechos, Productos y Aprovechamientos</t>
-  </si>
-  <si>
-    <t>http://www.tlaxcalaenlinea.gob.mx</t>
-  </si>
-  <si>
-    <t>Dirección Académica</t>
-  </si>
-  <si>
-    <t>Inscripción a Ciclo Escolar</t>
-  </si>
-  <si>
-    <t>Aspirantes seleccionados y seleccionadas para ingresar a planteles del Colegio de Bachilleres del Estado de Tlaxcala</t>
-  </si>
-  <si>
-    <t>Proceso mediante el cual, se formaliza el acceso de estudiantes, al primer periodo escolar</t>
-  </si>
-  <si>
-    <t>Acta de Nacimiento (original y copia), seis fotografías tamaño infantil (blanco y negro) fondo blanco, frente y oídos descubiertos, hombres sin bigote y sin barba, mujeres sin aretes y sin maquillaje, Certificado de Secundaria (original y copia), Clave Única de Registro de Población (original y copia), Certificado Médico expedido por el Sector Salud Secretaría de Salud, Instituto de Seguridad y Servicios Sociales de los Trabajadores del Estado o Instituto Mexicano del Seguro Social, con biometría hemática, copia de comprobante de domicilio</t>
-  </si>
-  <si>
-    <t>Un día hábil</t>
-  </si>
-  <si>
-    <t>Un semestre</t>
-  </si>
-  <si>
-    <t>8125221</t>
-  </si>
-  <si>
-    <t>Supervisar el registro y control escolar del estudiantado en los planteles</t>
-  </si>
-  <si>
-    <t>614</t>
-  </si>
-  <si>
-    <t>Constitución Política de los Estados Unidos Mexicanos Título Primero Capítulo I de los Derechos Humanos y sus Garantías Artículo 3. Ley que Crea el Colegio de Bachilleres del Estado de Tlaxcala Capítulo I personalidad y objetivos Artículo 2 Fracción II. Reglamento General de la Ley que Crea el Colegio de Bachilleres del Estado de Tlaxcala Capítulo Décimo de los alumnos Artículo 50. Reglamento Interior del Organismo Público Desconcentrado Colegio de Bachilleres del Estado de Tlaxcala Artículo 26 Fracción II</t>
-  </si>
-  <si>
-    <t>Acta de Nacimiento (copia), seis fotografías tamaño infantil (blanco y negro) fondo blanco, frente y oídos descubiertos, hombres sin bigote y sin barba, mujeres sin aretes y sin maquillaje, Certificado de Secundaria (copia), Clave Única de Registro de Población (copia), Certificado Médico expedido por el Sector Salud Secretaría de Salud, Instituto de Seguridad y Servicios Sociales de los Trabajadores del Estado o Instituto Mexicano del Seguro Social, con biometría hemática, copia de comprobante de domicilio; Pago de Derechos, Productos y Aprovechamientos</t>
-  </si>
-  <si>
-    <t>Examen Extraordinario</t>
-  </si>
-  <si>
-    <t>Instrumento aplicado a estudiantes que han reprobado la evaluación ordinaria, solo comprenderá los periodos parciales no acreditados y el instrumento será elaborado por el/la docente del campo disciplinar</t>
+    <t>14416370</t>
+  </si>
+  <si>
+    <t>02/07/2024</t>
+  </si>
+  <si>
+    <t>Durante el periodo del 01 de abril de 2024 al 30 de junio de 2024, el Colegio de Bachilleres del Estado de Tlaxcala no publica información inherente al Plazo con el que cuenta el sujeto obligado para prevenir al solicitante y Plazo con el que cuenta el solicitante para cumplir con la prevención según Artículo 46 Fracción XI de la Ley General de Mejora Regulatoria</t>
+  </si>
+  <si>
+    <t>B09A1972064FCFDD6EE5CB531980423B</t>
+  </si>
+  <si>
+    <t>14416372</t>
+  </si>
+  <si>
+    <t>D5E5D9C1AD1A635E69F69438AE55401A</t>
+  </si>
+  <si>
+    <t>14416374</t>
+  </si>
+  <si>
+    <t>1D47F265AA47ACF3D2FE71466056DAF4</t>
+  </si>
+  <si>
+    <t>14416375</t>
+  </si>
+  <si>
+    <t>FF004168F8109C0A7CBE5B22990D4803</t>
+  </si>
+  <si>
+    <t>14416373</t>
+  </si>
+  <si>
+    <t>CEADEB250E8C69217A8F3CE105813CBB</t>
   </si>
   <si>
     <t>http://cobatlaxcala.edu.mx/transparencia/TRANSPARENCIA%202022/Subdireccion%20Servicios%20Educativos/1er_Trimestre/EXAMEN%20EXTRAORDINARIO.pdf</t>
   </si>
   <si>
-    <t>8125219</t>
-  </si>
-  <si>
-    <t>94</t>
-  </si>
-  <si>
-    <t>Ficha de Examen de Selección</t>
-  </si>
-  <si>
-    <t>Aspirantes a ingresar a planteles del Colegio de Bachilleres del Estado de Tlaxcala</t>
-  </si>
-  <si>
-    <t>Solicitud de aspirante, copia de Acta de Nacimiento, dos fotografías tamaño infantil (blanco y negro) fondo blanco, frente y oídos descubiertos, hombres sin bigote y sin barba, mujeres sin aretes y sin maquillaje, copia de Certificado de Secundaria o constancia de que cursa el tercer año, copias de boletas de primero y segundo año de Secundaria</t>
-  </si>
-  <si>
-    <t>8125220</t>
-  </si>
-  <si>
-    <t>150</t>
-  </si>
-  <si>
-    <t>Constitución Política de los Estados Unidos Mexicanos Título Primero Capítulo I de los Derechos Humanos y sus Garantías Artículo 3. Ley que Crea el Colegio de Bachilleres del Estado de Tlaxcala Capítulo I personalidad y objetivos Artículo 2 Fracción II. Reglamento Interior del Organismo Público Desconcentrado Colegio de Bachilleres del Estado de Tlaxcala Artículo 26 Fracción VI</t>
-  </si>
-  <si>
-    <t>Solicitud de aspirante, Pago de Derechos, Productos y Aprovechamientos</t>
-  </si>
-  <si>
-    <t>Reinscripción por Semestre</t>
-  </si>
-  <si>
-    <t>Estudiantes regulares del Colegio de Bachilleres del Estado de Tlaxcala</t>
-  </si>
-  <si>
-    <t>Servicio que permite formalizar la reinscripción de segundo a sexto semestre a los planteles del Colegio de Bachilleres del Estado de Tlaxcala</t>
-  </si>
-  <si>
-    <t>Ser estudiante regular, no adeudar más de tres Unidades de Aprendizaje Curricular del Plan de Estudios del Colegio de Bachilleres del Estado de Tlaxcala, boleta de estudios del último semestre concluido</t>
-  </si>
-  <si>
-    <t>http://cobatlaxcala.edu.mx/transparencia/TRANSPARENCIA%202022/Subdireccion%20Servicios%20Educativos/1er_Trimestre/REINSCRIPCION%20POR%20SEMESTRE.pdf</t>
-  </si>
-  <si>
-    <t>8125222</t>
-  </si>
-  <si>
-    <t>Boleta de estudios del último semestre concluido, Pago de Derechos, Productos y Aprovechamientos</t>
-  </si>
-  <si>
-    <t>Derecho a Laboratorio</t>
-  </si>
-  <si>
-    <t>Uso de las instalaciones de los laboratorios en los planteles del Colegio de Bachilleres del Estado de Tlaxcala</t>
-  </si>
-  <si>
-    <t>Ficha de Pago</t>
-  </si>
-  <si>
-    <t>8125223</t>
-  </si>
-  <si>
-    <t>Reglamento General de la Ley que Crea el Colegio de Bachilleres del Estado de Tlaxcala Capítulo Décimo de los alumnos Artículo 55 Fracción VIII. Reglamento Interior del Organismo Público Desconcentrado Colegio de Bachilleres del Estado de Tlaxcala Artículo 24 Fracción I, Fracción VII</t>
-  </si>
-  <si>
-    <t>B840F3267CEE78BCFBBF59400594041D</t>
-  </si>
-  <si>
-    <t>01/04/2023</t>
-  </si>
-  <si>
-    <t>30/06/2023</t>
-  </si>
-  <si>
-    <t>8125227</t>
-  </si>
-  <si>
-    <t>20/07/2023</t>
-  </si>
-  <si>
-    <t>Durante el periodo del 01 de abril de 2023 al 30 de junio de 2023, el Colegio de Bachilleres del Estado de Tlaxcala no publica información inherente al Plazo con el que cuenta el sujeto obligado para prevenir al solicitante y Plazo con el que cuenta el solicitante para cumplir con la prevención según Artículo 46 Fracción XI de la Ley General de Mejora Regulatoria</t>
-  </si>
-  <si>
-    <t>AEFBBCCF82118A62869627ECEBDDEE6A</t>
-  </si>
-  <si>
-    <t>8125224</t>
-  </si>
-  <si>
-    <t>57EE9131EBF08FD21C938F805C336FA1</t>
-  </si>
-  <si>
-    <t>8125225</t>
-  </si>
-  <si>
-    <t>92FC4BC0D4458F17700A368E1380E411</t>
-  </si>
-  <si>
-    <t>8125226</t>
-  </si>
-  <si>
-    <t>66B1F626D7C7306FA1C50E920101A77D</t>
-  </si>
-  <si>
-    <t>8125228</t>
-  </si>
-  <si>
-    <t>5349935D12548E1C74101C9B24B62D41</t>
-  </si>
-  <si>
-    <t>8125229</t>
+    <t>14416371</t>
   </si>
   <si>
     <t>Indirecto</t>
@@ -611,13 +650,13 @@
     <t>Teléfono y extensión en su caso, de contacto de la oficina de atención</t>
   </si>
   <si>
-    <t>Medios electrónicos de comunicación de la oficina de atención y/o del responsable del Servicio</t>
+    <t>Medios electrónicos de comunicación de la oficina de atención y/o de la persona responsable del Servicio</t>
   </si>
   <si>
     <t>Horario de atención (días y horas)</t>
   </si>
   <si>
-    <t>3F6F76169DBECD7F3FE5E034A9A49504</t>
+    <t>14CE51798A7166B7E634333131B3DA90</t>
   </si>
   <si>
     <t>Control Escolar de cada uno de los 24 planteles del Colegio de Bachilleres del Estado de Tlaxcala</t>
@@ -656,37 +695,73 @@
     <t>Lunes a viernes de 8:30 a 17:30 horas</t>
   </si>
   <si>
-    <t>4E99472E78F8CCE965DAF4CDD0C57191</t>
-  </si>
-  <si>
-    <t>3F6F76169DBECD7F1CBB14B5A6DD61DF</t>
-  </si>
-  <si>
-    <t>3F6F76169DBECD7F3E3882F81A0F0BE0</t>
-  </si>
-  <si>
-    <t>4E99472E78F8CCE918B00FD805EEAC1E</t>
-  </si>
-  <si>
-    <t>4E99472E78F8CCE9B32A3B557D6F4A8E</t>
-  </si>
-  <si>
-    <t>1015A373E899A23C16F952845136278A</t>
-  </si>
-  <si>
-    <t>1015A373E899A23C1020E546D1E9B4F9</t>
-  </si>
-  <si>
-    <t>1015A373E899A23CEB32D01096BA8BFF</t>
-  </si>
-  <si>
-    <t>1015A373E899A23CC7F238A8376B0139</t>
-  </si>
-  <si>
-    <t>6DA1FEF752400B20DC14FD5847DBC4A9</t>
-  </si>
-  <si>
-    <t>6DA1FEF752400B200B0B792CA99FF501</t>
+    <t>14CE51798A7166B7E01B6C91C2B0D6E5</t>
+  </si>
+  <si>
+    <t>099B6EC7EF68D68EC4E1D3FF5A68961F</t>
+  </si>
+  <si>
+    <t>9F23BE227720651945A4E91199FD628A</t>
+  </si>
+  <si>
+    <t>14CE51798A7166B7B33FB4BD67B0C47E</t>
+  </si>
+  <si>
+    <t>33146F0C594CAF122F680D3DA9021318</t>
+  </si>
+  <si>
+    <t>9F23BE2277206519C13B32E68901F690</t>
+  </si>
+  <si>
+    <t>7ED020F1F1D425E7D8225AF92690B893</t>
+  </si>
+  <si>
+    <t>9F23BE2277206519632C82DDFE177116</t>
+  </si>
+  <si>
+    <t>7ED020F1F1D425E7FCAF89006DE38077</t>
+  </si>
+  <si>
+    <t>1B7BC4CF26343B4770704CF49A3ACCD7</t>
+  </si>
+  <si>
+    <t>1B7BC4CF26343B47DD38DF2C165F8D77</t>
+  </si>
+  <si>
+    <t>5A7BC07C9F455B4D4715B80E2C307A3A</t>
+  </si>
+  <si>
+    <t>5BF51939CB2072C93F0A67FDD300B303</t>
+  </si>
+  <si>
+    <t>5BF51939CB2072C963CD297E9CC5550D</t>
+  </si>
+  <si>
+    <t>5A7BC07C9F455B4D1B1E27288FE24308</t>
+  </si>
+  <si>
+    <t>7C0548F225F9567D6079CC805878B9FF</t>
+  </si>
+  <si>
+    <t>5A7BC07C9F455B4DA13BFDBC61A0EA7F</t>
+  </si>
+  <si>
+    <t>03AD0049D54A80815D5BB9834180F115</t>
+  </si>
+  <si>
+    <t>9B2E22B42403BBDB6F988B443E024D7B</t>
+  </si>
+  <si>
+    <t>7B79FC614A1029D7946BE8206D365018</t>
+  </si>
+  <si>
+    <t>7B79FC614A1029D74E3DEB047DA6017B</t>
+  </si>
+  <si>
+    <t>9B2E22B42403BBDB999EB92DCD400994</t>
+  </si>
+  <si>
+    <t>9B2E22B42403BBDB22AF0832B948550F</t>
   </si>
   <si>
     <t>Corredor</t>
@@ -1031,40 +1106,76 @@
     <t>Clave de la localidad</t>
   </si>
   <si>
-    <t>3F6F76169DBECD7F27E13D0D6380DA2F</t>
-  </si>
-  <si>
-    <t>4E99472E78F8CCE9FC600C5A910DCD1E</t>
-  </si>
-  <si>
-    <t>3F6F76169DBECD7F07491105FA8079E0</t>
-  </si>
-  <si>
-    <t>3F6F76169DBECD7F437EA67512EF825D</t>
-  </si>
-  <si>
-    <t>4E99472E78F8CCE9D35041E47818EEC9</t>
-  </si>
-  <si>
-    <t>4E99472E78F8CCE909EABFEE5E23A68B</t>
-  </si>
-  <si>
-    <t>6DA1FEF752400B20C9796548D11FE38F</t>
-  </si>
-  <si>
-    <t>1015A373E899A23CE7D4ECB2E280DEBE</t>
-  </si>
-  <si>
-    <t>1015A373E899A23CFF2AB07902D03FBA</t>
-  </si>
-  <si>
-    <t>1015A373E899A23CA09F8688E2E2B9B4</t>
-  </si>
-  <si>
-    <t>6DA1FEF752400B20F5EAD65469CA4E18</t>
-  </si>
-  <si>
-    <t>6DA1FEF752400B202E517F0E06AA3282</t>
+    <t>14CE51798A7166B7F82E34C68172FFDE</t>
+  </si>
+  <si>
+    <t>14CE51798A7166B7E5973B08D0802DF5</t>
+  </si>
+  <si>
+    <t>099B6EC7EF68D68E742CA8EB6B10AA1D</t>
+  </si>
+  <si>
+    <t>9F23BE2277206519387498611BC93929</t>
+  </si>
+  <si>
+    <t>14CE51798A7166B745618B4F1EA22CEA</t>
+  </si>
+  <si>
+    <t>14CE51798A7166B7F9842B30A2A3800D</t>
+  </si>
+  <si>
+    <t>9F23BE227720651986F7FACB7C3E9F47</t>
+  </si>
+  <si>
+    <t>7ED020F1F1D425E788EAD8EBD3C26265</t>
+  </si>
+  <si>
+    <t>9F23BE227720651914A8B41CFBD61DCF</t>
+  </si>
+  <si>
+    <t>7ED020F1F1D425E7260DF96D54B36B92</t>
+  </si>
+  <si>
+    <t>1B7BC4CF26343B47E4BE889FDAE5721C</t>
+  </si>
+  <si>
+    <t>1B7BC4CF26343B47A6999114E0C298FF</t>
+  </si>
+  <si>
+    <t>5A7BC07C9F455B4DBCE9DBA56E87F142</t>
+  </si>
+  <si>
+    <t>5BF51939CB2072C99B13224BA4FD2F50</t>
+  </si>
+  <si>
+    <t>5BF51939CB2072C901D4370130EA3598</t>
+  </si>
+  <si>
+    <t>5A7BC07C9F455B4D6E1E6508EF94D8E2</t>
+  </si>
+  <si>
+    <t>7C0548F225F9567D3A491F4F6160EFD3</t>
+  </si>
+  <si>
+    <t>5A7BC07C9F455B4D11120FFFD51C51F8</t>
+  </si>
+  <si>
+    <t>03AD0049D54A80815A1DEE117A83E60B</t>
+  </si>
+  <si>
+    <t>9B2E22B42403BBDB5E10B4DFB67CB93C</t>
+  </si>
+  <si>
+    <t>7B79FC614A1029D72BF8AC4770230609</t>
+  </si>
+  <si>
+    <t>7B79FC614A1029D752B85D7287B738C8</t>
+  </si>
+  <si>
+    <t>9B2E22B42403BBDB8BA6DADB36EEBC9C</t>
+  </si>
+  <si>
+    <t>9B2E22B42403BBDB29602679E36EF12C</t>
   </si>
   <si>
     <t>Viaducto</t>
@@ -1154,7 +1265,7 @@
     <t>Código Postal</t>
   </si>
   <si>
-    <t>3F6F76169DBECD7FAF8EBB67FDFBF2A3</t>
+    <t>14CE51798A7166B7C467E43316974C0E</t>
   </si>
   <si>
     <t>2464628521</t>
@@ -1175,46 +1286,79 @@
     <t>24</t>
   </si>
   <si>
-    <t>90150</t>
-  </si>
-  <si>
-    <t>4E99472E78F8CCE9C25EEB374347278E</t>
-  </si>
-  <si>
-    <t>3F6F76169DBECD7F1F8F0834B7B99002</t>
-  </si>
-  <si>
-    <t>4E99472E78F8CCE9FEE557C8E6464DDF</t>
-  </si>
-  <si>
-    <t>4E99472E78F8CCE95679ED4EB4841BBB</t>
-  </si>
-  <si>
-    <t>4E99472E78F8CCE9E6969871FA79DCC4</t>
-  </si>
-  <si>
-    <t>6DA1FEF752400B203096C66C6D982679</t>
-  </si>
-  <si>
-    <t>1015A373E899A23C171D492E77581D11</t>
-  </si>
-  <si>
-    <t>1015A373E899A23C86B5FD3072DA3EDD</t>
-  </si>
-  <si>
-    <t>1015A373E899A23C8B66F449BD755D66</t>
-  </si>
-  <si>
-    <t>6DA1FEF752400B206A2A5C7EF4B41D31</t>
-  </si>
-  <si>
-    <t>6DA1FEF752400B201A2C06EED621D14F</t>
+    <t>1B7BC4CF26343B47B0B552DFB011D61D</t>
+  </si>
+  <si>
+    <t>099B6EC7EF68D68E019F23D7201C87CD</t>
+  </si>
+  <si>
+    <t>9F23BE22772065193FBF87D7E9298807</t>
+  </si>
+  <si>
+    <t>14CE51798A7166B71A715EFD9A95D2D2</t>
+  </si>
+  <si>
+    <t>14CE51798A7166B7515BC6D59E00022A</t>
+  </si>
+  <si>
+    <t>9F23BE2277206519727A3C8EC2F33660</t>
+  </si>
+  <si>
+    <t>9F23BE22772065192E089FA5F57762EA</t>
+  </si>
+  <si>
+    <t>9F23BE22772065190E0C0E1A1A507517</t>
+  </si>
+  <si>
+    <t>7ED020F1F1D425E75614B63E2FEFA764</t>
+  </si>
+  <si>
+    <t>1B7BC4CF26343B4778DF90305066B6E3</t>
+  </si>
+  <si>
+    <t>1B7BC4CF26343B4723287805499414D4</t>
+  </si>
+  <si>
+    <t>5A7BC07C9F455B4D65913B3CD7EE3069</t>
+  </si>
+  <si>
+    <t>5BF51939CB2072C92B34970E46A5A92E</t>
+  </si>
+  <si>
+    <t>5BF51939CB2072C9F3B852FF6BC7E4C0</t>
+  </si>
+  <si>
+    <t>5A7BC07C9F455B4DD6934D2F06ECBDF3</t>
+  </si>
+  <si>
+    <t>5A7BC07C9F455B4D79CEB7856AB1E67A</t>
+  </si>
+  <si>
+    <t>5A7BC07C9F455B4D76187301D6C9E01B</t>
+  </si>
+  <si>
+    <t>9B2E22B42403BBDB3662B7037C2EEAA6</t>
+  </si>
+  <si>
+    <t>9B2E22B42403BBDB989B91A635EBE794</t>
+  </si>
+  <si>
+    <t>7B79FC614A1029D700F053372AC2B00B</t>
+  </si>
+  <si>
+    <t>7B79FC614A1029D72BEB3AF5B1F955E9</t>
+  </si>
+  <si>
+    <t>9B2E22B42403BBDB8A6CD43B33ACB5E2</t>
+  </si>
+  <si>
+    <t>9B2E22B42403BBDB6573667BA1638027</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <fonts count="4" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
@@ -1313,6 +1457,9 @@
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
     </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
   </extLst>
 </styleSheet>
 </file>
@@ -1328,44 +1475,44 @@
         <a:sysClr val="window" lastClr="FFFFFF"/>
       </a:lt1>
       <a:dk2>
-        <a:srgbClr val="1F497D"/>
+        <a:srgbClr val="44546A"/>
       </a:dk2>
       <a:lt2>
-        <a:srgbClr val="EEECE1"/>
+        <a:srgbClr val="E7E6E6"/>
       </a:lt2>
       <a:accent1>
-        <a:srgbClr val="4F81BD"/>
+        <a:srgbClr val="4472C4"/>
       </a:accent1>
       <a:accent2>
-        <a:srgbClr val="C0504D"/>
+        <a:srgbClr val="ED7D31"/>
       </a:accent2>
       <a:accent3>
-        <a:srgbClr val="9BBB59"/>
+        <a:srgbClr val="A5A5A5"/>
       </a:accent3>
       <a:accent4>
-        <a:srgbClr val="8064A2"/>
+        <a:srgbClr val="FFC000"/>
       </a:accent4>
       <a:accent5>
-        <a:srgbClr val="4BACC6"/>
+        <a:srgbClr val="5B9BD5"/>
       </a:accent5>
       <a:accent6>
-        <a:srgbClr val="F79646"/>
+        <a:srgbClr val="70AD47"/>
       </a:accent6>
       <a:hlink>
-        <a:srgbClr val="0000FF"/>
+        <a:srgbClr val="0563C1"/>
       </a:hlink>
       <a:folHlink>
-        <a:srgbClr val="800080"/>
+        <a:srgbClr val="954F72"/>
       </a:folHlink>
     </a:clrScheme>
     <a:fontScheme name="Office">
       <a:majorFont>
-        <a:latin typeface="Cambria"/>
+        <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
-        <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
+        <a:font script="Jpan" typeface="游ゴシック Light"/>
         <a:font script="Hang" typeface="맑은 고딕"/>
-        <a:font script="Hans" typeface="宋体"/>
+        <a:font script="Hans" typeface="等线 Light"/>
         <a:font script="Hant" typeface="新細明體"/>
         <a:font script="Arab" typeface="Times New Roman"/>
         <a:font script="Hebr" typeface="Times New Roman"/>
@@ -1393,14 +1540,31 @@
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
         <a:font script="Geor" typeface="Sylfaen"/>
+        <a:font script="Armn" typeface="Arial"/>
+        <a:font script="Bugi" typeface="Leelawadee UI"/>
+        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
+        <a:font script="Java" typeface="Javanese Text"/>
+        <a:font script="Lisu" typeface="Segoe UI"/>
+        <a:font script="Mymr" typeface="Myanmar Text"/>
+        <a:font script="Nkoo" typeface="Ebrima"/>
+        <a:font script="Olck" typeface="Nirmala UI"/>
+        <a:font script="Osma" typeface="Ebrima"/>
+        <a:font script="Phag" typeface="Phagspa"/>
+        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
+        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
+        <a:font script="Syre" typeface="Estrangelo Edessa"/>
+        <a:font script="Sora" typeface="Nirmala UI"/>
+        <a:font script="Tale" typeface="Microsoft Tai Le"/>
+        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
+        <a:font script="Tfng" typeface="Ebrima"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Calibri"/>
+        <a:latin typeface="Calibri" panose="020F0502020204030204"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
-        <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
+        <a:font script="Jpan" typeface="游ゴシック"/>
         <a:font script="Hang" typeface="맑은 고딕"/>
-        <a:font script="Hans" typeface="宋体"/>
+        <a:font script="Hans" typeface="等线"/>
         <a:font script="Hant" typeface="新細明體"/>
         <a:font script="Arab" typeface="Arial"/>
         <a:font script="Hebr" typeface="Arial"/>
@@ -1428,6 +1592,23 @@
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
         <a:font script="Geor" typeface="Sylfaen"/>
+        <a:font script="Armn" typeface="Arial"/>
+        <a:font script="Bugi" typeface="Leelawadee UI"/>
+        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
+        <a:font script="Java" typeface="Javanese Text"/>
+        <a:font script="Lisu" typeface="Segoe UI"/>
+        <a:font script="Mymr" typeface="Myanmar Text"/>
+        <a:font script="Nkoo" typeface="Ebrima"/>
+        <a:font script="Olck" typeface="Nirmala UI"/>
+        <a:font script="Osma" typeface="Ebrima"/>
+        <a:font script="Phag" typeface="Phagspa"/>
+        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
+        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
+        <a:font script="Syre" typeface="Estrangelo Edessa"/>
+        <a:font script="Sora" typeface="Nirmala UI"/>
+        <a:font script="Tale" typeface="Microsoft Tai Le"/>
+        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
+        <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
     <a:fmtScheme name="Office">
@@ -1439,172 +1620,148 @@
           <a:gsLst>
             <a:gs pos="0">
               <a:schemeClr val="phClr">
-                <a:tint val="50000"/>
-                <a:satMod val="300000"/>
+                <a:lumMod val="110000"/>
+                <a:satMod val="105000"/>
+                <a:tint val="67000"/>
               </a:schemeClr>
             </a:gs>
-            <a:gs pos="35000">
+            <a:gs pos="50000">
               <a:schemeClr val="phClr">
-                <a:tint val="37000"/>
-                <a:satMod val="300000"/>
+                <a:lumMod val="105000"/>
+                <a:satMod val="103000"/>
+                <a:tint val="73000"/>
               </a:schemeClr>
             </a:gs>
             <a:gs pos="100000">
               <a:schemeClr val="phClr">
-                <a:tint val="15000"/>
-                <a:satMod val="350000"/>
+                <a:lumMod val="105000"/>
+                <a:satMod val="109000"/>
+                <a:tint val="81000"/>
               </a:schemeClr>
             </a:gs>
           </a:gsLst>
-          <a:lin ang="16200000" scaled="1"/>
+          <a:lin ang="5400000" scaled="0"/>
         </a:gradFill>
         <a:gradFill rotWithShape="1">
           <a:gsLst>
             <a:gs pos="0">
               <a:schemeClr val="phClr">
-                <a:shade val="51000"/>
-                <a:satMod val="130000"/>
+                <a:satMod val="103000"/>
+                <a:lumMod val="102000"/>
+                <a:tint val="94000"/>
               </a:schemeClr>
             </a:gs>
-            <a:gs pos="80000">
+            <a:gs pos="50000">
               <a:schemeClr val="phClr">
-                <a:shade val="93000"/>
-                <a:satMod val="130000"/>
+                <a:satMod val="110000"/>
+                <a:lumMod val="100000"/>
+                <a:shade val="100000"/>
               </a:schemeClr>
             </a:gs>
             <a:gs pos="100000">
               <a:schemeClr val="phClr">
-                <a:shade val="94000"/>
-                <a:satMod val="135000"/>
+                <a:lumMod val="99000"/>
+                <a:satMod val="120000"/>
+                <a:shade val="78000"/>
               </a:schemeClr>
             </a:gs>
           </a:gsLst>
-          <a:lin ang="16200000" scaled="0"/>
+          <a:lin ang="5400000" scaled="0"/>
         </a:gradFill>
       </a:fillStyleLst>
       <a:lnStyleLst>
-        <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-          <a:solidFill>
-            <a:schemeClr val="phClr">
-              <a:shade val="95000"/>
-              <a:satMod val="105000"/>
-            </a:schemeClr>
-          </a:solidFill>
-          <a:prstDash val="solid"/>
-        </a:ln>
-        <a:ln w="25400" cap="flat" cmpd="sng" algn="ctr">
+        <a:ln w="6350" cap="flat" cmpd="sng" algn="ctr">
           <a:solidFill>
             <a:schemeClr val="phClr"/>
           </a:solidFill>
           <a:prstDash val="solid"/>
+          <a:miter lim="800000"/>
         </a:ln>
-        <a:ln w="38100" cap="flat" cmpd="sng" algn="ctr">
+        <a:ln w="12700" cap="flat" cmpd="sng" algn="ctr">
           <a:solidFill>
             <a:schemeClr val="phClr"/>
           </a:solidFill>
           <a:prstDash val="solid"/>
+          <a:miter lim="800000"/>
+        </a:ln>
+        <a:ln w="19050" cap="flat" cmpd="sng" algn="ctr">
+          <a:solidFill>
+            <a:schemeClr val="phClr"/>
+          </a:solidFill>
+          <a:prstDash val="solid"/>
+          <a:miter lim="800000"/>
         </a:ln>
       </a:lnStyleLst>
       <a:effectStyleLst>
         <a:effectStyle>
+          <a:effectLst/>
+        </a:effectStyle>
+        <a:effectStyle>
+          <a:effectLst/>
+        </a:effectStyle>
+        <a:effectStyle>
           <a:effectLst>
-            <a:outerShdw blurRad="40000" dist="20000" dir="5400000" rotWithShape="0">
+            <a:outerShdw blurRad="57150" dist="19050" dir="5400000" algn="ctr" rotWithShape="0">
               <a:srgbClr val="000000">
-                <a:alpha val="38000"/>
+                <a:alpha val="63000"/>
               </a:srgbClr>
             </a:outerShdw>
           </a:effectLst>
-        </a:effectStyle>
-        <a:effectStyle>
-          <a:effectLst>
-            <a:outerShdw blurRad="40000" dist="23000" dir="5400000" rotWithShape="0">
-              <a:srgbClr val="000000">
-                <a:alpha val="35000"/>
-              </a:srgbClr>
-            </a:outerShdw>
-          </a:effectLst>
-        </a:effectStyle>
-        <a:effectStyle>
-          <a:effectLst>
-            <a:outerShdw blurRad="40000" dist="23000" dir="5400000" rotWithShape="0">
-              <a:srgbClr val="000000">
-                <a:alpha val="35000"/>
-              </a:srgbClr>
-            </a:outerShdw>
-          </a:effectLst>
-          <a:scene3d>
-            <a:camera prst="orthographicFront">
-              <a:rot lat="0" lon="0" rev="0"/>
-            </a:camera>
-            <a:lightRig rig="threePt" dir="t">
-              <a:rot lat="0" lon="0" rev="1200000"/>
-            </a:lightRig>
-          </a:scene3d>
-          <a:sp3d>
-            <a:bevelT w="63500" h="25400"/>
-          </a:sp3d>
         </a:effectStyle>
       </a:effectStyleLst>
       <a:bgFillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
         </a:solidFill>
+        <a:solidFill>
+          <a:schemeClr val="phClr">
+            <a:tint val="95000"/>
+            <a:satMod val="170000"/>
+          </a:schemeClr>
+        </a:solidFill>
         <a:gradFill rotWithShape="1">
           <a:gsLst>
             <a:gs pos="0">
               <a:schemeClr val="phClr">
-                <a:tint val="40000"/>
-                <a:satMod val="350000"/>
+                <a:tint val="93000"/>
+                <a:satMod val="150000"/>
+                <a:shade val="98000"/>
+                <a:lumMod val="102000"/>
               </a:schemeClr>
             </a:gs>
-            <a:gs pos="40000">
+            <a:gs pos="50000">
               <a:schemeClr val="phClr">
-                <a:tint val="45000"/>
-                <a:shade val="99000"/>
-                <a:satMod val="350000"/>
+                <a:tint val="98000"/>
+                <a:satMod val="130000"/>
+                <a:shade val="90000"/>
+                <a:lumMod val="103000"/>
               </a:schemeClr>
             </a:gs>
             <a:gs pos="100000">
               <a:schemeClr val="phClr">
-                <a:shade val="20000"/>
-                <a:satMod val="255000"/>
+                <a:shade val="63000"/>
+                <a:satMod val="120000"/>
               </a:schemeClr>
             </a:gs>
           </a:gsLst>
-          <a:path path="circle">
-            <a:fillToRect l="50000" t="-80000" r="50000" b="180000"/>
-          </a:path>
-        </a:gradFill>
-        <a:gradFill rotWithShape="1">
-          <a:gsLst>
-            <a:gs pos="0">
-              <a:schemeClr val="phClr">
-                <a:tint val="80000"/>
-                <a:satMod val="300000"/>
-              </a:schemeClr>
-            </a:gs>
-            <a:gs pos="100000">
-              <a:schemeClr val="phClr">
-                <a:shade val="30000"/>
-                <a:satMod val="200000"/>
-              </a:schemeClr>
-            </a:gs>
-          </a:gsLst>
-          <a:path path="circle">
-            <a:fillToRect l="50000" t="50000" r="50000" b="50000"/>
-          </a:path>
+          <a:lin ang="5400000" scaled="0"/>
         </a:gradFill>
       </a:bgFillStyleLst>
     </a:fmtScheme>
   </a:themeElements>
   <a:objectDefaults/>
   <a:extraClrSchemeLst/>
+  <a:extLst>
+    <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+    </a:ext>
+  </a:extLst>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:AG13"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <dimension ref="A1:AF13"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="36.140625" hidden="1" customWidth="1"/>
@@ -1614,7 +1771,7 @@
     <col min="5" max="5" width="26.5703125" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="23.140625" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="98.7109375" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="174.42578125" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="181.7109375" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="19.5703125" bestFit="1" customWidth="1"/>
     <col min="10" max="10" width="63.5703125" bestFit="1" customWidth="1"/>
     <col min="11" max="11" width="255" bestFit="1" customWidth="1"/>
@@ -1636,17 +1793,16 @@
     <col min="28" max="28" width="35.85546875" bestFit="1" customWidth="1"/>
     <col min="29" max="29" width="80.7109375" bestFit="1" customWidth="1"/>
     <col min="30" max="30" width="73.140625" bestFit="1" customWidth="1"/>
-    <col min="31" max="31" width="17.5703125" bestFit="1" customWidth="1"/>
-    <col min="32" max="32" width="20" bestFit="1" customWidth="1"/>
-    <col min="33" max="33" width="255" bestFit="1" customWidth="1"/>
+    <col min="31" max="31" width="20" bestFit="1" customWidth="1"/>
+    <col min="32" max="32" width="255" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:33" hidden="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:32" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="2" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A2" s="4" t="s">
         <v>1</v>
       </c>
@@ -1663,7 +1819,7 @@
       <c r="H2" s="5"/>
       <c r="I2" s="5"/>
     </row>
-    <row r="3" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A3" s="6" t="s">
         <v>4</v>
       </c>
@@ -1678,7 +1834,7 @@
       <c r="H3" s="5"/>
       <c r="I3" s="5"/>
     </row>
-    <row r="4" spans="1:33" hidden="1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:32" hidden="1" x14ac:dyDescent="0.25">
       <c r="B4" t="s">
         <v>6</v>
       </c>
@@ -1767,16 +1923,13 @@
         <v>8</v>
       </c>
       <c r="AE4" t="s">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="AF4" t="s">
-        <v>12</v>
-      </c>
-      <c r="AG4" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="5" spans="1:33" hidden="1" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:32" hidden="1" x14ac:dyDescent="0.25">
       <c r="B5" t="s">
         <v>14</v>
       </c>
@@ -1870,13 +2023,10 @@
       <c r="AF5" t="s">
         <v>44</v>
       </c>
-      <c r="AG5" t="s">
+    </row>
+    <row r="6" spans="1:32" x14ac:dyDescent="0.25">
+      <c r="A6" s="4" t="s">
         <v>45</v>
-      </c>
-    </row>
-    <row r="6" spans="1:33" x14ac:dyDescent="0.25">
-      <c r="A6" s="4" t="s">
-        <v>46</v>
       </c>
       <c r="B6" s="5"/>
       <c r="C6" s="5"/>
@@ -1909,715 +2059,693 @@
       <c r="AD6" s="5"/>
       <c r="AE6" s="5"/>
       <c r="AF6" s="5"/>
-      <c r="AG6" s="5"/>
-    </row>
-    <row r="7" spans="1:33" ht="26.25" x14ac:dyDescent="0.25">
+    </row>
+    <row r="7" spans="1:32" ht="26.25" x14ac:dyDescent="0.25">
       <c r="B7" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="C7" s="2" t="s">
         <v>47</v>
       </c>
-      <c r="C7" s="2" t="s">
+      <c r="D7" s="2" t="s">
         <v>48</v>
       </c>
-      <c r="D7" s="2" t="s">
+      <c r="E7" s="2" t="s">
         <v>49</v>
       </c>
-      <c r="E7" s="2" t="s">
+      <c r="F7" s="2" t="s">
         <v>50</v>
       </c>
-      <c r="F7" s="2" t="s">
+      <c r="G7" s="2" t="s">
         <v>51</v>
       </c>
-      <c r="G7" s="2" t="s">
+      <c r="H7" s="2" t="s">
         <v>52</v>
       </c>
-      <c r="H7" s="2" t="s">
+      <c r="I7" s="2" t="s">
         <v>53</v>
       </c>
-      <c r="I7" s="2" t="s">
+      <c r="J7" s="2" t="s">
         <v>54</v>
       </c>
-      <c r="J7" s="2" t="s">
+      <c r="K7" s="2" t="s">
         <v>55</v>
       </c>
-      <c r="K7" s="2" t="s">
+      <c r="L7" s="2" t="s">
         <v>56</v>
       </c>
-      <c r="L7" s="2" t="s">
+      <c r="M7" s="2" t="s">
         <v>57</v>
       </c>
-      <c r="M7" s="2" t="s">
+      <c r="N7" s="2" t="s">
         <v>58</v>
       </c>
-      <c r="N7" s="2" t="s">
+      <c r="O7" s="2" t="s">
         <v>59</v>
       </c>
-      <c r="O7" s="2" t="s">
+      <c r="P7" s="2" t="s">
         <v>60</v>
       </c>
-      <c r="P7" s="2" t="s">
+      <c r="Q7" s="2" t="s">
         <v>61</v>
       </c>
-      <c r="Q7" s="2" t="s">
+      <c r="R7" s="2" t="s">
         <v>62</v>
       </c>
-      <c r="R7" s="2" t="s">
+      <c r="S7" s="2" t="s">
         <v>63</v>
       </c>
-      <c r="S7" s="2" t="s">
+      <c r="T7" s="2" t="s">
         <v>64</v>
       </c>
-      <c r="T7" s="2" t="s">
+      <c r="U7" s="2" t="s">
         <v>65</v>
       </c>
-      <c r="U7" s="2" t="s">
+      <c r="V7" s="2" t="s">
         <v>66</v>
       </c>
-      <c r="V7" s="2" t="s">
+      <c r="W7" s="2" t="s">
         <v>67</v>
       </c>
-      <c r="W7" s="2" t="s">
+      <c r="X7" s="2" t="s">
         <v>68</v>
       </c>
-      <c r="X7" s="2" t="s">
+      <c r="Y7" s="2" t="s">
         <v>69</v>
       </c>
-      <c r="Y7" s="2" t="s">
+      <c r="Z7" s="2" t="s">
         <v>70</v>
       </c>
-      <c r="Z7" s="2" t="s">
+      <c r="AA7" s="2" t="s">
         <v>71</v>
       </c>
-      <c r="AA7" s="2" t="s">
+      <c r="AB7" s="2" t="s">
         <v>72</v>
       </c>
-      <c r="AB7" s="2" t="s">
+      <c r="AC7" s="2" t="s">
         <v>73</v>
       </c>
-      <c r="AC7" s="2" t="s">
+      <c r="AD7" s="2" t="s">
         <v>74</v>
       </c>
-      <c r="AD7" s="2" t="s">
+      <c r="AE7" s="2" t="s">
         <v>75</v>
       </c>
-      <c r="AE7" s="2" t="s">
+      <c r="AF7" s="2" t="s">
         <v>76</v>
       </c>
-      <c r="AF7" s="2" t="s">
+    </row>
+    <row r="8" spans="1:32" ht="45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A8" s="3" t="s">
+        <v>146</v>
+      </c>
+      <c r="B8" s="3" t="s">
         <v>77</v>
       </c>
-      <c r="AG7" s="2" t="s">
+      <c r="C8" s="3" t="s">
+        <v>147</v>
+      </c>
+      <c r="D8" s="3" t="s">
+        <v>148</v>
+      </c>
+      <c r="E8" s="3" t="s">
+        <v>127</v>
+      </c>
+      <c r="F8" s="3" t="s">
+        <v>79</v>
+      </c>
+      <c r="G8" s="3" t="s">
+        <v>106</v>
+      </c>
+      <c r="H8" s="3" t="s">
+        <v>128</v>
+      </c>
+      <c r="I8" s="3" t="s">
+        <v>82</v>
+      </c>
+      <c r="J8" s="3" t="s">
+        <v>83</v>
+      </c>
+      <c r="K8" s="3" t="s">
+        <v>121</v>
+      </c>
+      <c r="L8" s="3" t="s">
+        <v>149</v>
+      </c>
+      <c r="M8" s="3" t="s">
+        <v>116</v>
+      </c>
+      <c r="N8" s="3" t="s">
+        <v>122</v>
+      </c>
+      <c r="O8" s="3" t="s">
+        <v>85</v>
+      </c>
+      <c r="P8" s="3" t="s">
+        <v>85</v>
+      </c>
+      <c r="Q8" s="3" t="s">
+        <v>87</v>
+      </c>
+      <c r="R8" s="3" t="s">
+        <v>150</v>
+      </c>
+      <c r="S8" s="3" t="s">
+        <v>124</v>
+      </c>
+      <c r="T8" s="3" t="s">
+        <v>143</v>
+      </c>
+      <c r="U8" s="3" t="s">
+        <v>90</v>
+      </c>
+      <c r="V8" s="3" t="s">
+        <v>91</v>
+      </c>
+      <c r="W8" s="3" t="s">
+        <v>125</v>
+      </c>
+      <c r="X8" s="3" t="s">
+        <v>93</v>
+      </c>
+      <c r="Y8" s="3" t="s">
+        <v>126</v>
+      </c>
+      <c r="Z8" s="3" t="s">
+        <v>85</v>
+      </c>
+      <c r="AA8" s="3" t="s">
+        <v>150</v>
+      </c>
+      <c r="AB8" s="3" t="s">
+        <v>150</v>
+      </c>
+      <c r="AC8" s="3" t="s">
+        <v>95</v>
+      </c>
+      <c r="AD8" s="3" t="s">
+        <v>96</v>
+      </c>
+      <c r="AE8" s="3" t="s">
+        <v>151</v>
+      </c>
+      <c r="AF8" s="3" t="s">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="9" spans="1:32" ht="45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A9" s="3" t="s">
+        <v>153</v>
+      </c>
+      <c r="B9" s="3" t="s">
+        <v>77</v>
+      </c>
+      <c r="C9" s="3" t="s">
+        <v>147</v>
+      </c>
+      <c r="D9" s="3" t="s">
+        <v>148</v>
+      </c>
+      <c r="E9" s="3" t="s">
         <v>78</v>
       </c>
-    </row>
-    <row r="8" spans="1:33" ht="45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="3" t="s">
+      <c r="F9" s="3" t="s">
+        <v>79</v>
+      </c>
+      <c r="G9" s="3" t="s">
+        <v>80</v>
+      </c>
+      <c r="H9" s="3" t="s">
+        <v>81</v>
+      </c>
+      <c r="I9" s="3" t="s">
+        <v>82</v>
+      </c>
+      <c r="J9" s="3" t="s">
+        <v>83</v>
+      </c>
+      <c r="K9" s="3" t="s">
+        <v>84</v>
+      </c>
+      <c r="L9" s="3" t="s">
+        <v>85</v>
+      </c>
+      <c r="M9" s="3" t="s">
+        <v>85</v>
+      </c>
+      <c r="N9" s="3" t="s">
+        <v>86</v>
+      </c>
+      <c r="O9" s="3" t="s">
+        <v>85</v>
+      </c>
+      <c r="P9" s="3" t="s">
+        <v>85</v>
+      </c>
+      <c r="Q9" s="3" t="s">
+        <v>87</v>
+      </c>
+      <c r="R9" s="3" t="s">
+        <v>154</v>
+      </c>
+      <c r="S9" s="3" t="s">
+        <v>89</v>
+      </c>
+      <c r="T9" s="3" t="s">
         <v>137</v>
       </c>
-      <c r="B8" s="3" t="s">
+      <c r="U9" s="3" t="s">
+        <v>90</v>
+      </c>
+      <c r="V9" s="3" t="s">
+        <v>91</v>
+      </c>
+      <c r="W9" s="3" t="s">
+        <v>92</v>
+      </c>
+      <c r="X9" s="3" t="s">
+        <v>93</v>
+      </c>
+      <c r="Y9" s="3" t="s">
+        <v>94</v>
+      </c>
+      <c r="Z9" s="3" t="s">
+        <v>85</v>
+      </c>
+      <c r="AA9" s="3" t="s">
+        <v>154</v>
+      </c>
+      <c r="AB9" s="3" t="s">
+        <v>154</v>
+      </c>
+      <c r="AC9" s="3" t="s">
+        <v>95</v>
+      </c>
+      <c r="AD9" s="3" t="s">
+        <v>96</v>
+      </c>
+      <c r="AE9" s="3" t="s">
+        <v>151</v>
+      </c>
+      <c r="AF9" s="3" t="s">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="10" spans="1:32" ht="45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A10" s="3" t="s">
+        <v>155</v>
+      </c>
+      <c r="B10" s="3" t="s">
+        <v>77</v>
+      </c>
+      <c r="C10" s="3" t="s">
+        <v>147</v>
+      </c>
+      <c r="D10" s="3" t="s">
+        <v>148</v>
+      </c>
+      <c r="E10" s="3" t="s">
+        <v>111</v>
+      </c>
+      <c r="F10" s="3" t="s">
         <v>79</v>
       </c>
-      <c r="C8" s="3" t="s">
-        <v>138</v>
-      </c>
-      <c r="D8" s="3" t="s">
-        <v>139</v>
-      </c>
-      <c r="E8" s="3" t="s">
-        <v>102</v>
-      </c>
-      <c r="F8" s="3" t="s">
-        <v>81</v>
-      </c>
-      <c r="G8" s="3" t="s">
-        <v>103</v>
-      </c>
-      <c r="H8" s="3" t="s">
-        <v>104</v>
-      </c>
-      <c r="I8" s="3" t="s">
-        <v>84</v>
-      </c>
-      <c r="J8" s="3" t="s">
-        <v>85</v>
-      </c>
-      <c r="K8" s="3" t="s">
-        <v>105</v>
-      </c>
-      <c r="L8" s="3" t="s">
-        <v>90</v>
-      </c>
-      <c r="M8" s="3" t="s">
-        <v>90</v>
-      </c>
-      <c r="N8" s="3" t="s">
-        <v>106</v>
-      </c>
-      <c r="O8" s="3" t="s">
-        <v>90</v>
-      </c>
-      <c r="P8" s="3" t="s">
-        <v>90</v>
-      </c>
-      <c r="Q8" s="3" t="s">
-        <v>107</v>
-      </c>
-      <c r="R8" s="3" t="s">
-        <v>140</v>
-      </c>
-      <c r="S8" s="3" t="s">
-        <v>109</v>
-      </c>
-      <c r="T8" s="3" t="s">
-        <v>110</v>
-      </c>
-      <c r="U8" s="3" t="s">
-        <v>95</v>
-      </c>
-      <c r="V8" s="3" t="s">
-        <v>96</v>
-      </c>
-      <c r="W8" s="3" t="s">
-        <v>111</v>
-      </c>
-      <c r="X8" s="3" t="s">
-        <v>98</v>
-      </c>
-      <c r="Y8" s="3" t="s">
+      <c r="G10" s="3" t="s">
         <v>112</v>
       </c>
-      <c r="Z8" s="3" t="s">
-        <v>90</v>
-      </c>
-      <c r="AA8" s="3" t="s">
-        <v>140</v>
-      </c>
-      <c r="AB8" s="3" t="s">
-        <v>140</v>
-      </c>
-      <c r="AC8" s="3" t="s">
-        <v>100</v>
-      </c>
-      <c r="AD8" s="3" t="s">
-        <v>101</v>
-      </c>
-      <c r="AE8" s="3" t="s">
-        <v>141</v>
-      </c>
-      <c r="AF8" s="3" t="s">
-        <v>141</v>
-      </c>
-      <c r="AG8" s="3" t="s">
-        <v>142</v>
-      </c>
-    </row>
-    <row r="9" spans="1:33" ht="45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A9" s="3" t="s">
-        <v>143</v>
-      </c>
-      <c r="B9" s="3" t="s">
-        <v>79</v>
-      </c>
-      <c r="C9" s="3" t="s">
-        <v>138</v>
-      </c>
-      <c r="D9" s="3" t="s">
-        <v>139</v>
-      </c>
-      <c r="E9" s="3" t="s">
-        <v>80</v>
-      </c>
-      <c r="F9" s="3" t="s">
-        <v>81</v>
-      </c>
-      <c r="G9" s="3" t="s">
+      <c r="H10" s="3" t="s">
+        <v>113</v>
+      </c>
+      <c r="I10" s="3" t="s">
         <v>82</v>
       </c>
-      <c r="H9" s="3" t="s">
+      <c r="J10" s="3" t="s">
         <v>83</v>
       </c>
-      <c r="I9" s="3" t="s">
-        <v>84</v>
-      </c>
-      <c r="J9" s="3" t="s">
-        <v>85</v>
-      </c>
-      <c r="K9" s="3" t="s">
-        <v>86</v>
-      </c>
-      <c r="L9" s="3" t="s">
-        <v>87</v>
-      </c>
-      <c r="M9" s="3" t="s">
-        <v>88</v>
-      </c>
-      <c r="N9" s="3" t="s">
-        <v>89</v>
-      </c>
-      <c r="O9" s="3" t="s">
-        <v>90</v>
-      </c>
-      <c r="P9" s="3" t="s">
-        <v>90</v>
-      </c>
-      <c r="Q9" s="3" t="s">
-        <v>91</v>
-      </c>
-      <c r="R9" s="3" t="s">
-        <v>144</v>
-      </c>
-      <c r="S9" s="3" t="s">
-        <v>93</v>
-      </c>
-      <c r="T9" s="3" t="s">
-        <v>94</v>
-      </c>
-      <c r="U9" s="3" t="s">
-        <v>95</v>
-      </c>
-      <c r="V9" s="3" t="s">
-        <v>96</v>
-      </c>
-      <c r="W9" s="3" t="s">
-        <v>97</v>
-      </c>
-      <c r="X9" s="3" t="s">
-        <v>98</v>
-      </c>
-      <c r="Y9" s="3" t="s">
-        <v>99</v>
-      </c>
-      <c r="Z9" s="3" t="s">
-        <v>90</v>
-      </c>
-      <c r="AA9" s="3" t="s">
-        <v>144</v>
-      </c>
-      <c r="AB9" s="3" t="s">
-        <v>144</v>
-      </c>
-      <c r="AC9" s="3" t="s">
-        <v>100</v>
-      </c>
-      <c r="AD9" s="3" t="s">
-        <v>101</v>
-      </c>
-      <c r="AE9" s="3" t="s">
-        <v>141</v>
-      </c>
-      <c r="AF9" s="3" t="s">
-        <v>88</v>
-      </c>
-      <c r="AG9" s="3" t="s">
-        <v>142</v>
-      </c>
-    </row>
-    <row r="10" spans="1:33" ht="45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A10" s="3" t="s">
-        <v>145</v>
-      </c>
-      <c r="B10" s="3" t="s">
-        <v>79</v>
-      </c>
-      <c r="C10" s="3" t="s">
-        <v>138</v>
-      </c>
-      <c r="D10" s="3" t="s">
-        <v>139</v>
-      </c>
-      <c r="E10" s="3" t="s">
-        <v>113</v>
-      </c>
-      <c r="F10" s="3" t="s">
-        <v>81</v>
-      </c>
-      <c r="G10" s="3" t="s">
-        <v>82</v>
-      </c>
-      <c r="H10" s="3" t="s">
+      <c r="K10" s="3" t="s">
         <v>114</v>
-      </c>
-      <c r="I10" s="3" t="s">
-        <v>84</v>
-      </c>
-      <c r="J10" s="3" t="s">
-        <v>85</v>
-      </c>
-      <c r="K10" s="3" t="s">
-        <v>86</v>
       </c>
       <c r="L10" s="3" t="s">
         <v>115</v>
       </c>
       <c r="M10" s="3" t="s">
-        <v>88</v>
+        <v>116</v>
       </c>
       <c r="N10" s="3" t="s">
+        <v>86</v>
+      </c>
+      <c r="O10" s="3" t="s">
+        <v>85</v>
+      </c>
+      <c r="P10" s="3" t="s">
+        <v>85</v>
+      </c>
+      <c r="Q10" s="3" t="s">
+        <v>101</v>
+      </c>
+      <c r="R10" s="3" t="s">
+        <v>156</v>
+      </c>
+      <c r="S10" s="3" t="s">
         <v>89</v>
       </c>
-      <c r="O10" s="3" t="s">
+      <c r="T10" s="3" t="s">
+        <v>140</v>
+      </c>
+      <c r="U10" s="3" t="s">
         <v>90</v>
       </c>
-      <c r="P10" s="3" t="s">
+      <c r="V10" s="3" t="s">
+        <v>91</v>
+      </c>
+      <c r="W10" s="3" t="s">
+        <v>103</v>
+      </c>
+      <c r="X10" s="3" t="s">
+        <v>93</v>
+      </c>
+      <c r="Y10" s="3" t="s">
+        <v>118</v>
+      </c>
+      <c r="Z10" s="3" t="s">
+        <v>85</v>
+      </c>
+      <c r="AA10" s="3" t="s">
+        <v>156</v>
+      </c>
+      <c r="AB10" s="3" t="s">
+        <v>156</v>
+      </c>
+      <c r="AC10" s="3" t="s">
+        <v>95</v>
+      </c>
+      <c r="AD10" s="3" t="s">
+        <v>96</v>
+      </c>
+      <c r="AE10" s="3" t="s">
+        <v>151</v>
+      </c>
+      <c r="AF10" s="3" t="s">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="11" spans="1:32" ht="45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A11" s="3" t="s">
+        <v>157</v>
+      </c>
+      <c r="B11" s="3" t="s">
+        <v>77</v>
+      </c>
+      <c r="C11" s="3" t="s">
+        <v>147</v>
+      </c>
+      <c r="D11" s="3" t="s">
+        <v>148</v>
+      </c>
+      <c r="E11" s="3" t="s">
+        <v>105</v>
+      </c>
+      <c r="F11" s="3" t="s">
+        <v>79</v>
+      </c>
+      <c r="G11" s="3" t="s">
+        <v>106</v>
+      </c>
+      <c r="H11" s="3" t="s">
+        <v>107</v>
+      </c>
+      <c r="I11" s="3" t="s">
+        <v>82</v>
+      </c>
+      <c r="J11" s="3" t="s">
+        <v>83</v>
+      </c>
+      <c r="K11" s="3" t="s">
+        <v>108</v>
+      </c>
+      <c r="L11" s="3" t="s">
+        <v>85</v>
+      </c>
+      <c r="M11" s="3" t="s">
+        <v>85</v>
+      </c>
+      <c r="N11" s="3" t="s">
+        <v>86</v>
+      </c>
+      <c r="O11" s="3" t="s">
+        <v>85</v>
+      </c>
+      <c r="P11" s="3" t="s">
+        <v>85</v>
+      </c>
+      <c r="Q11" s="3" t="s">
+        <v>101</v>
+      </c>
+      <c r="R11" s="3" t="s">
+        <v>158</v>
+      </c>
+      <c r="S11" s="3" t="s">
+        <v>89</v>
+      </c>
+      <c r="T11" s="3" t="s">
+        <v>137</v>
+      </c>
+      <c r="U11" s="3" t="s">
         <v>90</v>
       </c>
-      <c r="Q10" s="3" t="s">
+      <c r="V11" s="3" t="s">
         <v>91</v>
       </c>
-      <c r="R10" s="3" t="s">
-        <v>146</v>
-      </c>
-      <c r="S10" s="3" t="s">
+      <c r="W11" s="3" t="s">
+        <v>110</v>
+      </c>
+      <c r="X11" s="3" t="s">
         <v>93</v>
       </c>
-      <c r="T10" s="3" t="s">
-        <v>117</v>
-      </c>
-      <c r="U10" s="3" t="s">
+      <c r="Y11" s="3" t="s">
+        <v>108</v>
+      </c>
+      <c r="Z11" s="3" t="s">
+        <v>85</v>
+      </c>
+      <c r="AA11" s="3" t="s">
+        <v>158</v>
+      </c>
+      <c r="AB11" s="3" t="s">
+        <v>158</v>
+      </c>
+      <c r="AC11" s="3" t="s">
         <v>95</v>
       </c>
-      <c r="V10" s="3" t="s">
+      <c r="AD11" s="3" t="s">
         <v>96</v>
       </c>
-      <c r="W10" s="3" t="s">
+      <c r="AE11" s="3" t="s">
+        <v>151</v>
+      </c>
+      <c r="AF11" s="3" t="s">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="12" spans="1:32" ht="45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A12" s="3" t="s">
+        <v>159</v>
+      </c>
+      <c r="B12" s="3" t="s">
+        <v>77</v>
+      </c>
+      <c r="C12" s="3" t="s">
+        <v>147</v>
+      </c>
+      <c r="D12" s="3" t="s">
+        <v>148</v>
+      </c>
+      <c r="E12" s="3" t="s">
         <v>97</v>
       </c>
-      <c r="X10" s="3" t="s">
+      <c r="F12" s="3" t="s">
+        <v>79</v>
+      </c>
+      <c r="G12" s="3" t="s">
         <v>98</v>
       </c>
-      <c r="Y10" s="3" t="s">
+      <c r="H12" s="3" t="s">
         <v>99</v>
       </c>
-      <c r="Z10" s="3" t="s">
+      <c r="I12" s="3" t="s">
+        <v>82</v>
+      </c>
+      <c r="J12" s="3" t="s">
+        <v>83</v>
+      </c>
+      <c r="K12" s="3" t="s">
+        <v>100</v>
+      </c>
+      <c r="L12" s="3" t="s">
+        <v>85</v>
+      </c>
+      <c r="M12" s="3" t="s">
+        <v>85</v>
+      </c>
+      <c r="N12" s="3" t="s">
+        <v>86</v>
+      </c>
+      <c r="O12" s="3" t="s">
+        <v>85</v>
+      </c>
+      <c r="P12" s="3" t="s">
+        <v>85</v>
+      </c>
+      <c r="Q12" s="3" t="s">
+        <v>101</v>
+      </c>
+      <c r="R12" s="3" t="s">
+        <v>160</v>
+      </c>
+      <c r="S12" s="3" t="s">
+        <v>89</v>
+      </c>
+      <c r="T12" s="3" t="s">
+        <v>140</v>
+      </c>
+      <c r="U12" s="3" t="s">
         <v>90</v>
       </c>
-      <c r="AA10" s="3" t="s">
-        <v>146</v>
-      </c>
-      <c r="AB10" s="3" t="s">
-        <v>146</v>
-      </c>
-      <c r="AC10" s="3" t="s">
-        <v>100</v>
-      </c>
-      <c r="AD10" s="3" t="s">
-        <v>101</v>
-      </c>
-      <c r="AE10" s="3" t="s">
-        <v>141</v>
-      </c>
-      <c r="AF10" s="3" t="s">
-        <v>88</v>
-      </c>
-      <c r="AG10" s="3" t="s">
-        <v>142</v>
-      </c>
-    </row>
-    <row r="11" spans="1:33" ht="45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A11" s="3" t="s">
+      <c r="V12" s="3" t="s">
+        <v>91</v>
+      </c>
+      <c r="W12" s="3" t="s">
+        <v>103</v>
+      </c>
+      <c r="X12" s="3" t="s">
+        <v>93</v>
+      </c>
+      <c r="Y12" s="3" t="s">
+        <v>104</v>
+      </c>
+      <c r="Z12" s="3" t="s">
+        <v>85</v>
+      </c>
+      <c r="AA12" s="3" t="s">
+        <v>160</v>
+      </c>
+      <c r="AB12" s="3" t="s">
+        <v>160</v>
+      </c>
+      <c r="AC12" s="3" t="s">
+        <v>95</v>
+      </c>
+      <c r="AD12" s="3" t="s">
+        <v>96</v>
+      </c>
+      <c r="AE12" s="3" t="s">
+        <v>151</v>
+      </c>
+      <c r="AF12" s="3" t="s">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="13" spans="1:32" ht="45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A13" s="3" t="s">
+        <v>161</v>
+      </c>
+      <c r="B13" s="3" t="s">
+        <v>77</v>
+      </c>
+      <c r="C13" s="3" t="s">
         <v>147</v>
       </c>
-      <c r="B11" s="3" t="s">
+      <c r="D13" s="3" t="s">
+        <v>148</v>
+      </c>
+      <c r="E13" s="3" t="s">
+        <v>119</v>
+      </c>
+      <c r="F13" s="3" t="s">
         <v>79</v>
       </c>
-      <c r="C11" s="3" t="s">
-        <v>138</v>
-      </c>
-      <c r="D11" s="3" t="s">
-        <v>139</v>
-      </c>
-      <c r="E11" s="3" t="s">
-        <v>118</v>
-      </c>
-      <c r="F11" s="3" t="s">
-        <v>81</v>
-      </c>
-      <c r="G11" s="3" t="s">
-        <v>119</v>
-      </c>
-      <c r="H11" s="3" t="s">
+      <c r="G13" s="3" t="s">
+        <v>106</v>
+      </c>
+      <c r="H13" s="3" t="s">
+        <v>120</v>
+      </c>
+      <c r="I13" s="3" t="s">
+        <v>82</v>
+      </c>
+      <c r="J13" s="3" t="s">
         <v>83</v>
       </c>
-      <c r="I11" s="3" t="s">
-        <v>84</v>
-      </c>
-      <c r="J11" s="3" t="s">
-        <v>85</v>
-      </c>
-      <c r="K11" s="3" t="s">
-        <v>120</v>
-      </c>
-      <c r="L11" s="3" t="s">
+      <c r="K13" s="3" t="s">
+        <v>121</v>
+      </c>
+      <c r="L13" s="3" t="s">
+        <v>162</v>
+      </c>
+      <c r="M13" s="3" t="s">
+        <v>116</v>
+      </c>
+      <c r="N13" s="3" t="s">
+        <v>122</v>
+      </c>
+      <c r="O13" s="3" t="s">
+        <v>85</v>
+      </c>
+      <c r="P13" s="3" t="s">
+        <v>85</v>
+      </c>
+      <c r="Q13" s="3" t="s">
+        <v>87</v>
+      </c>
+      <c r="R13" s="3" t="s">
+        <v>163</v>
+      </c>
+      <c r="S13" s="3" t="s">
+        <v>124</v>
+      </c>
+      <c r="T13" s="3" t="s">
+        <v>145</v>
+      </c>
+      <c r="U13" s="3" t="s">
         <v>90</v>
       </c>
-      <c r="M11" s="3" t="s">
-        <v>90</v>
-      </c>
-      <c r="N11" s="3" t="s">
-        <v>106</v>
-      </c>
-      <c r="O11" s="3" t="s">
-        <v>90</v>
-      </c>
-      <c r="P11" s="3" t="s">
-        <v>90</v>
-      </c>
-      <c r="Q11" s="3" t="s">
+      <c r="V13" s="3" t="s">
         <v>91</v>
       </c>
-      <c r="R11" s="3" t="s">
-        <v>148</v>
-      </c>
-      <c r="S11" s="3" t="s">
-        <v>109</v>
-      </c>
-      <c r="T11" s="3" t="s">
-        <v>122</v>
-      </c>
-      <c r="U11" s="3" t="s">
+      <c r="W13" s="3" t="s">
+        <v>125</v>
+      </c>
+      <c r="X13" s="3" t="s">
+        <v>93</v>
+      </c>
+      <c r="Y13" s="3" t="s">
+        <v>126</v>
+      </c>
+      <c r="Z13" s="3" t="s">
+        <v>85</v>
+      </c>
+      <c r="AA13" s="3" t="s">
+        <v>163</v>
+      </c>
+      <c r="AB13" s="3" t="s">
+        <v>163</v>
+      </c>
+      <c r="AC13" s="3" t="s">
         <v>95</v>
       </c>
-      <c r="V11" s="3" t="s">
+      <c r="AD13" s="3" t="s">
         <v>96</v>
       </c>
-      <c r="W11" s="3" t="s">
-        <v>123</v>
-      </c>
-      <c r="X11" s="3" t="s">
-        <v>98</v>
-      </c>
-      <c r="Y11" s="3" t="s">
-        <v>124</v>
-      </c>
-      <c r="Z11" s="3" t="s">
-        <v>90</v>
-      </c>
-      <c r="AA11" s="3" t="s">
-        <v>148</v>
-      </c>
-      <c r="AB11" s="3" t="s">
-        <v>148</v>
-      </c>
-      <c r="AC11" s="3" t="s">
-        <v>100</v>
-      </c>
-      <c r="AD11" s="3" t="s">
-        <v>101</v>
-      </c>
-      <c r="AE11" s="3" t="s">
-        <v>141</v>
-      </c>
-      <c r="AF11" s="3" t="s">
-        <v>141</v>
-      </c>
-      <c r="AG11" s="3" t="s">
-        <v>142</v>
-      </c>
-    </row>
-    <row r="12" spans="1:33" ht="45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A12" s="3" t="s">
-        <v>149</v>
-      </c>
-      <c r="B12" s="3" t="s">
-        <v>79</v>
-      </c>
-      <c r="C12" s="3" t="s">
-        <v>138</v>
-      </c>
-      <c r="D12" s="3" t="s">
-        <v>139</v>
-      </c>
-      <c r="E12" s="3" t="s">
-        <v>125</v>
-      </c>
-      <c r="F12" s="3" t="s">
-        <v>81</v>
-      </c>
-      <c r="G12" s="3" t="s">
-        <v>126</v>
-      </c>
-      <c r="H12" s="3" t="s">
-        <v>127</v>
-      </c>
-      <c r="I12" s="3" t="s">
-        <v>84</v>
-      </c>
-      <c r="J12" s="3" t="s">
-        <v>85</v>
-      </c>
-      <c r="K12" s="3" t="s">
-        <v>128</v>
-      </c>
-      <c r="L12" s="3" t="s">
-        <v>129</v>
-      </c>
-      <c r="M12" s="3" t="s">
-        <v>88</v>
-      </c>
-      <c r="N12" s="3" t="s">
-        <v>106</v>
-      </c>
-      <c r="O12" s="3" t="s">
-        <v>90</v>
-      </c>
-      <c r="P12" s="3" t="s">
-        <v>90</v>
-      </c>
-      <c r="Q12" s="3" t="s">
-        <v>107</v>
-      </c>
-      <c r="R12" s="3" t="s">
-        <v>150</v>
-      </c>
-      <c r="S12" s="3" t="s">
-        <v>109</v>
-      </c>
-      <c r="T12" s="3" t="s">
-        <v>110</v>
-      </c>
-      <c r="U12" s="3" t="s">
-        <v>95</v>
-      </c>
-      <c r="V12" s="3" t="s">
-        <v>96</v>
-      </c>
-      <c r="W12" s="3" t="s">
-        <v>111</v>
-      </c>
-      <c r="X12" s="3" t="s">
-        <v>98</v>
-      </c>
-      <c r="Y12" s="3" t="s">
-        <v>131</v>
-      </c>
-      <c r="Z12" s="3" t="s">
-        <v>90</v>
-      </c>
-      <c r="AA12" s="3" t="s">
-        <v>150</v>
-      </c>
-      <c r="AB12" s="3" t="s">
-        <v>150</v>
-      </c>
-      <c r="AC12" s="3" t="s">
-        <v>100</v>
-      </c>
-      <c r="AD12" s="3" t="s">
-        <v>101</v>
-      </c>
-      <c r="AE12" s="3" t="s">
-        <v>141</v>
-      </c>
-      <c r="AF12" s="3" t="s">
-        <v>88</v>
-      </c>
-      <c r="AG12" s="3" t="s">
-        <v>142</v>
-      </c>
-    </row>
-    <row r="13" spans="1:33" ht="45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A13" s="3" t="s">
+      <c r="AE13" s="3" t="s">
         <v>151</v>
       </c>
-      <c r="B13" s="3" t="s">
-        <v>79</v>
-      </c>
-      <c r="C13" s="3" t="s">
-        <v>138</v>
-      </c>
-      <c r="D13" s="3" t="s">
-        <v>139</v>
-      </c>
-      <c r="E13" s="3" t="s">
-        <v>132</v>
-      </c>
-      <c r="F13" s="3" t="s">
-        <v>81</v>
-      </c>
-      <c r="G13" s="3" t="s">
-        <v>82</v>
-      </c>
-      <c r="H13" s="3" t="s">
-        <v>133</v>
-      </c>
-      <c r="I13" s="3" t="s">
-        <v>84</v>
-      </c>
-      <c r="J13" s="3" t="s">
-        <v>85</v>
-      </c>
-      <c r="K13" s="3" t="s">
-        <v>134</v>
-      </c>
-      <c r="L13" s="3" t="s">
-        <v>90</v>
-      </c>
-      <c r="M13" s="3" t="s">
-        <v>90</v>
-      </c>
-      <c r="N13" s="3" t="s">
-        <v>106</v>
-      </c>
-      <c r="O13" s="3" t="s">
-        <v>90</v>
-      </c>
-      <c r="P13" s="3" t="s">
-        <v>90</v>
-      </c>
-      <c r="Q13" s="3" t="s">
-        <v>107</v>
-      </c>
-      <c r="R13" s="3" t="s">
+      <c r="AF13" s="3" t="s">
         <v>152</v>
-      </c>
-      <c r="S13" s="3" t="s">
-        <v>109</v>
-      </c>
-      <c r="T13" s="3" t="s">
-        <v>122</v>
-      </c>
-      <c r="U13" s="3" t="s">
-        <v>95</v>
-      </c>
-      <c r="V13" s="3" t="s">
-        <v>96</v>
-      </c>
-      <c r="W13" s="3" t="s">
-        <v>136</v>
-      </c>
-      <c r="X13" s="3" t="s">
-        <v>98</v>
-      </c>
-      <c r="Y13" s="3" t="s">
-        <v>134</v>
-      </c>
-      <c r="Z13" s="3" t="s">
-        <v>90</v>
-      </c>
-      <c r="AA13" s="3" t="s">
-        <v>152</v>
-      </c>
-      <c r="AB13" s="3" t="s">
-        <v>152</v>
-      </c>
-      <c r="AC13" s="3" t="s">
-        <v>100</v>
-      </c>
-      <c r="AD13" s="3" t="s">
-        <v>101</v>
-      </c>
-      <c r="AE13" s="3" t="s">
-        <v>141</v>
-      </c>
-      <c r="AF13" s="3" t="s">
-        <v>141</v>
-      </c>
-      <c r="AG13" s="3" t="s">
-        <v>142</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="7">
-    <mergeCell ref="A6:AG6"/>
+    <mergeCell ref="A6:AF6"/>
     <mergeCell ref="A2:C2"/>
     <mergeCell ref="D2:F2"/>
     <mergeCell ref="G2:I2"/>
@@ -2626,7 +2754,7 @@
     <mergeCell ref="G3:I3"/>
   </mergeCells>
   <dataValidations count="1">
-    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="F8:F195">
+    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="F8:F183" xr:uid="{00000000-0002-0000-0000-000000000000}">
       <formula1>Hidden_15</formula1>
     </dataValidation>
   </dataValidations>
@@ -2635,168 +2763,168 @@
 </file>
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0900-000000000000}">
   <dimension ref="A1:A32"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
     <row r="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
-        <v>343</v>
+        <v>378</v>
       </c>
     </row>
     <row r="2" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>302</v>
+        <v>325</v>
       </c>
     </row>
     <row r="3" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>303</v>
+        <v>326</v>
       </c>
     </row>
     <row r="4" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>276</v>
+        <v>299</v>
       </c>
     </row>
     <row r="5" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>300</v>
+        <v>323</v>
       </c>
     </row>
     <row r="6" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>277</v>
+        <v>300</v>
       </c>
     </row>
     <row r="7" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>278</v>
+        <v>301</v>
       </c>
     </row>
     <row r="8" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>279</v>
+        <v>302</v>
       </c>
     </row>
     <row r="9" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>295</v>
+        <v>318</v>
       </c>
     </row>
     <row r="10" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>344</v>
+        <v>379</v>
       </c>
     </row>
     <row r="11" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>284</v>
+        <v>307</v>
       </c>
     </row>
     <row r="12" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>297</v>
+        <v>320</v>
       </c>
     </row>
     <row r="13" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>287</v>
+        <v>310</v>
       </c>
     </row>
     <row r="14" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>292</v>
+        <v>315</v>
       </c>
     </row>
     <row r="15" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>281</v>
+        <v>304</v>
       </c>
     </row>
     <row r="16" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>288</v>
+        <v>311</v>
       </c>
     </row>
     <row r="17" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>299</v>
+        <v>322</v>
       </c>
     </row>
     <row r="18" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>294</v>
+        <v>317</v>
       </c>
     </row>
     <row r="19" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>197</v>
+        <v>208</v>
       </c>
     </row>
     <row r="20" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>286</v>
+        <v>309</v>
       </c>
     </row>
     <row r="21" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>289</v>
+        <v>312</v>
       </c>
     </row>
     <row r="22" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
-        <v>290</v>
+        <v>313</v>
       </c>
     </row>
     <row r="23" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
-        <v>304</v>
+        <v>327</v>
       </c>
     </row>
     <row r="24" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
-        <v>283</v>
+        <v>306</v>
       </c>
     </row>
     <row r="25" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
-        <v>282</v>
+        <v>305</v>
       </c>
     </row>
     <row r="26" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
-        <v>280</v>
+        <v>303</v>
       </c>
     </row>
     <row r="27" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
-        <v>306</v>
+        <v>329</v>
       </c>
     </row>
     <row r="28" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
-        <v>291</v>
+        <v>314</v>
       </c>
     </row>
     <row r="29" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
-        <v>285</v>
+        <v>308</v>
       </c>
     </row>
     <row r="30" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
-        <v>345</v>
+        <v>380</v>
       </c>
     </row>
     <row r="31" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
-        <v>298</v>
+        <v>321</v>
       </c>
     </row>
     <row r="32" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
-        <v>293</v>
+        <v>316</v>
       </c>
     </row>
   </sheetData>
@@ -2805,12 +2933,12 @@
 </file>
 
 <file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:R15"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0A00-000000000000}">
+  <dimension ref="A1:R27"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="8.42578125" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="36.140625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="9.42578125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="36.28515625" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="33.140625" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="39.7109375" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="17.7109375" bestFit="1" customWidth="1"/>
@@ -2881,789 +3009,1461 @@
     </row>
     <row r="2" spans="1:18" hidden="1" x14ac:dyDescent="0.25">
       <c r="C2" t="s">
-        <v>346</v>
+        <v>381</v>
       </c>
       <c r="D2" t="s">
-        <v>347</v>
+        <v>382</v>
       </c>
       <c r="E2" t="s">
-        <v>348</v>
+        <v>383</v>
       </c>
       <c r="F2" t="s">
-        <v>349</v>
+        <v>384</v>
       </c>
       <c r="G2" t="s">
-        <v>350</v>
+        <v>385</v>
       </c>
       <c r="H2" t="s">
-        <v>351</v>
+        <v>386</v>
       </c>
       <c r="I2" t="s">
-        <v>352</v>
+        <v>387</v>
       </c>
       <c r="J2" t="s">
-        <v>353</v>
+        <v>388</v>
       </c>
       <c r="K2" t="s">
-        <v>354</v>
+        <v>389</v>
       </c>
       <c r="L2" t="s">
-        <v>355</v>
+        <v>390</v>
       </c>
       <c r="M2" t="s">
-        <v>356</v>
+        <v>391</v>
       </c>
       <c r="N2" t="s">
-        <v>357</v>
+        <v>392</v>
       </c>
       <c r="O2" t="s">
-        <v>358</v>
+        <v>393</v>
       </c>
       <c r="P2" t="s">
-        <v>359</v>
+        <v>394</v>
       </c>
       <c r="Q2" t="s">
-        <v>360</v>
+        <v>395</v>
       </c>
       <c r="R2" t="s">
-        <v>361</v>
+        <v>396</v>
       </c>
     </row>
     <row r="3" spans="1:18" ht="30" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
-        <v>172</v>
+        <v>183</v>
       </c>
       <c r="B3" s="1"/>
       <c r="C3" s="1" t="s">
-        <v>362</v>
+        <v>397</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>323</v>
+        <v>346</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>363</v>
+        <v>398</v>
       </c>
       <c r="F3" s="1" t="s">
-        <v>325</v>
+        <v>348</v>
       </c>
       <c r="G3" s="1" t="s">
-        <v>176</v>
+        <v>187</v>
       </c>
       <c r="H3" s="1" t="s">
-        <v>177</v>
+        <v>188</v>
       </c>
       <c r="I3" s="1" t="s">
-        <v>364</v>
+        <v>399</v>
       </c>
       <c r="J3" s="1" t="s">
-        <v>365</v>
+        <v>400</v>
       </c>
       <c r="K3" s="1" t="s">
-        <v>328</v>
+        <v>351</v>
       </c>
       <c r="L3" s="1" t="s">
-        <v>181</v>
+        <v>192</v>
       </c>
       <c r="M3" s="1" t="s">
-        <v>182</v>
+        <v>193</v>
       </c>
       <c r="N3" s="1" t="s">
-        <v>366</v>
+        <v>401</v>
       </c>
       <c r="O3" s="1" t="s">
-        <v>367</v>
+        <v>402</v>
       </c>
       <c r="P3" s="1" t="s">
-        <v>368</v>
+        <v>403</v>
       </c>
       <c r="Q3" s="1" t="s">
-        <v>369</v>
+        <v>404</v>
       </c>
       <c r="R3" s="1" t="s">
-        <v>187</v>
+        <v>198</v>
       </c>
     </row>
     <row r="4" spans="1:18" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="3" t="s">
-        <v>92</v>
+        <v>88</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>370</v>
+        <v>405</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>371</v>
+        <v>406</v>
       </c>
       <c r="D4" s="3" t="s">
-        <v>372</v>
+        <v>407</v>
       </c>
       <c r="E4" s="3" t="s">
-        <v>193</v>
+        <v>204</v>
       </c>
       <c r="F4" s="3" t="s">
-        <v>373</v>
+        <v>408</v>
       </c>
       <c r="G4" s="3" t="s">
-        <v>374</v>
+        <v>409</v>
       </c>
       <c r="H4" s="3" t="s">
-        <v>90</v>
+        <v>85</v>
       </c>
       <c r="I4" s="3" t="s">
-        <v>196</v>
+        <v>207</v>
       </c>
       <c r="J4" s="3" t="s">
-        <v>375</v>
+        <v>410</v>
       </c>
       <c r="K4" s="3" t="s">
-        <v>376</v>
+        <v>411</v>
       </c>
       <c r="L4" s="3" t="s">
-        <v>375</v>
+        <v>410</v>
       </c>
       <c r="M4" s="3" t="s">
-        <v>376</v>
+        <v>411</v>
       </c>
       <c r="N4" s="3" t="s">
-        <v>375</v>
+        <v>410</v>
       </c>
       <c r="O4" s="3" t="s">
-        <v>199</v>
+        <v>210</v>
       </c>
       <c r="P4" s="3" t="s">
-        <v>197</v>
+        <v>208</v>
       </c>
       <c r="Q4" s="3" t="s">
-        <v>377</v>
+        <v>211</v>
       </c>
       <c r="R4" s="3" t="s">
-        <v>90</v>
+        <v>85</v>
       </c>
     </row>
     <row r="5" spans="1:18" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="3" t="s">
-        <v>108</v>
+        <v>102</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>378</v>
+        <v>412</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>371</v>
+        <v>406</v>
       </c>
       <c r="D5" s="3" t="s">
-        <v>372</v>
+        <v>407</v>
       </c>
       <c r="E5" s="3" t="s">
-        <v>193</v>
+        <v>204</v>
       </c>
       <c r="F5" s="3" t="s">
-        <v>373</v>
+        <v>408</v>
       </c>
       <c r="G5" s="3" t="s">
-        <v>374</v>
+        <v>409</v>
       </c>
       <c r="H5" s="3" t="s">
-        <v>90</v>
+        <v>85</v>
       </c>
       <c r="I5" s="3" t="s">
-        <v>196</v>
+        <v>207</v>
       </c>
       <c r="J5" s="3" t="s">
-        <v>375</v>
+        <v>410</v>
       </c>
       <c r="K5" s="3" t="s">
-        <v>376</v>
+        <v>411</v>
       </c>
       <c r="L5" s="3" t="s">
-        <v>375</v>
+        <v>410</v>
       </c>
       <c r="M5" s="3" t="s">
-        <v>376</v>
+        <v>411</v>
       </c>
       <c r="N5" s="3" t="s">
-        <v>375</v>
+        <v>410</v>
       </c>
       <c r="O5" s="3" t="s">
-        <v>199</v>
+        <v>210</v>
       </c>
       <c r="P5" s="3" t="s">
-        <v>197</v>
+        <v>208</v>
       </c>
       <c r="Q5" s="3" t="s">
-        <v>377</v>
+        <v>211</v>
       </c>
       <c r="R5" s="3" t="s">
-        <v>90</v>
+        <v>85</v>
       </c>
     </row>
     <row r="6" spans="1:18" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="3" t="s">
-        <v>116</v>
+        <v>109</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>379</v>
+        <v>413</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>371</v>
+        <v>406</v>
       </c>
       <c r="D6" s="3" t="s">
-        <v>372</v>
+        <v>407</v>
       </c>
       <c r="E6" s="3" t="s">
-        <v>193</v>
+        <v>204</v>
       </c>
       <c r="F6" s="3" t="s">
-        <v>373</v>
+        <v>408</v>
       </c>
       <c r="G6" s="3" t="s">
-        <v>374</v>
+        <v>409</v>
       </c>
       <c r="H6" s="3" t="s">
-        <v>90</v>
+        <v>85</v>
       </c>
       <c r="I6" s="3" t="s">
-        <v>196</v>
+        <v>207</v>
       </c>
       <c r="J6" s="3" t="s">
-        <v>375</v>
+        <v>410</v>
       </c>
       <c r="K6" s="3" t="s">
-        <v>376</v>
+        <v>411</v>
       </c>
       <c r="L6" s="3" t="s">
-        <v>375</v>
+        <v>410</v>
       </c>
       <c r="M6" s="3" t="s">
-        <v>376</v>
+        <v>411</v>
       </c>
       <c r="N6" s="3" t="s">
-        <v>375</v>
+        <v>410</v>
       </c>
       <c r="O6" s="3" t="s">
-        <v>199</v>
+        <v>210</v>
       </c>
       <c r="P6" s="3" t="s">
-        <v>197</v>
+        <v>208</v>
       </c>
       <c r="Q6" s="3" t="s">
-        <v>377</v>
+        <v>211</v>
       </c>
       <c r="R6" s="3" t="s">
-        <v>90</v>
+        <v>85</v>
       </c>
     </row>
     <row r="7" spans="1:18" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="3" t="s">
-        <v>121</v>
+        <v>117</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>380</v>
+        <v>414</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>371</v>
+        <v>406</v>
       </c>
       <c r="D7" s="3" t="s">
-        <v>372</v>
+        <v>407</v>
       </c>
       <c r="E7" s="3" t="s">
-        <v>193</v>
+        <v>204</v>
       </c>
       <c r="F7" s="3" t="s">
-        <v>373</v>
+        <v>408</v>
       </c>
       <c r="G7" s="3" t="s">
-        <v>374</v>
+        <v>409</v>
       </c>
       <c r="H7" s="3" t="s">
-        <v>90</v>
+        <v>85</v>
       </c>
       <c r="I7" s="3" t="s">
-        <v>196</v>
+        <v>207</v>
       </c>
       <c r="J7" s="3" t="s">
-        <v>375</v>
+        <v>410</v>
       </c>
       <c r="K7" s="3" t="s">
-        <v>376</v>
+        <v>411</v>
       </c>
       <c r="L7" s="3" t="s">
-        <v>375</v>
+        <v>410</v>
       </c>
       <c r="M7" s="3" t="s">
-        <v>376</v>
+        <v>411</v>
       </c>
       <c r="N7" s="3" t="s">
-        <v>375</v>
+        <v>410</v>
       </c>
       <c r="O7" s="3" t="s">
-        <v>199</v>
+        <v>210</v>
       </c>
       <c r="P7" s="3" t="s">
-        <v>197</v>
+        <v>208</v>
       </c>
       <c r="Q7" s="3" t="s">
-        <v>377</v>
+        <v>211</v>
       </c>
       <c r="R7" s="3" t="s">
-        <v>90</v>
+        <v>85</v>
       </c>
     </row>
     <row r="8" spans="1:18" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="3" t="s">
-        <v>130</v>
+        <v>123</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>381</v>
+        <v>415</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>371</v>
+        <v>406</v>
       </c>
       <c r="D8" s="3" t="s">
-        <v>372</v>
+        <v>407</v>
       </c>
       <c r="E8" s="3" t="s">
-        <v>193</v>
+        <v>204</v>
       </c>
       <c r="F8" s="3" t="s">
-        <v>373</v>
+        <v>408</v>
       </c>
       <c r="G8" s="3" t="s">
-        <v>374</v>
+        <v>409</v>
       </c>
       <c r="H8" s="3" t="s">
-        <v>90</v>
+        <v>85</v>
       </c>
       <c r="I8" s="3" t="s">
-        <v>196</v>
+        <v>207</v>
       </c>
       <c r="J8" s="3" t="s">
-        <v>375</v>
+        <v>410</v>
       </c>
       <c r="K8" s="3" t="s">
-        <v>376</v>
+        <v>411</v>
       </c>
       <c r="L8" s="3" t="s">
-        <v>375</v>
+        <v>410</v>
       </c>
       <c r="M8" s="3" t="s">
-        <v>376</v>
+        <v>411</v>
       </c>
       <c r="N8" s="3" t="s">
-        <v>375</v>
+        <v>410</v>
       </c>
       <c r="O8" s="3" t="s">
-        <v>199</v>
+        <v>210</v>
       </c>
       <c r="P8" s="3" t="s">
-        <v>197</v>
+        <v>208</v>
       </c>
       <c r="Q8" s="3" t="s">
-        <v>377</v>
+        <v>211</v>
       </c>
       <c r="R8" s="3" t="s">
-        <v>90</v>
+        <v>85</v>
       </c>
     </row>
     <row r="9" spans="1:18" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="3" t="s">
-        <v>135</v>
+        <v>129</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>382</v>
+        <v>416</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>371</v>
+        <v>406</v>
       </c>
       <c r="D9" s="3" t="s">
-        <v>372</v>
+        <v>407</v>
       </c>
       <c r="E9" s="3" t="s">
-        <v>193</v>
+        <v>204</v>
       </c>
       <c r="F9" s="3" t="s">
-        <v>373</v>
+        <v>408</v>
       </c>
       <c r="G9" s="3" t="s">
-        <v>374</v>
+        <v>409</v>
       </c>
       <c r="H9" s="3" t="s">
-        <v>90</v>
+        <v>85</v>
       </c>
       <c r="I9" s="3" t="s">
-        <v>196</v>
+        <v>207</v>
       </c>
       <c r="J9" s="3" t="s">
-        <v>375</v>
+        <v>410</v>
       </c>
       <c r="K9" s="3" t="s">
-        <v>376</v>
+        <v>411</v>
       </c>
       <c r="L9" s="3" t="s">
-        <v>375</v>
+        <v>410</v>
       </c>
       <c r="M9" s="3" t="s">
-        <v>376</v>
+        <v>411</v>
       </c>
       <c r="N9" s="3" t="s">
-        <v>375</v>
+        <v>410</v>
       </c>
       <c r="O9" s="3" t="s">
-        <v>199</v>
+        <v>210</v>
       </c>
       <c r="P9" s="3" t="s">
-        <v>197</v>
+        <v>208</v>
       </c>
       <c r="Q9" s="3" t="s">
-        <v>377</v>
+        <v>211</v>
       </c>
       <c r="R9" s="3" t="s">
-        <v>90</v>
+        <v>85</v>
       </c>
     </row>
     <row r="10" spans="1:18" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="3" t="s">
-        <v>140</v>
+        <v>130</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>383</v>
+        <v>417</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>371</v>
+        <v>406</v>
       </c>
       <c r="D10" s="3" t="s">
-        <v>372</v>
+        <v>407</v>
       </c>
       <c r="E10" s="3" t="s">
-        <v>193</v>
+        <v>204</v>
       </c>
       <c r="F10" s="3" t="s">
-        <v>373</v>
+        <v>408</v>
       </c>
       <c r="G10" s="3" t="s">
-        <v>374</v>
+        <v>409</v>
       </c>
       <c r="H10" s="3" t="s">
-        <v>90</v>
+        <v>85</v>
       </c>
       <c r="I10" s="3" t="s">
-        <v>196</v>
+        <v>207</v>
       </c>
       <c r="J10" s="3" t="s">
-        <v>375</v>
+        <v>410</v>
       </c>
       <c r="K10" s="3" t="s">
-        <v>376</v>
+        <v>411</v>
       </c>
       <c r="L10" s="3" t="s">
-        <v>375</v>
+        <v>410</v>
       </c>
       <c r="M10" s="3" t="s">
-        <v>376</v>
+        <v>411</v>
       </c>
       <c r="N10" s="3" t="s">
-        <v>375</v>
+        <v>410</v>
       </c>
       <c r="O10" s="3" t="s">
-        <v>199</v>
+        <v>210</v>
       </c>
       <c r="P10" s="3" t="s">
-        <v>197</v>
+        <v>208</v>
       </c>
       <c r="Q10" s="3" t="s">
-        <v>377</v>
+        <v>211</v>
       </c>
       <c r="R10" s="3" t="s">
-        <v>90</v>
+        <v>85</v>
       </c>
     </row>
     <row r="11" spans="1:18" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="3" t="s">
-        <v>144</v>
+        <v>131</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>384</v>
+        <v>418</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>371</v>
+        <v>406</v>
       </c>
       <c r="D11" s="3" t="s">
-        <v>372</v>
+        <v>407</v>
       </c>
       <c r="E11" s="3" t="s">
-        <v>193</v>
+        <v>204</v>
       </c>
       <c r="F11" s="3" t="s">
-        <v>373</v>
+        <v>408</v>
       </c>
       <c r="G11" s="3" t="s">
-        <v>374</v>
+        <v>409</v>
       </c>
       <c r="H11" s="3" t="s">
-        <v>90</v>
+        <v>85</v>
       </c>
       <c r="I11" s="3" t="s">
-        <v>196</v>
+        <v>207</v>
       </c>
       <c r="J11" s="3" t="s">
-        <v>375</v>
+        <v>410</v>
       </c>
       <c r="K11" s="3" t="s">
-        <v>376</v>
+        <v>411</v>
       </c>
       <c r="L11" s="3" t="s">
-        <v>375</v>
+        <v>410</v>
       </c>
       <c r="M11" s="3" t="s">
-        <v>376</v>
+        <v>411</v>
       </c>
       <c r="N11" s="3" t="s">
-        <v>375</v>
+        <v>410</v>
       </c>
       <c r="O11" s="3" t="s">
-        <v>199</v>
+        <v>210</v>
       </c>
       <c r="P11" s="3" t="s">
-        <v>197</v>
+        <v>208</v>
       </c>
       <c r="Q11" s="3" t="s">
-        <v>377</v>
+        <v>211</v>
       </c>
       <c r="R11" s="3" t="s">
-        <v>90</v>
+        <v>85</v>
       </c>
     </row>
     <row r="12" spans="1:18" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="3" t="s">
-        <v>146</v>
+        <v>132</v>
       </c>
       <c r="B12" s="3" t="s">
-        <v>385</v>
+        <v>419</v>
       </c>
       <c r="C12" s="3" t="s">
-        <v>371</v>
+        <v>406</v>
       </c>
       <c r="D12" s="3" t="s">
-        <v>372</v>
+        <v>407</v>
       </c>
       <c r="E12" s="3" t="s">
-        <v>193</v>
+        <v>204</v>
       </c>
       <c r="F12" s="3" t="s">
-        <v>373</v>
+        <v>408</v>
       </c>
       <c r="G12" s="3" t="s">
-        <v>374</v>
+        <v>409</v>
       </c>
       <c r="H12" s="3" t="s">
-        <v>90</v>
+        <v>85</v>
       </c>
       <c r="I12" s="3" t="s">
-        <v>196</v>
+        <v>207</v>
       </c>
       <c r="J12" s="3" t="s">
-        <v>375</v>
+        <v>410</v>
       </c>
       <c r="K12" s="3" t="s">
-        <v>376</v>
+        <v>411</v>
       </c>
       <c r="L12" s="3" t="s">
-        <v>375</v>
+        <v>410</v>
       </c>
       <c r="M12" s="3" t="s">
-        <v>376</v>
+        <v>411</v>
       </c>
       <c r="N12" s="3" t="s">
-        <v>375</v>
+        <v>410</v>
       </c>
       <c r="O12" s="3" t="s">
-        <v>199</v>
+        <v>210</v>
       </c>
       <c r="P12" s="3" t="s">
-        <v>197</v>
+        <v>208</v>
       </c>
       <c r="Q12" s="3" t="s">
-        <v>377</v>
+        <v>211</v>
       </c>
       <c r="R12" s="3" t="s">
-        <v>90</v>
+        <v>85</v>
       </c>
     </row>
     <row r="13" spans="1:18" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="3" t="s">
-        <v>148</v>
+        <v>133</v>
       </c>
       <c r="B13" s="3" t="s">
-        <v>386</v>
+        <v>420</v>
       </c>
       <c r="C13" s="3" t="s">
-        <v>371</v>
+        <v>406</v>
       </c>
       <c r="D13" s="3" t="s">
-        <v>372</v>
+        <v>407</v>
       </c>
       <c r="E13" s="3" t="s">
-        <v>193</v>
+        <v>204</v>
       </c>
       <c r="F13" s="3" t="s">
-        <v>373</v>
+        <v>408</v>
       </c>
       <c r="G13" s="3" t="s">
-        <v>374</v>
+        <v>409</v>
       </c>
       <c r="H13" s="3" t="s">
-        <v>90</v>
+        <v>85</v>
       </c>
       <c r="I13" s="3" t="s">
-        <v>196</v>
+        <v>207</v>
       </c>
       <c r="J13" s="3" t="s">
-        <v>375</v>
+        <v>410</v>
       </c>
       <c r="K13" s="3" t="s">
-        <v>376</v>
+        <v>411</v>
       </c>
       <c r="L13" s="3" t="s">
-        <v>375</v>
+        <v>410</v>
       </c>
       <c r="M13" s="3" t="s">
-        <v>376</v>
+        <v>411</v>
       </c>
       <c r="N13" s="3" t="s">
-        <v>375</v>
+        <v>410</v>
       </c>
       <c r="O13" s="3" t="s">
-        <v>199</v>
+        <v>210</v>
       </c>
       <c r="P13" s="3" t="s">
-        <v>197</v>
+        <v>208</v>
       </c>
       <c r="Q13" s="3" t="s">
-        <v>377</v>
+        <v>211</v>
       </c>
       <c r="R13" s="3" t="s">
-        <v>90</v>
+        <v>85</v>
       </c>
     </row>
     <row r="14" spans="1:18" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="3" t="s">
-        <v>150</v>
+        <v>134</v>
       </c>
       <c r="B14" s="3" t="s">
-        <v>387</v>
+        <v>421</v>
       </c>
       <c r="C14" s="3" t="s">
-        <v>371</v>
+        <v>406</v>
       </c>
       <c r="D14" s="3" t="s">
-        <v>372</v>
+        <v>407</v>
       </c>
       <c r="E14" s="3" t="s">
-        <v>193</v>
+        <v>204</v>
       </c>
       <c r="F14" s="3" t="s">
-        <v>373</v>
+        <v>408</v>
       </c>
       <c r="G14" s="3" t="s">
-        <v>374</v>
+        <v>409</v>
       </c>
       <c r="H14" s="3" t="s">
-        <v>90</v>
+        <v>85</v>
       </c>
       <c r="I14" s="3" t="s">
-        <v>196</v>
+        <v>207</v>
       </c>
       <c r="J14" s="3" t="s">
-        <v>375</v>
+        <v>410</v>
       </c>
       <c r="K14" s="3" t="s">
-        <v>376</v>
+        <v>411</v>
       </c>
       <c r="L14" s="3" t="s">
-        <v>375</v>
+        <v>410</v>
       </c>
       <c r="M14" s="3" t="s">
-        <v>376</v>
+        <v>411</v>
       </c>
       <c r="N14" s="3" t="s">
-        <v>375</v>
+        <v>410</v>
       </c>
       <c r="O14" s="3" t="s">
-        <v>199</v>
+        <v>210</v>
       </c>
       <c r="P14" s="3" t="s">
-        <v>197</v>
+        <v>208</v>
       </c>
       <c r="Q14" s="3" t="s">
-        <v>377</v>
+        <v>211</v>
       </c>
       <c r="R14" s="3" t="s">
-        <v>90</v>
+        <v>85</v>
       </c>
     </row>
     <row r="15" spans="1:18" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" s="3" t="s">
-        <v>152</v>
+        <v>135</v>
       </c>
       <c r="B15" s="3" t="s">
-        <v>388</v>
+        <v>422</v>
       </c>
       <c r="C15" s="3" t="s">
-        <v>371</v>
+        <v>406</v>
       </c>
       <c r="D15" s="3" t="s">
-        <v>372</v>
+        <v>407</v>
       </c>
       <c r="E15" s="3" t="s">
-        <v>193</v>
+        <v>204</v>
       </c>
       <c r="F15" s="3" t="s">
-        <v>373</v>
+        <v>408</v>
       </c>
       <c r="G15" s="3" t="s">
-        <v>374</v>
+        <v>409</v>
       </c>
       <c r="H15" s="3" t="s">
-        <v>90</v>
+        <v>85</v>
       </c>
       <c r="I15" s="3" t="s">
-        <v>196</v>
+        <v>207</v>
       </c>
       <c r="J15" s="3" t="s">
-        <v>375</v>
+        <v>410</v>
       </c>
       <c r="K15" s="3" t="s">
-        <v>376</v>
+        <v>411</v>
       </c>
       <c r="L15" s="3" t="s">
-        <v>375</v>
+        <v>410</v>
       </c>
       <c r="M15" s="3" t="s">
-        <v>376</v>
+        <v>411</v>
       </c>
       <c r="N15" s="3" t="s">
-        <v>375</v>
+        <v>410</v>
       </c>
       <c r="O15" s="3" t="s">
-        <v>199</v>
+        <v>210</v>
       </c>
       <c r="P15" s="3" t="s">
-        <v>197</v>
+        <v>208</v>
       </c>
       <c r="Q15" s="3" t="s">
-        <v>377</v>
+        <v>211</v>
       </c>
       <c r="R15" s="3" t="s">
-        <v>90</v>
+        <v>85</v>
+      </c>
+    </row>
+    <row r="16" spans="1:18" ht="45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A16" s="3" t="s">
+        <v>136</v>
+      </c>
+      <c r="B16" s="3" t="s">
+        <v>423</v>
+      </c>
+      <c r="C16" s="3" t="s">
+        <v>406</v>
+      </c>
+      <c r="D16" s="3" t="s">
+        <v>407</v>
+      </c>
+      <c r="E16" s="3" t="s">
+        <v>204</v>
+      </c>
+      <c r="F16" s="3" t="s">
+        <v>408</v>
+      </c>
+      <c r="G16" s="3" t="s">
+        <v>409</v>
+      </c>
+      <c r="H16" s="3" t="s">
+        <v>85</v>
+      </c>
+      <c r="I16" s="3" t="s">
+        <v>207</v>
+      </c>
+      <c r="J16" s="3" t="s">
+        <v>410</v>
+      </c>
+      <c r="K16" s="3" t="s">
+        <v>411</v>
+      </c>
+      <c r="L16" s="3" t="s">
+        <v>410</v>
+      </c>
+      <c r="M16" s="3" t="s">
+        <v>411</v>
+      </c>
+      <c r="N16" s="3" t="s">
+        <v>410</v>
+      </c>
+      <c r="O16" s="3" t="s">
+        <v>210</v>
+      </c>
+      <c r="P16" s="3" t="s">
+        <v>208</v>
+      </c>
+      <c r="Q16" s="3" t="s">
+        <v>211</v>
+      </c>
+      <c r="R16" s="3" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="17" spans="1:18" ht="45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A17" s="3" t="s">
+        <v>138</v>
+      </c>
+      <c r="B17" s="3" t="s">
+        <v>424</v>
+      </c>
+      <c r="C17" s="3" t="s">
+        <v>406</v>
+      </c>
+      <c r="D17" s="3" t="s">
+        <v>407</v>
+      </c>
+      <c r="E17" s="3" t="s">
+        <v>204</v>
+      </c>
+      <c r="F17" s="3" t="s">
+        <v>408</v>
+      </c>
+      <c r="G17" s="3" t="s">
+        <v>409</v>
+      </c>
+      <c r="H17" s="3" t="s">
+        <v>85</v>
+      </c>
+      <c r="I17" s="3" t="s">
+        <v>207</v>
+      </c>
+      <c r="J17" s="3" t="s">
+        <v>410</v>
+      </c>
+      <c r="K17" s="3" t="s">
+        <v>411</v>
+      </c>
+      <c r="L17" s="3" t="s">
+        <v>410</v>
+      </c>
+      <c r="M17" s="3" t="s">
+        <v>411</v>
+      </c>
+      <c r="N17" s="3" t="s">
+        <v>410</v>
+      </c>
+      <c r="O17" s="3" t="s">
+        <v>210</v>
+      </c>
+      <c r="P17" s="3" t="s">
+        <v>208</v>
+      </c>
+      <c r="Q17" s="3" t="s">
+        <v>211</v>
+      </c>
+      <c r="R17" s="3" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="18" spans="1:18" ht="45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A18" s="3" t="s">
+        <v>139</v>
+      </c>
+      <c r="B18" s="3" t="s">
+        <v>425</v>
+      </c>
+      <c r="C18" s="3" t="s">
+        <v>406</v>
+      </c>
+      <c r="D18" s="3" t="s">
+        <v>407</v>
+      </c>
+      <c r="E18" s="3" t="s">
+        <v>204</v>
+      </c>
+      <c r="F18" s="3" t="s">
+        <v>408</v>
+      </c>
+      <c r="G18" s="3" t="s">
+        <v>409</v>
+      </c>
+      <c r="H18" s="3" t="s">
+        <v>85</v>
+      </c>
+      <c r="I18" s="3" t="s">
+        <v>207</v>
+      </c>
+      <c r="J18" s="3" t="s">
+        <v>410</v>
+      </c>
+      <c r="K18" s="3" t="s">
+        <v>411</v>
+      </c>
+      <c r="L18" s="3" t="s">
+        <v>410</v>
+      </c>
+      <c r="M18" s="3" t="s">
+        <v>411</v>
+      </c>
+      <c r="N18" s="3" t="s">
+        <v>410</v>
+      </c>
+      <c r="O18" s="3" t="s">
+        <v>210</v>
+      </c>
+      <c r="P18" s="3" t="s">
+        <v>208</v>
+      </c>
+      <c r="Q18" s="3" t="s">
+        <v>211</v>
+      </c>
+      <c r="R18" s="3" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="19" spans="1:18" ht="45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A19" s="3" t="s">
+        <v>141</v>
+      </c>
+      <c r="B19" s="3" t="s">
+        <v>426</v>
+      </c>
+      <c r="C19" s="3" t="s">
+        <v>406</v>
+      </c>
+      <c r="D19" s="3" t="s">
+        <v>407</v>
+      </c>
+      <c r="E19" s="3" t="s">
+        <v>204</v>
+      </c>
+      <c r="F19" s="3" t="s">
+        <v>408</v>
+      </c>
+      <c r="G19" s="3" t="s">
+        <v>409</v>
+      </c>
+      <c r="H19" s="3" t="s">
+        <v>85</v>
+      </c>
+      <c r="I19" s="3" t="s">
+        <v>207</v>
+      </c>
+      <c r="J19" s="3" t="s">
+        <v>410</v>
+      </c>
+      <c r="K19" s="3" t="s">
+        <v>411</v>
+      </c>
+      <c r="L19" s="3" t="s">
+        <v>410</v>
+      </c>
+      <c r="M19" s="3" t="s">
+        <v>411</v>
+      </c>
+      <c r="N19" s="3" t="s">
+        <v>410</v>
+      </c>
+      <c r="O19" s="3" t="s">
+        <v>210</v>
+      </c>
+      <c r="P19" s="3" t="s">
+        <v>208</v>
+      </c>
+      <c r="Q19" s="3" t="s">
+        <v>211</v>
+      </c>
+      <c r="R19" s="3" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="20" spans="1:18" ht="45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A20" s="3" t="s">
+        <v>142</v>
+      </c>
+      <c r="B20" s="3" t="s">
+        <v>427</v>
+      </c>
+      <c r="C20" s="3" t="s">
+        <v>406</v>
+      </c>
+      <c r="D20" s="3" t="s">
+        <v>407</v>
+      </c>
+      <c r="E20" s="3" t="s">
+        <v>204</v>
+      </c>
+      <c r="F20" s="3" t="s">
+        <v>408</v>
+      </c>
+      <c r="G20" s="3" t="s">
+        <v>409</v>
+      </c>
+      <c r="H20" s="3" t="s">
+        <v>85</v>
+      </c>
+      <c r="I20" s="3" t="s">
+        <v>207</v>
+      </c>
+      <c r="J20" s="3" t="s">
+        <v>410</v>
+      </c>
+      <c r="K20" s="3" t="s">
+        <v>411</v>
+      </c>
+      <c r="L20" s="3" t="s">
+        <v>410</v>
+      </c>
+      <c r="M20" s="3" t="s">
+        <v>411</v>
+      </c>
+      <c r="N20" s="3" t="s">
+        <v>410</v>
+      </c>
+      <c r="O20" s="3" t="s">
+        <v>210</v>
+      </c>
+      <c r="P20" s="3" t="s">
+        <v>208</v>
+      </c>
+      <c r="Q20" s="3" t="s">
+        <v>211</v>
+      </c>
+      <c r="R20" s="3" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="21" spans="1:18" ht="45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A21" s="3" t="s">
+        <v>144</v>
+      </c>
+      <c r="B21" s="3" t="s">
+        <v>428</v>
+      </c>
+      <c r="C21" s="3" t="s">
+        <v>406</v>
+      </c>
+      <c r="D21" s="3" t="s">
+        <v>407</v>
+      </c>
+      <c r="E21" s="3" t="s">
+        <v>204</v>
+      </c>
+      <c r="F21" s="3" t="s">
+        <v>408</v>
+      </c>
+      <c r="G21" s="3" t="s">
+        <v>409</v>
+      </c>
+      <c r="H21" s="3" t="s">
+        <v>85</v>
+      </c>
+      <c r="I21" s="3" t="s">
+        <v>207</v>
+      </c>
+      <c r="J21" s="3" t="s">
+        <v>410</v>
+      </c>
+      <c r="K21" s="3" t="s">
+        <v>411</v>
+      </c>
+      <c r="L21" s="3" t="s">
+        <v>410</v>
+      </c>
+      <c r="M21" s="3" t="s">
+        <v>411</v>
+      </c>
+      <c r="N21" s="3" t="s">
+        <v>410</v>
+      </c>
+      <c r="O21" s="3" t="s">
+        <v>210</v>
+      </c>
+      <c r="P21" s="3" t="s">
+        <v>208</v>
+      </c>
+      <c r="Q21" s="3" t="s">
+        <v>211</v>
+      </c>
+      <c r="R21" s="3" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="22" spans="1:18" ht="45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A22" s="3" t="s">
+        <v>150</v>
+      </c>
+      <c r="B22" s="3" t="s">
+        <v>429</v>
+      </c>
+      <c r="C22" s="3" t="s">
+        <v>406</v>
+      </c>
+      <c r="D22" s="3" t="s">
+        <v>407</v>
+      </c>
+      <c r="E22" s="3" t="s">
+        <v>204</v>
+      </c>
+      <c r="F22" s="3" t="s">
+        <v>408</v>
+      </c>
+      <c r="G22" s="3" t="s">
+        <v>409</v>
+      </c>
+      <c r="H22" s="3" t="s">
+        <v>85</v>
+      </c>
+      <c r="I22" s="3" t="s">
+        <v>207</v>
+      </c>
+      <c r="J22" s="3" t="s">
+        <v>410</v>
+      </c>
+      <c r="K22" s="3" t="s">
+        <v>411</v>
+      </c>
+      <c r="L22" s="3" t="s">
+        <v>410</v>
+      </c>
+      <c r="M22" s="3" t="s">
+        <v>411</v>
+      </c>
+      <c r="N22" s="3" t="s">
+        <v>410</v>
+      </c>
+      <c r="O22" s="3" t="s">
+        <v>210</v>
+      </c>
+      <c r="P22" s="3" t="s">
+        <v>208</v>
+      </c>
+      <c r="Q22" s="3" t="s">
+        <v>211</v>
+      </c>
+      <c r="R22" s="3" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="23" spans="1:18" ht="45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A23" s="3" t="s">
+        <v>154</v>
+      </c>
+      <c r="B23" s="3" t="s">
+        <v>430</v>
+      </c>
+      <c r="C23" s="3" t="s">
+        <v>406</v>
+      </c>
+      <c r="D23" s="3" t="s">
+        <v>407</v>
+      </c>
+      <c r="E23" s="3" t="s">
+        <v>204</v>
+      </c>
+      <c r="F23" s="3" t="s">
+        <v>408</v>
+      </c>
+      <c r="G23" s="3" t="s">
+        <v>409</v>
+      </c>
+      <c r="H23" s="3" t="s">
+        <v>85</v>
+      </c>
+      <c r="I23" s="3" t="s">
+        <v>207</v>
+      </c>
+      <c r="J23" s="3" t="s">
+        <v>410</v>
+      </c>
+      <c r="K23" s="3" t="s">
+        <v>411</v>
+      </c>
+      <c r="L23" s="3" t="s">
+        <v>410</v>
+      </c>
+      <c r="M23" s="3" t="s">
+        <v>411</v>
+      </c>
+      <c r="N23" s="3" t="s">
+        <v>410</v>
+      </c>
+      <c r="O23" s="3" t="s">
+        <v>210</v>
+      </c>
+      <c r="P23" s="3" t="s">
+        <v>208</v>
+      </c>
+      <c r="Q23" s="3" t="s">
+        <v>211</v>
+      </c>
+      <c r="R23" s="3" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="24" spans="1:18" ht="45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A24" s="3" t="s">
+        <v>156</v>
+      </c>
+      <c r="B24" s="3" t="s">
+        <v>431</v>
+      </c>
+      <c r="C24" s="3" t="s">
+        <v>406</v>
+      </c>
+      <c r="D24" s="3" t="s">
+        <v>407</v>
+      </c>
+      <c r="E24" s="3" t="s">
+        <v>204</v>
+      </c>
+      <c r="F24" s="3" t="s">
+        <v>408</v>
+      </c>
+      <c r="G24" s="3" t="s">
+        <v>409</v>
+      </c>
+      <c r="H24" s="3" t="s">
+        <v>85</v>
+      </c>
+      <c r="I24" s="3" t="s">
+        <v>207</v>
+      </c>
+      <c r="J24" s="3" t="s">
+        <v>410</v>
+      </c>
+      <c r="K24" s="3" t="s">
+        <v>411</v>
+      </c>
+      <c r="L24" s="3" t="s">
+        <v>410</v>
+      </c>
+      <c r="M24" s="3" t="s">
+        <v>411</v>
+      </c>
+      <c r="N24" s="3" t="s">
+        <v>410</v>
+      </c>
+      <c r="O24" s="3" t="s">
+        <v>210</v>
+      </c>
+      <c r="P24" s="3" t="s">
+        <v>208</v>
+      </c>
+      <c r="Q24" s="3" t="s">
+        <v>211</v>
+      </c>
+      <c r="R24" s="3" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="25" spans="1:18" ht="45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A25" s="3" t="s">
+        <v>158</v>
+      </c>
+      <c r="B25" s="3" t="s">
+        <v>432</v>
+      </c>
+      <c r="C25" s="3" t="s">
+        <v>406</v>
+      </c>
+      <c r="D25" s="3" t="s">
+        <v>407</v>
+      </c>
+      <c r="E25" s="3" t="s">
+        <v>204</v>
+      </c>
+      <c r="F25" s="3" t="s">
+        <v>408</v>
+      </c>
+      <c r="G25" s="3" t="s">
+        <v>409</v>
+      </c>
+      <c r="H25" s="3" t="s">
+        <v>85</v>
+      </c>
+      <c r="I25" s="3" t="s">
+        <v>207</v>
+      </c>
+      <c r="J25" s="3" t="s">
+        <v>410</v>
+      </c>
+      <c r="K25" s="3" t="s">
+        <v>411</v>
+      </c>
+      <c r="L25" s="3" t="s">
+        <v>410</v>
+      </c>
+      <c r="M25" s="3" t="s">
+        <v>411</v>
+      </c>
+      <c r="N25" s="3" t="s">
+        <v>410</v>
+      </c>
+      <c r="O25" s="3" t="s">
+        <v>210</v>
+      </c>
+      <c r="P25" s="3" t="s">
+        <v>208</v>
+      </c>
+      <c r="Q25" s="3" t="s">
+        <v>211</v>
+      </c>
+      <c r="R25" s="3" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="26" spans="1:18" ht="45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A26" s="3" t="s">
+        <v>160</v>
+      </c>
+      <c r="B26" s="3" t="s">
+        <v>433</v>
+      </c>
+      <c r="C26" s="3" t="s">
+        <v>406</v>
+      </c>
+      <c r="D26" s="3" t="s">
+        <v>407</v>
+      </c>
+      <c r="E26" s="3" t="s">
+        <v>204</v>
+      </c>
+      <c r="F26" s="3" t="s">
+        <v>408</v>
+      </c>
+      <c r="G26" s="3" t="s">
+        <v>409</v>
+      </c>
+      <c r="H26" s="3" t="s">
+        <v>85</v>
+      </c>
+      <c r="I26" s="3" t="s">
+        <v>207</v>
+      </c>
+      <c r="J26" s="3" t="s">
+        <v>410</v>
+      </c>
+      <c r="K26" s="3" t="s">
+        <v>411</v>
+      </c>
+      <c r="L26" s="3" t="s">
+        <v>410</v>
+      </c>
+      <c r="M26" s="3" t="s">
+        <v>411</v>
+      </c>
+      <c r="N26" s="3" t="s">
+        <v>410</v>
+      </c>
+      <c r="O26" s="3" t="s">
+        <v>210</v>
+      </c>
+      <c r="P26" s="3" t="s">
+        <v>208</v>
+      </c>
+      <c r="Q26" s="3" t="s">
+        <v>211</v>
+      </c>
+      <c r="R26" s="3" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="27" spans="1:18" ht="45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A27" s="3" t="s">
+        <v>163</v>
+      </c>
+      <c r="B27" s="3" t="s">
+        <v>434</v>
+      </c>
+      <c r="C27" s="3" t="s">
+        <v>406</v>
+      </c>
+      <c r="D27" s="3" t="s">
+        <v>407</v>
+      </c>
+      <c r="E27" s="3" t="s">
+        <v>204</v>
+      </c>
+      <c r="F27" s="3" t="s">
+        <v>408</v>
+      </c>
+      <c r="G27" s="3" t="s">
+        <v>409</v>
+      </c>
+      <c r="H27" s="3" t="s">
+        <v>85</v>
+      </c>
+      <c r="I27" s="3" t="s">
+        <v>207</v>
+      </c>
+      <c r="J27" s="3" t="s">
+        <v>410</v>
+      </c>
+      <c r="K27" s="3" t="s">
+        <v>411</v>
+      </c>
+      <c r="L27" s="3" t="s">
+        <v>410</v>
+      </c>
+      <c r="M27" s="3" t="s">
+        <v>411</v>
+      </c>
+      <c r="N27" s="3" t="s">
+        <v>410</v>
+      </c>
+      <c r="O27" s="3" t="s">
+        <v>210</v>
+      </c>
+      <c r="P27" s="3" t="s">
+        <v>208</v>
+      </c>
+      <c r="Q27" s="3" t="s">
+        <v>211</v>
+      </c>
+      <c r="R27" s="3" t="s">
+        <v>85</v>
       </c>
     </row>
   </sheetData>
   <dataValidations count="3">
-    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="E4:E201">
+    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="E4:E201" xr:uid="{00000000-0002-0000-0A00-000000000000}">
       <formula1>Hidden_1_Tabla_4361044</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="I4:I201">
+    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="I4:I201" xr:uid="{00000000-0002-0000-0A00-000001000000}">
       <formula1>Hidden_2_Tabla_4361048</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="P4:P201">
+    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="P4:P201" xr:uid="{00000000-0002-0000-0A00-000002000000}">
       <formula1>Hidden_3_Tabla_43610415</formula1>
     </dataValidation>
   </dataValidations>
@@ -3672,138 +4472,138 @@
 </file>
 
 <file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0B00-000000000000}">
   <dimension ref="A1:A26"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
     <row r="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
-        <v>232</v>
+        <v>255</v>
       </c>
     </row>
     <row r="2" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>226</v>
+        <v>249</v>
       </c>
     </row>
     <row r="3" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>225</v>
+        <v>248</v>
       </c>
     </row>
     <row r="4" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>216</v>
+        <v>239</v>
       </c>
     </row>
     <row r="5" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>219</v>
+        <v>242</v>
       </c>
     </row>
     <row r="6" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>217</v>
+        <v>240</v>
       </c>
     </row>
     <row r="7" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>193</v>
+        <v>204</v>
       </c>
     </row>
     <row r="8" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>215</v>
+        <v>238</v>
       </c>
     </row>
     <row r="9" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>220</v>
+        <v>243</v>
       </c>
     </row>
     <row r="10" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>222</v>
+        <v>245</v>
       </c>
     </row>
     <row r="11" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>237</v>
+        <v>260</v>
       </c>
     </row>
     <row r="12" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>224</v>
+        <v>247</v>
       </c>
     </row>
     <row r="13" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>341</v>
+        <v>376</v>
       </c>
     </row>
     <row r="14" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>258</v>
+        <v>281</v>
       </c>
     </row>
     <row r="15" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>234</v>
+        <v>257</v>
       </c>
     </row>
     <row r="16" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>229</v>
+        <v>252</v>
       </c>
     </row>
     <row r="17" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>236</v>
+        <v>259</v>
       </c>
     </row>
     <row r="18" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>235</v>
+        <v>258</v>
       </c>
     </row>
     <row r="19" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>221</v>
+        <v>244</v>
       </c>
     </row>
     <row r="20" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>231</v>
+        <v>254</v>
       </c>
     </row>
     <row r="21" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>230</v>
+        <v>253</v>
       </c>
     </row>
     <row r="22" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
-        <v>218</v>
+        <v>241</v>
       </c>
     </row>
     <row r="23" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
-        <v>342</v>
+        <v>377</v>
       </c>
     </row>
     <row r="24" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
-        <v>227</v>
+        <v>250</v>
       </c>
     </row>
     <row r="25" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
-        <v>228</v>
+        <v>251</v>
       </c>
     </row>
     <row r="26" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
-        <v>223</v>
+        <v>246</v>
       </c>
     </row>
   </sheetData>
@@ -3812,213 +4612,213 @@
 </file>
 
 <file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0C00-000000000000}">
   <dimension ref="A1:A41"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
     <row r="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
-        <v>238</v>
+        <v>261</v>
       </c>
     </row>
     <row r="2" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>230</v>
+        <v>253</v>
       </c>
     </row>
     <row r="3" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>239</v>
+        <v>262</v>
       </c>
     </row>
     <row r="4" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>240</v>
+        <v>263</v>
       </c>
     </row>
     <row r="5" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>241</v>
+        <v>264</v>
       </c>
     </row>
     <row r="6" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>242</v>
+        <v>265</v>
       </c>
     </row>
     <row r="7" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>196</v>
+        <v>207</v>
       </c>
     </row>
     <row r="8" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>243</v>
+        <v>266</v>
       </c>
     </row>
     <row r="9" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>244</v>
+        <v>267</v>
       </c>
     </row>
     <row r="10" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>245</v>
+        <v>268</v>
       </c>
     </row>
     <row r="11" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>246</v>
+        <v>269</v>
       </c>
     </row>
     <row r="12" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>247</v>
+        <v>270</v>
       </c>
     </row>
     <row r="13" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>248</v>
+        <v>271</v>
       </c>
     </row>
     <row r="14" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>249</v>
+        <v>272</v>
       </c>
     </row>
     <row r="15" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>250</v>
+        <v>273</v>
       </c>
     </row>
     <row r="16" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>251</v>
+        <v>274</v>
       </c>
     </row>
     <row r="17" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>252</v>
+        <v>275</v>
       </c>
     </row>
     <row r="18" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>253</v>
+        <v>276</v>
       </c>
     </row>
     <row r="19" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>254</v>
+        <v>277</v>
       </c>
     </row>
     <row r="20" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>255</v>
+        <v>278</v>
       </c>
     </row>
     <row r="21" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>256</v>
+        <v>279</v>
       </c>
     </row>
     <row r="22" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
-        <v>257</v>
+        <v>280</v>
       </c>
     </row>
     <row r="23" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
-        <v>226</v>
+        <v>249</v>
       </c>
     </row>
     <row r="24" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
-        <v>258</v>
+        <v>281</v>
       </c>
     </row>
     <row r="25" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
-        <v>259</v>
+        <v>282</v>
       </c>
     </row>
     <row r="26" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
-        <v>260</v>
+        <v>283</v>
       </c>
     </row>
     <row r="27" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
-        <v>261</v>
+        <v>284</v>
       </c>
     </row>
     <row r="28" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
-        <v>262</v>
+        <v>285</v>
       </c>
     </row>
     <row r="29" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
-        <v>263</v>
+        <v>286</v>
       </c>
     </row>
     <row r="30" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
-        <v>264</v>
+        <v>287</v>
       </c>
     </row>
     <row r="31" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
-        <v>265</v>
+        <v>288</v>
       </c>
     </row>
     <row r="32" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
-        <v>266</v>
+        <v>289</v>
       </c>
     </row>
     <row r="33" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
-        <v>267</v>
+        <v>290</v>
       </c>
     </row>
     <row r="34" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
-        <v>268</v>
+        <v>291</v>
       </c>
     </row>
     <row r="35" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
-        <v>269</v>
+        <v>292</v>
       </c>
     </row>
     <row r="36" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
-        <v>270</v>
+        <v>293</v>
       </c>
     </row>
     <row r="37" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
-        <v>271</v>
+        <v>294</v>
       </c>
     </row>
     <row r="38" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
-        <v>272</v>
+        <v>295</v>
       </c>
     </row>
     <row r="39" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
-        <v>273</v>
+        <v>296</v>
       </c>
     </row>
     <row r="40" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
-        <v>274</v>
+        <v>297</v>
       </c>
     </row>
     <row r="41" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
-        <v>275</v>
+        <v>298</v>
       </c>
     </row>
   </sheetData>
@@ -4027,168 +4827,168 @@
 </file>
 
 <file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0D00-000000000000}">
   <dimension ref="A1:A32"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
     <row r="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
-        <v>343</v>
+        <v>378</v>
       </c>
     </row>
     <row r="2" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>302</v>
+        <v>325</v>
       </c>
     </row>
     <row r="3" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>303</v>
+        <v>326</v>
       </c>
     </row>
     <row r="4" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>276</v>
+        <v>299</v>
       </c>
     </row>
     <row r="5" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>300</v>
+        <v>323</v>
       </c>
     </row>
     <row r="6" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>277</v>
+        <v>300</v>
       </c>
     </row>
     <row r="7" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>278</v>
+        <v>301</v>
       </c>
     </row>
     <row r="8" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>279</v>
+        <v>302</v>
       </c>
     </row>
     <row r="9" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>295</v>
+        <v>318</v>
       </c>
     </row>
     <row r="10" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>344</v>
+        <v>379</v>
       </c>
     </row>
     <row r="11" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>284</v>
+        <v>307</v>
       </c>
     </row>
     <row r="12" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>297</v>
+        <v>320</v>
       </c>
     </row>
     <row r="13" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>287</v>
+        <v>310</v>
       </c>
     </row>
     <row r="14" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>292</v>
+        <v>315</v>
       </c>
     </row>
     <row r="15" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>281</v>
+        <v>304</v>
       </c>
     </row>
     <row r="16" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>288</v>
+        <v>311</v>
       </c>
     </row>
     <row r="17" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>299</v>
+        <v>322</v>
       </c>
     </row>
     <row r="18" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>294</v>
+        <v>317</v>
       </c>
     </row>
     <row r="19" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>197</v>
+        <v>208</v>
       </c>
     </row>
     <row r="20" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>286</v>
+        <v>309</v>
       </c>
     </row>
     <row r="21" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>289</v>
+        <v>312</v>
       </c>
     </row>
     <row r="22" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
-        <v>290</v>
+        <v>313</v>
       </c>
     </row>
     <row r="23" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
-        <v>304</v>
+        <v>327</v>
       </c>
     </row>
     <row r="24" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
-        <v>283</v>
+        <v>306</v>
       </c>
     </row>
     <row r="25" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
-        <v>282</v>
+        <v>305</v>
       </c>
     </row>
     <row r="26" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
-        <v>280</v>
+        <v>303</v>
       </c>
     </row>
     <row r="27" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
-        <v>306</v>
+        <v>329</v>
       </c>
     </row>
     <row r="28" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
-        <v>291</v>
+        <v>314</v>
       </c>
     </row>
     <row r="29" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
-        <v>285</v>
+        <v>308</v>
       </c>
     </row>
     <row r="30" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
-        <v>345</v>
+        <v>380</v>
       </c>
     </row>
     <row r="31" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
-        <v>298</v>
+        <v>321</v>
       </c>
     </row>
     <row r="32" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
-        <v>293</v>
+        <v>316</v>
       </c>
     </row>
   </sheetData>
@@ -4197,18 +4997,18 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:A2"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
     <row r="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
     </row>
     <row r="2" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>153</v>
+        <v>164</v>
       </c>
     </row>
   </sheetData>
@@ -4217,11 +5017,11 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:T15"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
+  <dimension ref="A1:T27"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="8.42578125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="9.42578125" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="36.140625" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="121.85546875" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="28.85546875" bestFit="1" customWidth="1"/>
@@ -4239,7 +5039,7 @@
     <col min="16" max="16" width="15.28515625" bestFit="1" customWidth="1"/>
     <col min="17" max="17" width="40.140625" bestFit="1" customWidth="1"/>
     <col min="18" max="18" width="73.85546875" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="99.42578125" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="110.28515625" bestFit="1" customWidth="1"/>
     <col min="20" max="20" width="36.5703125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
@@ -4301,873 +5101,1617 @@
     </row>
     <row r="2" spans="1:20" hidden="1" x14ac:dyDescent="0.25">
       <c r="C2" t="s">
-        <v>154</v>
+        <v>165</v>
       </c>
       <c r="D2" t="s">
-        <v>155</v>
+        <v>166</v>
       </c>
       <c r="E2" t="s">
-        <v>156</v>
+        <v>167</v>
       </c>
       <c r="F2" t="s">
-        <v>157</v>
+        <v>168</v>
       </c>
       <c r="G2" t="s">
-        <v>158</v>
+        <v>169</v>
       </c>
       <c r="H2" t="s">
-        <v>159</v>
+        <v>170</v>
       </c>
       <c r="I2" t="s">
-        <v>160</v>
+        <v>171</v>
       </c>
       <c r="J2" t="s">
-        <v>161</v>
+        <v>172</v>
       </c>
       <c r="K2" t="s">
-        <v>162</v>
+        <v>173</v>
       </c>
       <c r="L2" t="s">
-        <v>163</v>
+        <v>174</v>
       </c>
       <c r="M2" t="s">
-        <v>164</v>
+        <v>175</v>
       </c>
       <c r="N2" t="s">
-        <v>165</v>
+        <v>176</v>
       </c>
       <c r="O2" t="s">
-        <v>166</v>
+        <v>177</v>
       </c>
       <c r="P2" t="s">
-        <v>167</v>
+        <v>178</v>
       </c>
       <c r="Q2" t="s">
-        <v>168</v>
+        <v>179</v>
       </c>
       <c r="R2" t="s">
-        <v>169</v>
+        <v>180</v>
       </c>
       <c r="S2" t="s">
-        <v>170</v>
+        <v>181</v>
       </c>
       <c r="T2" t="s">
-        <v>171</v>
+        <v>182</v>
       </c>
     </row>
     <row r="3" spans="1:20" ht="30" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
-        <v>172</v>
+        <v>183</v>
       </c>
       <c r="B3" s="1"/>
       <c r="C3" s="1" t="s">
-        <v>173</v>
+        <v>184</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>174</v>
+        <v>185</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>175</v>
+        <v>186</v>
       </c>
       <c r="F3" s="1" t="s">
-        <v>176</v>
+        <v>187</v>
       </c>
       <c r="G3" s="1" t="s">
-        <v>177</v>
+        <v>188</v>
       </c>
       <c r="H3" s="1" t="s">
-        <v>178</v>
+        <v>189</v>
       </c>
       <c r="I3" s="1" t="s">
-        <v>179</v>
+        <v>190</v>
       </c>
       <c r="J3" s="1" t="s">
-        <v>180</v>
+        <v>191</v>
       </c>
       <c r="K3" s="1" t="s">
-        <v>181</v>
+        <v>192</v>
       </c>
       <c r="L3" s="1" t="s">
-        <v>182</v>
+        <v>193</v>
       </c>
       <c r="M3" s="1" t="s">
-        <v>183</v>
+        <v>194</v>
       </c>
       <c r="N3" s="1" t="s">
-        <v>184</v>
+        <v>195</v>
       </c>
       <c r="O3" s="1" t="s">
-        <v>185</v>
+        <v>196</v>
       </c>
       <c r="P3" s="1" t="s">
-        <v>186</v>
+        <v>197</v>
       </c>
       <c r="Q3" s="1" t="s">
-        <v>187</v>
+        <v>198</v>
       </c>
       <c r="R3" s="1" t="s">
-        <v>188</v>
+        <v>199</v>
       </c>
       <c r="S3" s="1" t="s">
-        <v>189</v>
+        <v>200</v>
       </c>
       <c r="T3" s="1" t="s">
-        <v>190</v>
+        <v>201</v>
       </c>
     </row>
     <row r="4" spans="1:20" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="3" t="s">
-        <v>92</v>
+        <v>88</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>191</v>
+        <v>202</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>192</v>
+        <v>203</v>
       </c>
       <c r="D4" s="3" t="s">
-        <v>193</v>
+        <v>204</v>
       </c>
       <c r="E4" s="3" t="s">
-        <v>194</v>
+        <v>205</v>
       </c>
       <c r="F4" s="3" t="s">
-        <v>195</v>
+        <v>206</v>
       </c>
       <c r="G4" s="3" t="s">
-        <v>90</v>
+        <v>85</v>
       </c>
       <c r="H4" s="3" t="s">
-        <v>196</v>
+        <v>207</v>
       </c>
       <c r="I4" s="3" t="s">
-        <v>197</v>
+        <v>208</v>
       </c>
       <c r="J4" s="3" t="s">
-        <v>198</v>
+        <v>209</v>
       </c>
       <c r="K4" s="3" t="s">
-        <v>197</v>
+        <v>208</v>
       </c>
       <c r="L4" s="3" t="s">
-        <v>198</v>
+        <v>209</v>
       </c>
       <c r="M4" s="3" t="s">
-        <v>197</v>
+        <v>208</v>
       </c>
       <c r="N4" s="3" t="s">
-        <v>199</v>
+        <v>210</v>
       </c>
       <c r="O4" s="3" t="s">
-        <v>197</v>
+        <v>208</v>
       </c>
       <c r="P4" s="3" t="s">
-        <v>200</v>
+        <v>211</v>
       </c>
       <c r="Q4" s="3" t="s">
-        <v>90</v>
+        <v>85</v>
       </c>
       <c r="R4" s="3" t="s">
-        <v>201</v>
+        <v>212</v>
       </c>
       <c r="S4" s="3" t="s">
-        <v>202</v>
+        <v>213</v>
       </c>
       <c r="T4" s="3" t="s">
-        <v>203</v>
+        <v>214</v>
       </c>
     </row>
     <row r="5" spans="1:20" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="3" t="s">
-        <v>108</v>
+        <v>102</v>
       </c>
       <c r="B5" s="3" t="s">
+        <v>215</v>
+      </c>
+      <c r="C5" s="3" t="s">
+        <v>203</v>
+      </c>
+      <c r="D5" s="3" t="s">
         <v>204</v>
       </c>
-      <c r="C5" s="3" t="s">
-        <v>192</v>
-      </c>
-      <c r="D5" s="3" t="s">
-        <v>193</v>
-      </c>
       <c r="E5" s="3" t="s">
-        <v>194</v>
+        <v>205</v>
       </c>
       <c r="F5" s="3" t="s">
-        <v>195</v>
+        <v>206</v>
       </c>
       <c r="G5" s="3" t="s">
-        <v>90</v>
+        <v>85</v>
       </c>
       <c r="H5" s="3" t="s">
-        <v>196</v>
+        <v>207</v>
       </c>
       <c r="I5" s="3" t="s">
-        <v>197</v>
+        <v>208</v>
       </c>
       <c r="J5" s="3" t="s">
-        <v>198</v>
+        <v>209</v>
       </c>
       <c r="K5" s="3" t="s">
-        <v>197</v>
+        <v>208</v>
       </c>
       <c r="L5" s="3" t="s">
-        <v>198</v>
+        <v>209</v>
       </c>
       <c r="M5" s="3" t="s">
-        <v>197</v>
+        <v>208</v>
       </c>
       <c r="N5" s="3" t="s">
-        <v>199</v>
+        <v>210</v>
       </c>
       <c r="O5" s="3" t="s">
-        <v>197</v>
+        <v>208</v>
       </c>
       <c r="P5" s="3" t="s">
-        <v>200</v>
+        <v>211</v>
       </c>
       <c r="Q5" s="3" t="s">
-        <v>90</v>
+        <v>85</v>
       </c>
       <c r="R5" s="3" t="s">
-        <v>201</v>
+        <v>212</v>
       </c>
       <c r="S5" s="3" t="s">
-        <v>202</v>
+        <v>213</v>
       </c>
       <c r="T5" s="3" t="s">
-        <v>203</v>
+        <v>214</v>
       </c>
     </row>
     <row r="6" spans="1:20" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="3" t="s">
-        <v>116</v>
+        <v>109</v>
       </c>
       <c r="B6" s="3" t="s">
+        <v>216</v>
+      </c>
+      <c r="C6" s="3" t="s">
+        <v>203</v>
+      </c>
+      <c r="D6" s="3" t="s">
+        <v>204</v>
+      </c>
+      <c r="E6" s="3" t="s">
         <v>205</v>
       </c>
-      <c r="C6" s="3" t="s">
-        <v>192</v>
-      </c>
-      <c r="D6" s="3" t="s">
-        <v>193</v>
-      </c>
-      <c r="E6" s="3" t="s">
-        <v>194</v>
-      </c>
       <c r="F6" s="3" t="s">
-        <v>195</v>
+        <v>206</v>
       </c>
       <c r="G6" s="3" t="s">
-        <v>90</v>
+        <v>85</v>
       </c>
       <c r="H6" s="3" t="s">
-        <v>196</v>
+        <v>207</v>
       </c>
       <c r="I6" s="3" t="s">
-        <v>197</v>
+        <v>208</v>
       </c>
       <c r="J6" s="3" t="s">
-        <v>198</v>
+        <v>209</v>
       </c>
       <c r="K6" s="3" t="s">
-        <v>197</v>
+        <v>208</v>
       </c>
       <c r="L6" s="3" t="s">
-        <v>198</v>
+        <v>209</v>
       </c>
       <c r="M6" s="3" t="s">
-        <v>197</v>
+        <v>208</v>
       </c>
       <c r="N6" s="3" t="s">
-        <v>199</v>
+        <v>210</v>
       </c>
       <c r="O6" s="3" t="s">
-        <v>197</v>
+        <v>208</v>
       </c>
       <c r="P6" s="3" t="s">
-        <v>200</v>
+        <v>211</v>
       </c>
       <c r="Q6" s="3" t="s">
-        <v>90</v>
+        <v>85</v>
       </c>
       <c r="R6" s="3" t="s">
-        <v>201</v>
+        <v>212</v>
       </c>
       <c r="S6" s="3" t="s">
-        <v>202</v>
+        <v>213</v>
       </c>
       <c r="T6" s="3" t="s">
-        <v>203</v>
+        <v>214</v>
       </c>
     </row>
     <row r="7" spans="1:20" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="3" t="s">
-        <v>121</v>
+        <v>117</v>
       </c>
       <c r="B7" s="3" t="s">
+        <v>217</v>
+      </c>
+      <c r="C7" s="3" t="s">
+        <v>203</v>
+      </c>
+      <c r="D7" s="3" t="s">
+        <v>204</v>
+      </c>
+      <c r="E7" s="3" t="s">
+        <v>205</v>
+      </c>
+      <c r="F7" s="3" t="s">
         <v>206</v>
       </c>
-      <c r="C7" s="3" t="s">
-        <v>192</v>
-      </c>
-      <c r="D7" s="3" t="s">
-        <v>193</v>
-      </c>
-      <c r="E7" s="3" t="s">
-        <v>194</v>
-      </c>
-      <c r="F7" s="3" t="s">
-        <v>195</v>
-      </c>
       <c r="G7" s="3" t="s">
-        <v>90</v>
+        <v>85</v>
       </c>
       <c r="H7" s="3" t="s">
-        <v>196</v>
+        <v>207</v>
       </c>
       <c r="I7" s="3" t="s">
-        <v>197</v>
+        <v>208</v>
       </c>
       <c r="J7" s="3" t="s">
-        <v>198</v>
+        <v>209</v>
       </c>
       <c r="K7" s="3" t="s">
-        <v>197</v>
+        <v>208</v>
       </c>
       <c r="L7" s="3" t="s">
-        <v>198</v>
+        <v>209</v>
       </c>
       <c r="M7" s="3" t="s">
-        <v>197</v>
+        <v>208</v>
       </c>
       <c r="N7" s="3" t="s">
-        <v>199</v>
+        <v>210</v>
       </c>
       <c r="O7" s="3" t="s">
-        <v>197</v>
+        <v>208</v>
       </c>
       <c r="P7" s="3" t="s">
-        <v>200</v>
+        <v>211</v>
       </c>
       <c r="Q7" s="3" t="s">
-        <v>90</v>
+        <v>85</v>
       </c>
       <c r="R7" s="3" t="s">
-        <v>201</v>
+        <v>212</v>
       </c>
       <c r="S7" s="3" t="s">
-        <v>202</v>
+        <v>213</v>
       </c>
       <c r="T7" s="3" t="s">
-        <v>203</v>
+        <v>214</v>
       </c>
     </row>
     <row r="8" spans="1:20" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="3" t="s">
-        <v>130</v>
+        <v>123</v>
       </c>
       <c r="B8" s="3" t="s">
+        <v>218</v>
+      </c>
+      <c r="C8" s="3" t="s">
+        <v>203</v>
+      </c>
+      <c r="D8" s="3" t="s">
+        <v>204</v>
+      </c>
+      <c r="E8" s="3" t="s">
+        <v>205</v>
+      </c>
+      <c r="F8" s="3" t="s">
+        <v>206</v>
+      </c>
+      <c r="G8" s="3" t="s">
+        <v>85</v>
+      </c>
+      <c r="H8" s="3" t="s">
         <v>207</v>
       </c>
-      <c r="C8" s="3" t="s">
-        <v>192</v>
-      </c>
-      <c r="D8" s="3" t="s">
-        <v>193</v>
-      </c>
-      <c r="E8" s="3" t="s">
-        <v>194</v>
-      </c>
-      <c r="F8" s="3" t="s">
-        <v>195</v>
-      </c>
-      <c r="G8" s="3" t="s">
-        <v>90</v>
-      </c>
-      <c r="H8" s="3" t="s">
-        <v>196</v>
-      </c>
       <c r="I8" s="3" t="s">
-        <v>197</v>
+        <v>208</v>
       </c>
       <c r="J8" s="3" t="s">
-        <v>198</v>
+        <v>209</v>
       </c>
       <c r="K8" s="3" t="s">
-        <v>197</v>
+        <v>208</v>
       </c>
       <c r="L8" s="3" t="s">
-        <v>198</v>
+        <v>209</v>
       </c>
       <c r="M8" s="3" t="s">
-        <v>197</v>
+        <v>208</v>
       </c>
       <c r="N8" s="3" t="s">
-        <v>199</v>
+        <v>210</v>
       </c>
       <c r="O8" s="3" t="s">
-        <v>197</v>
+        <v>208</v>
       </c>
       <c r="P8" s="3" t="s">
-        <v>200</v>
+        <v>211</v>
       </c>
       <c r="Q8" s="3" t="s">
-        <v>90</v>
+        <v>85</v>
       </c>
       <c r="R8" s="3" t="s">
-        <v>201</v>
+        <v>212</v>
       </c>
       <c r="S8" s="3" t="s">
-        <v>202</v>
+        <v>213</v>
       </c>
       <c r="T8" s="3" t="s">
-        <v>203</v>
+        <v>214</v>
       </c>
     </row>
     <row r="9" spans="1:20" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="3" t="s">
-        <v>135</v>
+        <v>129</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>208</v>
+        <v>219</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>192</v>
+        <v>203</v>
       </c>
       <c r="D9" s="3" t="s">
-        <v>193</v>
+        <v>204</v>
       </c>
       <c r="E9" s="3" t="s">
-        <v>194</v>
+        <v>205</v>
       </c>
       <c r="F9" s="3" t="s">
-        <v>195</v>
+        <v>206</v>
       </c>
       <c r="G9" s="3" t="s">
-        <v>90</v>
+        <v>85</v>
       </c>
       <c r="H9" s="3" t="s">
-        <v>196</v>
+        <v>207</v>
       </c>
       <c r="I9" s="3" t="s">
-        <v>197</v>
+        <v>208</v>
       </c>
       <c r="J9" s="3" t="s">
-        <v>198</v>
+        <v>209</v>
       </c>
       <c r="K9" s="3" t="s">
-        <v>197</v>
+        <v>208</v>
       </c>
       <c r="L9" s="3" t="s">
-        <v>198</v>
+        <v>209</v>
       </c>
       <c r="M9" s="3" t="s">
-        <v>197</v>
+        <v>208</v>
       </c>
       <c r="N9" s="3" t="s">
-        <v>199</v>
+        <v>210</v>
       </c>
       <c r="O9" s="3" t="s">
-        <v>197</v>
+        <v>208</v>
       </c>
       <c r="P9" s="3" t="s">
-        <v>200</v>
+        <v>211</v>
       </c>
       <c r="Q9" s="3" t="s">
-        <v>90</v>
+        <v>85</v>
       </c>
       <c r="R9" s="3" t="s">
-        <v>201</v>
+        <v>212</v>
       </c>
       <c r="S9" s="3" t="s">
-        <v>202</v>
+        <v>213</v>
       </c>
       <c r="T9" s="3" t="s">
-        <v>203</v>
+        <v>214</v>
       </c>
     </row>
     <row r="10" spans="1:20" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="3" t="s">
-        <v>140</v>
+        <v>130</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>209</v>
+        <v>220</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>192</v>
+        <v>203</v>
       </c>
       <c r="D10" s="3" t="s">
-        <v>193</v>
+        <v>204</v>
       </c>
       <c r="E10" s="3" t="s">
-        <v>194</v>
+        <v>205</v>
       </c>
       <c r="F10" s="3" t="s">
-        <v>195</v>
+        <v>206</v>
       </c>
       <c r="G10" s="3" t="s">
-        <v>90</v>
+        <v>85</v>
       </c>
       <c r="H10" s="3" t="s">
-        <v>196</v>
+        <v>207</v>
       </c>
       <c r="I10" s="3" t="s">
-        <v>197</v>
+        <v>208</v>
       </c>
       <c r="J10" s="3" t="s">
-        <v>198</v>
+        <v>209</v>
       </c>
       <c r="K10" s="3" t="s">
-        <v>197</v>
+        <v>208</v>
       </c>
       <c r="L10" s="3" t="s">
-        <v>198</v>
+        <v>209</v>
       </c>
       <c r="M10" s="3" t="s">
-        <v>197</v>
+        <v>208</v>
       </c>
       <c r="N10" s="3" t="s">
-        <v>199</v>
+        <v>210</v>
       </c>
       <c r="O10" s="3" t="s">
-        <v>197</v>
+        <v>208</v>
       </c>
       <c r="P10" s="3" t="s">
-        <v>200</v>
+        <v>211</v>
       </c>
       <c r="Q10" s="3" t="s">
-        <v>90</v>
+        <v>85</v>
       </c>
       <c r="R10" s="3" t="s">
-        <v>201</v>
+        <v>212</v>
       </c>
       <c r="S10" s="3" t="s">
-        <v>202</v>
+        <v>213</v>
       </c>
       <c r="T10" s="3" t="s">
-        <v>203</v>
+        <v>214</v>
       </c>
     </row>
     <row r="11" spans="1:20" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="3" t="s">
-        <v>144</v>
+        <v>131</v>
       </c>
       <c r="B11" s="3" t="s">
+        <v>221</v>
+      </c>
+      <c r="C11" s="3" t="s">
+        <v>203</v>
+      </c>
+      <c r="D11" s="3" t="s">
+        <v>204</v>
+      </c>
+      <c r="E11" s="3" t="s">
+        <v>205</v>
+      </c>
+      <c r="F11" s="3" t="s">
+        <v>206</v>
+      </c>
+      <c r="G11" s="3" t="s">
+        <v>85</v>
+      </c>
+      <c r="H11" s="3" t="s">
+        <v>207</v>
+      </c>
+      <c r="I11" s="3" t="s">
+        <v>208</v>
+      </c>
+      <c r="J11" s="3" t="s">
+        <v>209</v>
+      </c>
+      <c r="K11" s="3" t="s">
+        <v>208</v>
+      </c>
+      <c r="L11" s="3" t="s">
+        <v>209</v>
+      </c>
+      <c r="M11" s="3" t="s">
+        <v>208</v>
+      </c>
+      <c r="N11" s="3" t="s">
         <v>210</v>
       </c>
-      <c r="C11" s="3" t="s">
-        <v>192</v>
-      </c>
-      <c r="D11" s="3" t="s">
-        <v>193</v>
-      </c>
-      <c r="E11" s="3" t="s">
-        <v>194</v>
-      </c>
-      <c r="F11" s="3" t="s">
-        <v>195</v>
-      </c>
-      <c r="G11" s="3" t="s">
-        <v>90</v>
-      </c>
-      <c r="H11" s="3" t="s">
-        <v>196</v>
-      </c>
-      <c r="I11" s="3" t="s">
-        <v>197</v>
-      </c>
-      <c r="J11" s="3" t="s">
-        <v>198</v>
-      </c>
-      <c r="K11" s="3" t="s">
-        <v>197</v>
-      </c>
-      <c r="L11" s="3" t="s">
-        <v>198</v>
-      </c>
-      <c r="M11" s="3" t="s">
-        <v>197</v>
-      </c>
-      <c r="N11" s="3" t="s">
-        <v>199</v>
-      </c>
       <c r="O11" s="3" t="s">
-        <v>197</v>
+        <v>208</v>
       </c>
       <c r="P11" s="3" t="s">
-        <v>200</v>
+        <v>211</v>
       </c>
       <c r="Q11" s="3" t="s">
-        <v>90</v>
+        <v>85</v>
       </c>
       <c r="R11" s="3" t="s">
-        <v>201</v>
+        <v>212</v>
       </c>
       <c r="S11" s="3" t="s">
-        <v>202</v>
+        <v>213</v>
       </c>
       <c r="T11" s="3" t="s">
-        <v>203</v>
+        <v>214</v>
       </c>
     </row>
     <row r="12" spans="1:20" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="3" t="s">
-        <v>146</v>
+        <v>132</v>
       </c>
       <c r="B12" s="3" t="s">
+        <v>222</v>
+      </c>
+      <c r="C12" s="3" t="s">
+        <v>203</v>
+      </c>
+      <c r="D12" s="3" t="s">
+        <v>204</v>
+      </c>
+      <c r="E12" s="3" t="s">
+        <v>205</v>
+      </c>
+      <c r="F12" s="3" t="s">
+        <v>206</v>
+      </c>
+      <c r="G12" s="3" t="s">
+        <v>85</v>
+      </c>
+      <c r="H12" s="3" t="s">
+        <v>207</v>
+      </c>
+      <c r="I12" s="3" t="s">
+        <v>208</v>
+      </c>
+      <c r="J12" s="3" t="s">
+        <v>209</v>
+      </c>
+      <c r="K12" s="3" t="s">
+        <v>208</v>
+      </c>
+      <c r="L12" s="3" t="s">
+        <v>209</v>
+      </c>
+      <c r="M12" s="3" t="s">
+        <v>208</v>
+      </c>
+      <c r="N12" s="3" t="s">
+        <v>210</v>
+      </c>
+      <c r="O12" s="3" t="s">
+        <v>208</v>
+      </c>
+      <c r="P12" s="3" t="s">
         <v>211</v>
       </c>
-      <c r="C12" s="3" t="s">
-        <v>192</v>
-      </c>
-      <c r="D12" s="3" t="s">
-        <v>193</v>
-      </c>
-      <c r="E12" s="3" t="s">
-        <v>194</v>
-      </c>
-      <c r="F12" s="3" t="s">
-        <v>195</v>
-      </c>
-      <c r="G12" s="3" t="s">
-        <v>90</v>
-      </c>
-      <c r="H12" s="3" t="s">
-        <v>196</v>
-      </c>
-      <c r="I12" s="3" t="s">
-        <v>197</v>
-      </c>
-      <c r="J12" s="3" t="s">
-        <v>198</v>
-      </c>
-      <c r="K12" s="3" t="s">
-        <v>197</v>
-      </c>
-      <c r="L12" s="3" t="s">
-        <v>198</v>
-      </c>
-      <c r="M12" s="3" t="s">
-        <v>197</v>
-      </c>
-      <c r="N12" s="3" t="s">
-        <v>199</v>
-      </c>
-      <c r="O12" s="3" t="s">
-        <v>197</v>
-      </c>
-      <c r="P12" s="3" t="s">
-        <v>200</v>
-      </c>
       <c r="Q12" s="3" t="s">
-        <v>90</v>
+        <v>85</v>
       </c>
       <c r="R12" s="3" t="s">
-        <v>201</v>
+        <v>212</v>
       </c>
       <c r="S12" s="3" t="s">
-        <v>202</v>
+        <v>213</v>
       </c>
       <c r="T12" s="3" t="s">
-        <v>203</v>
+        <v>214</v>
       </c>
     </row>
     <row r="13" spans="1:20" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="3" t="s">
-        <v>148</v>
+        <v>133</v>
       </c>
       <c r="B13" s="3" t="s">
+        <v>223</v>
+      </c>
+      <c r="C13" s="3" t="s">
+        <v>203</v>
+      </c>
+      <c r="D13" s="3" t="s">
+        <v>204</v>
+      </c>
+      <c r="E13" s="3" t="s">
+        <v>205</v>
+      </c>
+      <c r="F13" s="3" t="s">
+        <v>206</v>
+      </c>
+      <c r="G13" s="3" t="s">
+        <v>85</v>
+      </c>
+      <c r="H13" s="3" t="s">
+        <v>207</v>
+      </c>
+      <c r="I13" s="3" t="s">
+        <v>208</v>
+      </c>
+      <c r="J13" s="3" t="s">
+        <v>209</v>
+      </c>
+      <c r="K13" s="3" t="s">
+        <v>208</v>
+      </c>
+      <c r="L13" s="3" t="s">
+        <v>209</v>
+      </c>
+      <c r="M13" s="3" t="s">
+        <v>208</v>
+      </c>
+      <c r="N13" s="3" t="s">
+        <v>210</v>
+      </c>
+      <c r="O13" s="3" t="s">
+        <v>208</v>
+      </c>
+      <c r="P13" s="3" t="s">
+        <v>211</v>
+      </c>
+      <c r="Q13" s="3" t="s">
+        <v>85</v>
+      </c>
+      <c r="R13" s="3" t="s">
         <v>212</v>
       </c>
-      <c r="C13" s="3" t="s">
-        <v>192</v>
-      </c>
-      <c r="D13" s="3" t="s">
-        <v>193</v>
-      </c>
-      <c r="E13" s="3" t="s">
-        <v>194</v>
-      </c>
-      <c r="F13" s="3" t="s">
-        <v>195</v>
-      </c>
-      <c r="G13" s="3" t="s">
-        <v>90</v>
-      </c>
-      <c r="H13" s="3" t="s">
-        <v>196</v>
-      </c>
-      <c r="I13" s="3" t="s">
-        <v>197</v>
-      </c>
-      <c r="J13" s="3" t="s">
-        <v>198</v>
-      </c>
-      <c r="K13" s="3" t="s">
-        <v>197</v>
-      </c>
-      <c r="L13" s="3" t="s">
-        <v>198</v>
-      </c>
-      <c r="M13" s="3" t="s">
-        <v>197</v>
-      </c>
-      <c r="N13" s="3" t="s">
-        <v>199</v>
-      </c>
-      <c r="O13" s="3" t="s">
-        <v>197</v>
-      </c>
-      <c r="P13" s="3" t="s">
-        <v>200</v>
-      </c>
-      <c r="Q13" s="3" t="s">
-        <v>90</v>
-      </c>
-      <c r="R13" s="3" t="s">
-        <v>201</v>
-      </c>
       <c r="S13" s="3" t="s">
-        <v>202</v>
+        <v>213</v>
       </c>
       <c r="T13" s="3" t="s">
-        <v>203</v>
+        <v>214</v>
       </c>
     </row>
     <row r="14" spans="1:20" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="3" t="s">
-        <v>150</v>
+        <v>134</v>
       </c>
       <c r="B14" s="3" t="s">
+        <v>224</v>
+      </c>
+      <c r="C14" s="3" t="s">
+        <v>203</v>
+      </c>
+      <c r="D14" s="3" t="s">
+        <v>204</v>
+      </c>
+      <c r="E14" s="3" t="s">
+        <v>205</v>
+      </c>
+      <c r="F14" s="3" t="s">
+        <v>206</v>
+      </c>
+      <c r="G14" s="3" t="s">
+        <v>85</v>
+      </c>
+      <c r="H14" s="3" t="s">
+        <v>207</v>
+      </c>
+      <c r="I14" s="3" t="s">
+        <v>208</v>
+      </c>
+      <c r="J14" s="3" t="s">
+        <v>209</v>
+      </c>
+      <c r="K14" s="3" t="s">
+        <v>208</v>
+      </c>
+      <c r="L14" s="3" t="s">
+        <v>209</v>
+      </c>
+      <c r="M14" s="3" t="s">
+        <v>208</v>
+      </c>
+      <c r="N14" s="3" t="s">
+        <v>210</v>
+      </c>
+      <c r="O14" s="3" t="s">
+        <v>208</v>
+      </c>
+      <c r="P14" s="3" t="s">
+        <v>211</v>
+      </c>
+      <c r="Q14" s="3" t="s">
+        <v>85</v>
+      </c>
+      <c r="R14" s="3" t="s">
+        <v>212</v>
+      </c>
+      <c r="S14" s="3" t="s">
         <v>213</v>
       </c>
-      <c r="C14" s="3" t="s">
-        <v>192</v>
-      </c>
-      <c r="D14" s="3" t="s">
-        <v>193</v>
-      </c>
-      <c r="E14" s="3" t="s">
-        <v>194</v>
-      </c>
-      <c r="F14" s="3" t="s">
-        <v>195</v>
-      </c>
-      <c r="G14" s="3" t="s">
-        <v>90</v>
-      </c>
-      <c r="H14" s="3" t="s">
-        <v>196</v>
-      </c>
-      <c r="I14" s="3" t="s">
-        <v>197</v>
-      </c>
-      <c r="J14" s="3" t="s">
-        <v>198</v>
-      </c>
-      <c r="K14" s="3" t="s">
-        <v>197</v>
-      </c>
-      <c r="L14" s="3" t="s">
-        <v>198</v>
-      </c>
-      <c r="M14" s="3" t="s">
-        <v>197</v>
-      </c>
-      <c r="N14" s="3" t="s">
-        <v>199</v>
-      </c>
-      <c r="O14" s="3" t="s">
-        <v>197</v>
-      </c>
-      <c r="P14" s="3" t="s">
-        <v>200</v>
-      </c>
-      <c r="Q14" s="3" t="s">
-        <v>90</v>
-      </c>
-      <c r="R14" s="3" t="s">
-        <v>201</v>
-      </c>
-      <c r="S14" s="3" t="s">
-        <v>202</v>
-      </c>
       <c r="T14" s="3" t="s">
-        <v>203</v>
+        <v>214</v>
       </c>
     </row>
     <row r="15" spans="1:20" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" s="3" t="s">
-        <v>152</v>
+        <v>135</v>
       </c>
       <c r="B15" s="3" t="s">
+        <v>225</v>
+      </c>
+      <c r="C15" s="3" t="s">
+        <v>203</v>
+      </c>
+      <c r="D15" s="3" t="s">
+        <v>204</v>
+      </c>
+      <c r="E15" s="3" t="s">
+        <v>205</v>
+      </c>
+      <c r="F15" s="3" t="s">
+        <v>206</v>
+      </c>
+      <c r="G15" s="3" t="s">
+        <v>85</v>
+      </c>
+      <c r="H15" s="3" t="s">
+        <v>207</v>
+      </c>
+      <c r="I15" s="3" t="s">
+        <v>208</v>
+      </c>
+      <c r="J15" s="3" t="s">
+        <v>209</v>
+      </c>
+      <c r="K15" s="3" t="s">
+        <v>208</v>
+      </c>
+      <c r="L15" s="3" t="s">
+        <v>209</v>
+      </c>
+      <c r="M15" s="3" t="s">
+        <v>208</v>
+      </c>
+      <c r="N15" s="3" t="s">
+        <v>210</v>
+      </c>
+      <c r="O15" s="3" t="s">
+        <v>208</v>
+      </c>
+      <c r="P15" s="3" t="s">
+        <v>211</v>
+      </c>
+      <c r="Q15" s="3" t="s">
+        <v>85</v>
+      </c>
+      <c r="R15" s="3" t="s">
+        <v>212</v>
+      </c>
+      <c r="S15" s="3" t="s">
+        <v>213</v>
+      </c>
+      <c r="T15" s="3" t="s">
         <v>214</v>
       </c>
-      <c r="C15" s="3" t="s">
-        <v>192</v>
-      </c>
-      <c r="D15" s="3" t="s">
-        <v>193</v>
-      </c>
-      <c r="E15" s="3" t="s">
-        <v>194</v>
-      </c>
-      <c r="F15" s="3" t="s">
-        <v>195</v>
-      </c>
-      <c r="G15" s="3" t="s">
-        <v>90</v>
-      </c>
-      <c r="H15" s="3" t="s">
-        <v>196</v>
-      </c>
-      <c r="I15" s="3" t="s">
-        <v>197</v>
-      </c>
-      <c r="J15" s="3" t="s">
-        <v>198</v>
-      </c>
-      <c r="K15" s="3" t="s">
-        <v>197</v>
-      </c>
-      <c r="L15" s="3" t="s">
-        <v>198</v>
-      </c>
-      <c r="M15" s="3" t="s">
-        <v>197</v>
-      </c>
-      <c r="N15" s="3" t="s">
-        <v>199</v>
-      </c>
-      <c r="O15" s="3" t="s">
-        <v>197</v>
-      </c>
-      <c r="P15" s="3" t="s">
-        <v>200</v>
-      </c>
-      <c r="Q15" s="3" t="s">
-        <v>90</v>
-      </c>
-      <c r="R15" s="3" t="s">
-        <v>201</v>
-      </c>
-      <c r="S15" s="3" t="s">
-        <v>202</v>
-      </c>
-      <c r="T15" s="3" t="s">
+    </row>
+    <row r="16" spans="1:20" ht="45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A16" s="3" t="s">
+        <v>136</v>
+      </c>
+      <c r="B16" s="3" t="s">
+        <v>226</v>
+      </c>
+      <c r="C16" s="3" t="s">
         <v>203</v>
+      </c>
+      <c r="D16" s="3" t="s">
+        <v>204</v>
+      </c>
+      <c r="E16" s="3" t="s">
+        <v>205</v>
+      </c>
+      <c r="F16" s="3" t="s">
+        <v>206</v>
+      </c>
+      <c r="G16" s="3" t="s">
+        <v>85</v>
+      </c>
+      <c r="H16" s="3" t="s">
+        <v>207</v>
+      </c>
+      <c r="I16" s="3" t="s">
+        <v>208</v>
+      </c>
+      <c r="J16" s="3" t="s">
+        <v>209</v>
+      </c>
+      <c r="K16" s="3" t="s">
+        <v>208</v>
+      </c>
+      <c r="L16" s="3" t="s">
+        <v>209</v>
+      </c>
+      <c r="M16" s="3" t="s">
+        <v>208</v>
+      </c>
+      <c r="N16" s="3" t="s">
+        <v>210</v>
+      </c>
+      <c r="O16" s="3" t="s">
+        <v>208</v>
+      </c>
+      <c r="P16" s="3" t="s">
+        <v>211</v>
+      </c>
+      <c r="Q16" s="3" t="s">
+        <v>85</v>
+      </c>
+      <c r="R16" s="3" t="s">
+        <v>212</v>
+      </c>
+      <c r="S16" s="3" t="s">
+        <v>213</v>
+      </c>
+      <c r="T16" s="3" t="s">
+        <v>214</v>
+      </c>
+    </row>
+    <row r="17" spans="1:20" ht="45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A17" s="3" t="s">
+        <v>138</v>
+      </c>
+      <c r="B17" s="3" t="s">
+        <v>227</v>
+      </c>
+      <c r="C17" s="3" t="s">
+        <v>203</v>
+      </c>
+      <c r="D17" s="3" t="s">
+        <v>204</v>
+      </c>
+      <c r="E17" s="3" t="s">
+        <v>205</v>
+      </c>
+      <c r="F17" s="3" t="s">
+        <v>206</v>
+      </c>
+      <c r="G17" s="3" t="s">
+        <v>85</v>
+      </c>
+      <c r="H17" s="3" t="s">
+        <v>207</v>
+      </c>
+      <c r="I17" s="3" t="s">
+        <v>208</v>
+      </c>
+      <c r="J17" s="3" t="s">
+        <v>209</v>
+      </c>
+      <c r="K17" s="3" t="s">
+        <v>208</v>
+      </c>
+      <c r="L17" s="3" t="s">
+        <v>209</v>
+      </c>
+      <c r="M17" s="3" t="s">
+        <v>208</v>
+      </c>
+      <c r="N17" s="3" t="s">
+        <v>210</v>
+      </c>
+      <c r="O17" s="3" t="s">
+        <v>208</v>
+      </c>
+      <c r="P17" s="3" t="s">
+        <v>211</v>
+      </c>
+      <c r="Q17" s="3" t="s">
+        <v>85</v>
+      </c>
+      <c r="R17" s="3" t="s">
+        <v>212</v>
+      </c>
+      <c r="S17" s="3" t="s">
+        <v>213</v>
+      </c>
+      <c r="T17" s="3" t="s">
+        <v>214</v>
+      </c>
+    </row>
+    <row r="18" spans="1:20" ht="45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A18" s="3" t="s">
+        <v>139</v>
+      </c>
+      <c r="B18" s="3" t="s">
+        <v>228</v>
+      </c>
+      <c r="C18" s="3" t="s">
+        <v>203</v>
+      </c>
+      <c r="D18" s="3" t="s">
+        <v>204</v>
+      </c>
+      <c r="E18" s="3" t="s">
+        <v>205</v>
+      </c>
+      <c r="F18" s="3" t="s">
+        <v>206</v>
+      </c>
+      <c r="G18" s="3" t="s">
+        <v>85</v>
+      </c>
+      <c r="H18" s="3" t="s">
+        <v>207</v>
+      </c>
+      <c r="I18" s="3" t="s">
+        <v>208</v>
+      </c>
+      <c r="J18" s="3" t="s">
+        <v>209</v>
+      </c>
+      <c r="K18" s="3" t="s">
+        <v>208</v>
+      </c>
+      <c r="L18" s="3" t="s">
+        <v>209</v>
+      </c>
+      <c r="M18" s="3" t="s">
+        <v>208</v>
+      </c>
+      <c r="N18" s="3" t="s">
+        <v>210</v>
+      </c>
+      <c r="O18" s="3" t="s">
+        <v>208</v>
+      </c>
+      <c r="P18" s="3" t="s">
+        <v>211</v>
+      </c>
+      <c r="Q18" s="3" t="s">
+        <v>85</v>
+      </c>
+      <c r="R18" s="3" t="s">
+        <v>212</v>
+      </c>
+      <c r="S18" s="3" t="s">
+        <v>213</v>
+      </c>
+      <c r="T18" s="3" t="s">
+        <v>214</v>
+      </c>
+    </row>
+    <row r="19" spans="1:20" ht="45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A19" s="3" t="s">
+        <v>141</v>
+      </c>
+      <c r="B19" s="3" t="s">
+        <v>229</v>
+      </c>
+      <c r="C19" s="3" t="s">
+        <v>203</v>
+      </c>
+      <c r="D19" s="3" t="s">
+        <v>204</v>
+      </c>
+      <c r="E19" s="3" t="s">
+        <v>205</v>
+      </c>
+      <c r="F19" s="3" t="s">
+        <v>206</v>
+      </c>
+      <c r="G19" s="3" t="s">
+        <v>85</v>
+      </c>
+      <c r="H19" s="3" t="s">
+        <v>207</v>
+      </c>
+      <c r="I19" s="3" t="s">
+        <v>208</v>
+      </c>
+      <c r="J19" s="3" t="s">
+        <v>209</v>
+      </c>
+      <c r="K19" s="3" t="s">
+        <v>208</v>
+      </c>
+      <c r="L19" s="3" t="s">
+        <v>209</v>
+      </c>
+      <c r="M19" s="3" t="s">
+        <v>208</v>
+      </c>
+      <c r="N19" s="3" t="s">
+        <v>210</v>
+      </c>
+      <c r="O19" s="3" t="s">
+        <v>208</v>
+      </c>
+      <c r="P19" s="3" t="s">
+        <v>211</v>
+      </c>
+      <c r="Q19" s="3" t="s">
+        <v>85</v>
+      </c>
+      <c r="R19" s="3" t="s">
+        <v>212</v>
+      </c>
+      <c r="S19" s="3" t="s">
+        <v>213</v>
+      </c>
+      <c r="T19" s="3" t="s">
+        <v>214</v>
+      </c>
+    </row>
+    <row r="20" spans="1:20" ht="45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A20" s="3" t="s">
+        <v>142</v>
+      </c>
+      <c r="B20" s="3" t="s">
+        <v>230</v>
+      </c>
+      <c r="C20" s="3" t="s">
+        <v>203</v>
+      </c>
+      <c r="D20" s="3" t="s">
+        <v>204</v>
+      </c>
+      <c r="E20" s="3" t="s">
+        <v>205</v>
+      </c>
+      <c r="F20" s="3" t="s">
+        <v>206</v>
+      </c>
+      <c r="G20" s="3" t="s">
+        <v>85</v>
+      </c>
+      <c r="H20" s="3" t="s">
+        <v>207</v>
+      </c>
+      <c r="I20" s="3" t="s">
+        <v>208</v>
+      </c>
+      <c r="J20" s="3" t="s">
+        <v>209</v>
+      </c>
+      <c r="K20" s="3" t="s">
+        <v>208</v>
+      </c>
+      <c r="L20" s="3" t="s">
+        <v>209</v>
+      </c>
+      <c r="M20" s="3" t="s">
+        <v>208</v>
+      </c>
+      <c r="N20" s="3" t="s">
+        <v>210</v>
+      </c>
+      <c r="O20" s="3" t="s">
+        <v>208</v>
+      </c>
+      <c r="P20" s="3" t="s">
+        <v>211</v>
+      </c>
+      <c r="Q20" s="3" t="s">
+        <v>85</v>
+      </c>
+      <c r="R20" s="3" t="s">
+        <v>212</v>
+      </c>
+      <c r="S20" s="3" t="s">
+        <v>213</v>
+      </c>
+      <c r="T20" s="3" t="s">
+        <v>214</v>
+      </c>
+    </row>
+    <row r="21" spans="1:20" ht="45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A21" s="3" t="s">
+        <v>144</v>
+      </c>
+      <c r="B21" s="3" t="s">
+        <v>231</v>
+      </c>
+      <c r="C21" s="3" t="s">
+        <v>203</v>
+      </c>
+      <c r="D21" s="3" t="s">
+        <v>204</v>
+      </c>
+      <c r="E21" s="3" t="s">
+        <v>205</v>
+      </c>
+      <c r="F21" s="3" t="s">
+        <v>206</v>
+      </c>
+      <c r="G21" s="3" t="s">
+        <v>85</v>
+      </c>
+      <c r="H21" s="3" t="s">
+        <v>207</v>
+      </c>
+      <c r="I21" s="3" t="s">
+        <v>208</v>
+      </c>
+      <c r="J21" s="3" t="s">
+        <v>209</v>
+      </c>
+      <c r="K21" s="3" t="s">
+        <v>208</v>
+      </c>
+      <c r="L21" s="3" t="s">
+        <v>209</v>
+      </c>
+      <c r="M21" s="3" t="s">
+        <v>208</v>
+      </c>
+      <c r="N21" s="3" t="s">
+        <v>210</v>
+      </c>
+      <c r="O21" s="3" t="s">
+        <v>208</v>
+      </c>
+      <c r="P21" s="3" t="s">
+        <v>211</v>
+      </c>
+      <c r="Q21" s="3" t="s">
+        <v>85</v>
+      </c>
+      <c r="R21" s="3" t="s">
+        <v>212</v>
+      </c>
+      <c r="S21" s="3" t="s">
+        <v>213</v>
+      </c>
+      <c r="T21" s="3" t="s">
+        <v>214</v>
+      </c>
+    </row>
+    <row r="22" spans="1:20" ht="45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A22" s="3" t="s">
+        <v>150</v>
+      </c>
+      <c r="B22" s="3" t="s">
+        <v>232</v>
+      </c>
+      <c r="C22" s="3" t="s">
+        <v>203</v>
+      </c>
+      <c r="D22" s="3" t="s">
+        <v>204</v>
+      </c>
+      <c r="E22" s="3" t="s">
+        <v>205</v>
+      </c>
+      <c r="F22" s="3" t="s">
+        <v>206</v>
+      </c>
+      <c r="G22" s="3" t="s">
+        <v>85</v>
+      </c>
+      <c r="H22" s="3" t="s">
+        <v>207</v>
+      </c>
+      <c r="I22" s="3" t="s">
+        <v>208</v>
+      </c>
+      <c r="J22" s="3" t="s">
+        <v>209</v>
+      </c>
+      <c r="K22" s="3" t="s">
+        <v>208</v>
+      </c>
+      <c r="L22" s="3" t="s">
+        <v>209</v>
+      </c>
+      <c r="M22" s="3" t="s">
+        <v>208</v>
+      </c>
+      <c r="N22" s="3" t="s">
+        <v>210</v>
+      </c>
+      <c r="O22" s="3" t="s">
+        <v>208</v>
+      </c>
+      <c r="P22" s="3" t="s">
+        <v>211</v>
+      </c>
+      <c r="Q22" s="3" t="s">
+        <v>85</v>
+      </c>
+      <c r="R22" s="3" t="s">
+        <v>212</v>
+      </c>
+      <c r="S22" s="3" t="s">
+        <v>213</v>
+      </c>
+      <c r="T22" s="3" t="s">
+        <v>214</v>
+      </c>
+    </row>
+    <row r="23" spans="1:20" ht="45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A23" s="3" t="s">
+        <v>154</v>
+      </c>
+      <c r="B23" s="3" t="s">
+        <v>233</v>
+      </c>
+      <c r="C23" s="3" t="s">
+        <v>203</v>
+      </c>
+      <c r="D23" s="3" t="s">
+        <v>204</v>
+      </c>
+      <c r="E23" s="3" t="s">
+        <v>205</v>
+      </c>
+      <c r="F23" s="3" t="s">
+        <v>206</v>
+      </c>
+      <c r="G23" s="3" t="s">
+        <v>85</v>
+      </c>
+      <c r="H23" s="3" t="s">
+        <v>207</v>
+      </c>
+      <c r="I23" s="3" t="s">
+        <v>208</v>
+      </c>
+      <c r="J23" s="3" t="s">
+        <v>209</v>
+      </c>
+      <c r="K23" s="3" t="s">
+        <v>208</v>
+      </c>
+      <c r="L23" s="3" t="s">
+        <v>209</v>
+      </c>
+      <c r="M23" s="3" t="s">
+        <v>208</v>
+      </c>
+      <c r="N23" s="3" t="s">
+        <v>210</v>
+      </c>
+      <c r="O23" s="3" t="s">
+        <v>208</v>
+      </c>
+      <c r="P23" s="3" t="s">
+        <v>211</v>
+      </c>
+      <c r="Q23" s="3" t="s">
+        <v>85</v>
+      </c>
+      <c r="R23" s="3" t="s">
+        <v>212</v>
+      </c>
+      <c r="S23" s="3" t="s">
+        <v>213</v>
+      </c>
+      <c r="T23" s="3" t="s">
+        <v>214</v>
+      </c>
+    </row>
+    <row r="24" spans="1:20" ht="45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A24" s="3" t="s">
+        <v>156</v>
+      </c>
+      <c r="B24" s="3" t="s">
+        <v>234</v>
+      </c>
+      <c r="C24" s="3" t="s">
+        <v>203</v>
+      </c>
+      <c r="D24" s="3" t="s">
+        <v>204</v>
+      </c>
+      <c r="E24" s="3" t="s">
+        <v>205</v>
+      </c>
+      <c r="F24" s="3" t="s">
+        <v>206</v>
+      </c>
+      <c r="G24" s="3" t="s">
+        <v>85</v>
+      </c>
+      <c r="H24" s="3" t="s">
+        <v>207</v>
+      </c>
+      <c r="I24" s="3" t="s">
+        <v>208</v>
+      </c>
+      <c r="J24" s="3" t="s">
+        <v>209</v>
+      </c>
+      <c r="K24" s="3" t="s">
+        <v>208</v>
+      </c>
+      <c r="L24" s="3" t="s">
+        <v>209</v>
+      </c>
+      <c r="M24" s="3" t="s">
+        <v>208</v>
+      </c>
+      <c r="N24" s="3" t="s">
+        <v>210</v>
+      </c>
+      <c r="O24" s="3" t="s">
+        <v>208</v>
+      </c>
+      <c r="P24" s="3" t="s">
+        <v>211</v>
+      </c>
+      <c r="Q24" s="3" t="s">
+        <v>85</v>
+      </c>
+      <c r="R24" s="3" t="s">
+        <v>212</v>
+      </c>
+      <c r="S24" s="3" t="s">
+        <v>213</v>
+      </c>
+      <c r="T24" s="3" t="s">
+        <v>214</v>
+      </c>
+    </row>
+    <row r="25" spans="1:20" ht="45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A25" s="3" t="s">
+        <v>158</v>
+      </c>
+      <c r="B25" s="3" t="s">
+        <v>235</v>
+      </c>
+      <c r="C25" s="3" t="s">
+        <v>203</v>
+      </c>
+      <c r="D25" s="3" t="s">
+        <v>204</v>
+      </c>
+      <c r="E25" s="3" t="s">
+        <v>205</v>
+      </c>
+      <c r="F25" s="3" t="s">
+        <v>206</v>
+      </c>
+      <c r="G25" s="3" t="s">
+        <v>85</v>
+      </c>
+      <c r="H25" s="3" t="s">
+        <v>207</v>
+      </c>
+      <c r="I25" s="3" t="s">
+        <v>208</v>
+      </c>
+      <c r="J25" s="3" t="s">
+        <v>209</v>
+      </c>
+      <c r="K25" s="3" t="s">
+        <v>208</v>
+      </c>
+      <c r="L25" s="3" t="s">
+        <v>209</v>
+      </c>
+      <c r="M25" s="3" t="s">
+        <v>208</v>
+      </c>
+      <c r="N25" s="3" t="s">
+        <v>210</v>
+      </c>
+      <c r="O25" s="3" t="s">
+        <v>208</v>
+      </c>
+      <c r="P25" s="3" t="s">
+        <v>211</v>
+      </c>
+      <c r="Q25" s="3" t="s">
+        <v>85</v>
+      </c>
+      <c r="R25" s="3" t="s">
+        <v>212</v>
+      </c>
+      <c r="S25" s="3" t="s">
+        <v>213</v>
+      </c>
+      <c r="T25" s="3" t="s">
+        <v>214</v>
+      </c>
+    </row>
+    <row r="26" spans="1:20" ht="45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A26" s="3" t="s">
+        <v>160</v>
+      </c>
+      <c r="B26" s="3" t="s">
+        <v>236</v>
+      </c>
+      <c r="C26" s="3" t="s">
+        <v>203</v>
+      </c>
+      <c r="D26" s="3" t="s">
+        <v>204</v>
+      </c>
+      <c r="E26" s="3" t="s">
+        <v>205</v>
+      </c>
+      <c r="F26" s="3" t="s">
+        <v>206</v>
+      </c>
+      <c r="G26" s="3" t="s">
+        <v>85</v>
+      </c>
+      <c r="H26" s="3" t="s">
+        <v>207</v>
+      </c>
+      <c r="I26" s="3" t="s">
+        <v>208</v>
+      </c>
+      <c r="J26" s="3" t="s">
+        <v>209</v>
+      </c>
+      <c r="K26" s="3" t="s">
+        <v>208</v>
+      </c>
+      <c r="L26" s="3" t="s">
+        <v>209</v>
+      </c>
+      <c r="M26" s="3" t="s">
+        <v>208</v>
+      </c>
+      <c r="N26" s="3" t="s">
+        <v>210</v>
+      </c>
+      <c r="O26" s="3" t="s">
+        <v>208</v>
+      </c>
+      <c r="P26" s="3" t="s">
+        <v>211</v>
+      </c>
+      <c r="Q26" s="3" t="s">
+        <v>85</v>
+      </c>
+      <c r="R26" s="3" t="s">
+        <v>212</v>
+      </c>
+      <c r="S26" s="3" t="s">
+        <v>213</v>
+      </c>
+      <c r="T26" s="3" t="s">
+        <v>214</v>
+      </c>
+    </row>
+    <row r="27" spans="1:20" ht="45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A27" s="3" t="s">
+        <v>163</v>
+      </c>
+      <c r="B27" s="3" t="s">
+        <v>237</v>
+      </c>
+      <c r="C27" s="3" t="s">
+        <v>203</v>
+      </c>
+      <c r="D27" s="3" t="s">
+        <v>204</v>
+      </c>
+      <c r="E27" s="3" t="s">
+        <v>205</v>
+      </c>
+      <c r="F27" s="3" t="s">
+        <v>206</v>
+      </c>
+      <c r="G27" s="3" t="s">
+        <v>85</v>
+      </c>
+      <c r="H27" s="3" t="s">
+        <v>207</v>
+      </c>
+      <c r="I27" s="3" t="s">
+        <v>208</v>
+      </c>
+      <c r="J27" s="3" t="s">
+        <v>209</v>
+      </c>
+      <c r="K27" s="3" t="s">
+        <v>208</v>
+      </c>
+      <c r="L27" s="3" t="s">
+        <v>209</v>
+      </c>
+      <c r="M27" s="3" t="s">
+        <v>208</v>
+      </c>
+      <c r="N27" s="3" t="s">
+        <v>210</v>
+      </c>
+      <c r="O27" s="3" t="s">
+        <v>208</v>
+      </c>
+      <c r="P27" s="3" t="s">
+        <v>211</v>
+      </c>
+      <c r="Q27" s="3" t="s">
+        <v>85</v>
+      </c>
+      <c r="R27" s="3" t="s">
+        <v>212</v>
+      </c>
+      <c r="S27" s="3" t="s">
+        <v>213</v>
+      </c>
+      <c r="T27" s="3" t="s">
+        <v>214</v>
       </c>
     </row>
   </sheetData>
   <dataValidations count="3">
-    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="D4:D201">
+    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="D4:D201" xr:uid="{00000000-0002-0000-0200-000000000000}">
       <formula1>Hidden_1_Tabla_4361123</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="H4:H201">
+    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="H4:H201" xr:uid="{00000000-0002-0000-0200-000001000000}">
       <formula1>Hidden_2_Tabla_4361127</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="O4:O201">
+    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="O4:O201" xr:uid="{00000000-0002-0000-0200-000002000000}">
       <formula1>Hidden_3_Tabla_43611214</formula1>
     </dataValidation>
   </dataValidations>
@@ -5176,128 +6720,128 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
   <dimension ref="A1:A24"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
     <row r="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
-        <v>215</v>
+        <v>238</v>
       </c>
     </row>
     <row r="2" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>216</v>
+        <v>239</v>
       </c>
     </row>
     <row r="3" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>217</v>
+        <v>240</v>
       </c>
     </row>
     <row r="4" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>218</v>
+        <v>241</v>
       </c>
     </row>
     <row r="5" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>219</v>
+        <v>242</v>
       </c>
     </row>
     <row r="6" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>220</v>
+        <v>243</v>
       </c>
     </row>
     <row r="7" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>193</v>
+        <v>204</v>
       </c>
     </row>
     <row r="8" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>221</v>
+        <v>244</v>
       </c>
     </row>
     <row r="9" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>222</v>
+        <v>245</v>
       </c>
     </row>
     <row r="10" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>223</v>
+        <v>246</v>
       </c>
     </row>
     <row r="11" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>224</v>
+        <v>247</v>
       </c>
     </row>
     <row r="12" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>225</v>
+        <v>248</v>
       </c>
     </row>
     <row r="13" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>226</v>
+        <v>249</v>
       </c>
     </row>
     <row r="14" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>227</v>
+        <v>250</v>
       </c>
     </row>
     <row r="15" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>228</v>
+        <v>251</v>
       </c>
     </row>
     <row r="16" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>229</v>
+        <v>252</v>
       </c>
     </row>
     <row r="17" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>230</v>
+        <v>253</v>
       </c>
     </row>
     <row r="18" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>231</v>
+        <v>254</v>
       </c>
     </row>
     <row r="19" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>232</v>
+        <v>255</v>
       </c>
     </row>
     <row r="20" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>233</v>
+        <v>256</v>
       </c>
     </row>
     <row r="21" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>234</v>
+        <v>257</v>
       </c>
     </row>
     <row r="22" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
-        <v>235</v>
+        <v>258</v>
       </c>
     </row>
     <row r="23" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
-        <v>236</v>
+        <v>259</v>
       </c>
     </row>
     <row r="24" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
-        <v>237</v>
+        <v>260</v>
       </c>
     </row>
   </sheetData>
@@ -5306,213 +6850,213 @@
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
   <dimension ref="A1:A41"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
     <row r="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
-        <v>238</v>
+        <v>261</v>
       </c>
     </row>
     <row r="2" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>230</v>
+        <v>253</v>
       </c>
     </row>
     <row r="3" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>239</v>
+        <v>262</v>
       </c>
     </row>
     <row r="4" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>240</v>
+        <v>263</v>
       </c>
     </row>
     <row r="5" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>241</v>
+        <v>264</v>
       </c>
     </row>
     <row r="6" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>242</v>
+        <v>265</v>
       </c>
     </row>
     <row r="7" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>196</v>
+        <v>207</v>
       </c>
     </row>
     <row r="8" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>243</v>
+        <v>266</v>
       </c>
     </row>
     <row r="9" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>244</v>
+        <v>267</v>
       </c>
     </row>
     <row r="10" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>245</v>
+        <v>268</v>
       </c>
     </row>
     <row r="11" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>246</v>
+        <v>269</v>
       </c>
     </row>
     <row r="12" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>247</v>
+        <v>270</v>
       </c>
     </row>
     <row r="13" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>248</v>
+        <v>271</v>
       </c>
     </row>
     <row r="14" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>249</v>
+        <v>272</v>
       </c>
     </row>
     <row r="15" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>250</v>
+        <v>273</v>
       </c>
     </row>
     <row r="16" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>251</v>
+        <v>274</v>
       </c>
     </row>
     <row r="17" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>252</v>
+        <v>275</v>
       </c>
     </row>
     <row r="18" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>253</v>
+        <v>276</v>
       </c>
     </row>
     <row r="19" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>254</v>
+        <v>277</v>
       </c>
     </row>
     <row r="20" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>255</v>
+        <v>278</v>
       </c>
     </row>
     <row r="21" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>256</v>
+        <v>279</v>
       </c>
     </row>
     <row r="22" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
-        <v>257</v>
+        <v>280</v>
       </c>
     </row>
     <row r="23" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
-        <v>226</v>
+        <v>249</v>
       </c>
     </row>
     <row r="24" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
-        <v>258</v>
+        <v>281</v>
       </c>
     </row>
     <row r="25" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
-        <v>259</v>
+        <v>282</v>
       </c>
     </row>
     <row r="26" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
-        <v>260</v>
+        <v>283</v>
       </c>
     </row>
     <row r="27" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
-        <v>261</v>
+        <v>284</v>
       </c>
     </row>
     <row r="28" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
-        <v>262</v>
+        <v>285</v>
       </c>
     </row>
     <row r="29" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
-        <v>263</v>
+        <v>286</v>
       </c>
     </row>
     <row r="30" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
-        <v>264</v>
+        <v>287</v>
       </c>
     </row>
     <row r="31" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
-        <v>265</v>
+        <v>288</v>
       </c>
     </row>
     <row r="32" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
-        <v>266</v>
+        <v>289</v>
       </c>
     </row>
     <row r="33" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
-        <v>267</v>
+        <v>290</v>
       </c>
     </row>
     <row r="34" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
-        <v>268</v>
+        <v>291</v>
       </c>
     </row>
     <row r="35" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
-        <v>269</v>
+        <v>292</v>
       </c>
     </row>
     <row r="36" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
-        <v>270</v>
+        <v>293</v>
       </c>
     </row>
     <row r="37" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
-        <v>271</v>
+        <v>294</v>
       </c>
     </row>
     <row r="38" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
-        <v>272</v>
+        <v>295</v>
       </c>
     </row>
     <row r="39" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
-        <v>273</v>
+        <v>296</v>
       </c>
     </row>
     <row r="40" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
-        <v>274</v>
+        <v>297</v>
       </c>
     </row>
     <row r="41" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
-        <v>275</v>
+        <v>298</v>
       </c>
     </row>
   </sheetData>
@@ -5521,168 +7065,168 @@
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0500-000000000000}">
   <dimension ref="A1:A32"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
     <row r="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
-        <v>276</v>
+        <v>299</v>
       </c>
     </row>
     <row r="2" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>277</v>
+        <v>300</v>
       </c>
     </row>
     <row r="3" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>278</v>
+        <v>301</v>
       </c>
     </row>
     <row r="4" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>279</v>
+        <v>302</v>
       </c>
     </row>
     <row r="5" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>280</v>
+        <v>303</v>
       </c>
     </row>
     <row r="6" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>281</v>
+        <v>304</v>
       </c>
     </row>
     <row r="7" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>282</v>
+        <v>305</v>
       </c>
     </row>
     <row r="8" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>283</v>
+        <v>306</v>
       </c>
     </row>
     <row r="9" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>284</v>
+        <v>307</v>
       </c>
     </row>
     <row r="10" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>285</v>
+        <v>308</v>
       </c>
     </row>
     <row r="11" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>286</v>
+        <v>309</v>
       </c>
     </row>
     <row r="12" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>287</v>
+        <v>310</v>
       </c>
     </row>
     <row r="13" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>288</v>
+        <v>311</v>
       </c>
     </row>
     <row r="14" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>197</v>
+        <v>208</v>
       </c>
     </row>
     <row r="15" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>289</v>
+        <v>312</v>
       </c>
     </row>
     <row r="16" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>290</v>
+        <v>313</v>
       </c>
     </row>
     <row r="17" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>291</v>
+        <v>314</v>
       </c>
     </row>
     <row r="18" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>292</v>
+        <v>315</v>
       </c>
     </row>
     <row r="19" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>293</v>
+        <v>316</v>
       </c>
     </row>
     <row r="20" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>294</v>
+        <v>317</v>
       </c>
     </row>
     <row r="21" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>295</v>
+        <v>318</v>
       </c>
     </row>
     <row r="22" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
-        <v>296</v>
+        <v>319</v>
       </c>
     </row>
     <row r="23" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
-        <v>297</v>
+        <v>320</v>
       </c>
     </row>
     <row r="24" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
-        <v>298</v>
+        <v>321</v>
       </c>
     </row>
     <row r="25" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
-        <v>299</v>
+        <v>322</v>
       </c>
     </row>
     <row r="26" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
-        <v>300</v>
+        <v>323</v>
       </c>
     </row>
     <row r="27" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
-        <v>301</v>
+        <v>324</v>
       </c>
     </row>
     <row r="28" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
-        <v>302</v>
+        <v>325</v>
       </c>
     </row>
     <row r="29" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
-        <v>303</v>
+        <v>326</v>
       </c>
     </row>
     <row r="30" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
-        <v>304</v>
+        <v>327</v>
       </c>
     </row>
     <row r="31" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
-        <v>305</v>
+        <v>328</v>
       </c>
     </row>
     <row r="32" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
-        <v>306</v>
+        <v>329</v>
       </c>
     </row>
   </sheetData>
@@ -5691,12 +7235,12 @@
 </file>
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:Q15"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0600-000000000000}">
+  <dimension ref="A1:Q27"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="8.42578125" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="35.85546875" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="9.42578125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="36.5703125" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="42.42578125" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="39.7109375" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="36.5703125" bestFit="1" customWidth="1"/>
@@ -5763,747 +7307,1383 @@
     </row>
     <row r="2" spans="1:17" hidden="1" x14ac:dyDescent="0.25">
       <c r="C2" t="s">
-        <v>307</v>
+        <v>330</v>
       </c>
       <c r="D2" t="s">
-        <v>308</v>
+        <v>331</v>
       </c>
       <c r="E2" t="s">
-        <v>309</v>
+        <v>332</v>
       </c>
       <c r="F2" t="s">
-        <v>310</v>
+        <v>333</v>
       </c>
       <c r="G2" t="s">
-        <v>311</v>
+        <v>334</v>
       </c>
       <c r="H2" t="s">
-        <v>312</v>
+        <v>335</v>
       </c>
       <c r="I2" t="s">
-        <v>313</v>
+        <v>336</v>
       </c>
       <c r="J2" t="s">
-        <v>314</v>
+        <v>337</v>
       </c>
       <c r="K2" t="s">
-        <v>315</v>
+        <v>338</v>
       </c>
       <c r="L2" t="s">
-        <v>316</v>
+        <v>339</v>
       </c>
       <c r="M2" t="s">
-        <v>317</v>
+        <v>340</v>
       </c>
       <c r="N2" t="s">
-        <v>318</v>
+        <v>341</v>
       </c>
       <c r="O2" t="s">
-        <v>319</v>
+        <v>342</v>
       </c>
       <c r="P2" t="s">
-        <v>320</v>
+        <v>343</v>
       </c>
       <c r="Q2" t="s">
-        <v>321</v>
+        <v>344</v>
       </c>
     </row>
     <row r="3" spans="1:17" ht="30" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
-        <v>172</v>
+        <v>183</v>
       </c>
       <c r="B3" s="1"/>
       <c r="C3" s="1" t="s">
-        <v>322</v>
+        <v>345</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>323</v>
+        <v>346</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>324</v>
+        <v>347</v>
       </c>
       <c r="F3" s="1" t="s">
-        <v>325</v>
+        <v>348</v>
       </c>
       <c r="G3" s="1" t="s">
-        <v>176</v>
+        <v>187</v>
       </c>
       <c r="H3" s="1" t="s">
-        <v>177</v>
+        <v>188</v>
       </c>
       <c r="I3" s="1" t="s">
-        <v>326</v>
+        <v>349</v>
       </c>
       <c r="J3" s="1" t="s">
-        <v>327</v>
+        <v>350</v>
       </c>
       <c r="K3" s="1" t="s">
-        <v>328</v>
+        <v>351</v>
       </c>
       <c r="L3" s="1" t="s">
-        <v>181</v>
+        <v>192</v>
       </c>
       <c r="M3" s="1" t="s">
-        <v>182</v>
+        <v>193</v>
       </c>
       <c r="N3" s="1" t="s">
-        <v>183</v>
+        <v>194</v>
       </c>
       <c r="O3" s="1" t="s">
-        <v>184</v>
+        <v>195</v>
       </c>
       <c r="P3" s="1" t="s">
-        <v>185</v>
+        <v>196</v>
       </c>
       <c r="Q3" s="1" t="s">
-        <v>186</v>
+        <v>197</v>
       </c>
     </row>
     <row r="4" spans="1:17" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="3" t="s">
-        <v>92</v>
+        <v>88</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>329</v>
+        <v>352</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>201</v>
+        <v>212</v>
       </c>
       <c r="D4" s="3" t="s">
-        <v>202</v>
+        <v>213</v>
       </c>
       <c r="E4" s="3" t="s">
-        <v>193</v>
+        <v>204</v>
       </c>
       <c r="F4" s="3" t="s">
-        <v>194</v>
+        <v>205</v>
       </c>
       <c r="G4" s="3" t="s">
-        <v>195</v>
+        <v>206</v>
       </c>
       <c r="H4" s="3" t="s">
-        <v>90</v>
+        <v>85</v>
       </c>
       <c r="I4" s="3" t="s">
-        <v>196</v>
+        <v>207</v>
       </c>
       <c r="J4" s="3" t="s">
-        <v>197</v>
+        <v>208</v>
       </c>
       <c r="K4" s="3" t="s">
-        <v>198</v>
+        <v>209</v>
       </c>
       <c r="L4" s="3" t="s">
-        <v>197</v>
+        <v>208</v>
       </c>
       <c r="M4" s="3" t="s">
-        <v>198</v>
+        <v>209</v>
       </c>
       <c r="N4" s="3" t="s">
-        <v>197</v>
+        <v>208</v>
       </c>
       <c r="O4" s="3" t="s">
-        <v>199</v>
+        <v>210</v>
       </c>
       <c r="P4" s="3" t="s">
-        <v>197</v>
+        <v>208</v>
       </c>
       <c r="Q4" s="3" t="s">
-        <v>200</v>
+        <v>211</v>
       </c>
     </row>
     <row r="5" spans="1:17" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="3" t="s">
-        <v>108</v>
+        <v>102</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>330</v>
+        <v>353</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>201</v>
+        <v>212</v>
       </c>
       <c r="D5" s="3" t="s">
-        <v>202</v>
+        <v>213</v>
       </c>
       <c r="E5" s="3" t="s">
-        <v>193</v>
+        <v>204</v>
       </c>
       <c r="F5" s="3" t="s">
-        <v>194</v>
+        <v>205</v>
       </c>
       <c r="G5" s="3" t="s">
-        <v>195</v>
+        <v>206</v>
       </c>
       <c r="H5" s="3" t="s">
-        <v>90</v>
+        <v>85</v>
       </c>
       <c r="I5" s="3" t="s">
-        <v>196</v>
+        <v>207</v>
       </c>
       <c r="J5" s="3" t="s">
-        <v>197</v>
+        <v>208</v>
       </c>
       <c r="K5" s="3" t="s">
-        <v>198</v>
+        <v>209</v>
       </c>
       <c r="L5" s="3" t="s">
-        <v>197</v>
+        <v>208</v>
       </c>
       <c r="M5" s="3" t="s">
-        <v>198</v>
+        <v>209</v>
       </c>
       <c r="N5" s="3" t="s">
-        <v>197</v>
+        <v>208</v>
       </c>
       <c r="O5" s="3" t="s">
-        <v>199</v>
+        <v>210</v>
       </c>
       <c r="P5" s="3" t="s">
-        <v>197</v>
+        <v>208</v>
       </c>
       <c r="Q5" s="3" t="s">
-        <v>200</v>
+        <v>211</v>
       </c>
     </row>
     <row r="6" spans="1:17" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="3" t="s">
-        <v>116</v>
+        <v>109</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>331</v>
+        <v>354</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>201</v>
+        <v>212</v>
       </c>
       <c r="D6" s="3" t="s">
-        <v>202</v>
+        <v>213</v>
       </c>
       <c r="E6" s="3" t="s">
-        <v>193</v>
+        <v>204</v>
       </c>
       <c r="F6" s="3" t="s">
-        <v>194</v>
+        <v>205</v>
       </c>
       <c r="G6" s="3" t="s">
-        <v>195</v>
+        <v>206</v>
       </c>
       <c r="H6" s="3" t="s">
-        <v>90</v>
+        <v>85</v>
       </c>
       <c r="I6" s="3" t="s">
-        <v>196</v>
+        <v>207</v>
       </c>
       <c r="J6" s="3" t="s">
-        <v>197</v>
+        <v>208</v>
       </c>
       <c r="K6" s="3" t="s">
-        <v>198</v>
+        <v>209</v>
       </c>
       <c r="L6" s="3" t="s">
-        <v>197</v>
+        <v>208</v>
       </c>
       <c r="M6" s="3" t="s">
-        <v>198</v>
+        <v>209</v>
       </c>
       <c r="N6" s="3" t="s">
-        <v>197</v>
+        <v>208</v>
       </c>
       <c r="O6" s="3" t="s">
-        <v>199</v>
+        <v>210</v>
       </c>
       <c r="P6" s="3" t="s">
-        <v>197</v>
+        <v>208</v>
       </c>
       <c r="Q6" s="3" t="s">
-        <v>200</v>
+        <v>211</v>
       </c>
     </row>
     <row r="7" spans="1:17" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="3" t="s">
-        <v>121</v>
+        <v>117</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>332</v>
+        <v>355</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>201</v>
+        <v>212</v>
       </c>
       <c r="D7" s="3" t="s">
-        <v>202</v>
+        <v>213</v>
       </c>
       <c r="E7" s="3" t="s">
-        <v>193</v>
+        <v>204</v>
       </c>
       <c r="F7" s="3" t="s">
-        <v>194</v>
+        <v>205</v>
       </c>
       <c r="G7" s="3" t="s">
-        <v>195</v>
+        <v>206</v>
       </c>
       <c r="H7" s="3" t="s">
-        <v>90</v>
+        <v>85</v>
       </c>
       <c r="I7" s="3" t="s">
-        <v>196</v>
+        <v>207</v>
       </c>
       <c r="J7" s="3" t="s">
-        <v>197</v>
+        <v>208</v>
       </c>
       <c r="K7" s="3" t="s">
-        <v>198</v>
+        <v>209</v>
       </c>
       <c r="L7" s="3" t="s">
-        <v>197</v>
+        <v>208</v>
       </c>
       <c r="M7" s="3" t="s">
-        <v>198</v>
+        <v>209</v>
       </c>
       <c r="N7" s="3" t="s">
-        <v>197</v>
+        <v>208</v>
       </c>
       <c r="O7" s="3" t="s">
-        <v>199</v>
+        <v>210</v>
       </c>
       <c r="P7" s="3" t="s">
-        <v>197</v>
+        <v>208</v>
       </c>
       <c r="Q7" s="3" t="s">
-        <v>200</v>
+        <v>211</v>
       </c>
     </row>
     <row r="8" spans="1:17" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="3" t="s">
-        <v>130</v>
+        <v>123</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>333</v>
+        <v>356</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>201</v>
+        <v>212</v>
       </c>
       <c r="D8" s="3" t="s">
-        <v>202</v>
+        <v>213</v>
       </c>
       <c r="E8" s="3" t="s">
-        <v>193</v>
+        <v>204</v>
       </c>
       <c r="F8" s="3" t="s">
-        <v>194</v>
+        <v>205</v>
       </c>
       <c r="G8" s="3" t="s">
-        <v>195</v>
+        <v>206</v>
       </c>
       <c r="H8" s="3" t="s">
-        <v>90</v>
+        <v>85</v>
       </c>
       <c r="I8" s="3" t="s">
-        <v>196</v>
+        <v>207</v>
       </c>
       <c r="J8" s="3" t="s">
-        <v>197</v>
+        <v>208</v>
       </c>
       <c r="K8" s="3" t="s">
-        <v>198</v>
+        <v>209</v>
       </c>
       <c r="L8" s="3" t="s">
-        <v>197</v>
+        <v>208</v>
       </c>
       <c r="M8" s="3" t="s">
-        <v>198</v>
+        <v>209</v>
       </c>
       <c r="N8" s="3" t="s">
-        <v>197</v>
+        <v>208</v>
       </c>
       <c r="O8" s="3" t="s">
-        <v>199</v>
+        <v>210</v>
       </c>
       <c r="P8" s="3" t="s">
-        <v>197</v>
+        <v>208</v>
       </c>
       <c r="Q8" s="3" t="s">
-        <v>200</v>
+        <v>211</v>
       </c>
     </row>
     <row r="9" spans="1:17" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="3" t="s">
-        <v>135</v>
+        <v>129</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>334</v>
+        <v>357</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>201</v>
+        <v>212</v>
       </c>
       <c r="D9" s="3" t="s">
-        <v>202</v>
+        <v>213</v>
       </c>
       <c r="E9" s="3" t="s">
-        <v>193</v>
+        <v>204</v>
       </c>
       <c r="F9" s="3" t="s">
-        <v>194</v>
+        <v>205</v>
       </c>
       <c r="G9" s="3" t="s">
-        <v>195</v>
+        <v>206</v>
       </c>
       <c r="H9" s="3" t="s">
-        <v>90</v>
+        <v>85</v>
       </c>
       <c r="I9" s="3" t="s">
-        <v>196</v>
+        <v>207</v>
       </c>
       <c r="J9" s="3" t="s">
-        <v>197</v>
+        <v>208</v>
       </c>
       <c r="K9" s="3" t="s">
-        <v>198</v>
+        <v>209</v>
       </c>
       <c r="L9" s="3" t="s">
-        <v>197</v>
+        <v>208</v>
       </c>
       <c r="M9" s="3" t="s">
-        <v>198</v>
+        <v>209</v>
       </c>
       <c r="N9" s="3" t="s">
-        <v>197</v>
+        <v>208</v>
       </c>
       <c r="O9" s="3" t="s">
-        <v>199</v>
+        <v>210</v>
       </c>
       <c r="P9" s="3" t="s">
-        <v>197</v>
+        <v>208</v>
       </c>
       <c r="Q9" s="3" t="s">
-        <v>200</v>
+        <v>211</v>
       </c>
     </row>
     <row r="10" spans="1:17" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="3" t="s">
-        <v>140</v>
+        <v>130</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>335</v>
+        <v>358</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>201</v>
+        <v>212</v>
       </c>
       <c r="D10" s="3" t="s">
-        <v>202</v>
+        <v>213</v>
       </c>
       <c r="E10" s="3" t="s">
-        <v>193</v>
+        <v>204</v>
       </c>
       <c r="F10" s="3" t="s">
-        <v>194</v>
+        <v>205</v>
       </c>
       <c r="G10" s="3" t="s">
-        <v>195</v>
+        <v>206</v>
       </c>
       <c r="H10" s="3" t="s">
-        <v>90</v>
+        <v>85</v>
       </c>
       <c r="I10" s="3" t="s">
-        <v>196</v>
+        <v>207</v>
       </c>
       <c r="J10" s="3" t="s">
-        <v>197</v>
+        <v>208</v>
       </c>
       <c r="K10" s="3" t="s">
-        <v>198</v>
+        <v>209</v>
       </c>
       <c r="L10" s="3" t="s">
-        <v>197</v>
+        <v>208</v>
       </c>
       <c r="M10" s="3" t="s">
-        <v>198</v>
+        <v>209</v>
       </c>
       <c r="N10" s="3" t="s">
-        <v>197</v>
+        <v>208</v>
       </c>
       <c r="O10" s="3" t="s">
-        <v>199</v>
+        <v>210</v>
       </c>
       <c r="P10" s="3" t="s">
-        <v>197</v>
+        <v>208</v>
       </c>
       <c r="Q10" s="3" t="s">
-        <v>200</v>
+        <v>211</v>
       </c>
     </row>
     <row r="11" spans="1:17" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="3" t="s">
-        <v>144</v>
+        <v>131</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>336</v>
+        <v>359</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>201</v>
+        <v>212</v>
       </c>
       <c r="D11" s="3" t="s">
-        <v>202</v>
+        <v>213</v>
       </c>
       <c r="E11" s="3" t="s">
-        <v>193</v>
+        <v>204</v>
       </c>
       <c r="F11" s="3" t="s">
-        <v>194</v>
+        <v>205</v>
       </c>
       <c r="G11" s="3" t="s">
-        <v>195</v>
+        <v>206</v>
       </c>
       <c r="H11" s="3" t="s">
-        <v>90</v>
+        <v>85</v>
       </c>
       <c r="I11" s="3" t="s">
-        <v>196</v>
+        <v>207</v>
       </c>
       <c r="J11" s="3" t="s">
-        <v>197</v>
+        <v>208</v>
       </c>
       <c r="K11" s="3" t="s">
-        <v>198</v>
+        <v>209</v>
       </c>
       <c r="L11" s="3" t="s">
-        <v>197</v>
+        <v>208</v>
       </c>
       <c r="M11" s="3" t="s">
-        <v>198</v>
+        <v>209</v>
       </c>
       <c r="N11" s="3" t="s">
-        <v>197</v>
+        <v>208</v>
       </c>
       <c r="O11" s="3" t="s">
-        <v>199</v>
+        <v>210</v>
       </c>
       <c r="P11" s="3" t="s">
-        <v>197</v>
+        <v>208</v>
       </c>
       <c r="Q11" s="3" t="s">
-        <v>200</v>
+        <v>211</v>
       </c>
     </row>
     <row r="12" spans="1:17" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="3" t="s">
-        <v>146</v>
+        <v>132</v>
       </c>
       <c r="B12" s="3" t="s">
-        <v>337</v>
+        <v>360</v>
       </c>
       <c r="C12" s="3" t="s">
-        <v>201</v>
+        <v>212</v>
       </c>
       <c r="D12" s="3" t="s">
-        <v>202</v>
+        <v>213</v>
       </c>
       <c r="E12" s="3" t="s">
-        <v>193</v>
+        <v>204</v>
       </c>
       <c r="F12" s="3" t="s">
-        <v>194</v>
+        <v>205</v>
       </c>
       <c r="G12" s="3" t="s">
-        <v>195</v>
+        <v>206</v>
       </c>
       <c r="H12" s="3" t="s">
-        <v>90</v>
+        <v>85</v>
       </c>
       <c r="I12" s="3" t="s">
-        <v>196</v>
+        <v>207</v>
       </c>
       <c r="J12" s="3" t="s">
-        <v>197</v>
+        <v>208</v>
       </c>
       <c r="K12" s="3" t="s">
-        <v>198</v>
+        <v>209</v>
       </c>
       <c r="L12" s="3" t="s">
-        <v>197</v>
+        <v>208</v>
       </c>
       <c r="M12" s="3" t="s">
-        <v>198</v>
+        <v>209</v>
       </c>
       <c r="N12" s="3" t="s">
-        <v>197</v>
+        <v>208</v>
       </c>
       <c r="O12" s="3" t="s">
-        <v>199</v>
+        <v>210</v>
       </c>
       <c r="P12" s="3" t="s">
-        <v>197</v>
+        <v>208</v>
       </c>
       <c r="Q12" s="3" t="s">
-        <v>200</v>
+        <v>211</v>
       </c>
     </row>
     <row r="13" spans="1:17" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="3" t="s">
-        <v>148</v>
+        <v>133</v>
       </c>
       <c r="B13" s="3" t="s">
-        <v>338</v>
+        <v>361</v>
       </c>
       <c r="C13" s="3" t="s">
-        <v>201</v>
+        <v>212</v>
       </c>
       <c r="D13" s="3" t="s">
-        <v>202</v>
+        <v>213</v>
       </c>
       <c r="E13" s="3" t="s">
-        <v>193</v>
+        <v>204</v>
       </c>
       <c r="F13" s="3" t="s">
-        <v>194</v>
+        <v>205</v>
       </c>
       <c r="G13" s="3" t="s">
-        <v>195</v>
+        <v>206</v>
       </c>
       <c r="H13" s="3" t="s">
-        <v>90</v>
+        <v>85</v>
       </c>
       <c r="I13" s="3" t="s">
-        <v>196</v>
+        <v>207</v>
       </c>
       <c r="J13" s="3" t="s">
-        <v>197</v>
+        <v>208</v>
       </c>
       <c r="K13" s="3" t="s">
-        <v>198</v>
+        <v>209</v>
       </c>
       <c r="L13" s="3" t="s">
-        <v>197</v>
+        <v>208</v>
       </c>
       <c r="M13" s="3" t="s">
-        <v>198</v>
+        <v>209</v>
       </c>
       <c r="N13" s="3" t="s">
-        <v>197</v>
+        <v>208</v>
       </c>
       <c r="O13" s="3" t="s">
-        <v>199</v>
+        <v>210</v>
       </c>
       <c r="P13" s="3" t="s">
-        <v>197</v>
+        <v>208</v>
       </c>
       <c r="Q13" s="3" t="s">
-        <v>200</v>
+        <v>211</v>
       </c>
     </row>
     <row r="14" spans="1:17" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="3" t="s">
-        <v>150</v>
+        <v>134</v>
       </c>
       <c r="B14" s="3" t="s">
-        <v>339</v>
+        <v>362</v>
       </c>
       <c r="C14" s="3" t="s">
-        <v>201</v>
+        <v>212</v>
       </c>
       <c r="D14" s="3" t="s">
-        <v>202</v>
+        <v>213</v>
       </c>
       <c r="E14" s="3" t="s">
-        <v>193</v>
+        <v>204</v>
       </c>
       <c r="F14" s="3" t="s">
-        <v>194</v>
+        <v>205</v>
       </c>
       <c r="G14" s="3" t="s">
-        <v>195</v>
+        <v>206</v>
       </c>
       <c r="H14" s="3" t="s">
-        <v>90</v>
+        <v>85</v>
       </c>
       <c r="I14" s="3" t="s">
-        <v>196</v>
+        <v>207</v>
       </c>
       <c r="J14" s="3" t="s">
-        <v>197</v>
+        <v>208</v>
       </c>
       <c r="K14" s="3" t="s">
-        <v>198</v>
+        <v>209</v>
       </c>
       <c r="L14" s="3" t="s">
-        <v>197</v>
+        <v>208</v>
       </c>
       <c r="M14" s="3" t="s">
-        <v>198</v>
+        <v>209</v>
       </c>
       <c r="N14" s="3" t="s">
-        <v>197</v>
+        <v>208</v>
       </c>
       <c r="O14" s="3" t="s">
-        <v>199</v>
+        <v>210</v>
       </c>
       <c r="P14" s="3" t="s">
-        <v>197</v>
+        <v>208</v>
       </c>
       <c r="Q14" s="3" t="s">
-        <v>200</v>
+        <v>211</v>
       </c>
     </row>
     <row r="15" spans="1:17" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" s="3" t="s">
-        <v>152</v>
+        <v>135</v>
       </c>
       <c r="B15" s="3" t="s">
-        <v>340</v>
+        <v>363</v>
       </c>
       <c r="C15" s="3" t="s">
-        <v>201</v>
+        <v>212</v>
       </c>
       <c r="D15" s="3" t="s">
-        <v>202</v>
+        <v>213</v>
       </c>
       <c r="E15" s="3" t="s">
-        <v>193</v>
+        <v>204</v>
       </c>
       <c r="F15" s="3" t="s">
-        <v>194</v>
+        <v>205</v>
       </c>
       <c r="G15" s="3" t="s">
-        <v>195</v>
+        <v>206</v>
       </c>
       <c r="H15" s="3" t="s">
-        <v>90</v>
+        <v>85</v>
       </c>
       <c r="I15" s="3" t="s">
-        <v>196</v>
+        <v>207</v>
       </c>
       <c r="J15" s="3" t="s">
-        <v>197</v>
+        <v>208</v>
       </c>
       <c r="K15" s="3" t="s">
-        <v>198</v>
+        <v>209</v>
       </c>
       <c r="L15" s="3" t="s">
-        <v>197</v>
+        <v>208</v>
       </c>
       <c r="M15" s="3" t="s">
-        <v>198</v>
+        <v>209</v>
       </c>
       <c r="N15" s="3" t="s">
-        <v>197</v>
+        <v>208</v>
       </c>
       <c r="O15" s="3" t="s">
-        <v>199</v>
+        <v>210</v>
       </c>
       <c r="P15" s="3" t="s">
-        <v>197</v>
+        <v>208</v>
       </c>
       <c r="Q15" s="3" t="s">
-        <v>200</v>
+        <v>211</v>
+      </c>
+    </row>
+    <row r="16" spans="1:17" ht="45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A16" s="3" t="s">
+        <v>136</v>
+      </c>
+      <c r="B16" s="3" t="s">
+        <v>364</v>
+      </c>
+      <c r="C16" s="3" t="s">
+        <v>212</v>
+      </c>
+      <c r="D16" s="3" t="s">
+        <v>213</v>
+      </c>
+      <c r="E16" s="3" t="s">
+        <v>204</v>
+      </c>
+      <c r="F16" s="3" t="s">
+        <v>205</v>
+      </c>
+      <c r="G16" s="3" t="s">
+        <v>206</v>
+      </c>
+      <c r="H16" s="3" t="s">
+        <v>85</v>
+      </c>
+      <c r="I16" s="3" t="s">
+        <v>207</v>
+      </c>
+      <c r="J16" s="3" t="s">
+        <v>208</v>
+      </c>
+      <c r="K16" s="3" t="s">
+        <v>209</v>
+      </c>
+      <c r="L16" s="3" t="s">
+        <v>208</v>
+      </c>
+      <c r="M16" s="3" t="s">
+        <v>209</v>
+      </c>
+      <c r="N16" s="3" t="s">
+        <v>208</v>
+      </c>
+      <c r="O16" s="3" t="s">
+        <v>210</v>
+      </c>
+      <c r="P16" s="3" t="s">
+        <v>208</v>
+      </c>
+      <c r="Q16" s="3" t="s">
+        <v>211</v>
+      </c>
+    </row>
+    <row r="17" spans="1:17" ht="45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A17" s="3" t="s">
+        <v>138</v>
+      </c>
+      <c r="B17" s="3" t="s">
+        <v>365</v>
+      </c>
+      <c r="C17" s="3" t="s">
+        <v>212</v>
+      </c>
+      <c r="D17" s="3" t="s">
+        <v>213</v>
+      </c>
+      <c r="E17" s="3" t="s">
+        <v>204</v>
+      </c>
+      <c r="F17" s="3" t="s">
+        <v>205</v>
+      </c>
+      <c r="G17" s="3" t="s">
+        <v>206</v>
+      </c>
+      <c r="H17" s="3" t="s">
+        <v>85</v>
+      </c>
+      <c r="I17" s="3" t="s">
+        <v>207</v>
+      </c>
+      <c r="J17" s="3" t="s">
+        <v>208</v>
+      </c>
+      <c r="K17" s="3" t="s">
+        <v>209</v>
+      </c>
+      <c r="L17" s="3" t="s">
+        <v>208</v>
+      </c>
+      <c r="M17" s="3" t="s">
+        <v>209</v>
+      </c>
+      <c r="N17" s="3" t="s">
+        <v>208</v>
+      </c>
+      <c r="O17" s="3" t="s">
+        <v>210</v>
+      </c>
+      <c r="P17" s="3" t="s">
+        <v>208</v>
+      </c>
+      <c r="Q17" s="3" t="s">
+        <v>211</v>
+      </c>
+    </row>
+    <row r="18" spans="1:17" ht="45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A18" s="3" t="s">
+        <v>139</v>
+      </c>
+      <c r="B18" s="3" t="s">
+        <v>366</v>
+      </c>
+      <c r="C18" s="3" t="s">
+        <v>212</v>
+      </c>
+      <c r="D18" s="3" t="s">
+        <v>213</v>
+      </c>
+      <c r="E18" s="3" t="s">
+        <v>204</v>
+      </c>
+      <c r="F18" s="3" t="s">
+        <v>205</v>
+      </c>
+      <c r="G18" s="3" t="s">
+        <v>206</v>
+      </c>
+      <c r="H18" s="3" t="s">
+        <v>85</v>
+      </c>
+      <c r="I18" s="3" t="s">
+        <v>207</v>
+      </c>
+      <c r="J18" s="3" t="s">
+        <v>208</v>
+      </c>
+      <c r="K18" s="3" t="s">
+        <v>209</v>
+      </c>
+      <c r="L18" s="3" t="s">
+        <v>208</v>
+      </c>
+      <c r="M18" s="3" t="s">
+        <v>209</v>
+      </c>
+      <c r="N18" s="3" t="s">
+        <v>208</v>
+      </c>
+      <c r="O18" s="3" t="s">
+        <v>210</v>
+      </c>
+      <c r="P18" s="3" t="s">
+        <v>208</v>
+      </c>
+      <c r="Q18" s="3" t="s">
+        <v>211</v>
+      </c>
+    </row>
+    <row r="19" spans="1:17" ht="45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A19" s="3" t="s">
+        <v>141</v>
+      </c>
+      <c r="B19" s="3" t="s">
+        <v>367</v>
+      </c>
+      <c r="C19" s="3" t="s">
+        <v>212</v>
+      </c>
+      <c r="D19" s="3" t="s">
+        <v>213</v>
+      </c>
+      <c r="E19" s="3" t="s">
+        <v>204</v>
+      </c>
+      <c r="F19" s="3" t="s">
+        <v>205</v>
+      </c>
+      <c r="G19" s="3" t="s">
+        <v>206</v>
+      </c>
+      <c r="H19" s="3" t="s">
+        <v>85</v>
+      </c>
+      <c r="I19" s="3" t="s">
+        <v>207</v>
+      </c>
+      <c r="J19" s="3" t="s">
+        <v>208</v>
+      </c>
+      <c r="K19" s="3" t="s">
+        <v>209</v>
+      </c>
+      <c r="L19" s="3" t="s">
+        <v>208</v>
+      </c>
+      <c r="M19" s="3" t="s">
+        <v>209</v>
+      </c>
+      <c r="N19" s="3" t="s">
+        <v>208</v>
+      </c>
+      <c r="O19" s="3" t="s">
+        <v>210</v>
+      </c>
+      <c r="P19" s="3" t="s">
+        <v>208</v>
+      </c>
+      <c r="Q19" s="3" t="s">
+        <v>211</v>
+      </c>
+    </row>
+    <row r="20" spans="1:17" ht="45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A20" s="3" t="s">
+        <v>142</v>
+      </c>
+      <c r="B20" s="3" t="s">
+        <v>368</v>
+      </c>
+      <c r="C20" s="3" t="s">
+        <v>212</v>
+      </c>
+      <c r="D20" s="3" t="s">
+        <v>213</v>
+      </c>
+      <c r="E20" s="3" t="s">
+        <v>204</v>
+      </c>
+      <c r="F20" s="3" t="s">
+        <v>205</v>
+      </c>
+      <c r="G20" s="3" t="s">
+        <v>206</v>
+      </c>
+      <c r="H20" s="3" t="s">
+        <v>85</v>
+      </c>
+      <c r="I20" s="3" t="s">
+        <v>207</v>
+      </c>
+      <c r="J20" s="3" t="s">
+        <v>208</v>
+      </c>
+      <c r="K20" s="3" t="s">
+        <v>209</v>
+      </c>
+      <c r="L20" s="3" t="s">
+        <v>208</v>
+      </c>
+      <c r="M20" s="3" t="s">
+        <v>209</v>
+      </c>
+      <c r="N20" s="3" t="s">
+        <v>208</v>
+      </c>
+      <c r="O20" s="3" t="s">
+        <v>210</v>
+      </c>
+      <c r="P20" s="3" t="s">
+        <v>208</v>
+      </c>
+      <c r="Q20" s="3" t="s">
+        <v>211</v>
+      </c>
+    </row>
+    <row r="21" spans="1:17" ht="45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A21" s="3" t="s">
+        <v>144</v>
+      </c>
+      <c r="B21" s="3" t="s">
+        <v>369</v>
+      </c>
+      <c r="C21" s="3" t="s">
+        <v>212</v>
+      </c>
+      <c r="D21" s="3" t="s">
+        <v>213</v>
+      </c>
+      <c r="E21" s="3" t="s">
+        <v>204</v>
+      </c>
+      <c r="F21" s="3" t="s">
+        <v>205</v>
+      </c>
+      <c r="G21" s="3" t="s">
+        <v>206</v>
+      </c>
+      <c r="H21" s="3" t="s">
+        <v>85</v>
+      </c>
+      <c r="I21" s="3" t="s">
+        <v>207</v>
+      </c>
+      <c r="J21" s="3" t="s">
+        <v>208</v>
+      </c>
+      <c r="K21" s="3" t="s">
+        <v>209</v>
+      </c>
+      <c r="L21" s="3" t="s">
+        <v>208</v>
+      </c>
+      <c r="M21" s="3" t="s">
+        <v>209</v>
+      </c>
+      <c r="N21" s="3" t="s">
+        <v>208</v>
+      </c>
+      <c r="O21" s="3" t="s">
+        <v>210</v>
+      </c>
+      <c r="P21" s="3" t="s">
+        <v>208</v>
+      </c>
+      <c r="Q21" s="3" t="s">
+        <v>211</v>
+      </c>
+    </row>
+    <row r="22" spans="1:17" ht="45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A22" s="3" t="s">
+        <v>150</v>
+      </c>
+      <c r="B22" s="3" t="s">
+        <v>370</v>
+      </c>
+      <c r="C22" s="3" t="s">
+        <v>212</v>
+      </c>
+      <c r="D22" s="3" t="s">
+        <v>213</v>
+      </c>
+      <c r="E22" s="3" t="s">
+        <v>204</v>
+      </c>
+      <c r="F22" s="3" t="s">
+        <v>205</v>
+      </c>
+      <c r="G22" s="3" t="s">
+        <v>206</v>
+      </c>
+      <c r="H22" s="3" t="s">
+        <v>85</v>
+      </c>
+      <c r="I22" s="3" t="s">
+        <v>207</v>
+      </c>
+      <c r="J22" s="3" t="s">
+        <v>208</v>
+      </c>
+      <c r="K22" s="3" t="s">
+        <v>209</v>
+      </c>
+      <c r="L22" s="3" t="s">
+        <v>208</v>
+      </c>
+      <c r="M22" s="3" t="s">
+        <v>209</v>
+      </c>
+      <c r="N22" s="3" t="s">
+        <v>208</v>
+      </c>
+      <c r="O22" s="3" t="s">
+        <v>210</v>
+      </c>
+      <c r="P22" s="3" t="s">
+        <v>208</v>
+      </c>
+      <c r="Q22" s="3" t="s">
+        <v>211</v>
+      </c>
+    </row>
+    <row r="23" spans="1:17" ht="45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A23" s="3" t="s">
+        <v>154</v>
+      </c>
+      <c r="B23" s="3" t="s">
+        <v>371</v>
+      </c>
+      <c r="C23" s="3" t="s">
+        <v>212</v>
+      </c>
+      <c r="D23" s="3" t="s">
+        <v>213</v>
+      </c>
+      <c r="E23" s="3" t="s">
+        <v>204</v>
+      </c>
+      <c r="F23" s="3" t="s">
+        <v>205</v>
+      </c>
+      <c r="G23" s="3" t="s">
+        <v>206</v>
+      </c>
+      <c r="H23" s="3" t="s">
+        <v>85</v>
+      </c>
+      <c r="I23" s="3" t="s">
+        <v>207</v>
+      </c>
+      <c r="J23" s="3" t="s">
+        <v>208</v>
+      </c>
+      <c r="K23" s="3" t="s">
+        <v>209</v>
+      </c>
+      <c r="L23" s="3" t="s">
+        <v>208</v>
+      </c>
+      <c r="M23" s="3" t="s">
+        <v>209</v>
+      </c>
+      <c r="N23" s="3" t="s">
+        <v>208</v>
+      </c>
+      <c r="O23" s="3" t="s">
+        <v>210</v>
+      </c>
+      <c r="P23" s="3" t="s">
+        <v>208</v>
+      </c>
+      <c r="Q23" s="3" t="s">
+        <v>211</v>
+      </c>
+    </row>
+    <row r="24" spans="1:17" ht="45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A24" s="3" t="s">
+        <v>156</v>
+      </c>
+      <c r="B24" s="3" t="s">
+        <v>372</v>
+      </c>
+      <c r="C24" s="3" t="s">
+        <v>212</v>
+      </c>
+      <c r="D24" s="3" t="s">
+        <v>213</v>
+      </c>
+      <c r="E24" s="3" t="s">
+        <v>204</v>
+      </c>
+      <c r="F24" s="3" t="s">
+        <v>205</v>
+      </c>
+      <c r="G24" s="3" t="s">
+        <v>206</v>
+      </c>
+      <c r="H24" s="3" t="s">
+        <v>85</v>
+      </c>
+      <c r="I24" s="3" t="s">
+        <v>207</v>
+      </c>
+      <c r="J24" s="3" t="s">
+        <v>208</v>
+      </c>
+      <c r="K24" s="3" t="s">
+        <v>209</v>
+      </c>
+      <c r="L24" s="3" t="s">
+        <v>208</v>
+      </c>
+      <c r="M24" s="3" t="s">
+        <v>209</v>
+      </c>
+      <c r="N24" s="3" t="s">
+        <v>208</v>
+      </c>
+      <c r="O24" s="3" t="s">
+        <v>210</v>
+      </c>
+      <c r="P24" s="3" t="s">
+        <v>208</v>
+      </c>
+      <c r="Q24" s="3" t="s">
+        <v>211</v>
+      </c>
+    </row>
+    <row r="25" spans="1:17" ht="45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A25" s="3" t="s">
+        <v>158</v>
+      </c>
+      <c r="B25" s="3" t="s">
+        <v>373</v>
+      </c>
+      <c r="C25" s="3" t="s">
+        <v>212</v>
+      </c>
+      <c r="D25" s="3" t="s">
+        <v>213</v>
+      </c>
+      <c r="E25" s="3" t="s">
+        <v>204</v>
+      </c>
+      <c r="F25" s="3" t="s">
+        <v>205</v>
+      </c>
+      <c r="G25" s="3" t="s">
+        <v>206</v>
+      </c>
+      <c r="H25" s="3" t="s">
+        <v>85</v>
+      </c>
+      <c r="I25" s="3" t="s">
+        <v>207</v>
+      </c>
+      <c r="J25" s="3" t="s">
+        <v>208</v>
+      </c>
+      <c r="K25" s="3" t="s">
+        <v>209</v>
+      </c>
+      <c r="L25" s="3" t="s">
+        <v>208</v>
+      </c>
+      <c r="M25" s="3" t="s">
+        <v>209</v>
+      </c>
+      <c r="N25" s="3" t="s">
+        <v>208</v>
+      </c>
+      <c r="O25" s="3" t="s">
+        <v>210</v>
+      </c>
+      <c r="P25" s="3" t="s">
+        <v>208</v>
+      </c>
+      <c r="Q25" s="3" t="s">
+        <v>211</v>
+      </c>
+    </row>
+    <row r="26" spans="1:17" ht="45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A26" s="3" t="s">
+        <v>160</v>
+      </c>
+      <c r="B26" s="3" t="s">
+        <v>374</v>
+      </c>
+      <c r="C26" s="3" t="s">
+        <v>212</v>
+      </c>
+      <c r="D26" s="3" t="s">
+        <v>213</v>
+      </c>
+      <c r="E26" s="3" t="s">
+        <v>204</v>
+      </c>
+      <c r="F26" s="3" t="s">
+        <v>205</v>
+      </c>
+      <c r="G26" s="3" t="s">
+        <v>206</v>
+      </c>
+      <c r="H26" s="3" t="s">
+        <v>85</v>
+      </c>
+      <c r="I26" s="3" t="s">
+        <v>207</v>
+      </c>
+      <c r="J26" s="3" t="s">
+        <v>208</v>
+      </c>
+      <c r="K26" s="3" t="s">
+        <v>209</v>
+      </c>
+      <c r="L26" s="3" t="s">
+        <v>208</v>
+      </c>
+      <c r="M26" s="3" t="s">
+        <v>209</v>
+      </c>
+      <c r="N26" s="3" t="s">
+        <v>208</v>
+      </c>
+      <c r="O26" s="3" t="s">
+        <v>210</v>
+      </c>
+      <c r="P26" s="3" t="s">
+        <v>208</v>
+      </c>
+      <c r="Q26" s="3" t="s">
+        <v>211</v>
+      </c>
+    </row>
+    <row r="27" spans="1:17" ht="45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A27" s="3" t="s">
+        <v>163</v>
+      </c>
+      <c r="B27" s="3" t="s">
+        <v>375</v>
+      </c>
+      <c r="C27" s="3" t="s">
+        <v>212</v>
+      </c>
+      <c r="D27" s="3" t="s">
+        <v>213</v>
+      </c>
+      <c r="E27" s="3" t="s">
+        <v>204</v>
+      </c>
+      <c r="F27" s="3" t="s">
+        <v>205</v>
+      </c>
+      <c r="G27" s="3" t="s">
+        <v>206</v>
+      </c>
+      <c r="H27" s="3" t="s">
+        <v>85</v>
+      </c>
+      <c r="I27" s="3" t="s">
+        <v>207</v>
+      </c>
+      <c r="J27" s="3" t="s">
+        <v>208</v>
+      </c>
+      <c r="K27" s="3" t="s">
+        <v>209</v>
+      </c>
+      <c r="L27" s="3" t="s">
+        <v>208</v>
+      </c>
+      <c r="M27" s="3" t="s">
+        <v>209</v>
+      </c>
+      <c r="N27" s="3" t="s">
+        <v>208</v>
+      </c>
+      <c r="O27" s="3" t="s">
+        <v>210</v>
+      </c>
+      <c r="P27" s="3" t="s">
+        <v>208</v>
+      </c>
+      <c r="Q27" s="3" t="s">
+        <v>211</v>
       </c>
     </row>
   </sheetData>
   <dataValidations count="3">
-    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="E4:E201">
+    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="E4:E201" xr:uid="{00000000-0002-0000-0600-000000000000}">
       <formula1>Hidden_1_Tabla_5663954</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="I4:I201">
+    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="I4:I201" xr:uid="{00000000-0002-0000-0600-000001000000}">
       <formula1>Hidden_2_Tabla_5663958</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="P4:P201">
+    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="P4:P201" xr:uid="{00000000-0002-0000-0600-000002000000}">
       <formula1>Hidden_3_Tabla_56639515</formula1>
     </dataValidation>
   </dataValidations>
@@ -6512,138 +8692,138 @@
 </file>
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0700-000000000000}">
   <dimension ref="A1:A26"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
     <row r="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
-        <v>232</v>
+        <v>255</v>
       </c>
     </row>
     <row r="2" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>226</v>
+        <v>249</v>
       </c>
     </row>
     <row r="3" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>225</v>
+        <v>248</v>
       </c>
     </row>
     <row r="4" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>216</v>
+        <v>239</v>
       </c>
     </row>
     <row r="5" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>219</v>
+        <v>242</v>
       </c>
     </row>
     <row r="6" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>217</v>
+        <v>240</v>
       </c>
     </row>
     <row r="7" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>193</v>
+        <v>204</v>
       </c>
     </row>
     <row r="8" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>215</v>
+        <v>238</v>
       </c>
     </row>
     <row r="9" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>220</v>
+        <v>243</v>
       </c>
     </row>
     <row r="10" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>222</v>
+        <v>245</v>
       </c>
     </row>
     <row r="11" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>237</v>
+        <v>260</v>
       </c>
     </row>
     <row r="12" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>224</v>
+        <v>247</v>
       </c>
     </row>
     <row r="13" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>341</v>
+        <v>376</v>
       </c>
     </row>
     <row r="14" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>258</v>
+        <v>281</v>
       </c>
     </row>
     <row r="15" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>234</v>
+        <v>257</v>
       </c>
     </row>
     <row r="16" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>229</v>
+        <v>252</v>
       </c>
     </row>
     <row r="17" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>236</v>
+        <v>259</v>
       </c>
     </row>
     <row r="18" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>235</v>
+        <v>258</v>
       </c>
     </row>
     <row r="19" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>221</v>
+        <v>244</v>
       </c>
     </row>
     <row r="20" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>231</v>
+        <v>254</v>
       </c>
     </row>
     <row r="21" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>230</v>
+        <v>253</v>
       </c>
     </row>
     <row r="22" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
-        <v>218</v>
+        <v>241</v>
       </c>
     </row>
     <row r="23" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
-        <v>342</v>
+        <v>377</v>
       </c>
     </row>
     <row r="24" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
-        <v>227</v>
+        <v>250</v>
       </c>
     </row>
     <row r="25" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
-        <v>228</v>
+        <v>251</v>
       </c>
     </row>
     <row r="26" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
-        <v>223</v>
+        <v>246</v>
       </c>
     </row>
   </sheetData>
@@ -6652,213 +8832,213 @@
 </file>
 
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0800-000000000000}">
   <dimension ref="A1:A41"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
     <row r="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
-        <v>238</v>
+        <v>261</v>
       </c>
     </row>
     <row r="2" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>230</v>
+        <v>253</v>
       </c>
     </row>
     <row r="3" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>239</v>
+        <v>262</v>
       </c>
     </row>
     <row r="4" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>240</v>
+        <v>263</v>
       </c>
     </row>
     <row r="5" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>241</v>
+        <v>264</v>
       </c>
     </row>
     <row r="6" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>242</v>
+        <v>265</v>
       </c>
     </row>
     <row r="7" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>196</v>
+        <v>207</v>
       </c>
     </row>
     <row r="8" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>243</v>
+        <v>266</v>
       </c>
     </row>
     <row r="9" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>244</v>
+        <v>267</v>
       </c>
     </row>
     <row r="10" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>245</v>
+        <v>268</v>
       </c>
     </row>
     <row r="11" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>246</v>
+        <v>269</v>
       </c>
     </row>
     <row r="12" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>247</v>
+        <v>270</v>
       </c>
     </row>
     <row r="13" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>248</v>
+        <v>271</v>
       </c>
     </row>
     <row r="14" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>249</v>
+        <v>272</v>
       </c>
     </row>
     <row r="15" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>250</v>
+        <v>273</v>
       </c>
     </row>
     <row r="16" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>251</v>
+        <v>274</v>
       </c>
     </row>
     <row r="17" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>252</v>
+        <v>275</v>
       </c>
     </row>
     <row r="18" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>253</v>
+        <v>276</v>
       </c>
     </row>
     <row r="19" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>254</v>
+        <v>277</v>
       </c>
     </row>
     <row r="20" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>255</v>
+        <v>278</v>
       </c>
     </row>
     <row r="21" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>256</v>
+        <v>279</v>
       </c>
     </row>
     <row r="22" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
-        <v>257</v>
+        <v>280</v>
       </c>
     </row>
     <row r="23" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
-        <v>226</v>
+        <v>249</v>
       </c>
     </row>
     <row r="24" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
-        <v>258</v>
+        <v>281</v>
       </c>
     </row>
     <row r="25" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
-        <v>259</v>
+        <v>282</v>
       </c>
     </row>
     <row r="26" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
-        <v>260</v>
+        <v>283</v>
       </c>
     </row>
     <row r="27" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
-        <v>261</v>
+        <v>284</v>
       </c>
     </row>
     <row r="28" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
-        <v>262</v>
+        <v>285</v>
       </c>
     </row>
     <row r="29" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
-        <v>263</v>
+        <v>286</v>
       </c>
     </row>
     <row r="30" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
-        <v>264</v>
+        <v>287</v>
       </c>
     </row>
     <row r="31" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
-        <v>265</v>
+        <v>288</v>
       </c>
     </row>
     <row r="32" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
-        <v>266</v>
+        <v>289</v>
       </c>
     </row>
     <row r="33" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
-        <v>267</v>
+        <v>290</v>
       </c>
     </row>
     <row r="34" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
-        <v>268</v>
+        <v>291</v>
       </c>
     </row>
     <row r="35" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
-        <v>269</v>
+        <v>292</v>
       </c>
     </row>
     <row r="36" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
-        <v>270</v>
+        <v>293</v>
       </c>
     </row>
     <row r="37" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
-        <v>271</v>
+        <v>294</v>
       </c>
     </row>
     <row r="38" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
-        <v>272</v>
+        <v>295</v>
       </c>
     </row>
     <row r="39" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
-        <v>273</v>
+        <v>296</v>
       </c>
     </row>
     <row r="40" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
-        <v>274</v>
+        <v>297</v>
       </c>
     </row>
     <row r="41" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
-        <v>275</v>
+        <v>298</v>
       </c>
     </row>
   </sheetData>

--- a/assets/archivos/TRANSPARENCIA/ART 63 COMUNES 2024/2DO_TRIMESTRE/FRACCIONES XI-XX/FRACC XIX/LTAIPT_A63F19.xlsx
+++ b/assets/archivos/TRANSPARENCIA/ART 63 COMUNES 2024/2DO_TRIMESTRE/FRACCIONES XI-XX/FRACC XIX/LTAIPT_A63F19.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\COBAT\Downloads\SEGUNDO TRIMESTRE ABRIL-JUNIO 2024\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\COBAT\Downloads\TERCER TRIMESTRE JULIO-SEPTIEMBRE 2024\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{124F38E8-C8BB-49A6-BAF6-775D3259B3F8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D8A1294A-C7E2-41AC-9126-FFEB9CED9CA4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -45,7 +45,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2059" uniqueCount="435">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2059" uniqueCount="433">
   <si>
     <t>48968</t>
   </si>
@@ -458,85 +458,79 @@
     <t>16344187</t>
   </si>
   <si>
+    <t>C4099C76E9256B1152F32574883581E9</t>
+  </si>
+  <si>
+    <t>01/07/2024</t>
+  </si>
+  <si>
+    <t>30/09/2024</t>
+  </si>
+  <si>
     <t>15986461</t>
   </si>
   <si>
     <t>150</t>
   </si>
   <si>
+    <t>11/10/2024</t>
+  </si>
+  <si>
+    <t>Durante el periodo del 01 de Julio de 2024 al 30 de Septiembre de 2024, el Colegio de Bachilleres del Estado de Tlaxcala no publica información inherente al Plazo con el que cuenta el sujeto obligado para prevenir al solicitante y Plazo con el que cuenta el solicitante para cumplir con la prevención según Artículo 46 Fracción XI de la Ley General de Mejora Regulatoria</t>
+  </si>
+  <si>
+    <t>0386FF8E94B5A56CFF5945B54BC294AA</t>
+  </si>
+  <si>
     <t>15986464</t>
   </si>
   <si>
+    <t>553E5225B50001A6476C5F86644B00F6</t>
+  </si>
+  <si>
     <t>15986463</t>
   </si>
   <si>
     <t>614</t>
   </si>
   <si>
+    <t>AA56E93493F4B0B820B9C8336F290DDC</t>
+  </si>
+  <si>
     <t>15986462</t>
   </si>
   <si>
+    <t>B57EE337ABDC76EA1FA8FAF5F04CB0CA</t>
+  </si>
+  <si>
     <t>15986459</t>
   </si>
   <si>
     <t>103</t>
   </si>
   <si>
+    <t>460E8BAA12631CCCCFB0647A6F1906AE</t>
+  </si>
+  <si>
     <t>15986460</t>
   </si>
   <si>
     <t>94</t>
   </si>
   <si>
-    <t>81AF4ED8525E9393A103B52E382C1119</t>
-  </si>
-  <si>
-    <t>01/04/2024</t>
-  </si>
-  <si>
-    <t>30/06/2024</t>
-  </si>
-  <si>
-    <t>http://cobatlaxcala.edu.mx/transparencia/TRANSPARENCIA%202022/Subdireccion%20Servicios%20Educativos/1er_Trimestre/EXAMEN%20A%20TITULO%20DE%20SUFICIENCIA.pdf</t>
-  </si>
-  <si>
     <t>14416370</t>
   </si>
   <si>
-    <t>02/07/2024</t>
-  </si>
-  <si>
-    <t>Durante el periodo del 01 de abril de 2024 al 30 de junio de 2024, el Colegio de Bachilleres del Estado de Tlaxcala no publica información inherente al Plazo con el que cuenta el sujeto obligado para prevenir al solicitante y Plazo con el que cuenta el solicitante para cumplir con la prevención según Artículo 46 Fracción XI de la Ley General de Mejora Regulatoria</t>
-  </si>
-  <si>
-    <t>B09A1972064FCFDD6EE5CB531980423B</t>
-  </si>
-  <si>
     <t>14416372</t>
   </si>
   <si>
-    <t>D5E5D9C1AD1A635E69F69438AE55401A</t>
-  </si>
-  <si>
     <t>14416374</t>
   </si>
   <si>
-    <t>1D47F265AA47ACF3D2FE71466056DAF4</t>
-  </si>
-  <si>
     <t>14416375</t>
   </si>
   <si>
-    <t>FF004168F8109C0A7CBE5B22990D4803</t>
-  </si>
-  <si>
     <t>14416373</t>
-  </si>
-  <si>
-    <t>CEADEB250E8C69217A8F3CE105813CBB</t>
-  </si>
-  <si>
-    <t>http://cobatlaxcala.edu.mx/transparencia/TRANSPARENCIA%202022/Subdireccion%20Servicios%20Educativos/1er_Trimestre/EXAMEN%20EXTRAORDINARIO.pdf</t>
   </si>
   <si>
     <t>14416371</t>
@@ -2157,28 +2151,28 @@
     </row>
     <row r="8" spans="1:32" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="3" t="s">
-        <v>146</v>
+        <v>136</v>
       </c>
       <c r="B8" s="3" t="s">
         <v>77</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>147</v>
+        <v>137</v>
       </c>
       <c r="D8" s="3" t="s">
-        <v>148</v>
+        <v>138</v>
       </c>
       <c r="E8" s="3" t="s">
-        <v>127</v>
+        <v>78</v>
       </c>
       <c r="F8" s="3" t="s">
         <v>79</v>
       </c>
       <c r="G8" s="3" t="s">
-        <v>106</v>
+        <v>80</v>
       </c>
       <c r="H8" s="3" t="s">
-        <v>128</v>
+        <v>81</v>
       </c>
       <c r="I8" s="3" t="s">
         <v>82</v>
@@ -2187,16 +2181,16 @@
         <v>83</v>
       </c>
       <c r="K8" s="3" t="s">
-        <v>121</v>
+        <v>84</v>
       </c>
       <c r="L8" s="3" t="s">
-        <v>149</v>
+        <v>85</v>
       </c>
       <c r="M8" s="3" t="s">
-        <v>116</v>
+        <v>85</v>
       </c>
       <c r="N8" s="3" t="s">
-        <v>122</v>
+        <v>86</v>
       </c>
       <c r="O8" s="3" t="s">
         <v>85</v>
@@ -2208,13 +2202,13 @@
         <v>87</v>
       </c>
       <c r="R8" s="3" t="s">
-        <v>150</v>
+        <v>139</v>
       </c>
       <c r="S8" s="3" t="s">
-        <v>124</v>
+        <v>89</v>
       </c>
       <c r="T8" s="3" t="s">
-        <v>143</v>
+        <v>140</v>
       </c>
       <c r="U8" s="3" t="s">
         <v>90</v>
@@ -2223,22 +2217,22 @@
         <v>91</v>
       </c>
       <c r="W8" s="3" t="s">
-        <v>125</v>
+        <v>92</v>
       </c>
       <c r="X8" s="3" t="s">
         <v>93</v>
       </c>
       <c r="Y8" s="3" t="s">
-        <v>126</v>
+        <v>94</v>
       </c>
       <c r="Z8" s="3" t="s">
         <v>85</v>
       </c>
       <c r="AA8" s="3" t="s">
-        <v>150</v>
+        <v>139</v>
       </c>
       <c r="AB8" s="3" t="s">
-        <v>150</v>
+        <v>139</v>
       </c>
       <c r="AC8" s="3" t="s">
         <v>95</v>
@@ -2247,36 +2241,36 @@
         <v>96</v>
       </c>
       <c r="AE8" s="3" t="s">
-        <v>151</v>
+        <v>141</v>
       </c>
       <c r="AF8" s="3" t="s">
-        <v>152</v>
+        <v>142</v>
       </c>
     </row>
     <row r="9" spans="1:32" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="3" t="s">
-        <v>153</v>
+        <v>143</v>
       </c>
       <c r="B9" s="3" t="s">
         <v>77</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>147</v>
+        <v>137</v>
       </c>
       <c r="D9" s="3" t="s">
-        <v>148</v>
+        <v>138</v>
       </c>
       <c r="E9" s="3" t="s">
-        <v>78</v>
+        <v>105</v>
       </c>
       <c r="F9" s="3" t="s">
         <v>79</v>
       </c>
       <c r="G9" s="3" t="s">
-        <v>80</v>
+        <v>106</v>
       </c>
       <c r="H9" s="3" t="s">
-        <v>81</v>
+        <v>107</v>
       </c>
       <c r="I9" s="3" t="s">
         <v>82</v>
@@ -2285,7 +2279,7 @@
         <v>83</v>
       </c>
       <c r="K9" s="3" t="s">
-        <v>84</v>
+        <v>108</v>
       </c>
       <c r="L9" s="3" t="s">
         <v>85</v>
@@ -2303,16 +2297,16 @@
         <v>85</v>
       </c>
       <c r="Q9" s="3" t="s">
-        <v>87</v>
+        <v>101</v>
       </c>
       <c r="R9" s="3" t="s">
-        <v>154</v>
+        <v>144</v>
       </c>
       <c r="S9" s="3" t="s">
         <v>89</v>
       </c>
       <c r="T9" s="3" t="s">
-        <v>137</v>
+        <v>140</v>
       </c>
       <c r="U9" s="3" t="s">
         <v>90</v>
@@ -2321,22 +2315,22 @@
         <v>91</v>
       </c>
       <c r="W9" s="3" t="s">
-        <v>92</v>
+        <v>110</v>
       </c>
       <c r="X9" s="3" t="s">
         <v>93</v>
       </c>
       <c r="Y9" s="3" t="s">
-        <v>94</v>
+        <v>108</v>
       </c>
       <c r="Z9" s="3" t="s">
         <v>85</v>
       </c>
       <c r="AA9" s="3" t="s">
-        <v>154</v>
+        <v>144</v>
       </c>
       <c r="AB9" s="3" t="s">
-        <v>154</v>
+        <v>144</v>
       </c>
       <c r="AC9" s="3" t="s">
         <v>95</v>
@@ -2345,24 +2339,24 @@
         <v>96</v>
       </c>
       <c r="AE9" s="3" t="s">
-        <v>151</v>
+        <v>141</v>
       </c>
       <c r="AF9" s="3" t="s">
-        <v>152</v>
+        <v>142</v>
       </c>
     </row>
     <row r="10" spans="1:32" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="3" t="s">
-        <v>155</v>
+        <v>145</v>
       </c>
       <c r="B10" s="3" t="s">
         <v>77</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>147</v>
+        <v>137</v>
       </c>
       <c r="D10" s="3" t="s">
-        <v>148</v>
+        <v>138</v>
       </c>
       <c r="E10" s="3" t="s">
         <v>111</v>
@@ -2404,13 +2398,13 @@
         <v>101</v>
       </c>
       <c r="R10" s="3" t="s">
-        <v>156</v>
+        <v>146</v>
       </c>
       <c r="S10" s="3" t="s">
         <v>89</v>
       </c>
       <c r="T10" s="3" t="s">
-        <v>140</v>
+        <v>147</v>
       </c>
       <c r="U10" s="3" t="s">
         <v>90</v>
@@ -2431,10 +2425,10 @@
         <v>85</v>
       </c>
       <c r="AA10" s="3" t="s">
-        <v>156</v>
+        <v>146</v>
       </c>
       <c r="AB10" s="3" t="s">
-        <v>156</v>
+        <v>146</v>
       </c>
       <c r="AC10" s="3" t="s">
         <v>95</v>
@@ -2443,36 +2437,36 @@
         <v>96</v>
       </c>
       <c r="AE10" s="3" t="s">
-        <v>151</v>
+        <v>141</v>
       </c>
       <c r="AF10" s="3" t="s">
-        <v>152</v>
+        <v>142</v>
       </c>
     </row>
     <row r="11" spans="1:32" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="3" t="s">
-        <v>157</v>
+        <v>148</v>
       </c>
       <c r="B11" s="3" t="s">
         <v>77</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>147</v>
+        <v>137</v>
       </c>
       <c r="D11" s="3" t="s">
-        <v>148</v>
+        <v>138</v>
       </c>
       <c r="E11" s="3" t="s">
-        <v>105</v>
+        <v>97</v>
       </c>
       <c r="F11" s="3" t="s">
-        <v>79</v>
+        <v>85</v>
       </c>
       <c r="G11" s="3" t="s">
-        <v>106</v>
+        <v>98</v>
       </c>
       <c r="H11" s="3" t="s">
-        <v>107</v>
+        <v>99</v>
       </c>
       <c r="I11" s="3" t="s">
         <v>82</v>
@@ -2481,7 +2475,7 @@
         <v>83</v>
       </c>
       <c r="K11" s="3" t="s">
-        <v>108</v>
+        <v>100</v>
       </c>
       <c r="L11" s="3" t="s">
         <v>85</v>
@@ -2502,13 +2496,13 @@
         <v>101</v>
       </c>
       <c r="R11" s="3" t="s">
-        <v>158</v>
+        <v>149</v>
       </c>
       <c r="S11" s="3" t="s">
         <v>89</v>
       </c>
       <c r="T11" s="3" t="s">
-        <v>137</v>
+        <v>147</v>
       </c>
       <c r="U11" s="3" t="s">
         <v>90</v>
@@ -2517,22 +2511,22 @@
         <v>91</v>
       </c>
       <c r="W11" s="3" t="s">
-        <v>110</v>
+        <v>103</v>
       </c>
       <c r="X11" s="3" t="s">
         <v>93</v>
       </c>
       <c r="Y11" s="3" t="s">
-        <v>108</v>
+        <v>104</v>
       </c>
       <c r="Z11" s="3" t="s">
         <v>85</v>
       </c>
       <c r="AA11" s="3" t="s">
-        <v>158</v>
+        <v>149</v>
       </c>
       <c r="AB11" s="3" t="s">
-        <v>158</v>
+        <v>149</v>
       </c>
       <c r="AC11" s="3" t="s">
         <v>95</v>
@@ -2541,36 +2535,36 @@
         <v>96</v>
       </c>
       <c r="AE11" s="3" t="s">
-        <v>151</v>
+        <v>141</v>
       </c>
       <c r="AF11" s="3" t="s">
-        <v>152</v>
+        <v>142</v>
       </c>
     </row>
     <row r="12" spans="1:32" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="3" t="s">
-        <v>159</v>
+        <v>150</v>
       </c>
       <c r="B12" s="3" t="s">
         <v>77</v>
       </c>
       <c r="C12" s="3" t="s">
-        <v>147</v>
+        <v>137</v>
       </c>
       <c r="D12" s="3" t="s">
-        <v>148</v>
+        <v>138</v>
       </c>
       <c r="E12" s="3" t="s">
-        <v>97</v>
+        <v>127</v>
       </c>
       <c r="F12" s="3" t="s">
         <v>79</v>
       </c>
       <c r="G12" s="3" t="s">
-        <v>98</v>
+        <v>106</v>
       </c>
       <c r="H12" s="3" t="s">
-        <v>99</v>
+        <v>128</v>
       </c>
       <c r="I12" s="3" t="s">
         <v>82</v>
@@ -2579,16 +2573,16 @@
         <v>83</v>
       </c>
       <c r="K12" s="3" t="s">
-        <v>100</v>
+        <v>121</v>
       </c>
       <c r="L12" s="3" t="s">
-        <v>85</v>
+        <v>115</v>
       </c>
       <c r="M12" s="3" t="s">
-        <v>85</v>
+        <v>116</v>
       </c>
       <c r="N12" s="3" t="s">
-        <v>86</v>
+        <v>122</v>
       </c>
       <c r="O12" s="3" t="s">
         <v>85</v>
@@ -2597,16 +2591,16 @@
         <v>85</v>
       </c>
       <c r="Q12" s="3" t="s">
-        <v>101</v>
+        <v>87</v>
       </c>
       <c r="R12" s="3" t="s">
-        <v>160</v>
+        <v>151</v>
       </c>
       <c r="S12" s="3" t="s">
-        <v>89</v>
+        <v>124</v>
       </c>
       <c r="T12" s="3" t="s">
-        <v>140</v>
+        <v>152</v>
       </c>
       <c r="U12" s="3" t="s">
         <v>90</v>
@@ -2615,22 +2609,22 @@
         <v>91</v>
       </c>
       <c r="W12" s="3" t="s">
-        <v>103</v>
+        <v>125</v>
       </c>
       <c r="X12" s="3" t="s">
         <v>93</v>
       </c>
       <c r="Y12" s="3" t="s">
-        <v>104</v>
+        <v>126</v>
       </c>
       <c r="Z12" s="3" t="s">
         <v>85</v>
       </c>
       <c r="AA12" s="3" t="s">
-        <v>160</v>
+        <v>151</v>
       </c>
       <c r="AB12" s="3" t="s">
-        <v>160</v>
+        <v>151</v>
       </c>
       <c r="AC12" s="3" t="s">
         <v>95</v>
@@ -2639,24 +2633,24 @@
         <v>96</v>
       </c>
       <c r="AE12" s="3" t="s">
-        <v>151</v>
+        <v>141</v>
       </c>
       <c r="AF12" s="3" t="s">
-        <v>152</v>
+        <v>142</v>
       </c>
     </row>
     <row r="13" spans="1:32" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="3" t="s">
-        <v>161</v>
+        <v>153</v>
       </c>
       <c r="B13" s="3" t="s">
         <v>77</v>
       </c>
       <c r="C13" s="3" t="s">
-        <v>147</v>
+        <v>137</v>
       </c>
       <c r="D13" s="3" t="s">
-        <v>148</v>
+        <v>138</v>
       </c>
       <c r="E13" s="3" t="s">
         <v>119</v>
@@ -2680,7 +2674,7 @@
         <v>121</v>
       </c>
       <c r="L13" s="3" t="s">
-        <v>162</v>
+        <v>115</v>
       </c>
       <c r="M13" s="3" t="s">
         <v>116</v>
@@ -2698,13 +2692,13 @@
         <v>87</v>
       </c>
       <c r="R13" s="3" t="s">
-        <v>163</v>
+        <v>154</v>
       </c>
       <c r="S13" s="3" t="s">
         <v>124</v>
       </c>
       <c r="T13" s="3" t="s">
-        <v>145</v>
+        <v>155</v>
       </c>
       <c r="U13" s="3" t="s">
         <v>90</v>
@@ -2725,10 +2719,10 @@
         <v>85</v>
       </c>
       <c r="AA13" s="3" t="s">
-        <v>163</v>
+        <v>154</v>
       </c>
       <c r="AB13" s="3" t="s">
-        <v>163</v>
+        <v>154</v>
       </c>
       <c r="AC13" s="3" t="s">
         <v>95</v>
@@ -2737,10 +2731,10 @@
         <v>96</v>
       </c>
       <c r="AE13" s="3" t="s">
-        <v>151</v>
+        <v>141</v>
       </c>
       <c r="AF13" s="3" t="s">
-        <v>152</v>
+        <v>142</v>
       </c>
     </row>
   </sheetData>
@@ -2769,162 +2763,162 @@
   <sheetData>
     <row r="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
-        <v>378</v>
+        <v>376</v>
       </c>
     </row>
     <row r="2" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>325</v>
+        <v>323</v>
       </c>
     </row>
     <row r="3" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>326</v>
+        <v>324</v>
       </c>
     </row>
     <row r="4" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>299</v>
+        <v>297</v>
       </c>
     </row>
     <row r="5" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>323</v>
+        <v>321</v>
       </c>
     </row>
     <row r="6" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>300</v>
+        <v>298</v>
       </c>
     </row>
     <row r="7" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>301</v>
+        <v>299</v>
       </c>
     </row>
     <row r="8" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>302</v>
+        <v>300</v>
       </c>
     </row>
     <row r="9" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>318</v>
+        <v>316</v>
       </c>
     </row>
     <row r="10" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>379</v>
+        <v>377</v>
       </c>
     </row>
     <row r="11" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>307</v>
+        <v>305</v>
       </c>
     </row>
     <row r="12" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>320</v>
+        <v>318</v>
       </c>
     </row>
     <row r="13" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>310</v>
+        <v>308</v>
       </c>
     </row>
     <row r="14" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>315</v>
+        <v>313</v>
       </c>
     </row>
     <row r="15" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>304</v>
+        <v>302</v>
       </c>
     </row>
     <row r="16" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>311</v>
+        <v>309</v>
       </c>
     </row>
     <row r="17" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>322</v>
+        <v>320</v>
       </c>
     </row>
     <row r="18" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>317</v>
+        <v>315</v>
       </c>
     </row>
     <row r="19" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>208</v>
+        <v>206</v>
       </c>
     </row>
     <row r="20" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>309</v>
+        <v>307</v>
       </c>
     </row>
     <row r="21" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>312</v>
+        <v>310</v>
       </c>
     </row>
     <row r="22" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
-        <v>313</v>
+        <v>311</v>
       </c>
     </row>
     <row r="23" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
-        <v>327</v>
+        <v>325</v>
       </c>
     </row>
     <row r="24" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
-        <v>306</v>
+        <v>304</v>
       </c>
     </row>
     <row r="25" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
-        <v>305</v>
+        <v>303</v>
       </c>
     </row>
     <row r="26" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
-        <v>303</v>
+        <v>301</v>
       </c>
     </row>
     <row r="27" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
-        <v>329</v>
+        <v>327</v>
       </c>
     </row>
     <row r="28" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
-        <v>314</v>
+        <v>312</v>
       </c>
     </row>
     <row r="29" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
-        <v>308</v>
+        <v>306</v>
       </c>
     </row>
     <row r="30" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
-        <v>380</v>
+        <v>378</v>
       </c>
     </row>
     <row r="31" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
-        <v>321</v>
+        <v>319</v>
       </c>
     </row>
     <row r="32" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
-        <v>316</v>
+        <v>314</v>
       </c>
     </row>
   </sheetData>
@@ -3009,106 +3003,106 @@
     </row>
     <row r="2" spans="1:18" hidden="1" x14ac:dyDescent="0.25">
       <c r="C2" t="s">
+        <v>379</v>
+      </c>
+      <c r="D2" t="s">
+        <v>380</v>
+      </c>
+      <c r="E2" t="s">
         <v>381</v>
       </c>
-      <c r="D2" t="s">
+      <c r="F2" t="s">
         <v>382</v>
       </c>
-      <c r="E2" t="s">
+      <c r="G2" t="s">
         <v>383</v>
       </c>
-      <c r="F2" t="s">
+      <c r="H2" t="s">
         <v>384</v>
       </c>
-      <c r="G2" t="s">
+      <c r="I2" t="s">
         <v>385</v>
       </c>
-      <c r="H2" t="s">
+      <c r="J2" t="s">
         <v>386</v>
       </c>
-      <c r="I2" t="s">
+      <c r="K2" t="s">
         <v>387</v>
       </c>
-      <c r="J2" t="s">
+      <c r="L2" t="s">
         <v>388</v>
       </c>
-      <c r="K2" t="s">
+      <c r="M2" t="s">
         <v>389</v>
       </c>
-      <c r="L2" t="s">
+      <c r="N2" t="s">
         <v>390</v>
       </c>
-      <c r="M2" t="s">
+      <c r="O2" t="s">
         <v>391</v>
       </c>
-      <c r="N2" t="s">
+      <c r="P2" t="s">
         <v>392</v>
       </c>
-      <c r="O2" t="s">
+      <c r="Q2" t="s">
         <v>393</v>
       </c>
-      <c r="P2" t="s">
+      <c r="R2" t="s">
         <v>394</v>
-      </c>
-      <c r="Q2" t="s">
-        <v>395</v>
-      </c>
-      <c r="R2" t="s">
-        <v>396</v>
       </c>
     </row>
     <row r="3" spans="1:18" ht="30" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
       <c r="B3" s="1"/>
       <c r="C3" s="1" t="s">
+        <v>395</v>
+      </c>
+      <c r="D3" s="1" t="s">
+        <v>344</v>
+      </c>
+      <c r="E3" s="1" t="s">
+        <v>396</v>
+      </c>
+      <c r="F3" s="1" t="s">
+        <v>346</v>
+      </c>
+      <c r="G3" s="1" t="s">
+        <v>185</v>
+      </c>
+      <c r="H3" s="1" t="s">
+        <v>186</v>
+      </c>
+      <c r="I3" s="1" t="s">
         <v>397</v>
       </c>
-      <c r="D3" s="1" t="s">
-        <v>346</v>
-      </c>
-      <c r="E3" s="1" t="s">
+      <c r="J3" s="1" t="s">
         <v>398</v>
       </c>
-      <c r="F3" s="1" t="s">
-        <v>348</v>
-      </c>
-      <c r="G3" s="1" t="s">
-        <v>187</v>
-      </c>
-      <c r="H3" s="1" t="s">
-        <v>188</v>
-      </c>
-      <c r="I3" s="1" t="s">
+      <c r="K3" s="1" t="s">
+        <v>349</v>
+      </c>
+      <c r="L3" s="1" t="s">
+        <v>190</v>
+      </c>
+      <c r="M3" s="1" t="s">
+        <v>191</v>
+      </c>
+      <c r="N3" s="1" t="s">
         <v>399</v>
       </c>
-      <c r="J3" s="1" t="s">
+      <c r="O3" s="1" t="s">
         <v>400</v>
       </c>
-      <c r="K3" s="1" t="s">
-        <v>351</v>
-      </c>
-      <c r="L3" s="1" t="s">
-        <v>192</v>
-      </c>
-      <c r="M3" s="1" t="s">
-        <v>193</v>
-      </c>
-      <c r="N3" s="1" t="s">
+      <c r="P3" s="1" t="s">
         <v>401</v>
       </c>
-      <c r="O3" s="1" t="s">
+      <c r="Q3" s="1" t="s">
         <v>402</v>
       </c>
-      <c r="P3" s="1" t="s">
-        <v>403</v>
-      </c>
-      <c r="Q3" s="1" t="s">
-        <v>404</v>
-      </c>
       <c r="R3" s="1" t="s">
-        <v>198</v>
+        <v>196</v>
       </c>
     </row>
     <row r="4" spans="1:18" ht="45" customHeight="1" x14ac:dyDescent="0.25">
@@ -3116,52 +3110,52 @@
         <v>88</v>
       </c>
       <c r="B4" s="3" t="s">
+        <v>403</v>
+      </c>
+      <c r="C4" s="3" t="s">
+        <v>404</v>
+      </c>
+      <c r="D4" s="3" t="s">
         <v>405</v>
       </c>
-      <c r="C4" s="3" t="s">
+      <c r="E4" s="3" t="s">
+        <v>202</v>
+      </c>
+      <c r="F4" s="3" t="s">
         <v>406</v>
       </c>
-      <c r="D4" s="3" t="s">
+      <c r="G4" s="3" t="s">
         <v>407</v>
       </c>
-      <c r="E4" s="3" t="s">
-        <v>204</v>
-      </c>
-      <c r="F4" s="3" t="s">
+      <c r="H4" s="3" t="s">
+        <v>85</v>
+      </c>
+      <c r="I4" s="3" t="s">
+        <v>205</v>
+      </c>
+      <c r="J4" s="3" t="s">
         <v>408</v>
       </c>
-      <c r="G4" s="3" t="s">
+      <c r="K4" s="3" t="s">
         <v>409</v>
       </c>
-      <c r="H4" s="3" t="s">
-        <v>85</v>
-      </c>
-      <c r="I4" s="3" t="s">
-        <v>207</v>
-      </c>
-      <c r="J4" s="3" t="s">
-        <v>410</v>
-      </c>
-      <c r="K4" s="3" t="s">
-        <v>411</v>
-      </c>
       <c r="L4" s="3" t="s">
-        <v>410</v>
+        <v>408</v>
       </c>
       <c r="M4" s="3" t="s">
-        <v>411</v>
+        <v>409</v>
       </c>
       <c r="N4" s="3" t="s">
-        <v>410</v>
+        <v>408</v>
       </c>
       <c r="O4" s="3" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="P4" s="3" t="s">
-        <v>208</v>
+        <v>206</v>
       </c>
       <c r="Q4" s="3" t="s">
-        <v>211</v>
+        <v>209</v>
       </c>
       <c r="R4" s="3" t="s">
         <v>85</v>
@@ -3172,52 +3166,52 @@
         <v>102</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>412</v>
+        <v>410</v>
       </c>
       <c r="C5" s="3" t="s">
+        <v>404</v>
+      </c>
+      <c r="D5" s="3" t="s">
+        <v>405</v>
+      </c>
+      <c r="E5" s="3" t="s">
+        <v>202</v>
+      </c>
+      <c r="F5" s="3" t="s">
         <v>406</v>
       </c>
-      <c r="D5" s="3" t="s">
+      <c r="G5" s="3" t="s">
         <v>407</v>
       </c>
-      <c r="E5" s="3" t="s">
-        <v>204</v>
-      </c>
-      <c r="F5" s="3" t="s">
+      <c r="H5" s="3" t="s">
+        <v>85</v>
+      </c>
+      <c r="I5" s="3" t="s">
+        <v>205</v>
+      </c>
+      <c r="J5" s="3" t="s">
         <v>408</v>
       </c>
-      <c r="G5" s="3" t="s">
+      <c r="K5" s="3" t="s">
         <v>409</v>
       </c>
-      <c r="H5" s="3" t="s">
-        <v>85</v>
-      </c>
-      <c r="I5" s="3" t="s">
-        <v>207</v>
-      </c>
-      <c r="J5" s="3" t="s">
-        <v>410</v>
-      </c>
-      <c r="K5" s="3" t="s">
-        <v>411</v>
-      </c>
       <c r="L5" s="3" t="s">
-        <v>410</v>
+        <v>408</v>
       </c>
       <c r="M5" s="3" t="s">
-        <v>411</v>
+        <v>409</v>
       </c>
       <c r="N5" s="3" t="s">
-        <v>410</v>
+        <v>408</v>
       </c>
       <c r="O5" s="3" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="P5" s="3" t="s">
-        <v>208</v>
+        <v>206</v>
       </c>
       <c r="Q5" s="3" t="s">
-        <v>211</v>
+        <v>209</v>
       </c>
       <c r="R5" s="3" t="s">
         <v>85</v>
@@ -3228,52 +3222,52 @@
         <v>109</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>413</v>
+        <v>411</v>
       </c>
       <c r="C6" s="3" t="s">
+        <v>404</v>
+      </c>
+      <c r="D6" s="3" t="s">
+        <v>405</v>
+      </c>
+      <c r="E6" s="3" t="s">
+        <v>202</v>
+      </c>
+      <c r="F6" s="3" t="s">
         <v>406</v>
       </c>
-      <c r="D6" s="3" t="s">
+      <c r="G6" s="3" t="s">
         <v>407</v>
       </c>
-      <c r="E6" s="3" t="s">
-        <v>204</v>
-      </c>
-      <c r="F6" s="3" t="s">
+      <c r="H6" s="3" t="s">
+        <v>85</v>
+      </c>
+      <c r="I6" s="3" t="s">
+        <v>205</v>
+      </c>
+      <c r="J6" s="3" t="s">
         <v>408</v>
       </c>
-      <c r="G6" s="3" t="s">
+      <c r="K6" s="3" t="s">
         <v>409</v>
       </c>
-      <c r="H6" s="3" t="s">
-        <v>85</v>
-      </c>
-      <c r="I6" s="3" t="s">
-        <v>207</v>
-      </c>
-      <c r="J6" s="3" t="s">
-        <v>410</v>
-      </c>
-      <c r="K6" s="3" t="s">
-        <v>411</v>
-      </c>
       <c r="L6" s="3" t="s">
-        <v>410</v>
+        <v>408</v>
       </c>
       <c r="M6" s="3" t="s">
-        <v>411</v>
+        <v>409</v>
       </c>
       <c r="N6" s="3" t="s">
-        <v>410</v>
+        <v>408</v>
       </c>
       <c r="O6" s="3" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="P6" s="3" t="s">
-        <v>208</v>
+        <v>206</v>
       </c>
       <c r="Q6" s="3" t="s">
-        <v>211</v>
+        <v>209</v>
       </c>
       <c r="R6" s="3" t="s">
         <v>85</v>
@@ -3284,52 +3278,52 @@
         <v>117</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>414</v>
+        <v>412</v>
       </c>
       <c r="C7" s="3" t="s">
+        <v>404</v>
+      </c>
+      <c r="D7" s="3" t="s">
+        <v>405</v>
+      </c>
+      <c r="E7" s="3" t="s">
+        <v>202</v>
+      </c>
+      <c r="F7" s="3" t="s">
         <v>406</v>
       </c>
-      <c r="D7" s="3" t="s">
+      <c r="G7" s="3" t="s">
         <v>407</v>
       </c>
-      <c r="E7" s="3" t="s">
-        <v>204</v>
-      </c>
-      <c r="F7" s="3" t="s">
+      <c r="H7" s="3" t="s">
+        <v>85</v>
+      </c>
+      <c r="I7" s="3" t="s">
+        <v>205</v>
+      </c>
+      <c r="J7" s="3" t="s">
         <v>408</v>
       </c>
-      <c r="G7" s="3" t="s">
+      <c r="K7" s="3" t="s">
         <v>409</v>
       </c>
-      <c r="H7" s="3" t="s">
-        <v>85</v>
-      </c>
-      <c r="I7" s="3" t="s">
-        <v>207</v>
-      </c>
-      <c r="J7" s="3" t="s">
-        <v>410</v>
-      </c>
-      <c r="K7" s="3" t="s">
-        <v>411</v>
-      </c>
       <c r="L7" s="3" t="s">
-        <v>410</v>
+        <v>408</v>
       </c>
       <c r="M7" s="3" t="s">
-        <v>411</v>
+        <v>409</v>
       </c>
       <c r="N7" s="3" t="s">
-        <v>410</v>
+        <v>408</v>
       </c>
       <c r="O7" s="3" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="P7" s="3" t="s">
-        <v>208</v>
+        <v>206</v>
       </c>
       <c r="Q7" s="3" t="s">
-        <v>211</v>
+        <v>209</v>
       </c>
       <c r="R7" s="3" t="s">
         <v>85</v>
@@ -3340,52 +3334,52 @@
         <v>123</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>415</v>
+        <v>413</v>
       </c>
       <c r="C8" s="3" t="s">
+        <v>404</v>
+      </c>
+      <c r="D8" s="3" t="s">
+        <v>405</v>
+      </c>
+      <c r="E8" s="3" t="s">
+        <v>202</v>
+      </c>
+      <c r="F8" s="3" t="s">
         <v>406</v>
       </c>
-      <c r="D8" s="3" t="s">
+      <c r="G8" s="3" t="s">
         <v>407</v>
       </c>
-      <c r="E8" s="3" t="s">
-        <v>204</v>
-      </c>
-      <c r="F8" s="3" t="s">
+      <c r="H8" s="3" t="s">
+        <v>85</v>
+      </c>
+      <c r="I8" s="3" t="s">
+        <v>205</v>
+      </c>
+      <c r="J8" s="3" t="s">
         <v>408</v>
       </c>
-      <c r="G8" s="3" t="s">
+      <c r="K8" s="3" t="s">
         <v>409</v>
       </c>
-      <c r="H8" s="3" t="s">
-        <v>85</v>
-      </c>
-      <c r="I8" s="3" t="s">
-        <v>207</v>
-      </c>
-      <c r="J8" s="3" t="s">
-        <v>410</v>
-      </c>
-      <c r="K8" s="3" t="s">
-        <v>411</v>
-      </c>
       <c r="L8" s="3" t="s">
-        <v>410</v>
+        <v>408</v>
       </c>
       <c r="M8" s="3" t="s">
-        <v>411</v>
+        <v>409</v>
       </c>
       <c r="N8" s="3" t="s">
-        <v>410</v>
+        <v>408</v>
       </c>
       <c r="O8" s="3" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="P8" s="3" t="s">
-        <v>208</v>
+        <v>206</v>
       </c>
       <c r="Q8" s="3" t="s">
-        <v>211</v>
+        <v>209</v>
       </c>
       <c r="R8" s="3" t="s">
         <v>85</v>
@@ -3396,52 +3390,52 @@
         <v>129</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>416</v>
+        <v>414</v>
       </c>
       <c r="C9" s="3" t="s">
+        <v>404</v>
+      </c>
+      <c r="D9" s="3" t="s">
+        <v>405</v>
+      </c>
+      <c r="E9" s="3" t="s">
+        <v>202</v>
+      </c>
+      <c r="F9" s="3" t="s">
         <v>406</v>
       </c>
-      <c r="D9" s="3" t="s">
+      <c r="G9" s="3" t="s">
         <v>407</v>
       </c>
-      <c r="E9" s="3" t="s">
-        <v>204</v>
-      </c>
-      <c r="F9" s="3" t="s">
+      <c r="H9" s="3" t="s">
+        <v>85</v>
+      </c>
+      <c r="I9" s="3" t="s">
+        <v>205</v>
+      </c>
+      <c r="J9" s="3" t="s">
         <v>408</v>
       </c>
-      <c r="G9" s="3" t="s">
+      <c r="K9" s="3" t="s">
         <v>409</v>
       </c>
-      <c r="H9" s="3" t="s">
-        <v>85</v>
-      </c>
-      <c r="I9" s="3" t="s">
-        <v>207</v>
-      </c>
-      <c r="J9" s="3" t="s">
-        <v>410</v>
-      </c>
-      <c r="K9" s="3" t="s">
-        <v>411</v>
-      </c>
       <c r="L9" s="3" t="s">
-        <v>410</v>
+        <v>408</v>
       </c>
       <c r="M9" s="3" t="s">
-        <v>411</v>
+        <v>409</v>
       </c>
       <c r="N9" s="3" t="s">
-        <v>410</v>
+        <v>408</v>
       </c>
       <c r="O9" s="3" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="P9" s="3" t="s">
-        <v>208</v>
+        <v>206</v>
       </c>
       <c r="Q9" s="3" t="s">
-        <v>211</v>
+        <v>209</v>
       </c>
       <c r="R9" s="3" t="s">
         <v>85</v>
@@ -3452,52 +3446,52 @@
         <v>130</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>417</v>
+        <v>415</v>
       </c>
       <c r="C10" s="3" t="s">
+        <v>404</v>
+      </c>
+      <c r="D10" s="3" t="s">
+        <v>405</v>
+      </c>
+      <c r="E10" s="3" t="s">
+        <v>202</v>
+      </c>
+      <c r="F10" s="3" t="s">
         <v>406</v>
       </c>
-      <c r="D10" s="3" t="s">
+      <c r="G10" s="3" t="s">
         <v>407</v>
       </c>
-      <c r="E10" s="3" t="s">
-        <v>204</v>
-      </c>
-      <c r="F10" s="3" t="s">
+      <c r="H10" s="3" t="s">
+        <v>85</v>
+      </c>
+      <c r="I10" s="3" t="s">
+        <v>205</v>
+      </c>
+      <c r="J10" s="3" t="s">
         <v>408</v>
       </c>
-      <c r="G10" s="3" t="s">
+      <c r="K10" s="3" t="s">
         <v>409</v>
       </c>
-      <c r="H10" s="3" t="s">
-        <v>85</v>
-      </c>
-      <c r="I10" s="3" t="s">
-        <v>207</v>
-      </c>
-      <c r="J10" s="3" t="s">
-        <v>410</v>
-      </c>
-      <c r="K10" s="3" t="s">
-        <v>411</v>
-      </c>
       <c r="L10" s="3" t="s">
-        <v>410</v>
+        <v>408</v>
       </c>
       <c r="M10" s="3" t="s">
-        <v>411</v>
+        <v>409</v>
       </c>
       <c r="N10" s="3" t="s">
-        <v>410</v>
+        <v>408</v>
       </c>
       <c r="O10" s="3" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="P10" s="3" t="s">
-        <v>208</v>
+        <v>206</v>
       </c>
       <c r="Q10" s="3" t="s">
-        <v>211</v>
+        <v>209</v>
       </c>
       <c r="R10" s="3" t="s">
         <v>85</v>
@@ -3508,52 +3502,52 @@
         <v>131</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>418</v>
+        <v>416</v>
       </c>
       <c r="C11" s="3" t="s">
+        <v>404</v>
+      </c>
+      <c r="D11" s="3" t="s">
+        <v>405</v>
+      </c>
+      <c r="E11" s="3" t="s">
+        <v>202</v>
+      </c>
+      <c r="F11" s="3" t="s">
         <v>406</v>
       </c>
-      <c r="D11" s="3" t="s">
+      <c r="G11" s="3" t="s">
         <v>407</v>
       </c>
-      <c r="E11" s="3" t="s">
-        <v>204</v>
-      </c>
-      <c r="F11" s="3" t="s">
+      <c r="H11" s="3" t="s">
+        <v>85</v>
+      </c>
+      <c r="I11" s="3" t="s">
+        <v>205</v>
+      </c>
+      <c r="J11" s="3" t="s">
         <v>408</v>
       </c>
-      <c r="G11" s="3" t="s">
+      <c r="K11" s="3" t="s">
         <v>409</v>
       </c>
-      <c r="H11" s="3" t="s">
-        <v>85</v>
-      </c>
-      <c r="I11" s="3" t="s">
-        <v>207</v>
-      </c>
-      <c r="J11" s="3" t="s">
-        <v>410</v>
-      </c>
-      <c r="K11" s="3" t="s">
-        <v>411</v>
-      </c>
       <c r="L11" s="3" t="s">
-        <v>410</v>
+        <v>408</v>
       </c>
       <c r="M11" s="3" t="s">
-        <v>411</v>
+        <v>409</v>
       </c>
       <c r="N11" s="3" t="s">
-        <v>410</v>
+        <v>408</v>
       </c>
       <c r="O11" s="3" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="P11" s="3" t="s">
-        <v>208</v>
+        <v>206</v>
       </c>
       <c r="Q11" s="3" t="s">
-        <v>211</v>
+        <v>209</v>
       </c>
       <c r="R11" s="3" t="s">
         <v>85</v>
@@ -3564,52 +3558,52 @@
         <v>132</v>
       </c>
       <c r="B12" s="3" t="s">
-        <v>419</v>
+        <v>417</v>
       </c>
       <c r="C12" s="3" t="s">
+        <v>404</v>
+      </c>
+      <c r="D12" s="3" t="s">
+        <v>405</v>
+      </c>
+      <c r="E12" s="3" t="s">
+        <v>202</v>
+      </c>
+      <c r="F12" s="3" t="s">
         <v>406</v>
       </c>
-      <c r="D12" s="3" t="s">
+      <c r="G12" s="3" t="s">
         <v>407</v>
       </c>
-      <c r="E12" s="3" t="s">
-        <v>204</v>
-      </c>
-      <c r="F12" s="3" t="s">
+      <c r="H12" s="3" t="s">
+        <v>85</v>
+      </c>
+      <c r="I12" s="3" t="s">
+        <v>205</v>
+      </c>
+      <c r="J12" s="3" t="s">
         <v>408</v>
       </c>
-      <c r="G12" s="3" t="s">
+      <c r="K12" s="3" t="s">
         <v>409</v>
       </c>
-      <c r="H12" s="3" t="s">
-        <v>85</v>
-      </c>
-      <c r="I12" s="3" t="s">
-        <v>207</v>
-      </c>
-      <c r="J12" s="3" t="s">
-        <v>410</v>
-      </c>
-      <c r="K12" s="3" t="s">
-        <v>411</v>
-      </c>
       <c r="L12" s="3" t="s">
-        <v>410</v>
+        <v>408</v>
       </c>
       <c r="M12" s="3" t="s">
-        <v>411</v>
+        <v>409</v>
       </c>
       <c r="N12" s="3" t="s">
-        <v>410</v>
+        <v>408</v>
       </c>
       <c r="O12" s="3" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="P12" s="3" t="s">
-        <v>208</v>
+        <v>206</v>
       </c>
       <c r="Q12" s="3" t="s">
-        <v>211</v>
+        <v>209</v>
       </c>
       <c r="R12" s="3" t="s">
         <v>85</v>
@@ -3620,52 +3614,52 @@
         <v>133</v>
       </c>
       <c r="B13" s="3" t="s">
-        <v>420</v>
+        <v>418</v>
       </c>
       <c r="C13" s="3" t="s">
+        <v>404</v>
+      </c>
+      <c r="D13" s="3" t="s">
+        <v>405</v>
+      </c>
+      <c r="E13" s="3" t="s">
+        <v>202</v>
+      </c>
+      <c r="F13" s="3" t="s">
         <v>406</v>
       </c>
-      <c r="D13" s="3" t="s">
+      <c r="G13" s="3" t="s">
         <v>407</v>
       </c>
-      <c r="E13" s="3" t="s">
-        <v>204</v>
-      </c>
-      <c r="F13" s="3" t="s">
+      <c r="H13" s="3" t="s">
+        <v>85</v>
+      </c>
+      <c r="I13" s="3" t="s">
+        <v>205</v>
+      </c>
+      <c r="J13" s="3" t="s">
         <v>408</v>
       </c>
-      <c r="G13" s="3" t="s">
+      <c r="K13" s="3" t="s">
         <v>409</v>
       </c>
-      <c r="H13" s="3" t="s">
-        <v>85</v>
-      </c>
-      <c r="I13" s="3" t="s">
-        <v>207</v>
-      </c>
-      <c r="J13" s="3" t="s">
-        <v>410</v>
-      </c>
-      <c r="K13" s="3" t="s">
-        <v>411</v>
-      </c>
       <c r="L13" s="3" t="s">
-        <v>410</v>
+        <v>408</v>
       </c>
       <c r="M13" s="3" t="s">
-        <v>411</v>
+        <v>409</v>
       </c>
       <c r="N13" s="3" t="s">
-        <v>410</v>
+        <v>408</v>
       </c>
       <c r="O13" s="3" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="P13" s="3" t="s">
-        <v>208</v>
+        <v>206</v>
       </c>
       <c r="Q13" s="3" t="s">
-        <v>211</v>
+        <v>209</v>
       </c>
       <c r="R13" s="3" t="s">
         <v>85</v>
@@ -3676,52 +3670,52 @@
         <v>134</v>
       </c>
       <c r="B14" s="3" t="s">
-        <v>421</v>
+        <v>419</v>
       </c>
       <c r="C14" s="3" t="s">
+        <v>404</v>
+      </c>
+      <c r="D14" s="3" t="s">
+        <v>405</v>
+      </c>
+      <c r="E14" s="3" t="s">
+        <v>202</v>
+      </c>
+      <c r="F14" s="3" t="s">
         <v>406</v>
       </c>
-      <c r="D14" s="3" t="s">
+      <c r="G14" s="3" t="s">
         <v>407</v>
       </c>
-      <c r="E14" s="3" t="s">
-        <v>204</v>
-      </c>
-      <c r="F14" s="3" t="s">
+      <c r="H14" s="3" t="s">
+        <v>85</v>
+      </c>
+      <c r="I14" s="3" t="s">
+        <v>205</v>
+      </c>
+      <c r="J14" s="3" t="s">
         <v>408</v>
       </c>
-      <c r="G14" s="3" t="s">
+      <c r="K14" s="3" t="s">
         <v>409</v>
       </c>
-      <c r="H14" s="3" t="s">
-        <v>85</v>
-      </c>
-      <c r="I14" s="3" t="s">
-        <v>207</v>
-      </c>
-      <c r="J14" s="3" t="s">
-        <v>410</v>
-      </c>
-      <c r="K14" s="3" t="s">
-        <v>411</v>
-      </c>
       <c r="L14" s="3" t="s">
-        <v>410</v>
+        <v>408</v>
       </c>
       <c r="M14" s="3" t="s">
-        <v>411</v>
+        <v>409</v>
       </c>
       <c r="N14" s="3" t="s">
-        <v>410</v>
+        <v>408</v>
       </c>
       <c r="O14" s="3" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="P14" s="3" t="s">
-        <v>208</v>
+        <v>206</v>
       </c>
       <c r="Q14" s="3" t="s">
-        <v>211</v>
+        <v>209</v>
       </c>
       <c r="R14" s="3" t="s">
         <v>85</v>
@@ -3732,52 +3726,52 @@
         <v>135</v>
       </c>
       <c r="B15" s="3" t="s">
-        <v>422</v>
+        <v>420</v>
       </c>
       <c r="C15" s="3" t="s">
+        <v>404</v>
+      </c>
+      <c r="D15" s="3" t="s">
+        <v>405</v>
+      </c>
+      <c r="E15" s="3" t="s">
+        <v>202</v>
+      </c>
+      <c r="F15" s="3" t="s">
         <v>406</v>
       </c>
-      <c r="D15" s="3" t="s">
+      <c r="G15" s="3" t="s">
         <v>407</v>
       </c>
-      <c r="E15" s="3" t="s">
-        <v>204</v>
-      </c>
-      <c r="F15" s="3" t="s">
+      <c r="H15" s="3" t="s">
+        <v>85</v>
+      </c>
+      <c r="I15" s="3" t="s">
+        <v>205</v>
+      </c>
+      <c r="J15" s="3" t="s">
         <v>408</v>
       </c>
-      <c r="G15" s="3" t="s">
+      <c r="K15" s="3" t="s">
         <v>409</v>
       </c>
-      <c r="H15" s="3" t="s">
-        <v>85</v>
-      </c>
-      <c r="I15" s="3" t="s">
-        <v>207</v>
-      </c>
-      <c r="J15" s="3" t="s">
-        <v>410</v>
-      </c>
-      <c r="K15" s="3" t="s">
-        <v>411</v>
-      </c>
       <c r="L15" s="3" t="s">
-        <v>410</v>
+        <v>408</v>
       </c>
       <c r="M15" s="3" t="s">
-        <v>411</v>
+        <v>409</v>
       </c>
       <c r="N15" s="3" t="s">
-        <v>410</v>
+        <v>408</v>
       </c>
       <c r="O15" s="3" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="P15" s="3" t="s">
-        <v>208</v>
+        <v>206</v>
       </c>
       <c r="Q15" s="3" t="s">
-        <v>211</v>
+        <v>209</v>
       </c>
       <c r="R15" s="3" t="s">
         <v>85</v>
@@ -3785,55 +3779,55 @@
     </row>
     <row r="16" spans="1:18" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16" s="3" t="s">
-        <v>136</v>
+        <v>139</v>
       </c>
       <c r="B16" s="3" t="s">
-        <v>423</v>
+        <v>421</v>
       </c>
       <c r="C16" s="3" t="s">
+        <v>404</v>
+      </c>
+      <c r="D16" s="3" t="s">
+        <v>405</v>
+      </c>
+      <c r="E16" s="3" t="s">
+        <v>202</v>
+      </c>
+      <c r="F16" s="3" t="s">
         <v>406</v>
       </c>
-      <c r="D16" s="3" t="s">
+      <c r="G16" s="3" t="s">
         <v>407</v>
       </c>
-      <c r="E16" s="3" t="s">
-        <v>204</v>
-      </c>
-      <c r="F16" s="3" t="s">
+      <c r="H16" s="3" t="s">
+        <v>85</v>
+      </c>
+      <c r="I16" s="3" t="s">
+        <v>205</v>
+      </c>
+      <c r="J16" s="3" t="s">
         <v>408</v>
       </c>
-      <c r="G16" s="3" t="s">
+      <c r="K16" s="3" t="s">
         <v>409</v>
       </c>
-      <c r="H16" s="3" t="s">
-        <v>85</v>
-      </c>
-      <c r="I16" s="3" t="s">
-        <v>207</v>
-      </c>
-      <c r="J16" s="3" t="s">
-        <v>410</v>
-      </c>
-      <c r="K16" s="3" t="s">
-        <v>411</v>
-      </c>
       <c r="L16" s="3" t="s">
-        <v>410</v>
+        <v>408</v>
       </c>
       <c r="M16" s="3" t="s">
-        <v>411</v>
+        <v>409</v>
       </c>
       <c r="N16" s="3" t="s">
-        <v>410</v>
+        <v>408</v>
       </c>
       <c r="O16" s="3" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="P16" s="3" t="s">
-        <v>208</v>
+        <v>206</v>
       </c>
       <c r="Q16" s="3" t="s">
-        <v>211</v>
+        <v>209</v>
       </c>
       <c r="R16" s="3" t="s">
         <v>85</v>
@@ -3841,55 +3835,55 @@
     </row>
     <row r="17" spans="1:18" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17" s="3" t="s">
-        <v>138</v>
+        <v>144</v>
       </c>
       <c r="B17" s="3" t="s">
-        <v>424</v>
+        <v>422</v>
       </c>
       <c r="C17" s="3" t="s">
+        <v>404</v>
+      </c>
+      <c r="D17" s="3" t="s">
+        <v>405</v>
+      </c>
+      <c r="E17" s="3" t="s">
+        <v>202</v>
+      </c>
+      <c r="F17" s="3" t="s">
         <v>406</v>
       </c>
-      <c r="D17" s="3" t="s">
+      <c r="G17" s="3" t="s">
         <v>407</v>
       </c>
-      <c r="E17" s="3" t="s">
-        <v>204</v>
-      </c>
-      <c r="F17" s="3" t="s">
+      <c r="H17" s="3" t="s">
+        <v>85</v>
+      </c>
+      <c r="I17" s="3" t="s">
+        <v>205</v>
+      </c>
+      <c r="J17" s="3" t="s">
         <v>408</v>
       </c>
-      <c r="G17" s="3" t="s">
+      <c r="K17" s="3" t="s">
         <v>409</v>
       </c>
-      <c r="H17" s="3" t="s">
-        <v>85</v>
-      </c>
-      <c r="I17" s="3" t="s">
-        <v>207</v>
-      </c>
-      <c r="J17" s="3" t="s">
-        <v>410</v>
-      </c>
-      <c r="K17" s="3" t="s">
-        <v>411</v>
-      </c>
       <c r="L17" s="3" t="s">
-        <v>410</v>
+        <v>408</v>
       </c>
       <c r="M17" s="3" t="s">
-        <v>411</v>
+        <v>409</v>
       </c>
       <c r="N17" s="3" t="s">
-        <v>410</v>
+        <v>408</v>
       </c>
       <c r="O17" s="3" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="P17" s="3" t="s">
-        <v>208</v>
+        <v>206</v>
       </c>
       <c r="Q17" s="3" t="s">
-        <v>211</v>
+        <v>209</v>
       </c>
       <c r="R17" s="3" t="s">
         <v>85</v>
@@ -3897,55 +3891,55 @@
     </row>
     <row r="18" spans="1:18" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A18" s="3" t="s">
-        <v>139</v>
+        <v>146</v>
       </c>
       <c r="B18" s="3" t="s">
-        <v>425</v>
+        <v>423</v>
       </c>
       <c r="C18" s="3" t="s">
+        <v>404</v>
+      </c>
+      <c r="D18" s="3" t="s">
+        <v>405</v>
+      </c>
+      <c r="E18" s="3" t="s">
+        <v>202</v>
+      </c>
+      <c r="F18" s="3" t="s">
         <v>406</v>
       </c>
-      <c r="D18" s="3" t="s">
+      <c r="G18" s="3" t="s">
         <v>407</v>
       </c>
-      <c r="E18" s="3" t="s">
-        <v>204</v>
-      </c>
-      <c r="F18" s="3" t="s">
+      <c r="H18" s="3" t="s">
+        <v>85</v>
+      </c>
+      <c r="I18" s="3" t="s">
+        <v>205</v>
+      </c>
+      <c r="J18" s="3" t="s">
         <v>408</v>
       </c>
-      <c r="G18" s="3" t="s">
+      <c r="K18" s="3" t="s">
         <v>409</v>
       </c>
-      <c r="H18" s="3" t="s">
-        <v>85</v>
-      </c>
-      <c r="I18" s="3" t="s">
-        <v>207</v>
-      </c>
-      <c r="J18" s="3" t="s">
-        <v>410</v>
-      </c>
-      <c r="K18" s="3" t="s">
-        <v>411</v>
-      </c>
       <c r="L18" s="3" t="s">
-        <v>410</v>
+        <v>408</v>
       </c>
       <c r="M18" s="3" t="s">
-        <v>411</v>
+        <v>409</v>
       </c>
       <c r="N18" s="3" t="s">
-        <v>410</v>
+        <v>408</v>
       </c>
       <c r="O18" s="3" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="P18" s="3" t="s">
-        <v>208</v>
+        <v>206</v>
       </c>
       <c r="Q18" s="3" t="s">
-        <v>211</v>
+        <v>209</v>
       </c>
       <c r="R18" s="3" t="s">
         <v>85</v>
@@ -3953,55 +3947,55 @@
     </row>
     <row r="19" spans="1:18" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A19" s="3" t="s">
-        <v>141</v>
+        <v>149</v>
       </c>
       <c r="B19" s="3" t="s">
-        <v>426</v>
+        <v>424</v>
       </c>
       <c r="C19" s="3" t="s">
+        <v>404</v>
+      </c>
+      <c r="D19" s="3" t="s">
+        <v>405</v>
+      </c>
+      <c r="E19" s="3" t="s">
+        <v>202</v>
+      </c>
+      <c r="F19" s="3" t="s">
         <v>406</v>
       </c>
-      <c r="D19" s="3" t="s">
+      <c r="G19" s="3" t="s">
         <v>407</v>
       </c>
-      <c r="E19" s="3" t="s">
-        <v>204</v>
-      </c>
-      <c r="F19" s="3" t="s">
+      <c r="H19" s="3" t="s">
+        <v>85</v>
+      </c>
+      <c r="I19" s="3" t="s">
+        <v>205</v>
+      </c>
+      <c r="J19" s="3" t="s">
         <v>408</v>
       </c>
-      <c r="G19" s="3" t="s">
+      <c r="K19" s="3" t="s">
         <v>409</v>
       </c>
-      <c r="H19" s="3" t="s">
-        <v>85</v>
-      </c>
-      <c r="I19" s="3" t="s">
-        <v>207</v>
-      </c>
-      <c r="J19" s="3" t="s">
-        <v>410</v>
-      </c>
-      <c r="K19" s="3" t="s">
-        <v>411</v>
-      </c>
       <c r="L19" s="3" t="s">
-        <v>410</v>
+        <v>408</v>
       </c>
       <c r="M19" s="3" t="s">
-        <v>411</v>
+        <v>409</v>
       </c>
       <c r="N19" s="3" t="s">
-        <v>410</v>
+        <v>408</v>
       </c>
       <c r="O19" s="3" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="P19" s="3" t="s">
-        <v>208</v>
+        <v>206</v>
       </c>
       <c r="Q19" s="3" t="s">
-        <v>211</v>
+        <v>209</v>
       </c>
       <c r="R19" s="3" t="s">
         <v>85</v>
@@ -4009,55 +4003,55 @@
     </row>
     <row r="20" spans="1:18" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A20" s="3" t="s">
-        <v>142</v>
+        <v>151</v>
       </c>
       <c r="B20" s="3" t="s">
-        <v>427</v>
+        <v>425</v>
       </c>
       <c r="C20" s="3" t="s">
+        <v>404</v>
+      </c>
+      <c r="D20" s="3" t="s">
+        <v>405</v>
+      </c>
+      <c r="E20" s="3" t="s">
+        <v>202</v>
+      </c>
+      <c r="F20" s="3" t="s">
         <v>406</v>
       </c>
-      <c r="D20" s="3" t="s">
+      <c r="G20" s="3" t="s">
         <v>407</v>
       </c>
-      <c r="E20" s="3" t="s">
-        <v>204</v>
-      </c>
-      <c r="F20" s="3" t="s">
+      <c r="H20" s="3" t="s">
+        <v>85</v>
+      </c>
+      <c r="I20" s="3" t="s">
+        <v>205</v>
+      </c>
+      <c r="J20" s="3" t="s">
         <v>408</v>
       </c>
-      <c r="G20" s="3" t="s">
+      <c r="K20" s="3" t="s">
         <v>409</v>
       </c>
-      <c r="H20" s="3" t="s">
-        <v>85</v>
-      </c>
-      <c r="I20" s="3" t="s">
-        <v>207</v>
-      </c>
-      <c r="J20" s="3" t="s">
-        <v>410</v>
-      </c>
-      <c r="K20" s="3" t="s">
-        <v>411</v>
-      </c>
       <c r="L20" s="3" t="s">
-        <v>410</v>
+        <v>408</v>
       </c>
       <c r="M20" s="3" t="s">
-        <v>411</v>
+        <v>409</v>
       </c>
       <c r="N20" s="3" t="s">
-        <v>410</v>
+        <v>408</v>
       </c>
       <c r="O20" s="3" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="P20" s="3" t="s">
-        <v>208</v>
+        <v>206</v>
       </c>
       <c r="Q20" s="3" t="s">
-        <v>211</v>
+        <v>209</v>
       </c>
       <c r="R20" s="3" t="s">
         <v>85</v>
@@ -4065,55 +4059,55 @@
     </row>
     <row r="21" spans="1:18" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A21" s="3" t="s">
-        <v>144</v>
+        <v>154</v>
       </c>
       <c r="B21" s="3" t="s">
-        <v>428</v>
+        <v>426</v>
       </c>
       <c r="C21" s="3" t="s">
+        <v>404</v>
+      </c>
+      <c r="D21" s="3" t="s">
+        <v>405</v>
+      </c>
+      <c r="E21" s="3" t="s">
+        <v>202</v>
+      </c>
+      <c r="F21" s="3" t="s">
         <v>406</v>
       </c>
-      <c r="D21" s="3" t="s">
+      <c r="G21" s="3" t="s">
         <v>407</v>
       </c>
-      <c r="E21" s="3" t="s">
-        <v>204</v>
-      </c>
-      <c r="F21" s="3" t="s">
+      <c r="H21" s="3" t="s">
+        <v>85</v>
+      </c>
+      <c r="I21" s="3" t="s">
+        <v>205</v>
+      </c>
+      <c r="J21" s="3" t="s">
         <v>408</v>
       </c>
-      <c r="G21" s="3" t="s">
+      <c r="K21" s="3" t="s">
         <v>409</v>
       </c>
-      <c r="H21" s="3" t="s">
-        <v>85</v>
-      </c>
-      <c r="I21" s="3" t="s">
-        <v>207</v>
-      </c>
-      <c r="J21" s="3" t="s">
-        <v>410</v>
-      </c>
-      <c r="K21" s="3" t="s">
-        <v>411</v>
-      </c>
       <c r="L21" s="3" t="s">
-        <v>410</v>
+        <v>408</v>
       </c>
       <c r="M21" s="3" t="s">
-        <v>411</v>
+        <v>409</v>
       </c>
       <c r="N21" s="3" t="s">
-        <v>410</v>
+        <v>408</v>
       </c>
       <c r="O21" s="3" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="P21" s="3" t="s">
-        <v>208</v>
+        <v>206</v>
       </c>
       <c r="Q21" s="3" t="s">
-        <v>211</v>
+        <v>209</v>
       </c>
       <c r="R21" s="3" t="s">
         <v>85</v>
@@ -4121,55 +4115,55 @@
     </row>
     <row r="22" spans="1:18" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A22" s="3" t="s">
-        <v>150</v>
+        <v>156</v>
       </c>
       <c r="B22" s="3" t="s">
-        <v>429</v>
+        <v>427</v>
       </c>
       <c r="C22" s="3" t="s">
+        <v>404</v>
+      </c>
+      <c r="D22" s="3" t="s">
+        <v>405</v>
+      </c>
+      <c r="E22" s="3" t="s">
+        <v>202</v>
+      </c>
+      <c r="F22" s="3" t="s">
         <v>406</v>
       </c>
-      <c r="D22" s="3" t="s">
+      <c r="G22" s="3" t="s">
         <v>407</v>
       </c>
-      <c r="E22" s="3" t="s">
-        <v>204</v>
-      </c>
-      <c r="F22" s="3" t="s">
+      <c r="H22" s="3" t="s">
+        <v>85</v>
+      </c>
+      <c r="I22" s="3" t="s">
+        <v>205</v>
+      </c>
+      <c r="J22" s="3" t="s">
         <v>408</v>
       </c>
-      <c r="G22" s="3" t="s">
+      <c r="K22" s="3" t="s">
         <v>409</v>
       </c>
-      <c r="H22" s="3" t="s">
-        <v>85</v>
-      </c>
-      <c r="I22" s="3" t="s">
-        <v>207</v>
-      </c>
-      <c r="J22" s="3" t="s">
-        <v>410</v>
-      </c>
-      <c r="K22" s="3" t="s">
-        <v>411</v>
-      </c>
       <c r="L22" s="3" t="s">
-        <v>410</v>
+        <v>408</v>
       </c>
       <c r="M22" s="3" t="s">
-        <v>411</v>
+        <v>409</v>
       </c>
       <c r="N22" s="3" t="s">
-        <v>410</v>
+        <v>408</v>
       </c>
       <c r="O22" s="3" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="P22" s="3" t="s">
-        <v>208</v>
+        <v>206</v>
       </c>
       <c r="Q22" s="3" t="s">
-        <v>211</v>
+        <v>209</v>
       </c>
       <c r="R22" s="3" t="s">
         <v>85</v>
@@ -4177,55 +4171,55 @@
     </row>
     <row r="23" spans="1:18" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A23" s="3" t="s">
-        <v>154</v>
+        <v>157</v>
       </c>
       <c r="B23" s="3" t="s">
-        <v>430</v>
+        <v>428</v>
       </c>
       <c r="C23" s="3" t="s">
+        <v>404</v>
+      </c>
+      <c r="D23" s="3" t="s">
+        <v>405</v>
+      </c>
+      <c r="E23" s="3" t="s">
+        <v>202</v>
+      </c>
+      <c r="F23" s="3" t="s">
         <v>406</v>
       </c>
-      <c r="D23" s="3" t="s">
+      <c r="G23" s="3" t="s">
         <v>407</v>
       </c>
-      <c r="E23" s="3" t="s">
-        <v>204</v>
-      </c>
-      <c r="F23" s="3" t="s">
+      <c r="H23" s="3" t="s">
+        <v>85</v>
+      </c>
+      <c r="I23" s="3" t="s">
+        <v>205</v>
+      </c>
+      <c r="J23" s="3" t="s">
         <v>408</v>
       </c>
-      <c r="G23" s="3" t="s">
+      <c r="K23" s="3" t="s">
         <v>409</v>
       </c>
-      <c r="H23" s="3" t="s">
-        <v>85</v>
-      </c>
-      <c r="I23" s="3" t="s">
-        <v>207</v>
-      </c>
-      <c r="J23" s="3" t="s">
-        <v>410</v>
-      </c>
-      <c r="K23" s="3" t="s">
-        <v>411</v>
-      </c>
       <c r="L23" s="3" t="s">
-        <v>410</v>
+        <v>408</v>
       </c>
       <c r="M23" s="3" t="s">
-        <v>411</v>
+        <v>409</v>
       </c>
       <c r="N23" s="3" t="s">
-        <v>410</v>
+        <v>408</v>
       </c>
       <c r="O23" s="3" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="P23" s="3" t="s">
-        <v>208</v>
+        <v>206</v>
       </c>
       <c r="Q23" s="3" t="s">
-        <v>211</v>
+        <v>209</v>
       </c>
       <c r="R23" s="3" t="s">
         <v>85</v>
@@ -4233,55 +4227,55 @@
     </row>
     <row r="24" spans="1:18" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A24" s="3" t="s">
-        <v>156</v>
+        <v>158</v>
       </c>
       <c r="B24" s="3" t="s">
-        <v>431</v>
+        <v>429</v>
       </c>
       <c r="C24" s="3" t="s">
+        <v>404</v>
+      </c>
+      <c r="D24" s="3" t="s">
+        <v>405</v>
+      </c>
+      <c r="E24" s="3" t="s">
+        <v>202</v>
+      </c>
+      <c r="F24" s="3" t="s">
         <v>406</v>
       </c>
-      <c r="D24" s="3" t="s">
+      <c r="G24" s="3" t="s">
         <v>407</v>
       </c>
-      <c r="E24" s="3" t="s">
-        <v>204</v>
-      </c>
-      <c r="F24" s="3" t="s">
+      <c r="H24" s="3" t="s">
+        <v>85</v>
+      </c>
+      <c r="I24" s="3" t="s">
+        <v>205</v>
+      </c>
+      <c r="J24" s="3" t="s">
         <v>408</v>
       </c>
-      <c r="G24" s="3" t="s">
+      <c r="K24" s="3" t="s">
         <v>409</v>
       </c>
-      <c r="H24" s="3" t="s">
-        <v>85</v>
-      </c>
-      <c r="I24" s="3" t="s">
-        <v>207</v>
-      </c>
-      <c r="J24" s="3" t="s">
-        <v>410</v>
-      </c>
-      <c r="K24" s="3" t="s">
-        <v>411</v>
-      </c>
       <c r="L24" s="3" t="s">
-        <v>410</v>
+        <v>408</v>
       </c>
       <c r="M24" s="3" t="s">
-        <v>411</v>
+        <v>409</v>
       </c>
       <c r="N24" s="3" t="s">
-        <v>410</v>
+        <v>408</v>
       </c>
       <c r="O24" s="3" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="P24" s="3" t="s">
-        <v>208</v>
+        <v>206</v>
       </c>
       <c r="Q24" s="3" t="s">
-        <v>211</v>
+        <v>209</v>
       </c>
       <c r="R24" s="3" t="s">
         <v>85</v>
@@ -4289,55 +4283,55 @@
     </row>
     <row r="25" spans="1:18" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A25" s="3" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="B25" s="3" t="s">
-        <v>432</v>
+        <v>430</v>
       </c>
       <c r="C25" s="3" t="s">
+        <v>404</v>
+      </c>
+      <c r="D25" s="3" t="s">
+        <v>405</v>
+      </c>
+      <c r="E25" s="3" t="s">
+        <v>202</v>
+      </c>
+      <c r="F25" s="3" t="s">
         <v>406</v>
       </c>
-      <c r="D25" s="3" t="s">
+      <c r="G25" s="3" t="s">
         <v>407</v>
       </c>
-      <c r="E25" s="3" t="s">
-        <v>204</v>
-      </c>
-      <c r="F25" s="3" t="s">
+      <c r="H25" s="3" t="s">
+        <v>85</v>
+      </c>
+      <c r="I25" s="3" t="s">
+        <v>205</v>
+      </c>
+      <c r="J25" s="3" t="s">
         <v>408</v>
       </c>
-      <c r="G25" s="3" t="s">
+      <c r="K25" s="3" t="s">
         <v>409</v>
       </c>
-      <c r="H25" s="3" t="s">
-        <v>85</v>
-      </c>
-      <c r="I25" s="3" t="s">
-        <v>207</v>
-      </c>
-      <c r="J25" s="3" t="s">
-        <v>410</v>
-      </c>
-      <c r="K25" s="3" t="s">
-        <v>411</v>
-      </c>
       <c r="L25" s="3" t="s">
-        <v>410</v>
+        <v>408</v>
       </c>
       <c r="M25" s="3" t="s">
-        <v>411</v>
+        <v>409</v>
       </c>
       <c r="N25" s="3" t="s">
-        <v>410</v>
+        <v>408</v>
       </c>
       <c r="O25" s="3" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="P25" s="3" t="s">
-        <v>208</v>
+        <v>206</v>
       </c>
       <c r="Q25" s="3" t="s">
-        <v>211</v>
+        <v>209</v>
       </c>
       <c r="R25" s="3" t="s">
         <v>85</v>
@@ -4348,52 +4342,52 @@
         <v>160</v>
       </c>
       <c r="B26" s="3" t="s">
-        <v>433</v>
+        <v>431</v>
       </c>
       <c r="C26" s="3" t="s">
+        <v>404</v>
+      </c>
+      <c r="D26" s="3" t="s">
+        <v>405</v>
+      </c>
+      <c r="E26" s="3" t="s">
+        <v>202</v>
+      </c>
+      <c r="F26" s="3" t="s">
         <v>406</v>
       </c>
-      <c r="D26" s="3" t="s">
+      <c r="G26" s="3" t="s">
         <v>407</v>
       </c>
-      <c r="E26" s="3" t="s">
-        <v>204</v>
-      </c>
-      <c r="F26" s="3" t="s">
+      <c r="H26" s="3" t="s">
+        <v>85</v>
+      </c>
+      <c r="I26" s="3" t="s">
+        <v>205</v>
+      </c>
+      <c r="J26" s="3" t="s">
         <v>408</v>
       </c>
-      <c r="G26" s="3" t="s">
+      <c r="K26" s="3" t="s">
         <v>409</v>
       </c>
-      <c r="H26" s="3" t="s">
-        <v>85</v>
-      </c>
-      <c r="I26" s="3" t="s">
-        <v>207</v>
-      </c>
-      <c r="J26" s="3" t="s">
-        <v>410</v>
-      </c>
-      <c r="K26" s="3" t="s">
-        <v>411</v>
-      </c>
       <c r="L26" s="3" t="s">
-        <v>410</v>
+        <v>408</v>
       </c>
       <c r="M26" s="3" t="s">
-        <v>411</v>
+        <v>409</v>
       </c>
       <c r="N26" s="3" t="s">
-        <v>410</v>
+        <v>408</v>
       </c>
       <c r="O26" s="3" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="P26" s="3" t="s">
-        <v>208</v>
+        <v>206</v>
       </c>
       <c r="Q26" s="3" t="s">
-        <v>211</v>
+        <v>209</v>
       </c>
       <c r="R26" s="3" t="s">
         <v>85</v>
@@ -4401,55 +4395,55 @@
     </row>
     <row r="27" spans="1:18" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A27" s="3" t="s">
-        <v>163</v>
+        <v>161</v>
       </c>
       <c r="B27" s="3" t="s">
-        <v>434</v>
+        <v>432</v>
       </c>
       <c r="C27" s="3" t="s">
+        <v>404</v>
+      </c>
+      <c r="D27" s="3" t="s">
+        <v>405</v>
+      </c>
+      <c r="E27" s="3" t="s">
+        <v>202</v>
+      </c>
+      <c r="F27" s="3" t="s">
         <v>406</v>
       </c>
-      <c r="D27" s="3" t="s">
+      <c r="G27" s="3" t="s">
         <v>407</v>
       </c>
-      <c r="E27" s="3" t="s">
-        <v>204</v>
-      </c>
-      <c r="F27" s="3" t="s">
+      <c r="H27" s="3" t="s">
+        <v>85</v>
+      </c>
+      <c r="I27" s="3" t="s">
+        <v>205</v>
+      </c>
+      <c r="J27" s="3" t="s">
         <v>408</v>
       </c>
-      <c r="G27" s="3" t="s">
+      <c r="K27" s="3" t="s">
         <v>409</v>
       </c>
-      <c r="H27" s="3" t="s">
-        <v>85</v>
-      </c>
-      <c r="I27" s="3" t="s">
-        <v>207</v>
-      </c>
-      <c r="J27" s="3" t="s">
-        <v>410</v>
-      </c>
-      <c r="K27" s="3" t="s">
-        <v>411</v>
-      </c>
       <c r="L27" s="3" t="s">
-        <v>410</v>
+        <v>408</v>
       </c>
       <c r="M27" s="3" t="s">
-        <v>411</v>
+        <v>409</v>
       </c>
       <c r="N27" s="3" t="s">
-        <v>410</v>
+        <v>408</v>
       </c>
       <c r="O27" s="3" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="P27" s="3" t="s">
-        <v>208</v>
+        <v>206</v>
       </c>
       <c r="Q27" s="3" t="s">
-        <v>211</v>
+        <v>209</v>
       </c>
       <c r="R27" s="3" t="s">
         <v>85</v>
@@ -4478,132 +4472,132 @@
   <sheetData>
     <row r="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
-        <v>255</v>
+        <v>253</v>
       </c>
     </row>
     <row r="2" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>249</v>
+        <v>247</v>
       </c>
     </row>
     <row r="3" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>248</v>
+        <v>246</v>
       </c>
     </row>
     <row r="4" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>239</v>
+        <v>237</v>
       </c>
     </row>
     <row r="5" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>242</v>
+        <v>240</v>
       </c>
     </row>
     <row r="6" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>240</v>
+        <v>238</v>
       </c>
     </row>
     <row r="7" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>204</v>
+        <v>202</v>
       </c>
     </row>
     <row r="8" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>238</v>
+        <v>236</v>
       </c>
     </row>
     <row r="9" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>243</v>
+        <v>241</v>
       </c>
     </row>
     <row r="10" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>245</v>
+        <v>243</v>
       </c>
     </row>
     <row r="11" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>260</v>
+        <v>258</v>
       </c>
     </row>
     <row r="12" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>247</v>
+        <v>245</v>
       </c>
     </row>
     <row r="13" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>376</v>
+        <v>374</v>
       </c>
     </row>
     <row r="14" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>281</v>
+        <v>279</v>
       </c>
     </row>
     <row r="15" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>257</v>
+        <v>255</v>
       </c>
     </row>
     <row r="16" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>252</v>
+        <v>250</v>
       </c>
     </row>
     <row r="17" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>259</v>
+        <v>257</v>
       </c>
     </row>
     <row r="18" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>258</v>
+        <v>256</v>
       </c>
     </row>
     <row r="19" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>244</v>
+        <v>242</v>
       </c>
     </row>
     <row r="20" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>254</v>
+        <v>252</v>
       </c>
     </row>
     <row r="21" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>253</v>
+        <v>251</v>
       </c>
     </row>
     <row r="22" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
-        <v>241</v>
+        <v>239</v>
       </c>
     </row>
     <row r="23" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
-        <v>377</v>
+        <v>375</v>
       </c>
     </row>
     <row r="24" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
-        <v>250</v>
+        <v>248</v>
       </c>
     </row>
     <row r="25" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
-        <v>251</v>
+        <v>249</v>
       </c>
     </row>
     <row r="26" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
-        <v>246</v>
+        <v>244</v>
       </c>
     </row>
   </sheetData>
@@ -4618,207 +4612,207 @@
   <sheetData>
     <row r="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
     </row>
     <row r="2" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>253</v>
+        <v>251</v>
       </c>
     </row>
     <row r="3" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>262</v>
+        <v>260</v>
       </c>
     </row>
     <row r="4" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>263</v>
+        <v>261</v>
       </c>
     </row>
     <row r="5" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>264</v>
+        <v>262</v>
       </c>
     </row>
     <row r="6" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>265</v>
+        <v>263</v>
       </c>
     </row>
     <row r="7" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>207</v>
+        <v>205</v>
       </c>
     </row>
     <row r="8" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>266</v>
+        <v>264</v>
       </c>
     </row>
     <row r="9" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>267</v>
+        <v>265</v>
       </c>
     </row>
     <row r="10" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>268</v>
+        <v>266</v>
       </c>
     </row>
     <row r="11" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>269</v>
+        <v>267</v>
       </c>
     </row>
     <row r="12" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>270</v>
+        <v>268</v>
       </c>
     </row>
     <row r="13" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>271</v>
+        <v>269</v>
       </c>
     </row>
     <row r="14" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>272</v>
+        <v>270</v>
       </c>
     </row>
     <row r="15" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>273</v>
+        <v>271</v>
       </c>
     </row>
     <row r="16" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>274</v>
+        <v>272</v>
       </c>
     </row>
     <row r="17" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>275</v>
+        <v>273</v>
       </c>
     </row>
     <row r="18" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>276</v>
+        <v>274</v>
       </c>
     </row>
     <row r="19" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>277</v>
+        <v>275</v>
       </c>
     </row>
     <row r="20" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>278</v>
+        <v>276</v>
       </c>
     </row>
     <row r="21" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>279</v>
+        <v>277</v>
       </c>
     </row>
     <row r="22" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
-        <v>280</v>
+        <v>278</v>
       </c>
     </row>
     <row r="23" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
-        <v>249</v>
+        <v>247</v>
       </c>
     </row>
     <row r="24" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
-        <v>281</v>
+        <v>279</v>
       </c>
     </row>
     <row r="25" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
-        <v>282</v>
+        <v>280</v>
       </c>
     </row>
     <row r="26" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
-        <v>283</v>
+        <v>281</v>
       </c>
     </row>
     <row r="27" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
-        <v>284</v>
+        <v>282</v>
       </c>
     </row>
     <row r="28" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
-        <v>285</v>
+        <v>283</v>
       </c>
     </row>
     <row r="29" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
-        <v>286</v>
+        <v>284</v>
       </c>
     </row>
     <row r="30" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
-        <v>287</v>
+        <v>285</v>
       </c>
     </row>
     <row r="31" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
-        <v>288</v>
+        <v>286</v>
       </c>
     </row>
     <row r="32" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
-        <v>289</v>
+        <v>287</v>
       </c>
     </row>
     <row r="33" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
-        <v>290</v>
+        <v>288</v>
       </c>
     </row>
     <row r="34" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
-        <v>291</v>
+        <v>289</v>
       </c>
     </row>
     <row r="35" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
-        <v>292</v>
+        <v>290</v>
       </c>
     </row>
     <row r="36" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
-        <v>293</v>
+        <v>291</v>
       </c>
     </row>
     <row r="37" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
-        <v>294</v>
+        <v>292</v>
       </c>
     </row>
     <row r="38" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
-        <v>295</v>
+        <v>293</v>
       </c>
     </row>
     <row r="39" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
-        <v>296</v>
+        <v>294</v>
       </c>
     </row>
     <row r="40" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
-        <v>297</v>
+        <v>295</v>
       </c>
     </row>
     <row r="41" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
-        <v>298</v>
+        <v>296</v>
       </c>
     </row>
   </sheetData>
@@ -4833,162 +4827,162 @@
   <sheetData>
     <row r="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
-        <v>378</v>
+        <v>376</v>
       </c>
     </row>
     <row r="2" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>325</v>
+        <v>323</v>
       </c>
     </row>
     <row r="3" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>326</v>
+        <v>324</v>
       </c>
     </row>
     <row r="4" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>299</v>
+        <v>297</v>
       </c>
     </row>
     <row r="5" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>323</v>
+        <v>321</v>
       </c>
     </row>
     <row r="6" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>300</v>
+        <v>298</v>
       </c>
     </row>
     <row r="7" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>301</v>
+        <v>299</v>
       </c>
     </row>
     <row r="8" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>302</v>
+        <v>300</v>
       </c>
     </row>
     <row r="9" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>318</v>
+        <v>316</v>
       </c>
     </row>
     <row r="10" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>379</v>
+        <v>377</v>
       </c>
     </row>
     <row r="11" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>307</v>
+        <v>305</v>
       </c>
     </row>
     <row r="12" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>320</v>
+        <v>318</v>
       </c>
     </row>
     <row r="13" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>310</v>
+        <v>308</v>
       </c>
     </row>
     <row r="14" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>315</v>
+        <v>313</v>
       </c>
     </row>
     <row r="15" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>304</v>
+        <v>302</v>
       </c>
     </row>
     <row r="16" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>311</v>
+        <v>309</v>
       </c>
     </row>
     <row r="17" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>322</v>
+        <v>320</v>
       </c>
     </row>
     <row r="18" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>317</v>
+        <v>315</v>
       </c>
     </row>
     <row r="19" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>208</v>
+        <v>206</v>
       </c>
     </row>
     <row r="20" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>309</v>
+        <v>307</v>
       </c>
     </row>
     <row r="21" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>312</v>
+        <v>310</v>
       </c>
     </row>
     <row r="22" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
-        <v>313</v>
+        <v>311</v>
       </c>
     </row>
     <row r="23" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
-        <v>327</v>
+        <v>325</v>
       </c>
     </row>
     <row r="24" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
-        <v>306</v>
+        <v>304</v>
       </c>
     </row>
     <row r="25" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
-        <v>305</v>
+        <v>303</v>
       </c>
     </row>
     <row r="26" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
-        <v>303</v>
+        <v>301</v>
       </c>
     </row>
     <row r="27" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
-        <v>329</v>
+        <v>327</v>
       </c>
     </row>
     <row r="28" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
-        <v>314</v>
+        <v>312</v>
       </c>
     </row>
     <row r="29" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
-        <v>308</v>
+        <v>306</v>
       </c>
     </row>
     <row r="30" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
-        <v>380</v>
+        <v>378</v>
       </c>
     </row>
     <row r="31" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
-        <v>321</v>
+        <v>319</v>
       </c>
     </row>
     <row r="32" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
-        <v>316</v>
+        <v>314</v>
       </c>
     </row>
   </sheetData>
@@ -5008,7 +5002,7 @@
     </row>
     <row r="2" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>164</v>
+        <v>162</v>
       </c>
     </row>
   </sheetData>
@@ -5101,118 +5095,118 @@
     </row>
     <row r="2" spans="1:20" hidden="1" x14ac:dyDescent="0.25">
       <c r="C2" t="s">
+        <v>163</v>
+      </c>
+      <c r="D2" t="s">
+        <v>164</v>
+      </c>
+      <c r="E2" t="s">
         <v>165</v>
       </c>
-      <c r="D2" t="s">
+      <c r="F2" t="s">
         <v>166</v>
       </c>
-      <c r="E2" t="s">
+      <c r="G2" t="s">
         <v>167</v>
       </c>
-      <c r="F2" t="s">
+      <c r="H2" t="s">
         <v>168</v>
       </c>
-      <c r="G2" t="s">
+      <c r="I2" t="s">
         <v>169</v>
       </c>
-      <c r="H2" t="s">
+      <c r="J2" t="s">
         <v>170</v>
       </c>
-      <c r="I2" t="s">
+      <c r="K2" t="s">
         <v>171</v>
       </c>
-      <c r="J2" t="s">
+      <c r="L2" t="s">
         <v>172</v>
       </c>
-      <c r="K2" t="s">
+      <c r="M2" t="s">
         <v>173</v>
       </c>
-      <c r="L2" t="s">
+      <c r="N2" t="s">
         <v>174</v>
       </c>
-      <c r="M2" t="s">
+      <c r="O2" t="s">
         <v>175</v>
       </c>
-      <c r="N2" t="s">
+      <c r="P2" t="s">
         <v>176</v>
       </c>
-      <c r="O2" t="s">
+      <c r="Q2" t="s">
         <v>177</v>
       </c>
-      <c r="P2" t="s">
+      <c r="R2" t="s">
         <v>178</v>
       </c>
-      <c r="Q2" t="s">
+      <c r="S2" t="s">
         <v>179</v>
       </c>
-      <c r="R2" t="s">
+      <c r="T2" t="s">
         <v>180</v>
-      </c>
-      <c r="S2" t="s">
-        <v>181</v>
-      </c>
-      <c r="T2" t="s">
-        <v>182</v>
       </c>
     </row>
     <row r="3" spans="1:20" ht="30" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
       <c r="B3" s="1"/>
       <c r="C3" s="1" t="s">
+        <v>182</v>
+      </c>
+      <c r="D3" s="1" t="s">
+        <v>183</v>
+      </c>
+      <c r="E3" s="1" t="s">
         <v>184</v>
       </c>
-      <c r="D3" s="1" t="s">
+      <c r="F3" s="1" t="s">
         <v>185</v>
       </c>
-      <c r="E3" s="1" t="s">
+      <c r="G3" s="1" t="s">
         <v>186</v>
       </c>
-      <c r="F3" s="1" t="s">
+      <c r="H3" s="1" t="s">
         <v>187</v>
       </c>
-      <c r="G3" s="1" t="s">
+      <c r="I3" s="1" t="s">
         <v>188</v>
       </c>
-      <c r="H3" s="1" t="s">
+      <c r="J3" s="1" t="s">
         <v>189</v>
       </c>
-      <c r="I3" s="1" t="s">
+      <c r="K3" s="1" t="s">
         <v>190</v>
       </c>
-      <c r="J3" s="1" t="s">
+      <c r="L3" s="1" t="s">
         <v>191</v>
       </c>
-      <c r="K3" s="1" t="s">
+      <c r="M3" s="1" t="s">
         <v>192</v>
       </c>
-      <c r="L3" s="1" t="s">
+      <c r="N3" s="1" t="s">
         <v>193</v>
       </c>
-      <c r="M3" s="1" t="s">
+      <c r="O3" s="1" t="s">
         <v>194</v>
       </c>
-      <c r="N3" s="1" t="s">
+      <c r="P3" s="1" t="s">
         <v>195</v>
       </c>
-      <c r="O3" s="1" t="s">
+      <c r="Q3" s="1" t="s">
         <v>196</v>
       </c>
-      <c r="P3" s="1" t="s">
+      <c r="R3" s="1" t="s">
         <v>197</v>
       </c>
-      <c r="Q3" s="1" t="s">
+      <c r="S3" s="1" t="s">
         <v>198</v>
       </c>
-      <c r="R3" s="1" t="s">
+      <c r="T3" s="1" t="s">
         <v>199</v>
-      </c>
-      <c r="S3" s="1" t="s">
-        <v>200</v>
-      </c>
-      <c r="T3" s="1" t="s">
-        <v>201</v>
       </c>
     </row>
     <row r="4" spans="1:20" ht="45" customHeight="1" x14ac:dyDescent="0.25">
@@ -5220,61 +5214,61 @@
         <v>88</v>
       </c>
       <c r="B4" s="3" t="s">
+        <v>200</v>
+      </c>
+      <c r="C4" s="3" t="s">
+        <v>201</v>
+      </c>
+      <c r="D4" s="3" t="s">
         <v>202</v>
       </c>
-      <c r="C4" s="3" t="s">
+      <c r="E4" s="3" t="s">
         <v>203</v>
       </c>
-      <c r="D4" s="3" t="s">
+      <c r="F4" s="3" t="s">
         <v>204</v>
       </c>
-      <c r="E4" s="3" t="s">
+      <c r="G4" s="3" t="s">
+        <v>85</v>
+      </c>
+      <c r="H4" s="3" t="s">
         <v>205</v>
       </c>
-      <c r="F4" s="3" t="s">
-        <v>206</v>
-      </c>
-      <c r="G4" s="3" t="s">
-        <v>85</v>
-      </c>
-      <c r="H4" s="3" t="s">
-        <v>207</v>
-      </c>
       <c r="I4" s="3" t="s">
+        <v>206</v>
+      </c>
+      <c r="J4" s="3" t="s">
+        <v>207</v>
+      </c>
+      <c r="K4" s="3" t="s">
+        <v>206</v>
+      </c>
+      <c r="L4" s="3" t="s">
+        <v>207</v>
+      </c>
+      <c r="M4" s="3" t="s">
+        <v>206</v>
+      </c>
+      <c r="N4" s="3" t="s">
         <v>208</v>
       </c>
-      <c r="J4" s="3" t="s">
+      <c r="O4" s="3" t="s">
+        <v>206</v>
+      </c>
+      <c r="P4" s="3" t="s">
         <v>209</v>
       </c>
-      <c r="K4" s="3" t="s">
-        <v>208</v>
-      </c>
-      <c r="L4" s="3" t="s">
-        <v>209</v>
-      </c>
-      <c r="M4" s="3" t="s">
-        <v>208</v>
-      </c>
-      <c r="N4" s="3" t="s">
+      <c r="Q4" s="3" t="s">
+        <v>85</v>
+      </c>
+      <c r="R4" s="3" t="s">
         <v>210</v>
       </c>
-      <c r="O4" s="3" t="s">
-        <v>208</v>
-      </c>
-      <c r="P4" s="3" t="s">
+      <c r="S4" s="3" t="s">
         <v>211</v>
       </c>
-      <c r="Q4" s="3" t="s">
-        <v>85</v>
-      </c>
-      <c r="R4" s="3" t="s">
+      <c r="T4" s="3" t="s">
         <v>212</v>
-      </c>
-      <c r="S4" s="3" t="s">
-        <v>213</v>
-      </c>
-      <c r="T4" s="3" t="s">
-        <v>214</v>
       </c>
     </row>
     <row r="5" spans="1:20" ht="45" customHeight="1" x14ac:dyDescent="0.25">
@@ -5282,61 +5276,61 @@
         <v>102</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>215</v>
+        <v>213</v>
       </c>
       <c r="C5" s="3" t="s">
+        <v>201</v>
+      </c>
+      <c r="D5" s="3" t="s">
+        <v>202</v>
+      </c>
+      <c r="E5" s="3" t="s">
         <v>203</v>
       </c>
-      <c r="D5" s="3" t="s">
+      <c r="F5" s="3" t="s">
         <v>204</v>
       </c>
-      <c r="E5" s="3" t="s">
+      <c r="G5" s="3" t="s">
+        <v>85</v>
+      </c>
+      <c r="H5" s="3" t="s">
         <v>205</v>
       </c>
-      <c r="F5" s="3" t="s">
-        <v>206</v>
-      </c>
-      <c r="G5" s="3" t="s">
-        <v>85</v>
-      </c>
-      <c r="H5" s="3" t="s">
-        <v>207</v>
-      </c>
       <c r="I5" s="3" t="s">
+        <v>206</v>
+      </c>
+      <c r="J5" s="3" t="s">
+        <v>207</v>
+      </c>
+      <c r="K5" s="3" t="s">
+        <v>206</v>
+      </c>
+      <c r="L5" s="3" t="s">
+        <v>207</v>
+      </c>
+      <c r="M5" s="3" t="s">
+        <v>206</v>
+      </c>
+      <c r="N5" s="3" t="s">
         <v>208</v>
       </c>
-      <c r="J5" s="3" t="s">
+      <c r="O5" s="3" t="s">
+        <v>206</v>
+      </c>
+      <c r="P5" s="3" t="s">
         <v>209</v>
       </c>
-      <c r="K5" s="3" t="s">
-        <v>208</v>
-      </c>
-      <c r="L5" s="3" t="s">
-        <v>209</v>
-      </c>
-      <c r="M5" s="3" t="s">
-        <v>208</v>
-      </c>
-      <c r="N5" s="3" t="s">
+      <c r="Q5" s="3" t="s">
+        <v>85</v>
+      </c>
+      <c r="R5" s="3" t="s">
         <v>210</v>
       </c>
-      <c r="O5" s="3" t="s">
-        <v>208</v>
-      </c>
-      <c r="P5" s="3" t="s">
+      <c r="S5" s="3" t="s">
         <v>211</v>
       </c>
-      <c r="Q5" s="3" t="s">
-        <v>85</v>
-      </c>
-      <c r="R5" s="3" t="s">
+      <c r="T5" s="3" t="s">
         <v>212</v>
-      </c>
-      <c r="S5" s="3" t="s">
-        <v>213</v>
-      </c>
-      <c r="T5" s="3" t="s">
-        <v>214</v>
       </c>
     </row>
     <row r="6" spans="1:20" ht="45" customHeight="1" x14ac:dyDescent="0.25">
@@ -5344,61 +5338,61 @@
         <v>109</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>216</v>
+        <v>214</v>
       </c>
       <c r="C6" s="3" t="s">
+        <v>201</v>
+      </c>
+      <c r="D6" s="3" t="s">
+        <v>202</v>
+      </c>
+      <c r="E6" s="3" t="s">
         <v>203</v>
       </c>
-      <c r="D6" s="3" t="s">
+      <c r="F6" s="3" t="s">
         <v>204</v>
       </c>
-      <c r="E6" s="3" t="s">
+      <c r="G6" s="3" t="s">
+        <v>85</v>
+      </c>
+      <c r="H6" s="3" t="s">
         <v>205</v>
       </c>
-      <c r="F6" s="3" t="s">
-        <v>206</v>
-      </c>
-      <c r="G6" s="3" t="s">
-        <v>85</v>
-      </c>
-      <c r="H6" s="3" t="s">
-        <v>207</v>
-      </c>
       <c r="I6" s="3" t="s">
+        <v>206</v>
+      </c>
+      <c r="J6" s="3" t="s">
+        <v>207</v>
+      </c>
+      <c r="K6" s="3" t="s">
+        <v>206</v>
+      </c>
+      <c r="L6" s="3" t="s">
+        <v>207</v>
+      </c>
+      <c r="M6" s="3" t="s">
+        <v>206</v>
+      </c>
+      <c r="N6" s="3" t="s">
         <v>208</v>
       </c>
-      <c r="J6" s="3" t="s">
+      <c r="O6" s="3" t="s">
+        <v>206</v>
+      </c>
+      <c r="P6" s="3" t="s">
         <v>209</v>
       </c>
-      <c r="K6" s="3" t="s">
-        <v>208</v>
-      </c>
-      <c r="L6" s="3" t="s">
-        <v>209</v>
-      </c>
-      <c r="M6" s="3" t="s">
-        <v>208</v>
-      </c>
-      <c r="N6" s="3" t="s">
+      <c r="Q6" s="3" t="s">
+        <v>85</v>
+      </c>
+      <c r="R6" s="3" t="s">
         <v>210</v>
       </c>
-      <c r="O6" s="3" t="s">
-        <v>208</v>
-      </c>
-      <c r="P6" s="3" t="s">
+      <c r="S6" s="3" t="s">
         <v>211</v>
       </c>
-      <c r="Q6" s="3" t="s">
-        <v>85</v>
-      </c>
-      <c r="R6" s="3" t="s">
+      <c r="T6" s="3" t="s">
         <v>212</v>
-      </c>
-      <c r="S6" s="3" t="s">
-        <v>213</v>
-      </c>
-      <c r="T6" s="3" t="s">
-        <v>214</v>
       </c>
     </row>
     <row r="7" spans="1:20" ht="45" customHeight="1" x14ac:dyDescent="0.25">
@@ -5406,61 +5400,61 @@
         <v>117</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>217</v>
+        <v>215</v>
       </c>
       <c r="C7" s="3" t="s">
+        <v>201</v>
+      </c>
+      <c r="D7" s="3" t="s">
+        <v>202</v>
+      </c>
+      <c r="E7" s="3" t="s">
         <v>203</v>
       </c>
-      <c r="D7" s="3" t="s">
+      <c r="F7" s="3" t="s">
         <v>204</v>
       </c>
-      <c r="E7" s="3" t="s">
+      <c r="G7" s="3" t="s">
+        <v>85</v>
+      </c>
+      <c r="H7" s="3" t="s">
         <v>205</v>
       </c>
-      <c r="F7" s="3" t="s">
-        <v>206</v>
-      </c>
-      <c r="G7" s="3" t="s">
-        <v>85</v>
-      </c>
-      <c r="H7" s="3" t="s">
-        <v>207</v>
-      </c>
       <c r="I7" s="3" t="s">
+        <v>206</v>
+      </c>
+      <c r="J7" s="3" t="s">
+        <v>207</v>
+      </c>
+      <c r="K7" s="3" t="s">
+        <v>206</v>
+      </c>
+      <c r="L7" s="3" t="s">
+        <v>207</v>
+      </c>
+      <c r="M7" s="3" t="s">
+        <v>206</v>
+      </c>
+      <c r="N7" s="3" t="s">
         <v>208</v>
       </c>
-      <c r="J7" s="3" t="s">
+      <c r="O7" s="3" t="s">
+        <v>206</v>
+      </c>
+      <c r="P7" s="3" t="s">
         <v>209</v>
       </c>
-      <c r="K7" s="3" t="s">
-        <v>208</v>
-      </c>
-      <c r="L7" s="3" t="s">
-        <v>209</v>
-      </c>
-      <c r="M7" s="3" t="s">
-        <v>208</v>
-      </c>
-      <c r="N7" s="3" t="s">
+      <c r="Q7" s="3" t="s">
+        <v>85</v>
+      </c>
+      <c r="R7" s="3" t="s">
         <v>210</v>
       </c>
-      <c r="O7" s="3" t="s">
-        <v>208</v>
-      </c>
-      <c r="P7" s="3" t="s">
+      <c r="S7" s="3" t="s">
         <v>211</v>
       </c>
-      <c r="Q7" s="3" t="s">
-        <v>85</v>
-      </c>
-      <c r="R7" s="3" t="s">
+      <c r="T7" s="3" t="s">
         <v>212</v>
-      </c>
-      <c r="S7" s="3" t="s">
-        <v>213</v>
-      </c>
-      <c r="T7" s="3" t="s">
-        <v>214</v>
       </c>
     </row>
     <row r="8" spans="1:20" ht="45" customHeight="1" x14ac:dyDescent="0.25">
@@ -5468,61 +5462,61 @@
         <v>123</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>218</v>
+        <v>216</v>
       </c>
       <c r="C8" s="3" t="s">
+        <v>201</v>
+      </c>
+      <c r="D8" s="3" t="s">
+        <v>202</v>
+      </c>
+      <c r="E8" s="3" t="s">
         <v>203</v>
       </c>
-      <c r="D8" s="3" t="s">
+      <c r="F8" s="3" t="s">
         <v>204</v>
       </c>
-      <c r="E8" s="3" t="s">
+      <c r="G8" s="3" t="s">
+        <v>85</v>
+      </c>
+      <c r="H8" s="3" t="s">
         <v>205</v>
       </c>
-      <c r="F8" s="3" t="s">
-        <v>206</v>
-      </c>
-      <c r="G8" s="3" t="s">
-        <v>85</v>
-      </c>
-      <c r="H8" s="3" t="s">
-        <v>207</v>
-      </c>
       <c r="I8" s="3" t="s">
+        <v>206</v>
+      </c>
+      <c r="J8" s="3" t="s">
+        <v>207</v>
+      </c>
+      <c r="K8" s="3" t="s">
+        <v>206</v>
+      </c>
+      <c r="L8" s="3" t="s">
+        <v>207</v>
+      </c>
+      <c r="M8" s="3" t="s">
+        <v>206</v>
+      </c>
+      <c r="N8" s="3" t="s">
         <v>208</v>
       </c>
-      <c r="J8" s="3" t="s">
+      <c r="O8" s="3" t="s">
+        <v>206</v>
+      </c>
+      <c r="P8" s="3" t="s">
         <v>209</v>
       </c>
-      <c r="K8" s="3" t="s">
-        <v>208</v>
-      </c>
-      <c r="L8" s="3" t="s">
-        <v>209</v>
-      </c>
-      <c r="M8" s="3" t="s">
-        <v>208</v>
-      </c>
-      <c r="N8" s="3" t="s">
+      <c r="Q8" s="3" t="s">
+        <v>85</v>
+      </c>
+      <c r="R8" s="3" t="s">
         <v>210</v>
       </c>
-      <c r="O8" s="3" t="s">
-        <v>208</v>
-      </c>
-      <c r="P8" s="3" t="s">
+      <c r="S8" s="3" t="s">
         <v>211</v>
       </c>
-      <c r="Q8" s="3" t="s">
-        <v>85</v>
-      </c>
-      <c r="R8" s="3" t="s">
+      <c r="T8" s="3" t="s">
         <v>212</v>
-      </c>
-      <c r="S8" s="3" t="s">
-        <v>213</v>
-      </c>
-      <c r="T8" s="3" t="s">
-        <v>214</v>
       </c>
     </row>
     <row r="9" spans="1:20" ht="45" customHeight="1" x14ac:dyDescent="0.25">
@@ -5530,61 +5524,61 @@
         <v>129</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>219</v>
+        <v>217</v>
       </c>
       <c r="C9" s="3" t="s">
+        <v>201</v>
+      </c>
+      <c r="D9" s="3" t="s">
+        <v>202</v>
+      </c>
+      <c r="E9" s="3" t="s">
         <v>203</v>
       </c>
-      <c r="D9" s="3" t="s">
+      <c r="F9" s="3" t="s">
         <v>204</v>
       </c>
-      <c r="E9" s="3" t="s">
+      <c r="G9" s="3" t="s">
+        <v>85</v>
+      </c>
+      <c r="H9" s="3" t="s">
         <v>205</v>
       </c>
-      <c r="F9" s="3" t="s">
-        <v>206</v>
-      </c>
-      <c r="G9" s="3" t="s">
-        <v>85</v>
-      </c>
-      <c r="H9" s="3" t="s">
-        <v>207</v>
-      </c>
       <c r="I9" s="3" t="s">
+        <v>206</v>
+      </c>
+      <c r="J9" s="3" t="s">
+        <v>207</v>
+      </c>
+      <c r="K9" s="3" t="s">
+        <v>206</v>
+      </c>
+      <c r="L9" s="3" t="s">
+        <v>207</v>
+      </c>
+      <c r="M9" s="3" t="s">
+        <v>206</v>
+      </c>
+      <c r="N9" s="3" t="s">
         <v>208</v>
       </c>
-      <c r="J9" s="3" t="s">
+      <c r="O9" s="3" t="s">
+        <v>206</v>
+      </c>
+      <c r="P9" s="3" t="s">
         <v>209</v>
       </c>
-      <c r="K9" s="3" t="s">
-        <v>208</v>
-      </c>
-      <c r="L9" s="3" t="s">
-        <v>209</v>
-      </c>
-      <c r="M9" s="3" t="s">
-        <v>208</v>
-      </c>
-      <c r="N9" s="3" t="s">
+      <c r="Q9" s="3" t="s">
+        <v>85</v>
+      </c>
+      <c r="R9" s="3" t="s">
         <v>210</v>
       </c>
-      <c r="O9" s="3" t="s">
-        <v>208</v>
-      </c>
-      <c r="P9" s="3" t="s">
+      <c r="S9" s="3" t="s">
         <v>211</v>
       </c>
-      <c r="Q9" s="3" t="s">
-        <v>85</v>
-      </c>
-      <c r="R9" s="3" t="s">
+      <c r="T9" s="3" t="s">
         <v>212</v>
-      </c>
-      <c r="S9" s="3" t="s">
-        <v>213</v>
-      </c>
-      <c r="T9" s="3" t="s">
-        <v>214</v>
       </c>
     </row>
     <row r="10" spans="1:20" ht="45" customHeight="1" x14ac:dyDescent="0.25">
@@ -5592,61 +5586,61 @@
         <v>130</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>220</v>
+        <v>218</v>
       </c>
       <c r="C10" s="3" t="s">
+        <v>201</v>
+      </c>
+      <c r="D10" s="3" t="s">
+        <v>202</v>
+      </c>
+      <c r="E10" s="3" t="s">
         <v>203</v>
       </c>
-      <c r="D10" s="3" t="s">
+      <c r="F10" s="3" t="s">
         <v>204</v>
       </c>
-      <c r="E10" s="3" t="s">
+      <c r="G10" s="3" t="s">
+        <v>85</v>
+      </c>
+      <c r="H10" s="3" t="s">
         <v>205</v>
       </c>
-      <c r="F10" s="3" t="s">
-        <v>206</v>
-      </c>
-      <c r="G10" s="3" t="s">
-        <v>85</v>
-      </c>
-      <c r="H10" s="3" t="s">
-        <v>207</v>
-      </c>
       <c r="I10" s="3" t="s">
+        <v>206</v>
+      </c>
+      <c r="J10" s="3" t="s">
+        <v>207</v>
+      </c>
+      <c r="K10" s="3" t="s">
+        <v>206</v>
+      </c>
+      <c r="L10" s="3" t="s">
+        <v>207</v>
+      </c>
+      <c r="M10" s="3" t="s">
+        <v>206</v>
+      </c>
+      <c r="N10" s="3" t="s">
         <v>208</v>
       </c>
-      <c r="J10" s="3" t="s">
+      <c r="O10" s="3" t="s">
+        <v>206</v>
+      </c>
+      <c r="P10" s="3" t="s">
         <v>209</v>
       </c>
-      <c r="K10" s="3" t="s">
-        <v>208</v>
-      </c>
-      <c r="L10" s="3" t="s">
-        <v>209</v>
-      </c>
-      <c r="M10" s="3" t="s">
-        <v>208</v>
-      </c>
-      <c r="N10" s="3" t="s">
+      <c r="Q10" s="3" t="s">
+        <v>85</v>
+      </c>
+      <c r="R10" s="3" t="s">
         <v>210</v>
       </c>
-      <c r="O10" s="3" t="s">
-        <v>208</v>
-      </c>
-      <c r="P10" s="3" t="s">
+      <c r="S10" s="3" t="s">
         <v>211</v>
       </c>
-      <c r="Q10" s="3" t="s">
-        <v>85</v>
-      </c>
-      <c r="R10" s="3" t="s">
+      <c r="T10" s="3" t="s">
         <v>212</v>
-      </c>
-      <c r="S10" s="3" t="s">
-        <v>213</v>
-      </c>
-      <c r="T10" s="3" t="s">
-        <v>214</v>
       </c>
     </row>
     <row r="11" spans="1:20" ht="45" customHeight="1" x14ac:dyDescent="0.25">
@@ -5654,61 +5648,61 @@
         <v>131</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>221</v>
+        <v>219</v>
       </c>
       <c r="C11" s="3" t="s">
+        <v>201</v>
+      </c>
+      <c r="D11" s="3" t="s">
+        <v>202</v>
+      </c>
+      <c r="E11" s="3" t="s">
         <v>203</v>
       </c>
-      <c r="D11" s="3" t="s">
+      <c r="F11" s="3" t="s">
         <v>204</v>
       </c>
-      <c r="E11" s="3" t="s">
+      <c r="G11" s="3" t="s">
+        <v>85</v>
+      </c>
+      <c r="H11" s="3" t="s">
         <v>205</v>
       </c>
-      <c r="F11" s="3" t="s">
-        <v>206</v>
-      </c>
-      <c r="G11" s="3" t="s">
-        <v>85</v>
-      </c>
-      <c r="H11" s="3" t="s">
-        <v>207</v>
-      </c>
       <c r="I11" s="3" t="s">
+        <v>206</v>
+      </c>
+      <c r="J11" s="3" t="s">
+        <v>207</v>
+      </c>
+      <c r="K11" s="3" t="s">
+        <v>206</v>
+      </c>
+      <c r="L11" s="3" t="s">
+        <v>207</v>
+      </c>
+      <c r="M11" s="3" t="s">
+        <v>206</v>
+      </c>
+      <c r="N11" s="3" t="s">
         <v>208</v>
       </c>
-      <c r="J11" s="3" t="s">
+      <c r="O11" s="3" t="s">
+        <v>206</v>
+      </c>
+      <c r="P11" s="3" t="s">
         <v>209</v>
       </c>
-      <c r="K11" s="3" t="s">
-        <v>208</v>
-      </c>
-      <c r="L11" s="3" t="s">
-        <v>209</v>
-      </c>
-      <c r="M11" s="3" t="s">
-        <v>208</v>
-      </c>
-      <c r="N11" s="3" t="s">
+      <c r="Q11" s="3" t="s">
+        <v>85</v>
+      </c>
+      <c r="R11" s="3" t="s">
         <v>210</v>
       </c>
-      <c r="O11" s="3" t="s">
-        <v>208</v>
-      </c>
-      <c r="P11" s="3" t="s">
+      <c r="S11" s="3" t="s">
         <v>211</v>
       </c>
-      <c r="Q11" s="3" t="s">
-        <v>85</v>
-      </c>
-      <c r="R11" s="3" t="s">
+      <c r="T11" s="3" t="s">
         <v>212</v>
-      </c>
-      <c r="S11" s="3" t="s">
-        <v>213</v>
-      </c>
-      <c r="T11" s="3" t="s">
-        <v>214</v>
       </c>
     </row>
     <row r="12" spans="1:20" ht="45" customHeight="1" x14ac:dyDescent="0.25">
@@ -5716,61 +5710,61 @@
         <v>132</v>
       </c>
       <c r="B12" s="3" t="s">
-        <v>222</v>
+        <v>220</v>
       </c>
       <c r="C12" s="3" t="s">
+        <v>201</v>
+      </c>
+      <c r="D12" s="3" t="s">
+        <v>202</v>
+      </c>
+      <c r="E12" s="3" t="s">
         <v>203</v>
       </c>
-      <c r="D12" s="3" t="s">
+      <c r="F12" s="3" t="s">
         <v>204</v>
       </c>
-      <c r="E12" s="3" t="s">
+      <c r="G12" s="3" t="s">
+        <v>85</v>
+      </c>
+      <c r="H12" s="3" t="s">
         <v>205</v>
       </c>
-      <c r="F12" s="3" t="s">
-        <v>206</v>
-      </c>
-      <c r="G12" s="3" t="s">
-        <v>85</v>
-      </c>
-      <c r="H12" s="3" t="s">
-        <v>207</v>
-      </c>
       <c r="I12" s="3" t="s">
+        <v>206</v>
+      </c>
+      <c r="J12" s="3" t="s">
+        <v>207</v>
+      </c>
+      <c r="K12" s="3" t="s">
+        <v>206</v>
+      </c>
+      <c r="L12" s="3" t="s">
+        <v>207</v>
+      </c>
+      <c r="M12" s="3" t="s">
+        <v>206</v>
+      </c>
+      <c r="N12" s="3" t="s">
         <v>208</v>
       </c>
-      <c r="J12" s="3" t="s">
+      <c r="O12" s="3" t="s">
+        <v>206</v>
+      </c>
+      <c r="P12" s="3" t="s">
         <v>209</v>
       </c>
-      <c r="K12" s="3" t="s">
-        <v>208</v>
-      </c>
-      <c r="L12" s="3" t="s">
-        <v>209</v>
-      </c>
-      <c r="M12" s="3" t="s">
-        <v>208</v>
-      </c>
-      <c r="N12" s="3" t="s">
+      <c r="Q12" s="3" t="s">
+        <v>85</v>
+      </c>
+      <c r="R12" s="3" t="s">
         <v>210</v>
       </c>
-      <c r="O12" s="3" t="s">
-        <v>208</v>
-      </c>
-      <c r="P12" s="3" t="s">
+      <c r="S12" s="3" t="s">
         <v>211</v>
       </c>
-      <c r="Q12" s="3" t="s">
-        <v>85</v>
-      </c>
-      <c r="R12" s="3" t="s">
+      <c r="T12" s="3" t="s">
         <v>212</v>
-      </c>
-      <c r="S12" s="3" t="s">
-        <v>213</v>
-      </c>
-      <c r="T12" s="3" t="s">
-        <v>214</v>
       </c>
     </row>
     <row r="13" spans="1:20" ht="45" customHeight="1" x14ac:dyDescent="0.25">
@@ -5778,61 +5772,61 @@
         <v>133</v>
       </c>
       <c r="B13" s="3" t="s">
-        <v>223</v>
+        <v>221</v>
       </c>
       <c r="C13" s="3" t="s">
+        <v>201</v>
+      </c>
+      <c r="D13" s="3" t="s">
+        <v>202</v>
+      </c>
+      <c r="E13" s="3" t="s">
         <v>203</v>
       </c>
-      <c r="D13" s="3" t="s">
+      <c r="F13" s="3" t="s">
         <v>204</v>
       </c>
-      <c r="E13" s="3" t="s">
+      <c r="G13" s="3" t="s">
+        <v>85</v>
+      </c>
+      <c r="H13" s="3" t="s">
         <v>205</v>
       </c>
-      <c r="F13" s="3" t="s">
-        <v>206</v>
-      </c>
-      <c r="G13" s="3" t="s">
-        <v>85</v>
-      </c>
-      <c r="H13" s="3" t="s">
-        <v>207</v>
-      </c>
       <c r="I13" s="3" t="s">
+        <v>206</v>
+      </c>
+      <c r="J13" s="3" t="s">
+        <v>207</v>
+      </c>
+      <c r="K13" s="3" t="s">
+        <v>206</v>
+      </c>
+      <c r="L13" s="3" t="s">
+        <v>207</v>
+      </c>
+      <c r="M13" s="3" t="s">
+        <v>206</v>
+      </c>
+      <c r="N13" s="3" t="s">
         <v>208</v>
       </c>
-      <c r="J13" s="3" t="s">
+      <c r="O13" s="3" t="s">
+        <v>206</v>
+      </c>
+      <c r="P13" s="3" t="s">
         <v>209</v>
       </c>
-      <c r="K13" s="3" t="s">
-        <v>208</v>
-      </c>
-      <c r="L13" s="3" t="s">
-        <v>209</v>
-      </c>
-      <c r="M13" s="3" t="s">
-        <v>208</v>
-      </c>
-      <c r="N13" s="3" t="s">
+      <c r="Q13" s="3" t="s">
+        <v>85</v>
+      </c>
+      <c r="R13" s="3" t="s">
         <v>210</v>
       </c>
-      <c r="O13" s="3" t="s">
-        <v>208</v>
-      </c>
-      <c r="P13" s="3" t="s">
+      <c r="S13" s="3" t="s">
         <v>211</v>
       </c>
-      <c r="Q13" s="3" t="s">
-        <v>85</v>
-      </c>
-      <c r="R13" s="3" t="s">
+      <c r="T13" s="3" t="s">
         <v>212</v>
-      </c>
-      <c r="S13" s="3" t="s">
-        <v>213</v>
-      </c>
-      <c r="T13" s="3" t="s">
-        <v>214</v>
       </c>
     </row>
     <row r="14" spans="1:20" ht="45" customHeight="1" x14ac:dyDescent="0.25">
@@ -5840,61 +5834,61 @@
         <v>134</v>
       </c>
       <c r="B14" s="3" t="s">
-        <v>224</v>
+        <v>222</v>
       </c>
       <c r="C14" s="3" t="s">
+        <v>201</v>
+      </c>
+      <c r="D14" s="3" t="s">
+        <v>202</v>
+      </c>
+      <c r="E14" s="3" t="s">
         <v>203</v>
       </c>
-      <c r="D14" s="3" t="s">
+      <c r="F14" s="3" t="s">
         <v>204</v>
       </c>
-      <c r="E14" s="3" t="s">
+      <c r="G14" s="3" t="s">
+        <v>85</v>
+      </c>
+      <c r="H14" s="3" t="s">
         <v>205</v>
       </c>
-      <c r="F14" s="3" t="s">
-        <v>206</v>
-      </c>
-      <c r="G14" s="3" t="s">
-        <v>85</v>
-      </c>
-      <c r="H14" s="3" t="s">
-        <v>207</v>
-      </c>
       <c r="I14" s="3" t="s">
+        <v>206</v>
+      </c>
+      <c r="J14" s="3" t="s">
+        <v>207</v>
+      </c>
+      <c r="K14" s="3" t="s">
+        <v>206</v>
+      </c>
+      <c r="L14" s="3" t="s">
+        <v>207</v>
+      </c>
+      <c r="M14" s="3" t="s">
+        <v>206</v>
+      </c>
+      <c r="N14" s="3" t="s">
         <v>208</v>
       </c>
-      <c r="J14" s="3" t="s">
+      <c r="O14" s="3" t="s">
+        <v>206</v>
+      </c>
+      <c r="P14" s="3" t="s">
         <v>209</v>
       </c>
-      <c r="K14" s="3" t="s">
-        <v>208</v>
-      </c>
-      <c r="L14" s="3" t="s">
-        <v>209</v>
-      </c>
-      <c r="M14" s="3" t="s">
-        <v>208</v>
-      </c>
-      <c r="N14" s="3" t="s">
+      <c r="Q14" s="3" t="s">
+        <v>85</v>
+      </c>
+      <c r="R14" s="3" t="s">
         <v>210</v>
       </c>
-      <c r="O14" s="3" t="s">
-        <v>208</v>
-      </c>
-      <c r="P14" s="3" t="s">
+      <c r="S14" s="3" t="s">
         <v>211</v>
       </c>
-      <c r="Q14" s="3" t="s">
-        <v>85</v>
-      </c>
-      <c r="R14" s="3" t="s">
+      <c r="T14" s="3" t="s">
         <v>212</v>
-      </c>
-      <c r="S14" s="3" t="s">
-        <v>213</v>
-      </c>
-      <c r="T14" s="3" t="s">
-        <v>214</v>
       </c>
     </row>
     <row r="15" spans="1:20" ht="45" customHeight="1" x14ac:dyDescent="0.25">
@@ -5902,681 +5896,681 @@
         <v>135</v>
       </c>
       <c r="B15" s="3" t="s">
-        <v>225</v>
+        <v>223</v>
       </c>
       <c r="C15" s="3" t="s">
+        <v>201</v>
+      </c>
+      <c r="D15" s="3" t="s">
+        <v>202</v>
+      </c>
+      <c r="E15" s="3" t="s">
         <v>203</v>
       </c>
-      <c r="D15" s="3" t="s">
+      <c r="F15" s="3" t="s">
         <v>204</v>
       </c>
-      <c r="E15" s="3" t="s">
+      <c r="G15" s="3" t="s">
+        <v>85</v>
+      </c>
+      <c r="H15" s="3" t="s">
         <v>205</v>
       </c>
-      <c r="F15" s="3" t="s">
-        <v>206</v>
-      </c>
-      <c r="G15" s="3" t="s">
-        <v>85</v>
-      </c>
-      <c r="H15" s="3" t="s">
-        <v>207</v>
-      </c>
       <c r="I15" s="3" t="s">
+        <v>206</v>
+      </c>
+      <c r="J15" s="3" t="s">
+        <v>207</v>
+      </c>
+      <c r="K15" s="3" t="s">
+        <v>206</v>
+      </c>
+      <c r="L15" s="3" t="s">
+        <v>207</v>
+      </c>
+      <c r="M15" s="3" t="s">
+        <v>206</v>
+      </c>
+      <c r="N15" s="3" t="s">
         <v>208</v>
       </c>
-      <c r="J15" s="3" t="s">
+      <c r="O15" s="3" t="s">
+        <v>206</v>
+      </c>
+      <c r="P15" s="3" t="s">
         <v>209</v>
       </c>
-      <c r="K15" s="3" t="s">
-        <v>208</v>
-      </c>
-      <c r="L15" s="3" t="s">
-        <v>209</v>
-      </c>
-      <c r="M15" s="3" t="s">
-        <v>208</v>
-      </c>
-      <c r="N15" s="3" t="s">
+      <c r="Q15" s="3" t="s">
+        <v>85</v>
+      </c>
+      <c r="R15" s="3" t="s">
         <v>210</v>
       </c>
-      <c r="O15" s="3" t="s">
-        <v>208</v>
-      </c>
-      <c r="P15" s="3" t="s">
+      <c r="S15" s="3" t="s">
         <v>211</v>
       </c>
-      <c r="Q15" s="3" t="s">
-        <v>85</v>
-      </c>
-      <c r="R15" s="3" t="s">
+      <c r="T15" s="3" t="s">
         <v>212</v>
-      </c>
-      <c r="S15" s="3" t="s">
-        <v>213</v>
-      </c>
-      <c r="T15" s="3" t="s">
-        <v>214</v>
       </c>
     </row>
     <row r="16" spans="1:20" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16" s="3" t="s">
-        <v>136</v>
+        <v>139</v>
       </c>
       <c r="B16" s="3" t="s">
-        <v>226</v>
+        <v>224</v>
       </c>
       <c r="C16" s="3" t="s">
+        <v>201</v>
+      </c>
+      <c r="D16" s="3" t="s">
+        <v>202</v>
+      </c>
+      <c r="E16" s="3" t="s">
         <v>203</v>
       </c>
-      <c r="D16" s="3" t="s">
+      <c r="F16" s="3" t="s">
         <v>204</v>
       </c>
-      <c r="E16" s="3" t="s">
+      <c r="G16" s="3" t="s">
+        <v>85</v>
+      </c>
+      <c r="H16" s="3" t="s">
         <v>205</v>
       </c>
-      <c r="F16" s="3" t="s">
-        <v>206</v>
-      </c>
-      <c r="G16" s="3" t="s">
-        <v>85</v>
-      </c>
-      <c r="H16" s="3" t="s">
-        <v>207</v>
-      </c>
       <c r="I16" s="3" t="s">
+        <v>206</v>
+      </c>
+      <c r="J16" s="3" t="s">
+        <v>207</v>
+      </c>
+      <c r="K16" s="3" t="s">
+        <v>206</v>
+      </c>
+      <c r="L16" s="3" t="s">
+        <v>207</v>
+      </c>
+      <c r="M16" s="3" t="s">
+        <v>206</v>
+      </c>
+      <c r="N16" s="3" t="s">
         <v>208</v>
       </c>
-      <c r="J16" s="3" t="s">
+      <c r="O16" s="3" t="s">
+        <v>206</v>
+      </c>
+      <c r="P16" s="3" t="s">
         <v>209</v>
       </c>
-      <c r="K16" s="3" t="s">
-        <v>208</v>
-      </c>
-      <c r="L16" s="3" t="s">
-        <v>209</v>
-      </c>
-      <c r="M16" s="3" t="s">
-        <v>208</v>
-      </c>
-      <c r="N16" s="3" t="s">
+      <c r="Q16" s="3" t="s">
+        <v>85</v>
+      </c>
+      <c r="R16" s="3" t="s">
         <v>210</v>
       </c>
-      <c r="O16" s="3" t="s">
-        <v>208</v>
-      </c>
-      <c r="P16" s="3" t="s">
+      <c r="S16" s="3" t="s">
         <v>211</v>
       </c>
-      <c r="Q16" s="3" t="s">
-        <v>85</v>
-      </c>
-      <c r="R16" s="3" t="s">
+      <c r="T16" s="3" t="s">
         <v>212</v>
-      </c>
-      <c r="S16" s="3" t="s">
-        <v>213</v>
-      </c>
-      <c r="T16" s="3" t="s">
-        <v>214</v>
       </c>
     </row>
     <row r="17" spans="1:20" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17" s="3" t="s">
-        <v>138</v>
+        <v>144</v>
       </c>
       <c r="B17" s="3" t="s">
-        <v>227</v>
+        <v>225</v>
       </c>
       <c r="C17" s="3" t="s">
+        <v>201</v>
+      </c>
+      <c r="D17" s="3" t="s">
+        <v>202</v>
+      </c>
+      <c r="E17" s="3" t="s">
         <v>203</v>
       </c>
-      <c r="D17" s="3" t="s">
+      <c r="F17" s="3" t="s">
         <v>204</v>
       </c>
-      <c r="E17" s="3" t="s">
+      <c r="G17" s="3" t="s">
+        <v>85</v>
+      </c>
+      <c r="H17" s="3" t="s">
         <v>205</v>
       </c>
-      <c r="F17" s="3" t="s">
-        <v>206</v>
-      </c>
-      <c r="G17" s="3" t="s">
-        <v>85</v>
-      </c>
-      <c r="H17" s="3" t="s">
-        <v>207</v>
-      </c>
       <c r="I17" s="3" t="s">
+        <v>206</v>
+      </c>
+      <c r="J17" s="3" t="s">
+        <v>207</v>
+      </c>
+      <c r="K17" s="3" t="s">
+        <v>206</v>
+      </c>
+      <c r="L17" s="3" t="s">
+        <v>207</v>
+      </c>
+      <c r="M17" s="3" t="s">
+        <v>206</v>
+      </c>
+      <c r="N17" s="3" t="s">
         <v>208</v>
       </c>
-      <c r="J17" s="3" t="s">
+      <c r="O17" s="3" t="s">
+        <v>206</v>
+      </c>
+      <c r="P17" s="3" t="s">
         <v>209</v>
       </c>
-      <c r="K17" s="3" t="s">
-        <v>208</v>
-      </c>
-      <c r="L17" s="3" t="s">
-        <v>209</v>
-      </c>
-      <c r="M17" s="3" t="s">
-        <v>208</v>
-      </c>
-      <c r="N17" s="3" t="s">
+      <c r="Q17" s="3" t="s">
+        <v>85</v>
+      </c>
+      <c r="R17" s="3" t="s">
         <v>210</v>
       </c>
-      <c r="O17" s="3" t="s">
-        <v>208</v>
-      </c>
-      <c r="P17" s="3" t="s">
+      <c r="S17" s="3" t="s">
         <v>211</v>
       </c>
-      <c r="Q17" s="3" t="s">
-        <v>85</v>
-      </c>
-      <c r="R17" s="3" t="s">
+      <c r="T17" s="3" t="s">
         <v>212</v>
-      </c>
-      <c r="S17" s="3" t="s">
-        <v>213</v>
-      </c>
-      <c r="T17" s="3" t="s">
-        <v>214</v>
       </c>
     </row>
     <row r="18" spans="1:20" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A18" s="3" t="s">
-        <v>139</v>
+        <v>146</v>
       </c>
       <c r="B18" s="3" t="s">
-        <v>228</v>
+        <v>226</v>
       </c>
       <c r="C18" s="3" t="s">
+        <v>201</v>
+      </c>
+      <c r="D18" s="3" t="s">
+        <v>202</v>
+      </c>
+      <c r="E18" s="3" t="s">
         <v>203</v>
       </c>
-      <c r="D18" s="3" t="s">
+      <c r="F18" s="3" t="s">
         <v>204</v>
       </c>
-      <c r="E18" s="3" t="s">
+      <c r="G18" s="3" t="s">
+        <v>85</v>
+      </c>
+      <c r="H18" s="3" t="s">
         <v>205</v>
       </c>
-      <c r="F18" s="3" t="s">
-        <v>206</v>
-      </c>
-      <c r="G18" s="3" t="s">
-        <v>85</v>
-      </c>
-      <c r="H18" s="3" t="s">
-        <v>207</v>
-      </c>
       <c r="I18" s="3" t="s">
+        <v>206</v>
+      </c>
+      <c r="J18" s="3" t="s">
+        <v>207</v>
+      </c>
+      <c r="K18" s="3" t="s">
+        <v>206</v>
+      </c>
+      <c r="L18" s="3" t="s">
+        <v>207</v>
+      </c>
+      <c r="M18" s="3" t="s">
+        <v>206</v>
+      </c>
+      <c r="N18" s="3" t="s">
         <v>208</v>
       </c>
-      <c r="J18" s="3" t="s">
+      <c r="O18" s="3" t="s">
+        <v>206</v>
+      </c>
+      <c r="P18" s="3" t="s">
         <v>209</v>
       </c>
-      <c r="K18" s="3" t="s">
-        <v>208</v>
-      </c>
-      <c r="L18" s="3" t="s">
-        <v>209</v>
-      </c>
-      <c r="M18" s="3" t="s">
-        <v>208</v>
-      </c>
-      <c r="N18" s="3" t="s">
+      <c r="Q18" s="3" t="s">
+        <v>85</v>
+      </c>
+      <c r="R18" s="3" t="s">
         <v>210</v>
       </c>
-      <c r="O18" s="3" t="s">
-        <v>208</v>
-      </c>
-      <c r="P18" s="3" t="s">
+      <c r="S18" s="3" t="s">
         <v>211</v>
       </c>
-      <c r="Q18" s="3" t="s">
-        <v>85</v>
-      </c>
-      <c r="R18" s="3" t="s">
+      <c r="T18" s="3" t="s">
         <v>212</v>
-      </c>
-      <c r="S18" s="3" t="s">
-        <v>213</v>
-      </c>
-      <c r="T18" s="3" t="s">
-        <v>214</v>
       </c>
     </row>
     <row r="19" spans="1:20" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A19" s="3" t="s">
-        <v>141</v>
+        <v>149</v>
       </c>
       <c r="B19" s="3" t="s">
-        <v>229</v>
+        <v>227</v>
       </c>
       <c r="C19" s="3" t="s">
+        <v>201</v>
+      </c>
+      <c r="D19" s="3" t="s">
+        <v>202</v>
+      </c>
+      <c r="E19" s="3" t="s">
         <v>203</v>
       </c>
-      <c r="D19" s="3" t="s">
+      <c r="F19" s="3" t="s">
         <v>204</v>
       </c>
-      <c r="E19" s="3" t="s">
+      <c r="G19" s="3" t="s">
+        <v>85</v>
+      </c>
+      <c r="H19" s="3" t="s">
         <v>205</v>
       </c>
-      <c r="F19" s="3" t="s">
-        <v>206</v>
-      </c>
-      <c r="G19" s="3" t="s">
-        <v>85</v>
-      </c>
-      <c r="H19" s="3" t="s">
-        <v>207</v>
-      </c>
       <c r="I19" s="3" t="s">
+        <v>206</v>
+      </c>
+      <c r="J19" s="3" t="s">
+        <v>207</v>
+      </c>
+      <c r="K19" s="3" t="s">
+        <v>206</v>
+      </c>
+      <c r="L19" s="3" t="s">
+        <v>207</v>
+      </c>
+      <c r="M19" s="3" t="s">
+        <v>206</v>
+      </c>
+      <c r="N19" s="3" t="s">
         <v>208</v>
       </c>
-      <c r="J19" s="3" t="s">
+      <c r="O19" s="3" t="s">
+        <v>206</v>
+      </c>
+      <c r="P19" s="3" t="s">
         <v>209</v>
       </c>
-      <c r="K19" s="3" t="s">
-        <v>208</v>
-      </c>
-      <c r="L19" s="3" t="s">
-        <v>209</v>
-      </c>
-      <c r="M19" s="3" t="s">
-        <v>208</v>
-      </c>
-      <c r="N19" s="3" t="s">
+      <c r="Q19" s="3" t="s">
+        <v>85</v>
+      </c>
+      <c r="R19" s="3" t="s">
         <v>210</v>
       </c>
-      <c r="O19" s="3" t="s">
-        <v>208</v>
-      </c>
-      <c r="P19" s="3" t="s">
+      <c r="S19" s="3" t="s">
         <v>211</v>
       </c>
-      <c r="Q19" s="3" t="s">
-        <v>85</v>
-      </c>
-      <c r="R19" s="3" t="s">
+      <c r="T19" s="3" t="s">
         <v>212</v>
-      </c>
-      <c r="S19" s="3" t="s">
-        <v>213</v>
-      </c>
-      <c r="T19" s="3" t="s">
-        <v>214</v>
       </c>
     </row>
     <row r="20" spans="1:20" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A20" s="3" t="s">
-        <v>142</v>
+        <v>151</v>
       </c>
       <c r="B20" s="3" t="s">
-        <v>230</v>
+        <v>228</v>
       </c>
       <c r="C20" s="3" t="s">
+        <v>201</v>
+      </c>
+      <c r="D20" s="3" t="s">
+        <v>202</v>
+      </c>
+      <c r="E20" s="3" t="s">
         <v>203</v>
       </c>
-      <c r="D20" s="3" t="s">
+      <c r="F20" s="3" t="s">
         <v>204</v>
       </c>
-      <c r="E20" s="3" t="s">
+      <c r="G20" s="3" t="s">
+        <v>85</v>
+      </c>
+      <c r="H20" s="3" t="s">
         <v>205</v>
       </c>
-      <c r="F20" s="3" t="s">
-        <v>206</v>
-      </c>
-      <c r="G20" s="3" t="s">
-        <v>85</v>
-      </c>
-      <c r="H20" s="3" t="s">
-        <v>207</v>
-      </c>
       <c r="I20" s="3" t="s">
+        <v>206</v>
+      </c>
+      <c r="J20" s="3" t="s">
+        <v>207</v>
+      </c>
+      <c r="K20" s="3" t="s">
+        <v>206</v>
+      </c>
+      <c r="L20" s="3" t="s">
+        <v>207</v>
+      </c>
+      <c r="M20" s="3" t="s">
+        <v>206</v>
+      </c>
+      <c r="N20" s="3" t="s">
         <v>208</v>
       </c>
-      <c r="J20" s="3" t="s">
+      <c r="O20" s="3" t="s">
+        <v>206</v>
+      </c>
+      <c r="P20" s="3" t="s">
         <v>209</v>
       </c>
-      <c r="K20" s="3" t="s">
-        <v>208</v>
-      </c>
-      <c r="L20" s="3" t="s">
-        <v>209</v>
-      </c>
-      <c r="M20" s="3" t="s">
-        <v>208</v>
-      </c>
-      <c r="N20" s="3" t="s">
+      <c r="Q20" s="3" t="s">
+        <v>85</v>
+      </c>
+      <c r="R20" s="3" t="s">
         <v>210</v>
       </c>
-      <c r="O20" s="3" t="s">
-        <v>208</v>
-      </c>
-      <c r="P20" s="3" t="s">
+      <c r="S20" s="3" t="s">
         <v>211</v>
       </c>
-      <c r="Q20" s="3" t="s">
-        <v>85</v>
-      </c>
-      <c r="R20" s="3" t="s">
+      <c r="T20" s="3" t="s">
         <v>212</v>
-      </c>
-      <c r="S20" s="3" t="s">
-        <v>213</v>
-      </c>
-      <c r="T20" s="3" t="s">
-        <v>214</v>
       </c>
     </row>
     <row r="21" spans="1:20" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A21" s="3" t="s">
-        <v>144</v>
+        <v>154</v>
       </c>
       <c r="B21" s="3" t="s">
-        <v>231</v>
+        <v>229</v>
       </c>
       <c r="C21" s="3" t="s">
+        <v>201</v>
+      </c>
+      <c r="D21" s="3" t="s">
+        <v>202</v>
+      </c>
+      <c r="E21" s="3" t="s">
         <v>203</v>
       </c>
-      <c r="D21" s="3" t="s">
+      <c r="F21" s="3" t="s">
         <v>204</v>
       </c>
-      <c r="E21" s="3" t="s">
+      <c r="G21" s="3" t="s">
+        <v>85</v>
+      </c>
+      <c r="H21" s="3" t="s">
         <v>205</v>
       </c>
-      <c r="F21" s="3" t="s">
-        <v>206</v>
-      </c>
-      <c r="G21" s="3" t="s">
-        <v>85</v>
-      </c>
-      <c r="H21" s="3" t="s">
-        <v>207</v>
-      </c>
       <c r="I21" s="3" t="s">
+        <v>206</v>
+      </c>
+      <c r="J21" s="3" t="s">
+        <v>207</v>
+      </c>
+      <c r="K21" s="3" t="s">
+        <v>206</v>
+      </c>
+      <c r="L21" s="3" t="s">
+        <v>207</v>
+      </c>
+      <c r="M21" s="3" t="s">
+        <v>206</v>
+      </c>
+      <c r="N21" s="3" t="s">
         <v>208</v>
       </c>
-      <c r="J21" s="3" t="s">
+      <c r="O21" s="3" t="s">
+        <v>206</v>
+      </c>
+      <c r="P21" s="3" t="s">
         <v>209</v>
       </c>
-      <c r="K21" s="3" t="s">
-        <v>208</v>
-      </c>
-      <c r="L21" s="3" t="s">
-        <v>209</v>
-      </c>
-      <c r="M21" s="3" t="s">
-        <v>208</v>
-      </c>
-      <c r="N21" s="3" t="s">
+      <c r="Q21" s="3" t="s">
+        <v>85</v>
+      </c>
+      <c r="R21" s="3" t="s">
         <v>210</v>
       </c>
-      <c r="O21" s="3" t="s">
-        <v>208</v>
-      </c>
-      <c r="P21" s="3" t="s">
+      <c r="S21" s="3" t="s">
         <v>211</v>
       </c>
-      <c r="Q21" s="3" t="s">
-        <v>85</v>
-      </c>
-      <c r="R21" s="3" t="s">
+      <c r="T21" s="3" t="s">
         <v>212</v>
-      </c>
-      <c r="S21" s="3" t="s">
-        <v>213</v>
-      </c>
-      <c r="T21" s="3" t="s">
-        <v>214</v>
       </c>
     </row>
     <row r="22" spans="1:20" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A22" s="3" t="s">
-        <v>150</v>
+        <v>156</v>
       </c>
       <c r="B22" s="3" t="s">
-        <v>232</v>
+        <v>230</v>
       </c>
       <c r="C22" s="3" t="s">
+        <v>201</v>
+      </c>
+      <c r="D22" s="3" t="s">
+        <v>202</v>
+      </c>
+      <c r="E22" s="3" t="s">
         <v>203</v>
       </c>
-      <c r="D22" s="3" t="s">
+      <c r="F22" s="3" t="s">
         <v>204</v>
       </c>
-      <c r="E22" s="3" t="s">
+      <c r="G22" s="3" t="s">
+        <v>85</v>
+      </c>
+      <c r="H22" s="3" t="s">
         <v>205</v>
       </c>
-      <c r="F22" s="3" t="s">
-        <v>206</v>
-      </c>
-      <c r="G22" s="3" t="s">
-        <v>85</v>
-      </c>
-      <c r="H22" s="3" t="s">
-        <v>207</v>
-      </c>
       <c r="I22" s="3" t="s">
+        <v>206</v>
+      </c>
+      <c r="J22" s="3" t="s">
+        <v>207</v>
+      </c>
+      <c r="K22" s="3" t="s">
+        <v>206</v>
+      </c>
+      <c r="L22" s="3" t="s">
+        <v>207</v>
+      </c>
+      <c r="M22" s="3" t="s">
+        <v>206</v>
+      </c>
+      <c r="N22" s="3" t="s">
         <v>208</v>
       </c>
-      <c r="J22" s="3" t="s">
+      <c r="O22" s="3" t="s">
+        <v>206</v>
+      </c>
+      <c r="P22" s="3" t="s">
         <v>209</v>
       </c>
-      <c r="K22" s="3" t="s">
-        <v>208</v>
-      </c>
-      <c r="L22" s="3" t="s">
-        <v>209</v>
-      </c>
-      <c r="M22" s="3" t="s">
-        <v>208</v>
-      </c>
-      <c r="N22" s="3" t="s">
+      <c r="Q22" s="3" t="s">
+        <v>85</v>
+      </c>
+      <c r="R22" s="3" t="s">
         <v>210</v>
       </c>
-      <c r="O22" s="3" t="s">
-        <v>208</v>
-      </c>
-      <c r="P22" s="3" t="s">
+      <c r="S22" s="3" t="s">
         <v>211</v>
       </c>
-      <c r="Q22" s="3" t="s">
-        <v>85</v>
-      </c>
-      <c r="R22" s="3" t="s">
+      <c r="T22" s="3" t="s">
         <v>212</v>
-      </c>
-      <c r="S22" s="3" t="s">
-        <v>213</v>
-      </c>
-      <c r="T22" s="3" t="s">
-        <v>214</v>
       </c>
     </row>
     <row r="23" spans="1:20" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A23" s="3" t="s">
-        <v>154</v>
+        <v>157</v>
       </c>
       <c r="B23" s="3" t="s">
-        <v>233</v>
+        <v>231</v>
       </c>
       <c r="C23" s="3" t="s">
+        <v>201</v>
+      </c>
+      <c r="D23" s="3" t="s">
+        <v>202</v>
+      </c>
+      <c r="E23" s="3" t="s">
         <v>203</v>
       </c>
-      <c r="D23" s="3" t="s">
+      <c r="F23" s="3" t="s">
         <v>204</v>
       </c>
-      <c r="E23" s="3" t="s">
+      <c r="G23" s="3" t="s">
+        <v>85</v>
+      </c>
+      <c r="H23" s="3" t="s">
         <v>205</v>
       </c>
-      <c r="F23" s="3" t="s">
-        <v>206</v>
-      </c>
-      <c r="G23" s="3" t="s">
-        <v>85</v>
-      </c>
-      <c r="H23" s="3" t="s">
-        <v>207</v>
-      </c>
       <c r="I23" s="3" t="s">
+        <v>206</v>
+      </c>
+      <c r="J23" s="3" t="s">
+        <v>207</v>
+      </c>
+      <c r="K23" s="3" t="s">
+        <v>206</v>
+      </c>
+      <c r="L23" s="3" t="s">
+        <v>207</v>
+      </c>
+      <c r="M23" s="3" t="s">
+        <v>206</v>
+      </c>
+      <c r="N23" s="3" t="s">
         <v>208</v>
       </c>
-      <c r="J23" s="3" t="s">
+      <c r="O23" s="3" t="s">
+        <v>206</v>
+      </c>
+      <c r="P23" s="3" t="s">
         <v>209</v>
       </c>
-      <c r="K23" s="3" t="s">
-        <v>208</v>
-      </c>
-      <c r="L23" s="3" t="s">
-        <v>209</v>
-      </c>
-      <c r="M23" s="3" t="s">
-        <v>208</v>
-      </c>
-      <c r="N23" s="3" t="s">
+      <c r="Q23" s="3" t="s">
+        <v>85</v>
+      </c>
+      <c r="R23" s="3" t="s">
         <v>210</v>
       </c>
-      <c r="O23" s="3" t="s">
-        <v>208</v>
-      </c>
-      <c r="P23" s="3" t="s">
+      <c r="S23" s="3" t="s">
         <v>211</v>
       </c>
-      <c r="Q23" s="3" t="s">
-        <v>85</v>
-      </c>
-      <c r="R23" s="3" t="s">
+      <c r="T23" s="3" t="s">
         <v>212</v>
-      </c>
-      <c r="S23" s="3" t="s">
-        <v>213</v>
-      </c>
-      <c r="T23" s="3" t="s">
-        <v>214</v>
       </c>
     </row>
     <row r="24" spans="1:20" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A24" s="3" t="s">
-        <v>156</v>
+        <v>158</v>
       </c>
       <c r="B24" s="3" t="s">
-        <v>234</v>
+        <v>232</v>
       </c>
       <c r="C24" s="3" t="s">
+        <v>201</v>
+      </c>
+      <c r="D24" s="3" t="s">
+        <v>202</v>
+      </c>
+      <c r="E24" s="3" t="s">
         <v>203</v>
       </c>
-      <c r="D24" s="3" t="s">
+      <c r="F24" s="3" t="s">
         <v>204</v>
       </c>
-      <c r="E24" s="3" t="s">
+      <c r="G24" s="3" t="s">
+        <v>85</v>
+      </c>
+      <c r="H24" s="3" t="s">
         <v>205</v>
       </c>
-      <c r="F24" s="3" t="s">
-        <v>206</v>
-      </c>
-      <c r="G24" s="3" t="s">
-        <v>85</v>
-      </c>
-      <c r="H24" s="3" t="s">
-        <v>207</v>
-      </c>
       <c r="I24" s="3" t="s">
+        <v>206</v>
+      </c>
+      <c r="J24" s="3" t="s">
+        <v>207</v>
+      </c>
+      <c r="K24" s="3" t="s">
+        <v>206</v>
+      </c>
+      <c r="L24" s="3" t="s">
+        <v>207</v>
+      </c>
+      <c r="M24" s="3" t="s">
+        <v>206</v>
+      </c>
+      <c r="N24" s="3" t="s">
         <v>208</v>
       </c>
-      <c r="J24" s="3" t="s">
+      <c r="O24" s="3" t="s">
+        <v>206</v>
+      </c>
+      <c r="P24" s="3" t="s">
         <v>209</v>
       </c>
-      <c r="K24" s="3" t="s">
-        <v>208</v>
-      </c>
-      <c r="L24" s="3" t="s">
-        <v>209</v>
-      </c>
-      <c r="M24" s="3" t="s">
-        <v>208</v>
-      </c>
-      <c r="N24" s="3" t="s">
+      <c r="Q24" s="3" t="s">
+        <v>85</v>
+      </c>
+      <c r="R24" s="3" t="s">
         <v>210</v>
       </c>
-      <c r="O24" s="3" t="s">
-        <v>208</v>
-      </c>
-      <c r="P24" s="3" t="s">
+      <c r="S24" s="3" t="s">
         <v>211</v>
       </c>
-      <c r="Q24" s="3" t="s">
-        <v>85</v>
-      </c>
-      <c r="R24" s="3" t="s">
+      <c r="T24" s="3" t="s">
         <v>212</v>
-      </c>
-      <c r="S24" s="3" t="s">
-        <v>213</v>
-      </c>
-      <c r="T24" s="3" t="s">
-        <v>214</v>
       </c>
     </row>
     <row r="25" spans="1:20" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A25" s="3" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="B25" s="3" t="s">
-        <v>235</v>
+        <v>233</v>
       </c>
       <c r="C25" s="3" t="s">
+        <v>201</v>
+      </c>
+      <c r="D25" s="3" t="s">
+        <v>202</v>
+      </c>
+      <c r="E25" s="3" t="s">
         <v>203</v>
       </c>
-      <c r="D25" s="3" t="s">
+      <c r="F25" s="3" t="s">
         <v>204</v>
       </c>
-      <c r="E25" s="3" t="s">
+      <c r="G25" s="3" t="s">
+        <v>85</v>
+      </c>
+      <c r="H25" s="3" t="s">
         <v>205</v>
       </c>
-      <c r="F25" s="3" t="s">
-        <v>206</v>
-      </c>
-      <c r="G25" s="3" t="s">
-        <v>85</v>
-      </c>
-      <c r="H25" s="3" t="s">
-        <v>207</v>
-      </c>
       <c r="I25" s="3" t="s">
+        <v>206</v>
+      </c>
+      <c r="J25" s="3" t="s">
+        <v>207</v>
+      </c>
+      <c r="K25" s="3" t="s">
+        <v>206</v>
+      </c>
+      <c r="L25" s="3" t="s">
+        <v>207</v>
+      </c>
+      <c r="M25" s="3" t="s">
+        <v>206</v>
+      </c>
+      <c r="N25" s="3" t="s">
         <v>208</v>
       </c>
-      <c r="J25" s="3" t="s">
+      <c r="O25" s="3" t="s">
+        <v>206</v>
+      </c>
+      <c r="P25" s="3" t="s">
         <v>209</v>
       </c>
-      <c r="K25" s="3" t="s">
-        <v>208</v>
-      </c>
-      <c r="L25" s="3" t="s">
-        <v>209</v>
-      </c>
-      <c r="M25" s="3" t="s">
-        <v>208</v>
-      </c>
-      <c r="N25" s="3" t="s">
+      <c r="Q25" s="3" t="s">
+        <v>85</v>
+      </c>
+      <c r="R25" s="3" t="s">
         <v>210</v>
       </c>
-      <c r="O25" s="3" t="s">
-        <v>208</v>
-      </c>
-      <c r="P25" s="3" t="s">
+      <c r="S25" s="3" t="s">
         <v>211</v>
       </c>
-      <c r="Q25" s="3" t="s">
-        <v>85</v>
-      </c>
-      <c r="R25" s="3" t="s">
+      <c r="T25" s="3" t="s">
         <v>212</v>
-      </c>
-      <c r="S25" s="3" t="s">
-        <v>213</v>
-      </c>
-      <c r="T25" s="3" t="s">
-        <v>214</v>
       </c>
     </row>
     <row r="26" spans="1:20" ht="45" customHeight="1" x14ac:dyDescent="0.25">
@@ -6584,123 +6578,123 @@
         <v>160</v>
       </c>
       <c r="B26" s="3" t="s">
-        <v>236</v>
+        <v>234</v>
       </c>
       <c r="C26" s="3" t="s">
+        <v>201</v>
+      </c>
+      <c r="D26" s="3" t="s">
+        <v>202</v>
+      </c>
+      <c r="E26" s="3" t="s">
         <v>203</v>
       </c>
-      <c r="D26" s="3" t="s">
+      <c r="F26" s="3" t="s">
         <v>204</v>
       </c>
-      <c r="E26" s="3" t="s">
+      <c r="G26" s="3" t="s">
+        <v>85</v>
+      </c>
+      <c r="H26" s="3" t="s">
         <v>205</v>
       </c>
-      <c r="F26" s="3" t="s">
-        <v>206</v>
-      </c>
-      <c r="G26" s="3" t="s">
-        <v>85</v>
-      </c>
-      <c r="H26" s="3" t="s">
-        <v>207</v>
-      </c>
       <c r="I26" s="3" t="s">
+        <v>206</v>
+      </c>
+      <c r="J26" s="3" t="s">
+        <v>207</v>
+      </c>
+      <c r="K26" s="3" t="s">
+        <v>206</v>
+      </c>
+      <c r="L26" s="3" t="s">
+        <v>207</v>
+      </c>
+      <c r="M26" s="3" t="s">
+        <v>206</v>
+      </c>
+      <c r="N26" s="3" t="s">
         <v>208</v>
       </c>
-      <c r="J26" s="3" t="s">
+      <c r="O26" s="3" t="s">
+        <v>206</v>
+      </c>
+      <c r="P26" s="3" t="s">
         <v>209</v>
       </c>
-      <c r="K26" s="3" t="s">
-        <v>208</v>
-      </c>
-      <c r="L26" s="3" t="s">
-        <v>209</v>
-      </c>
-      <c r="M26" s="3" t="s">
-        <v>208</v>
-      </c>
-      <c r="N26" s="3" t="s">
+      <c r="Q26" s="3" t="s">
+        <v>85</v>
+      </c>
+      <c r="R26" s="3" t="s">
         <v>210</v>
       </c>
-      <c r="O26" s="3" t="s">
-        <v>208</v>
-      </c>
-      <c r="P26" s="3" t="s">
+      <c r="S26" s="3" t="s">
         <v>211</v>
       </c>
-      <c r="Q26" s="3" t="s">
-        <v>85</v>
-      </c>
-      <c r="R26" s="3" t="s">
+      <c r="T26" s="3" t="s">
         <v>212</v>
-      </c>
-      <c r="S26" s="3" t="s">
-        <v>213</v>
-      </c>
-      <c r="T26" s="3" t="s">
-        <v>214</v>
       </c>
     </row>
     <row r="27" spans="1:20" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A27" s="3" t="s">
-        <v>163</v>
+        <v>161</v>
       </c>
       <c r="B27" s="3" t="s">
-        <v>237</v>
+        <v>235</v>
       </c>
       <c r="C27" s="3" t="s">
+        <v>201</v>
+      </c>
+      <c r="D27" s="3" t="s">
+        <v>202</v>
+      </c>
+      <c r="E27" s="3" t="s">
         <v>203</v>
       </c>
-      <c r="D27" s="3" t="s">
+      <c r="F27" s="3" t="s">
         <v>204</v>
       </c>
-      <c r="E27" s="3" t="s">
+      <c r="G27" s="3" t="s">
+        <v>85</v>
+      </c>
+      <c r="H27" s="3" t="s">
         <v>205</v>
       </c>
-      <c r="F27" s="3" t="s">
-        <v>206</v>
-      </c>
-      <c r="G27" s="3" t="s">
-        <v>85</v>
-      </c>
-      <c r="H27" s="3" t="s">
-        <v>207</v>
-      </c>
       <c r="I27" s="3" t="s">
+        <v>206</v>
+      </c>
+      <c r="J27" s="3" t="s">
+        <v>207</v>
+      </c>
+      <c r="K27" s="3" t="s">
+        <v>206</v>
+      </c>
+      <c r="L27" s="3" t="s">
+        <v>207</v>
+      </c>
+      <c r="M27" s="3" t="s">
+        <v>206</v>
+      </c>
+      <c r="N27" s="3" t="s">
         <v>208</v>
       </c>
-      <c r="J27" s="3" t="s">
+      <c r="O27" s="3" t="s">
+        <v>206</v>
+      </c>
+      <c r="P27" s="3" t="s">
         <v>209</v>
       </c>
-      <c r="K27" s="3" t="s">
-        <v>208</v>
-      </c>
-      <c r="L27" s="3" t="s">
-        <v>209</v>
-      </c>
-      <c r="M27" s="3" t="s">
-        <v>208</v>
-      </c>
-      <c r="N27" s="3" t="s">
+      <c r="Q27" s="3" t="s">
+        <v>85</v>
+      </c>
+      <c r="R27" s="3" t="s">
         <v>210</v>
       </c>
-      <c r="O27" s="3" t="s">
-        <v>208</v>
-      </c>
-      <c r="P27" s="3" t="s">
+      <c r="S27" s="3" t="s">
         <v>211</v>
       </c>
-      <c r="Q27" s="3" t="s">
-        <v>85</v>
-      </c>
-      <c r="R27" s="3" t="s">
+      <c r="T27" s="3" t="s">
         <v>212</v>
-      </c>
-      <c r="S27" s="3" t="s">
-        <v>213</v>
-      </c>
-      <c r="T27" s="3" t="s">
-        <v>214</v>
       </c>
     </row>
   </sheetData>
@@ -6726,122 +6720,122 @@
   <sheetData>
     <row r="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
-        <v>238</v>
+        <v>236</v>
       </c>
     </row>
     <row r="2" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>239</v>
+        <v>237</v>
       </c>
     </row>
     <row r="3" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>240</v>
+        <v>238</v>
       </c>
     </row>
     <row r="4" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>241</v>
+        <v>239</v>
       </c>
     </row>
     <row r="5" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>242</v>
+        <v>240</v>
       </c>
     </row>
     <row r="6" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>243</v>
+        <v>241</v>
       </c>
     </row>
     <row r="7" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>204</v>
+        <v>202</v>
       </c>
     </row>
     <row r="8" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>244</v>
+        <v>242</v>
       </c>
     </row>
     <row r="9" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>245</v>
+        <v>243</v>
       </c>
     </row>
     <row r="10" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>246</v>
+        <v>244</v>
       </c>
     </row>
     <row r="11" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>247</v>
+        <v>245</v>
       </c>
     </row>
     <row r="12" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>248</v>
+        <v>246</v>
       </c>
     </row>
     <row r="13" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>249</v>
+        <v>247</v>
       </c>
     </row>
     <row r="14" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>250</v>
+        <v>248</v>
       </c>
     </row>
     <row r="15" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>251</v>
+        <v>249</v>
       </c>
     </row>
     <row r="16" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>252</v>
+        <v>250</v>
       </c>
     </row>
     <row r="17" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>253</v>
+        <v>251</v>
       </c>
     </row>
     <row r="18" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>254</v>
+        <v>252</v>
       </c>
     </row>
     <row r="19" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>255</v>
+        <v>253</v>
       </c>
     </row>
     <row r="20" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>256</v>
+        <v>254</v>
       </c>
     </row>
     <row r="21" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>257</v>
+        <v>255</v>
       </c>
     </row>
     <row r="22" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
-        <v>258</v>
+        <v>256</v>
       </c>
     </row>
     <row r="23" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
-        <v>259</v>
+        <v>257</v>
       </c>
     </row>
     <row r="24" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
-        <v>260</v>
+        <v>258</v>
       </c>
     </row>
   </sheetData>
@@ -6856,207 +6850,207 @@
   <sheetData>
     <row r="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
     </row>
     <row r="2" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>253</v>
+        <v>251</v>
       </c>
     </row>
     <row r="3" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>262</v>
+        <v>260</v>
       </c>
     </row>
     <row r="4" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>263</v>
+        <v>261</v>
       </c>
     </row>
     <row r="5" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>264</v>
+        <v>262</v>
       </c>
     </row>
     <row r="6" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>265</v>
+        <v>263</v>
       </c>
     </row>
     <row r="7" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>207</v>
+        <v>205</v>
       </c>
     </row>
     <row r="8" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>266</v>
+        <v>264</v>
       </c>
     </row>
     <row r="9" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>267</v>
+        <v>265</v>
       </c>
     </row>
     <row r="10" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>268</v>
+        <v>266</v>
       </c>
     </row>
     <row r="11" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>269</v>
+        <v>267</v>
       </c>
     </row>
     <row r="12" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>270</v>
+        <v>268</v>
       </c>
     </row>
     <row r="13" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>271</v>
+        <v>269</v>
       </c>
     </row>
     <row r="14" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>272</v>
+        <v>270</v>
       </c>
     </row>
     <row r="15" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>273</v>
+        <v>271</v>
       </c>
     </row>
     <row r="16" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>274</v>
+        <v>272</v>
       </c>
     </row>
     <row r="17" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>275</v>
+        <v>273</v>
       </c>
     </row>
     <row r="18" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>276</v>
+        <v>274</v>
       </c>
     </row>
     <row r="19" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>277</v>
+        <v>275</v>
       </c>
     </row>
     <row r="20" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>278</v>
+        <v>276</v>
       </c>
     </row>
     <row r="21" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>279</v>
+        <v>277</v>
       </c>
     </row>
     <row r="22" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
-        <v>280</v>
+        <v>278</v>
       </c>
     </row>
     <row r="23" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
-        <v>249</v>
+        <v>247</v>
       </c>
     </row>
     <row r="24" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
-        <v>281</v>
+        <v>279</v>
       </c>
     </row>
     <row r="25" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
-        <v>282</v>
+        <v>280</v>
       </c>
     </row>
     <row r="26" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
-        <v>283</v>
+        <v>281</v>
       </c>
     </row>
     <row r="27" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
-        <v>284</v>
+        <v>282</v>
       </c>
     </row>
     <row r="28" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
-        <v>285</v>
+        <v>283</v>
       </c>
     </row>
     <row r="29" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
-        <v>286</v>
+        <v>284</v>
       </c>
     </row>
     <row r="30" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
-        <v>287</v>
+        <v>285</v>
       </c>
     </row>
     <row r="31" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
-        <v>288</v>
+        <v>286</v>
       </c>
     </row>
     <row r="32" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
-        <v>289</v>
+        <v>287</v>
       </c>
     </row>
     <row r="33" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
-        <v>290</v>
+        <v>288</v>
       </c>
     </row>
     <row r="34" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
-        <v>291</v>
+        <v>289</v>
       </c>
     </row>
     <row r="35" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
-        <v>292</v>
+        <v>290</v>
       </c>
     </row>
     <row r="36" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
-        <v>293</v>
+        <v>291</v>
       </c>
     </row>
     <row r="37" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
-        <v>294</v>
+        <v>292</v>
       </c>
     </row>
     <row r="38" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
-        <v>295</v>
+        <v>293</v>
       </c>
     </row>
     <row r="39" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
-        <v>296</v>
+        <v>294</v>
       </c>
     </row>
     <row r="40" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
-        <v>297</v>
+        <v>295</v>
       </c>
     </row>
     <row r="41" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
-        <v>298</v>
+        <v>296</v>
       </c>
     </row>
   </sheetData>
@@ -7071,162 +7065,162 @@
   <sheetData>
     <row r="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
-        <v>299</v>
+        <v>297</v>
       </c>
     </row>
     <row r="2" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>300</v>
+        <v>298</v>
       </c>
     </row>
     <row r="3" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>301</v>
+        <v>299</v>
       </c>
     </row>
     <row r="4" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>302</v>
+        <v>300</v>
       </c>
     </row>
     <row r="5" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>303</v>
+        <v>301</v>
       </c>
     </row>
     <row r="6" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>304</v>
+        <v>302</v>
       </c>
     </row>
     <row r="7" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>305</v>
+        <v>303</v>
       </c>
     </row>
     <row r="8" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>306</v>
+        <v>304</v>
       </c>
     </row>
     <row r="9" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>307</v>
+        <v>305</v>
       </c>
     </row>
     <row r="10" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>308</v>
+        <v>306</v>
       </c>
     </row>
     <row r="11" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>309</v>
+        <v>307</v>
       </c>
     </row>
     <row r="12" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>310</v>
+        <v>308</v>
       </c>
     </row>
     <row r="13" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>311</v>
+        <v>309</v>
       </c>
     </row>
     <row r="14" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>208</v>
+        <v>206</v>
       </c>
     </row>
     <row r="15" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>312</v>
+        <v>310</v>
       </c>
     </row>
     <row r="16" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>313</v>
+        <v>311</v>
       </c>
     </row>
     <row r="17" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>314</v>
+        <v>312</v>
       </c>
     </row>
     <row r="18" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>315</v>
+        <v>313</v>
       </c>
     </row>
     <row r="19" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>316</v>
+        <v>314</v>
       </c>
     </row>
     <row r="20" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>317</v>
+        <v>315</v>
       </c>
     </row>
     <row r="21" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>318</v>
+        <v>316</v>
       </c>
     </row>
     <row r="22" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
-        <v>319</v>
+        <v>317</v>
       </c>
     </row>
     <row r="23" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
-        <v>320</v>
+        <v>318</v>
       </c>
     </row>
     <row r="24" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
-        <v>321</v>
+        <v>319</v>
       </c>
     </row>
     <row r="25" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
-        <v>322</v>
+        <v>320</v>
       </c>
     </row>
     <row r="26" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
-        <v>323</v>
+        <v>321</v>
       </c>
     </row>
     <row r="27" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
-        <v>324</v>
+        <v>322</v>
       </c>
     </row>
     <row r="28" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
-        <v>325</v>
+        <v>323</v>
       </c>
     </row>
     <row r="29" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
-        <v>326</v>
+        <v>324</v>
       </c>
     </row>
     <row r="30" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
-        <v>327</v>
+        <v>325</v>
       </c>
     </row>
     <row r="31" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
-        <v>328</v>
+        <v>326</v>
       </c>
     </row>
     <row r="32" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
-        <v>329</v>
+        <v>327</v>
       </c>
     </row>
   </sheetData>
@@ -7307,100 +7301,100 @@
     </row>
     <row r="2" spans="1:17" hidden="1" x14ac:dyDescent="0.25">
       <c r="C2" t="s">
+        <v>328</v>
+      </c>
+      <c r="D2" t="s">
+        <v>329</v>
+      </c>
+      <c r="E2" t="s">
         <v>330</v>
       </c>
-      <c r="D2" t="s">
+      <c r="F2" t="s">
         <v>331</v>
       </c>
-      <c r="E2" t="s">
+      <c r="G2" t="s">
         <v>332</v>
       </c>
-      <c r="F2" t="s">
+      <c r="H2" t="s">
         <v>333</v>
       </c>
-      <c r="G2" t="s">
+      <c r="I2" t="s">
         <v>334</v>
       </c>
-      <c r="H2" t="s">
+      <c r="J2" t="s">
         <v>335</v>
       </c>
-      <c r="I2" t="s">
+      <c r="K2" t="s">
         <v>336</v>
       </c>
-      <c r="J2" t="s">
+      <c r="L2" t="s">
         <v>337</v>
       </c>
-      <c r="K2" t="s">
+      <c r="M2" t="s">
         <v>338</v>
       </c>
-      <c r="L2" t="s">
+      <c r="N2" t="s">
         <v>339</v>
       </c>
-      <c r="M2" t="s">
+      <c r="O2" t="s">
         <v>340</v>
       </c>
-      <c r="N2" t="s">
+      <c r="P2" t="s">
         <v>341</v>
       </c>
-      <c r="O2" t="s">
+      <c r="Q2" t="s">
         <v>342</v>
-      </c>
-      <c r="P2" t="s">
-        <v>343</v>
-      </c>
-      <c r="Q2" t="s">
-        <v>344</v>
       </c>
     </row>
     <row r="3" spans="1:17" ht="30" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
       <c r="B3" s="1"/>
       <c r="C3" s="1" t="s">
+        <v>343</v>
+      </c>
+      <c r="D3" s="1" t="s">
+        <v>344</v>
+      </c>
+      <c r="E3" s="1" t="s">
         <v>345</v>
       </c>
-      <c r="D3" s="1" t="s">
+      <c r="F3" s="1" t="s">
         <v>346</v>
       </c>
-      <c r="E3" s="1" t="s">
+      <c r="G3" s="1" t="s">
+        <v>185</v>
+      </c>
+      <c r="H3" s="1" t="s">
+        <v>186</v>
+      </c>
+      <c r="I3" s="1" t="s">
         <v>347</v>
       </c>
-      <c r="F3" s="1" t="s">
+      <c r="J3" s="1" t="s">
         <v>348</v>
       </c>
-      <c r="G3" s="1" t="s">
-        <v>187</v>
-      </c>
-      <c r="H3" s="1" t="s">
-        <v>188</v>
-      </c>
-      <c r="I3" s="1" t="s">
+      <c r="K3" s="1" t="s">
         <v>349</v>
       </c>
-      <c r="J3" s="1" t="s">
-        <v>350</v>
-      </c>
-      <c r="K3" s="1" t="s">
-        <v>351</v>
-      </c>
       <c r="L3" s="1" t="s">
+        <v>190</v>
+      </c>
+      <c r="M3" s="1" t="s">
+        <v>191</v>
+      </c>
+      <c r="N3" s="1" t="s">
         <v>192</v>
       </c>
-      <c r="M3" s="1" t="s">
+      <c r="O3" s="1" t="s">
         <v>193</v>
       </c>
-      <c r="N3" s="1" t="s">
+      <c r="P3" s="1" t="s">
         <v>194</v>
       </c>
-      <c r="O3" s="1" t="s">
+      <c r="Q3" s="1" t="s">
         <v>195</v>
-      </c>
-      <c r="P3" s="1" t="s">
-        <v>196</v>
-      </c>
-      <c r="Q3" s="1" t="s">
-        <v>197</v>
       </c>
     </row>
     <row r="4" spans="1:17" ht="45" customHeight="1" x14ac:dyDescent="0.25">
@@ -7408,52 +7402,52 @@
         <v>88</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>352</v>
+        <v>350</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>212</v>
+        <v>210</v>
       </c>
       <c r="D4" s="3" t="s">
-        <v>213</v>
+        <v>211</v>
       </c>
       <c r="E4" s="3" t="s">
+        <v>202</v>
+      </c>
+      <c r="F4" s="3" t="s">
+        <v>203</v>
+      </c>
+      <c r="G4" s="3" t="s">
         <v>204</v>
       </c>
-      <c r="F4" s="3" t="s">
+      <c r="H4" s="3" t="s">
+        <v>85</v>
+      </c>
+      <c r="I4" s="3" t="s">
         <v>205</v>
       </c>
-      <c r="G4" s="3" t="s">
-        <v>206</v>
-      </c>
-      <c r="H4" s="3" t="s">
-        <v>85</v>
-      </c>
-      <c r="I4" s="3" t="s">
-        <v>207</v>
-      </c>
       <c r="J4" s="3" t="s">
+        <v>206</v>
+      </c>
+      <c r="K4" s="3" t="s">
+        <v>207</v>
+      </c>
+      <c r="L4" s="3" t="s">
+        <v>206</v>
+      </c>
+      <c r="M4" s="3" t="s">
+        <v>207</v>
+      </c>
+      <c r="N4" s="3" t="s">
+        <v>206</v>
+      </c>
+      <c r="O4" s="3" t="s">
         <v>208</v>
       </c>
-      <c r="K4" s="3" t="s">
+      <c r="P4" s="3" t="s">
+        <v>206</v>
+      </c>
+      <c r="Q4" s="3" t="s">
         <v>209</v>
-      </c>
-      <c r="L4" s="3" t="s">
-        <v>208</v>
-      </c>
-      <c r="M4" s="3" t="s">
-        <v>209</v>
-      </c>
-      <c r="N4" s="3" t="s">
-        <v>208</v>
-      </c>
-      <c r="O4" s="3" t="s">
-        <v>210</v>
-      </c>
-      <c r="P4" s="3" t="s">
-        <v>208</v>
-      </c>
-      <c r="Q4" s="3" t="s">
-        <v>211</v>
       </c>
     </row>
     <row r="5" spans="1:17" ht="45" customHeight="1" x14ac:dyDescent="0.25">
@@ -7461,52 +7455,52 @@
         <v>102</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>353</v>
+        <v>351</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>212</v>
+        <v>210</v>
       </c>
       <c r="D5" s="3" t="s">
-        <v>213</v>
+        <v>211</v>
       </c>
       <c r="E5" s="3" t="s">
+        <v>202</v>
+      </c>
+      <c r="F5" s="3" t="s">
+        <v>203</v>
+      </c>
+      <c r="G5" s="3" t="s">
         <v>204</v>
       </c>
-      <c r="F5" s="3" t="s">
+      <c r="H5" s="3" t="s">
+        <v>85</v>
+      </c>
+      <c r="I5" s="3" t="s">
         <v>205</v>
       </c>
-      <c r="G5" s="3" t="s">
-        <v>206</v>
-      </c>
-      <c r="H5" s="3" t="s">
-        <v>85</v>
-      </c>
-      <c r="I5" s="3" t="s">
-        <v>207</v>
-      </c>
       <c r="J5" s="3" t="s">
+        <v>206</v>
+      </c>
+      <c r="K5" s="3" t="s">
+        <v>207</v>
+      </c>
+      <c r="L5" s="3" t="s">
+        <v>206</v>
+      </c>
+      <c r="M5" s="3" t="s">
+        <v>207</v>
+      </c>
+      <c r="N5" s="3" t="s">
+        <v>206</v>
+      </c>
+      <c r="O5" s="3" t="s">
         <v>208</v>
       </c>
-      <c r="K5" s="3" t="s">
+      <c r="P5" s="3" t="s">
+        <v>206</v>
+      </c>
+      <c r="Q5" s="3" t="s">
         <v>209</v>
-      </c>
-      <c r="L5" s="3" t="s">
-        <v>208</v>
-      </c>
-      <c r="M5" s="3" t="s">
-        <v>209</v>
-      </c>
-      <c r="N5" s="3" t="s">
-        <v>208</v>
-      </c>
-      <c r="O5" s="3" t="s">
-        <v>210</v>
-      </c>
-      <c r="P5" s="3" t="s">
-        <v>208</v>
-      </c>
-      <c r="Q5" s="3" t="s">
-        <v>211</v>
       </c>
     </row>
     <row r="6" spans="1:17" ht="45" customHeight="1" x14ac:dyDescent="0.25">
@@ -7514,52 +7508,52 @@
         <v>109</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>354</v>
+        <v>352</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>212</v>
+        <v>210</v>
       </c>
       <c r="D6" s="3" t="s">
-        <v>213</v>
+        <v>211</v>
       </c>
       <c r="E6" s="3" t="s">
+        <v>202</v>
+      </c>
+      <c r="F6" s="3" t="s">
+        <v>203</v>
+      </c>
+      <c r="G6" s="3" t="s">
         <v>204</v>
       </c>
-      <c r="F6" s="3" t="s">
+      <c r="H6" s="3" t="s">
+        <v>85</v>
+      </c>
+      <c r="I6" s="3" t="s">
         <v>205</v>
       </c>
-      <c r="G6" s="3" t="s">
-        <v>206</v>
-      </c>
-      <c r="H6" s="3" t="s">
-        <v>85</v>
-      </c>
-      <c r="I6" s="3" t="s">
-        <v>207</v>
-      </c>
       <c r="J6" s="3" t="s">
+        <v>206</v>
+      </c>
+      <c r="K6" s="3" t="s">
+        <v>207</v>
+      </c>
+      <c r="L6" s="3" t="s">
+        <v>206</v>
+      </c>
+      <c r="M6" s="3" t="s">
+        <v>207</v>
+      </c>
+      <c r="N6" s="3" t="s">
+        <v>206</v>
+      </c>
+      <c r="O6" s="3" t="s">
         <v>208</v>
       </c>
-      <c r="K6" s="3" t="s">
+      <c r="P6" s="3" t="s">
+        <v>206</v>
+      </c>
+      <c r="Q6" s="3" t="s">
         <v>209</v>
-      </c>
-      <c r="L6" s="3" t="s">
-        <v>208</v>
-      </c>
-      <c r="M6" s="3" t="s">
-        <v>209</v>
-      </c>
-      <c r="N6" s="3" t="s">
-        <v>208</v>
-      </c>
-      <c r="O6" s="3" t="s">
-        <v>210</v>
-      </c>
-      <c r="P6" s="3" t="s">
-        <v>208</v>
-      </c>
-      <c r="Q6" s="3" t="s">
-        <v>211</v>
       </c>
     </row>
     <row r="7" spans="1:17" ht="45" customHeight="1" x14ac:dyDescent="0.25">
@@ -7567,52 +7561,52 @@
         <v>117</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>355</v>
+        <v>353</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>212</v>
+        <v>210</v>
       </c>
       <c r="D7" s="3" t="s">
-        <v>213</v>
+        <v>211</v>
       </c>
       <c r="E7" s="3" t="s">
+        <v>202</v>
+      </c>
+      <c r="F7" s="3" t="s">
+        <v>203</v>
+      </c>
+      <c r="G7" s="3" t="s">
         <v>204</v>
       </c>
-      <c r="F7" s="3" t="s">
+      <c r="H7" s="3" t="s">
+        <v>85</v>
+      </c>
+      <c r="I7" s="3" t="s">
         <v>205</v>
       </c>
-      <c r="G7" s="3" t="s">
-        <v>206</v>
-      </c>
-      <c r="H7" s="3" t="s">
-        <v>85</v>
-      </c>
-      <c r="I7" s="3" t="s">
-        <v>207</v>
-      </c>
       <c r="J7" s="3" t="s">
+        <v>206</v>
+      </c>
+      <c r="K7" s="3" t="s">
+        <v>207</v>
+      </c>
+      <c r="L7" s="3" t="s">
+        <v>206</v>
+      </c>
+      <c r="M7" s="3" t="s">
+        <v>207</v>
+      </c>
+      <c r="N7" s="3" t="s">
+        <v>206</v>
+      </c>
+      <c r="O7" s="3" t="s">
         <v>208</v>
       </c>
-      <c r="K7" s="3" t="s">
+      <c r="P7" s="3" t="s">
+        <v>206</v>
+      </c>
+      <c r="Q7" s="3" t="s">
         <v>209</v>
-      </c>
-      <c r="L7" s="3" t="s">
-        <v>208</v>
-      </c>
-      <c r="M7" s="3" t="s">
-        <v>209</v>
-      </c>
-      <c r="N7" s="3" t="s">
-        <v>208</v>
-      </c>
-      <c r="O7" s="3" t="s">
-        <v>210</v>
-      </c>
-      <c r="P7" s="3" t="s">
-        <v>208</v>
-      </c>
-      <c r="Q7" s="3" t="s">
-        <v>211</v>
       </c>
     </row>
     <row r="8" spans="1:17" ht="45" customHeight="1" x14ac:dyDescent="0.25">
@@ -7620,52 +7614,52 @@
         <v>123</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>356</v>
+        <v>354</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>212</v>
+        <v>210</v>
       </c>
       <c r="D8" s="3" t="s">
-        <v>213</v>
+        <v>211</v>
       </c>
       <c r="E8" s="3" t="s">
+        <v>202</v>
+      </c>
+      <c r="F8" s="3" t="s">
+        <v>203</v>
+      </c>
+      <c r="G8" s="3" t="s">
         <v>204</v>
       </c>
-      <c r="F8" s="3" t="s">
+      <c r="H8" s="3" t="s">
+        <v>85</v>
+      </c>
+      <c r="I8" s="3" t="s">
         <v>205</v>
       </c>
-      <c r="G8" s="3" t="s">
-        <v>206</v>
-      </c>
-      <c r="H8" s="3" t="s">
-        <v>85</v>
-      </c>
-      <c r="I8" s="3" t="s">
-        <v>207</v>
-      </c>
       <c r="J8" s="3" t="s">
+        <v>206</v>
+      </c>
+      <c r="K8" s="3" t="s">
+        <v>207</v>
+      </c>
+      <c r="L8" s="3" t="s">
+        <v>206</v>
+      </c>
+      <c r="M8" s="3" t="s">
+        <v>207</v>
+      </c>
+      <c r="N8" s="3" t="s">
+        <v>206</v>
+      </c>
+      <c r="O8" s="3" t="s">
         <v>208</v>
       </c>
-      <c r="K8" s="3" t="s">
+      <c r="P8" s="3" t="s">
+        <v>206</v>
+      </c>
+      <c r="Q8" s="3" t="s">
         <v>209</v>
-      </c>
-      <c r="L8" s="3" t="s">
-        <v>208</v>
-      </c>
-      <c r="M8" s="3" t="s">
-        <v>209</v>
-      </c>
-      <c r="N8" s="3" t="s">
-        <v>208</v>
-      </c>
-      <c r="O8" s="3" t="s">
-        <v>210</v>
-      </c>
-      <c r="P8" s="3" t="s">
-        <v>208</v>
-      </c>
-      <c r="Q8" s="3" t="s">
-        <v>211</v>
       </c>
     </row>
     <row r="9" spans="1:17" ht="45" customHeight="1" x14ac:dyDescent="0.25">
@@ -7673,52 +7667,52 @@
         <v>129</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>357</v>
+        <v>355</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>212</v>
+        <v>210</v>
       </c>
       <c r="D9" s="3" t="s">
-        <v>213</v>
+        <v>211</v>
       </c>
       <c r="E9" s="3" t="s">
+        <v>202</v>
+      </c>
+      <c r="F9" s="3" t="s">
+        <v>203</v>
+      </c>
+      <c r="G9" s="3" t="s">
         <v>204</v>
       </c>
-      <c r="F9" s="3" t="s">
+      <c r="H9" s="3" t="s">
+        <v>85</v>
+      </c>
+      <c r="I9" s="3" t="s">
         <v>205</v>
       </c>
-      <c r="G9" s="3" t="s">
-        <v>206</v>
-      </c>
-      <c r="H9" s="3" t="s">
-        <v>85</v>
-      </c>
-      <c r="I9" s="3" t="s">
-        <v>207</v>
-      </c>
       <c r="J9" s="3" t="s">
+        <v>206</v>
+      </c>
+      <c r="K9" s="3" t="s">
+        <v>207</v>
+      </c>
+      <c r="L9" s="3" t="s">
+        <v>206</v>
+      </c>
+      <c r="M9" s="3" t="s">
+        <v>207</v>
+      </c>
+      <c r="N9" s="3" t="s">
+        <v>206</v>
+      </c>
+      <c r="O9" s="3" t="s">
         <v>208</v>
       </c>
-      <c r="K9" s="3" t="s">
+      <c r="P9" s="3" t="s">
+        <v>206</v>
+      </c>
+      <c r="Q9" s="3" t="s">
         <v>209</v>
-      </c>
-      <c r="L9" s="3" t="s">
-        <v>208</v>
-      </c>
-      <c r="M9" s="3" t="s">
-        <v>209</v>
-      </c>
-      <c r="N9" s="3" t="s">
-        <v>208</v>
-      </c>
-      <c r="O9" s="3" t="s">
-        <v>210</v>
-      </c>
-      <c r="P9" s="3" t="s">
-        <v>208</v>
-      </c>
-      <c r="Q9" s="3" t="s">
-        <v>211</v>
       </c>
     </row>
     <row r="10" spans="1:17" ht="45" customHeight="1" x14ac:dyDescent="0.25">
@@ -7726,52 +7720,52 @@
         <v>130</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>358</v>
+        <v>356</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>212</v>
+        <v>210</v>
       </c>
       <c r="D10" s="3" t="s">
-        <v>213</v>
+        <v>211</v>
       </c>
       <c r="E10" s="3" t="s">
+        <v>202</v>
+      </c>
+      <c r="F10" s="3" t="s">
+        <v>203</v>
+      </c>
+      <c r="G10" s="3" t="s">
         <v>204</v>
       </c>
-      <c r="F10" s="3" t="s">
+      <c r="H10" s="3" t="s">
+        <v>85</v>
+      </c>
+      <c r="I10" s="3" t="s">
         <v>205</v>
       </c>
-      <c r="G10" s="3" t="s">
-        <v>206</v>
-      </c>
-      <c r="H10" s="3" t="s">
-        <v>85</v>
-      </c>
-      <c r="I10" s="3" t="s">
-        <v>207</v>
-      </c>
       <c r="J10" s="3" t="s">
+        <v>206</v>
+      </c>
+      <c r="K10" s="3" t="s">
+        <v>207</v>
+      </c>
+      <c r="L10" s="3" t="s">
+        <v>206</v>
+      </c>
+      <c r="M10" s="3" t="s">
+        <v>207</v>
+      </c>
+      <c r="N10" s="3" t="s">
+        <v>206</v>
+      </c>
+      <c r="O10" s="3" t="s">
         <v>208</v>
       </c>
-      <c r="K10" s="3" t="s">
+      <c r="P10" s="3" t="s">
+        <v>206</v>
+      </c>
+      <c r="Q10" s="3" t="s">
         <v>209</v>
-      </c>
-      <c r="L10" s="3" t="s">
-        <v>208</v>
-      </c>
-      <c r="M10" s="3" t="s">
-        <v>209</v>
-      </c>
-      <c r="N10" s="3" t="s">
-        <v>208</v>
-      </c>
-      <c r="O10" s="3" t="s">
-        <v>210</v>
-      </c>
-      <c r="P10" s="3" t="s">
-        <v>208</v>
-      </c>
-      <c r="Q10" s="3" t="s">
-        <v>211</v>
       </c>
     </row>
     <row r="11" spans="1:17" ht="45" customHeight="1" x14ac:dyDescent="0.25">
@@ -7779,52 +7773,52 @@
         <v>131</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>359</v>
+        <v>357</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>212</v>
+        <v>210</v>
       </c>
       <c r="D11" s="3" t="s">
-        <v>213</v>
+        <v>211</v>
       </c>
       <c r="E11" s="3" t="s">
+        <v>202</v>
+      </c>
+      <c r="F11" s="3" t="s">
+        <v>203</v>
+      </c>
+      <c r="G11" s="3" t="s">
         <v>204</v>
       </c>
-      <c r="F11" s="3" t="s">
+      <c r="H11" s="3" t="s">
+        <v>85</v>
+      </c>
+      <c r="I11" s="3" t="s">
         <v>205</v>
       </c>
-      <c r="G11" s="3" t="s">
-        <v>206</v>
-      </c>
-      <c r="H11" s="3" t="s">
-        <v>85</v>
-      </c>
-      <c r="I11" s="3" t="s">
-        <v>207</v>
-      </c>
       <c r="J11" s="3" t="s">
+        <v>206</v>
+      </c>
+      <c r="K11" s="3" t="s">
+        <v>207</v>
+      </c>
+      <c r="L11" s="3" t="s">
+        <v>206</v>
+      </c>
+      <c r="M11" s="3" t="s">
+        <v>207</v>
+      </c>
+      <c r="N11" s="3" t="s">
+        <v>206</v>
+      </c>
+      <c r="O11" s="3" t="s">
         <v>208</v>
       </c>
-      <c r="K11" s="3" t="s">
+      <c r="P11" s="3" t="s">
+        <v>206</v>
+      </c>
+      <c r="Q11" s="3" t="s">
         <v>209</v>
-      </c>
-      <c r="L11" s="3" t="s">
-        <v>208</v>
-      </c>
-      <c r="M11" s="3" t="s">
-        <v>209</v>
-      </c>
-      <c r="N11" s="3" t="s">
-        <v>208</v>
-      </c>
-      <c r="O11" s="3" t="s">
-        <v>210</v>
-      </c>
-      <c r="P11" s="3" t="s">
-        <v>208</v>
-      </c>
-      <c r="Q11" s="3" t="s">
-        <v>211</v>
       </c>
     </row>
     <row r="12" spans="1:17" ht="45" customHeight="1" x14ac:dyDescent="0.25">
@@ -7832,52 +7826,52 @@
         <v>132</v>
       </c>
       <c r="B12" s="3" t="s">
-        <v>360</v>
+        <v>358</v>
       </c>
       <c r="C12" s="3" t="s">
-        <v>212</v>
+        <v>210</v>
       </c>
       <c r="D12" s="3" t="s">
-        <v>213</v>
+        <v>211</v>
       </c>
       <c r="E12" s="3" t="s">
+        <v>202</v>
+      </c>
+      <c r="F12" s="3" t="s">
+        <v>203</v>
+      </c>
+      <c r="G12" s="3" t="s">
         <v>204</v>
       </c>
-      <c r="F12" s="3" t="s">
+      <c r="H12" s="3" t="s">
+        <v>85</v>
+      </c>
+      <c r="I12" s="3" t="s">
         <v>205</v>
       </c>
-      <c r="G12" s="3" t="s">
-        <v>206</v>
-      </c>
-      <c r="H12" s="3" t="s">
-        <v>85</v>
-      </c>
-      <c r="I12" s="3" t="s">
-        <v>207</v>
-      </c>
       <c r="J12" s="3" t="s">
+        <v>206</v>
+      </c>
+      <c r="K12" s="3" t="s">
+        <v>207</v>
+      </c>
+      <c r="L12" s="3" t="s">
+        <v>206</v>
+      </c>
+      <c r="M12" s="3" t="s">
+        <v>207</v>
+      </c>
+      <c r="N12" s="3" t="s">
+        <v>206</v>
+      </c>
+      <c r="O12" s="3" t="s">
         <v>208</v>
       </c>
-      <c r="K12" s="3" t="s">
+      <c r="P12" s="3" t="s">
+        <v>206</v>
+      </c>
+      <c r="Q12" s="3" t="s">
         <v>209</v>
-      </c>
-      <c r="L12" s="3" t="s">
-        <v>208</v>
-      </c>
-      <c r="M12" s="3" t="s">
-        <v>209</v>
-      </c>
-      <c r="N12" s="3" t="s">
-        <v>208</v>
-      </c>
-      <c r="O12" s="3" t="s">
-        <v>210</v>
-      </c>
-      <c r="P12" s="3" t="s">
-        <v>208</v>
-      </c>
-      <c r="Q12" s="3" t="s">
-        <v>211</v>
       </c>
     </row>
     <row r="13" spans="1:17" ht="45" customHeight="1" x14ac:dyDescent="0.25">
@@ -7885,52 +7879,52 @@
         <v>133</v>
       </c>
       <c r="B13" s="3" t="s">
-        <v>361</v>
+        <v>359</v>
       </c>
       <c r="C13" s="3" t="s">
-        <v>212</v>
+        <v>210</v>
       </c>
       <c r="D13" s="3" t="s">
-        <v>213</v>
+        <v>211</v>
       </c>
       <c r="E13" s="3" t="s">
+        <v>202</v>
+      </c>
+      <c r="F13" s="3" t="s">
+        <v>203</v>
+      </c>
+      <c r="G13" s="3" t="s">
         <v>204</v>
       </c>
-      <c r="F13" s="3" t="s">
+      <c r="H13" s="3" t="s">
+        <v>85</v>
+      </c>
+      <c r="I13" s="3" t="s">
         <v>205</v>
       </c>
-      <c r="G13" s="3" t="s">
-        <v>206</v>
-      </c>
-      <c r="H13" s="3" t="s">
-        <v>85</v>
-      </c>
-      <c r="I13" s="3" t="s">
-        <v>207</v>
-      </c>
       <c r="J13" s="3" t="s">
+        <v>206</v>
+      </c>
+      <c r="K13" s="3" t="s">
+        <v>207</v>
+      </c>
+      <c r="L13" s="3" t="s">
+        <v>206</v>
+      </c>
+      <c r="M13" s="3" t="s">
+        <v>207</v>
+      </c>
+      <c r="N13" s="3" t="s">
+        <v>206</v>
+      </c>
+      <c r="O13" s="3" t="s">
         <v>208</v>
       </c>
-      <c r="K13" s="3" t="s">
+      <c r="P13" s="3" t="s">
+        <v>206</v>
+      </c>
+      <c r="Q13" s="3" t="s">
         <v>209</v>
-      </c>
-      <c r="L13" s="3" t="s">
-        <v>208</v>
-      </c>
-      <c r="M13" s="3" t="s">
-        <v>209</v>
-      </c>
-      <c r="N13" s="3" t="s">
-        <v>208</v>
-      </c>
-      <c r="O13" s="3" t="s">
-        <v>210</v>
-      </c>
-      <c r="P13" s="3" t="s">
-        <v>208</v>
-      </c>
-      <c r="Q13" s="3" t="s">
-        <v>211</v>
       </c>
     </row>
     <row r="14" spans="1:17" ht="45" customHeight="1" x14ac:dyDescent="0.25">
@@ -7938,52 +7932,52 @@
         <v>134</v>
       </c>
       <c r="B14" s="3" t="s">
-        <v>362</v>
+        <v>360</v>
       </c>
       <c r="C14" s="3" t="s">
-        <v>212</v>
+        <v>210</v>
       </c>
       <c r="D14" s="3" t="s">
-        <v>213</v>
+        <v>211</v>
       </c>
       <c r="E14" s="3" t="s">
+        <v>202</v>
+      </c>
+      <c r="F14" s="3" t="s">
+        <v>203</v>
+      </c>
+      <c r="G14" s="3" t="s">
         <v>204</v>
       </c>
-      <c r="F14" s="3" t="s">
+      <c r="H14" s="3" t="s">
+        <v>85</v>
+      </c>
+      <c r="I14" s="3" t="s">
         <v>205</v>
       </c>
-      <c r="G14" s="3" t="s">
-        <v>206</v>
-      </c>
-      <c r="H14" s="3" t="s">
-        <v>85</v>
-      </c>
-      <c r="I14" s="3" t="s">
-        <v>207</v>
-      </c>
       <c r="J14" s="3" t="s">
+        <v>206</v>
+      </c>
+      <c r="K14" s="3" t="s">
+        <v>207</v>
+      </c>
+      <c r="L14" s="3" t="s">
+        <v>206</v>
+      </c>
+      <c r="M14" s="3" t="s">
+        <v>207</v>
+      </c>
+      <c r="N14" s="3" t="s">
+        <v>206</v>
+      </c>
+      <c r="O14" s="3" t="s">
         <v>208</v>
       </c>
-      <c r="K14" s="3" t="s">
+      <c r="P14" s="3" t="s">
+        <v>206</v>
+      </c>
+      <c r="Q14" s="3" t="s">
         <v>209</v>
-      </c>
-      <c r="L14" s="3" t="s">
-        <v>208</v>
-      </c>
-      <c r="M14" s="3" t="s">
-        <v>209</v>
-      </c>
-      <c r="N14" s="3" t="s">
-        <v>208</v>
-      </c>
-      <c r="O14" s="3" t="s">
-        <v>210</v>
-      </c>
-      <c r="P14" s="3" t="s">
-        <v>208</v>
-      </c>
-      <c r="Q14" s="3" t="s">
-        <v>211</v>
       </c>
     </row>
     <row r="15" spans="1:17" ht="45" customHeight="1" x14ac:dyDescent="0.25">
@@ -7991,582 +7985,582 @@
         <v>135</v>
       </c>
       <c r="B15" s="3" t="s">
-        <v>363</v>
+        <v>361</v>
       </c>
       <c r="C15" s="3" t="s">
-        <v>212</v>
+        <v>210</v>
       </c>
       <c r="D15" s="3" t="s">
-        <v>213</v>
+        <v>211</v>
       </c>
       <c r="E15" s="3" t="s">
+        <v>202</v>
+      </c>
+      <c r="F15" s="3" t="s">
+        <v>203</v>
+      </c>
+      <c r="G15" s="3" t="s">
         <v>204</v>
       </c>
-      <c r="F15" s="3" t="s">
+      <c r="H15" s="3" t="s">
+        <v>85</v>
+      </c>
+      <c r="I15" s="3" t="s">
         <v>205</v>
       </c>
-      <c r="G15" s="3" t="s">
-        <v>206</v>
-      </c>
-      <c r="H15" s="3" t="s">
-        <v>85</v>
-      </c>
-      <c r="I15" s="3" t="s">
-        <v>207</v>
-      </c>
       <c r="J15" s="3" t="s">
+        <v>206</v>
+      </c>
+      <c r="K15" s="3" t="s">
+        <v>207</v>
+      </c>
+      <c r="L15" s="3" t="s">
+        <v>206</v>
+      </c>
+      <c r="M15" s="3" t="s">
+        <v>207</v>
+      </c>
+      <c r="N15" s="3" t="s">
+        <v>206</v>
+      </c>
+      <c r="O15" s="3" t="s">
         <v>208</v>
       </c>
-      <c r="K15" s="3" t="s">
+      <c r="P15" s="3" t="s">
+        <v>206</v>
+      </c>
+      <c r="Q15" s="3" t="s">
         <v>209</v>
-      </c>
-      <c r="L15" s="3" t="s">
-        <v>208</v>
-      </c>
-      <c r="M15" s="3" t="s">
-        <v>209</v>
-      </c>
-      <c r="N15" s="3" t="s">
-        <v>208</v>
-      </c>
-      <c r="O15" s="3" t="s">
-        <v>210</v>
-      </c>
-      <c r="P15" s="3" t="s">
-        <v>208</v>
-      </c>
-      <c r="Q15" s="3" t="s">
-        <v>211</v>
       </c>
     </row>
     <row r="16" spans="1:17" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16" s="3" t="s">
-        <v>136</v>
+        <v>139</v>
       </c>
       <c r="B16" s="3" t="s">
-        <v>364</v>
+        <v>362</v>
       </c>
       <c r="C16" s="3" t="s">
-        <v>212</v>
+        <v>210</v>
       </c>
       <c r="D16" s="3" t="s">
-        <v>213</v>
+        <v>211</v>
       </c>
       <c r="E16" s="3" t="s">
+        <v>202</v>
+      </c>
+      <c r="F16" s="3" t="s">
+        <v>203</v>
+      </c>
+      <c r="G16" s="3" t="s">
         <v>204</v>
       </c>
-      <c r="F16" s="3" t="s">
+      <c r="H16" s="3" t="s">
+        <v>85</v>
+      </c>
+      <c r="I16" s="3" t="s">
         <v>205</v>
       </c>
-      <c r="G16" s="3" t="s">
-        <v>206</v>
-      </c>
-      <c r="H16" s="3" t="s">
-        <v>85</v>
-      </c>
-      <c r="I16" s="3" t="s">
-        <v>207</v>
-      </c>
       <c r="J16" s="3" t="s">
+        <v>206</v>
+      </c>
+      <c r="K16" s="3" t="s">
+        <v>207</v>
+      </c>
+      <c r="L16" s="3" t="s">
+        <v>206</v>
+      </c>
+      <c r="M16" s="3" t="s">
+        <v>207</v>
+      </c>
+      <c r="N16" s="3" t="s">
+        <v>206</v>
+      </c>
+      <c r="O16" s="3" t="s">
         <v>208</v>
       </c>
-      <c r="K16" s="3" t="s">
+      <c r="P16" s="3" t="s">
+        <v>206</v>
+      </c>
+      <c r="Q16" s="3" t="s">
         <v>209</v>
-      </c>
-      <c r="L16" s="3" t="s">
-        <v>208</v>
-      </c>
-      <c r="M16" s="3" t="s">
-        <v>209</v>
-      </c>
-      <c r="N16" s="3" t="s">
-        <v>208</v>
-      </c>
-      <c r="O16" s="3" t="s">
-        <v>210</v>
-      </c>
-      <c r="P16" s="3" t="s">
-        <v>208</v>
-      </c>
-      <c r="Q16" s="3" t="s">
-        <v>211</v>
       </c>
     </row>
     <row r="17" spans="1:17" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17" s="3" t="s">
-        <v>138</v>
+        <v>144</v>
       </c>
       <c r="B17" s="3" t="s">
-        <v>365</v>
+        <v>363</v>
       </c>
       <c r="C17" s="3" t="s">
-        <v>212</v>
+        <v>210</v>
       </c>
       <c r="D17" s="3" t="s">
-        <v>213</v>
+        <v>211</v>
       </c>
       <c r="E17" s="3" t="s">
+        <v>202</v>
+      </c>
+      <c r="F17" s="3" t="s">
+        <v>203</v>
+      </c>
+      <c r="G17" s="3" t="s">
         <v>204</v>
       </c>
-      <c r="F17" s="3" t="s">
+      <c r="H17" s="3" t="s">
+        <v>85</v>
+      </c>
+      <c r="I17" s="3" t="s">
         <v>205</v>
       </c>
-      <c r="G17" s="3" t="s">
-        <v>206</v>
-      </c>
-      <c r="H17" s="3" t="s">
-        <v>85</v>
-      </c>
-      <c r="I17" s="3" t="s">
-        <v>207</v>
-      </c>
       <c r="J17" s="3" t="s">
+        <v>206</v>
+      </c>
+      <c r="K17" s="3" t="s">
+        <v>207</v>
+      </c>
+      <c r="L17" s="3" t="s">
+        <v>206</v>
+      </c>
+      <c r="M17" s="3" t="s">
+        <v>207</v>
+      </c>
+      <c r="N17" s="3" t="s">
+        <v>206</v>
+      </c>
+      <c r="O17" s="3" t="s">
         <v>208</v>
       </c>
-      <c r="K17" s="3" t="s">
+      <c r="P17" s="3" t="s">
+        <v>206</v>
+      </c>
+      <c r="Q17" s="3" t="s">
         <v>209</v>
-      </c>
-      <c r="L17" s="3" t="s">
-        <v>208</v>
-      </c>
-      <c r="M17" s="3" t="s">
-        <v>209</v>
-      </c>
-      <c r="N17" s="3" t="s">
-        <v>208</v>
-      </c>
-      <c r="O17" s="3" t="s">
-        <v>210</v>
-      </c>
-      <c r="P17" s="3" t="s">
-        <v>208</v>
-      </c>
-      <c r="Q17" s="3" t="s">
-        <v>211</v>
       </c>
     </row>
     <row r="18" spans="1:17" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A18" s="3" t="s">
-        <v>139</v>
+        <v>146</v>
       </c>
       <c r="B18" s="3" t="s">
-        <v>366</v>
+        <v>364</v>
       </c>
       <c r="C18" s="3" t="s">
-        <v>212</v>
+        <v>210</v>
       </c>
       <c r="D18" s="3" t="s">
-        <v>213</v>
+        <v>211</v>
       </c>
       <c r="E18" s="3" t="s">
+        <v>202</v>
+      </c>
+      <c r="F18" s="3" t="s">
+        <v>203</v>
+      </c>
+      <c r="G18" s="3" t="s">
         <v>204</v>
       </c>
-      <c r="F18" s="3" t="s">
+      <c r="H18" s="3" t="s">
+        <v>85</v>
+      </c>
+      <c r="I18" s="3" t="s">
         <v>205</v>
       </c>
-      <c r="G18" s="3" t="s">
-        <v>206</v>
-      </c>
-      <c r="H18" s="3" t="s">
-        <v>85</v>
-      </c>
-      <c r="I18" s="3" t="s">
-        <v>207</v>
-      </c>
       <c r="J18" s="3" t="s">
+        <v>206</v>
+      </c>
+      <c r="K18" s="3" t="s">
+        <v>207</v>
+      </c>
+      <c r="L18" s="3" t="s">
+        <v>206</v>
+      </c>
+      <c r="M18" s="3" t="s">
+        <v>207</v>
+      </c>
+      <c r="N18" s="3" t="s">
+        <v>206</v>
+      </c>
+      <c r="O18" s="3" t="s">
         <v>208</v>
       </c>
-      <c r="K18" s="3" t="s">
+      <c r="P18" s="3" t="s">
+        <v>206</v>
+      </c>
+      <c r="Q18" s="3" t="s">
         <v>209</v>
-      </c>
-      <c r="L18" s="3" t="s">
-        <v>208</v>
-      </c>
-      <c r="M18" s="3" t="s">
-        <v>209</v>
-      </c>
-      <c r="N18" s="3" t="s">
-        <v>208</v>
-      </c>
-      <c r="O18" s="3" t="s">
-        <v>210</v>
-      </c>
-      <c r="P18" s="3" t="s">
-        <v>208</v>
-      </c>
-      <c r="Q18" s="3" t="s">
-        <v>211</v>
       </c>
     </row>
     <row r="19" spans="1:17" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A19" s="3" t="s">
-        <v>141</v>
+        <v>149</v>
       </c>
       <c r="B19" s="3" t="s">
-        <v>367</v>
+        <v>365</v>
       </c>
       <c r="C19" s="3" t="s">
-        <v>212</v>
+        <v>210</v>
       </c>
       <c r="D19" s="3" t="s">
-        <v>213</v>
+        <v>211</v>
       </c>
       <c r="E19" s="3" t="s">
+        <v>202</v>
+      </c>
+      <c r="F19" s="3" t="s">
+        <v>203</v>
+      </c>
+      <c r="G19" s="3" t="s">
         <v>204</v>
       </c>
-      <c r="F19" s="3" t="s">
+      <c r="H19" s="3" t="s">
+        <v>85</v>
+      </c>
+      <c r="I19" s="3" t="s">
         <v>205</v>
       </c>
-      <c r="G19" s="3" t="s">
-        <v>206</v>
-      </c>
-      <c r="H19" s="3" t="s">
-        <v>85</v>
-      </c>
-      <c r="I19" s="3" t="s">
-        <v>207</v>
-      </c>
       <c r="J19" s="3" t="s">
+        <v>206</v>
+      </c>
+      <c r="K19" s="3" t="s">
+        <v>207</v>
+      </c>
+      <c r="L19" s="3" t="s">
+        <v>206</v>
+      </c>
+      <c r="M19" s="3" t="s">
+        <v>207</v>
+      </c>
+      <c r="N19" s="3" t="s">
+        <v>206</v>
+      </c>
+      <c r="O19" s="3" t="s">
         <v>208</v>
       </c>
-      <c r="K19" s="3" t="s">
+      <c r="P19" s="3" t="s">
+        <v>206</v>
+      </c>
+      <c r="Q19" s="3" t="s">
         <v>209</v>
-      </c>
-      <c r="L19" s="3" t="s">
-        <v>208</v>
-      </c>
-      <c r="M19" s="3" t="s">
-        <v>209</v>
-      </c>
-      <c r="N19" s="3" t="s">
-        <v>208</v>
-      </c>
-      <c r="O19" s="3" t="s">
-        <v>210</v>
-      </c>
-      <c r="P19" s="3" t="s">
-        <v>208</v>
-      </c>
-      <c r="Q19" s="3" t="s">
-        <v>211</v>
       </c>
     </row>
     <row r="20" spans="1:17" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A20" s="3" t="s">
-        <v>142</v>
+        <v>151</v>
       </c>
       <c r="B20" s="3" t="s">
-        <v>368</v>
+        <v>366</v>
       </c>
       <c r="C20" s="3" t="s">
-        <v>212</v>
+        <v>210</v>
       </c>
       <c r="D20" s="3" t="s">
-        <v>213</v>
+        <v>211</v>
       </c>
       <c r="E20" s="3" t="s">
+        <v>202</v>
+      </c>
+      <c r="F20" s="3" t="s">
+        <v>203</v>
+      </c>
+      <c r="G20" s="3" t="s">
         <v>204</v>
       </c>
-      <c r="F20" s="3" t="s">
+      <c r="H20" s="3" t="s">
+        <v>85</v>
+      </c>
+      <c r="I20" s="3" t="s">
         <v>205</v>
       </c>
-      <c r="G20" s="3" t="s">
-        <v>206</v>
-      </c>
-      <c r="H20" s="3" t="s">
-        <v>85</v>
-      </c>
-      <c r="I20" s="3" t="s">
-        <v>207</v>
-      </c>
       <c r="J20" s="3" t="s">
+        <v>206</v>
+      </c>
+      <c r="K20" s="3" t="s">
+        <v>207</v>
+      </c>
+      <c r="L20" s="3" t="s">
+        <v>206</v>
+      </c>
+      <c r="M20" s="3" t="s">
+        <v>207</v>
+      </c>
+      <c r="N20" s="3" t="s">
+        <v>206</v>
+      </c>
+      <c r="O20" s="3" t="s">
         <v>208</v>
       </c>
-      <c r="K20" s="3" t="s">
+      <c r="P20" s="3" t="s">
+        <v>206</v>
+      </c>
+      <c r="Q20" s="3" t="s">
         <v>209</v>
-      </c>
-      <c r="L20" s="3" t="s">
-        <v>208</v>
-      </c>
-      <c r="M20" s="3" t="s">
-        <v>209</v>
-      </c>
-      <c r="N20" s="3" t="s">
-        <v>208</v>
-      </c>
-      <c r="O20" s="3" t="s">
-        <v>210</v>
-      </c>
-      <c r="P20" s="3" t="s">
-        <v>208</v>
-      </c>
-      <c r="Q20" s="3" t="s">
-        <v>211</v>
       </c>
     </row>
     <row r="21" spans="1:17" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A21" s="3" t="s">
-        <v>144</v>
+        <v>154</v>
       </c>
       <c r="B21" s="3" t="s">
-        <v>369</v>
+        <v>367</v>
       </c>
       <c r="C21" s="3" t="s">
-        <v>212</v>
+        <v>210</v>
       </c>
       <c r="D21" s="3" t="s">
-        <v>213</v>
+        <v>211</v>
       </c>
       <c r="E21" s="3" t="s">
+        <v>202</v>
+      </c>
+      <c r="F21" s="3" t="s">
+        <v>203</v>
+      </c>
+      <c r="G21" s="3" t="s">
         <v>204</v>
       </c>
-      <c r="F21" s="3" t="s">
+      <c r="H21" s="3" t="s">
+        <v>85</v>
+      </c>
+      <c r="I21" s="3" t="s">
         <v>205</v>
       </c>
-      <c r="G21" s="3" t="s">
-        <v>206</v>
-      </c>
-      <c r="H21" s="3" t="s">
-        <v>85</v>
-      </c>
-      <c r="I21" s="3" t="s">
-        <v>207</v>
-      </c>
       <c r="J21" s="3" t="s">
+        <v>206</v>
+      </c>
+      <c r="K21" s="3" t="s">
+        <v>207</v>
+      </c>
+      <c r="L21" s="3" t="s">
+        <v>206</v>
+      </c>
+      <c r="M21" s="3" t="s">
+        <v>207</v>
+      </c>
+      <c r="N21" s="3" t="s">
+        <v>206</v>
+      </c>
+      <c r="O21" s="3" t="s">
         <v>208</v>
       </c>
-      <c r="K21" s="3" t="s">
+      <c r="P21" s="3" t="s">
+        <v>206</v>
+      </c>
+      <c r="Q21" s="3" t="s">
         <v>209</v>
-      </c>
-      <c r="L21" s="3" t="s">
-        <v>208</v>
-      </c>
-      <c r="M21" s="3" t="s">
-        <v>209</v>
-      </c>
-      <c r="N21" s="3" t="s">
-        <v>208</v>
-      </c>
-      <c r="O21" s="3" t="s">
-        <v>210</v>
-      </c>
-      <c r="P21" s="3" t="s">
-        <v>208</v>
-      </c>
-      <c r="Q21" s="3" t="s">
-        <v>211</v>
       </c>
     </row>
     <row r="22" spans="1:17" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A22" s="3" t="s">
-        <v>150</v>
+        <v>156</v>
       </c>
       <c r="B22" s="3" t="s">
-        <v>370</v>
+        <v>368</v>
       </c>
       <c r="C22" s="3" t="s">
-        <v>212</v>
+        <v>210</v>
       </c>
       <c r="D22" s="3" t="s">
-        <v>213</v>
+        <v>211</v>
       </c>
       <c r="E22" s="3" t="s">
+        <v>202</v>
+      </c>
+      <c r="F22" s="3" t="s">
+        <v>203</v>
+      </c>
+      <c r="G22" s="3" t="s">
         <v>204</v>
       </c>
-      <c r="F22" s="3" t="s">
+      <c r="H22" s="3" t="s">
+        <v>85</v>
+      </c>
+      <c r="I22" s="3" t="s">
         <v>205</v>
       </c>
-      <c r="G22" s="3" t="s">
-        <v>206</v>
-      </c>
-      <c r="H22" s="3" t="s">
-        <v>85</v>
-      </c>
-      <c r="I22" s="3" t="s">
-        <v>207</v>
-      </c>
       <c r="J22" s="3" t="s">
+        <v>206</v>
+      </c>
+      <c r="K22" s="3" t="s">
+        <v>207</v>
+      </c>
+      <c r="L22" s="3" t="s">
+        <v>206</v>
+      </c>
+      <c r="M22" s="3" t="s">
+        <v>207</v>
+      </c>
+      <c r="N22" s="3" t="s">
+        <v>206</v>
+      </c>
+      <c r="O22" s="3" t="s">
         <v>208</v>
       </c>
-      <c r="K22" s="3" t="s">
+      <c r="P22" s="3" t="s">
+        <v>206</v>
+      </c>
+      <c r="Q22" s="3" t="s">
         <v>209</v>
-      </c>
-      <c r="L22" s="3" t="s">
-        <v>208</v>
-      </c>
-      <c r="M22" s="3" t="s">
-        <v>209</v>
-      </c>
-      <c r="N22" s="3" t="s">
-        <v>208</v>
-      </c>
-      <c r="O22" s="3" t="s">
-        <v>210</v>
-      </c>
-      <c r="P22" s="3" t="s">
-        <v>208</v>
-      </c>
-      <c r="Q22" s="3" t="s">
-        <v>211</v>
       </c>
     </row>
     <row r="23" spans="1:17" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A23" s="3" t="s">
-        <v>154</v>
+        <v>157</v>
       </c>
       <c r="B23" s="3" t="s">
-        <v>371</v>
+        <v>369</v>
       </c>
       <c r="C23" s="3" t="s">
-        <v>212</v>
+        <v>210</v>
       </c>
       <c r="D23" s="3" t="s">
-        <v>213</v>
+        <v>211</v>
       </c>
       <c r="E23" s="3" t="s">
+        <v>202</v>
+      </c>
+      <c r="F23" s="3" t="s">
+        <v>203</v>
+      </c>
+      <c r="G23" s="3" t="s">
         <v>204</v>
       </c>
-      <c r="F23" s="3" t="s">
+      <c r="H23" s="3" t="s">
+        <v>85</v>
+      </c>
+      <c r="I23" s="3" t="s">
         <v>205</v>
       </c>
-      <c r="G23" s="3" t="s">
-        <v>206</v>
-      </c>
-      <c r="H23" s="3" t="s">
-        <v>85</v>
-      </c>
-      <c r="I23" s="3" t="s">
-        <v>207</v>
-      </c>
       <c r="J23" s="3" t="s">
+        <v>206</v>
+      </c>
+      <c r="K23" s="3" t="s">
+        <v>207</v>
+      </c>
+      <c r="L23" s="3" t="s">
+        <v>206</v>
+      </c>
+      <c r="M23" s="3" t="s">
+        <v>207</v>
+      </c>
+      <c r="N23" s="3" t="s">
+        <v>206</v>
+      </c>
+      <c r="O23" s="3" t="s">
         <v>208</v>
       </c>
-      <c r="K23" s="3" t="s">
+      <c r="P23" s="3" t="s">
+        <v>206</v>
+      </c>
+      <c r="Q23" s="3" t="s">
         <v>209</v>
-      </c>
-      <c r="L23" s="3" t="s">
-        <v>208</v>
-      </c>
-      <c r="M23" s="3" t="s">
-        <v>209</v>
-      </c>
-      <c r="N23" s="3" t="s">
-        <v>208</v>
-      </c>
-      <c r="O23" s="3" t="s">
-        <v>210</v>
-      </c>
-      <c r="P23" s="3" t="s">
-        <v>208</v>
-      </c>
-      <c r="Q23" s="3" t="s">
-        <v>211</v>
       </c>
     </row>
     <row r="24" spans="1:17" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A24" s="3" t="s">
-        <v>156</v>
+        <v>158</v>
       </c>
       <c r="B24" s="3" t="s">
-        <v>372</v>
+        <v>370</v>
       </c>
       <c r="C24" s="3" t="s">
-        <v>212</v>
+        <v>210</v>
       </c>
       <c r="D24" s="3" t="s">
-        <v>213</v>
+        <v>211</v>
       </c>
       <c r="E24" s="3" t="s">
+        <v>202</v>
+      </c>
+      <c r="F24" s="3" t="s">
+        <v>203</v>
+      </c>
+      <c r="G24" s="3" t="s">
         <v>204</v>
       </c>
-      <c r="F24" s="3" t="s">
+      <c r="H24" s="3" t="s">
+        <v>85</v>
+      </c>
+      <c r="I24" s="3" t="s">
         <v>205</v>
       </c>
-      <c r="G24" s="3" t="s">
-        <v>206</v>
-      </c>
-      <c r="H24" s="3" t="s">
-        <v>85</v>
-      </c>
-      <c r="I24" s="3" t="s">
-        <v>207</v>
-      </c>
       <c r="J24" s="3" t="s">
+        <v>206</v>
+      </c>
+      <c r="K24" s="3" t="s">
+        <v>207</v>
+      </c>
+      <c r="L24" s="3" t="s">
+        <v>206</v>
+      </c>
+      <c r="M24" s="3" t="s">
+        <v>207</v>
+      </c>
+      <c r="N24" s="3" t="s">
+        <v>206</v>
+      </c>
+      <c r="O24" s="3" t="s">
         <v>208</v>
       </c>
-      <c r="K24" s="3" t="s">
+      <c r="P24" s="3" t="s">
+        <v>206</v>
+      </c>
+      <c r="Q24" s="3" t="s">
         <v>209</v>
-      </c>
-      <c r="L24" s="3" t="s">
-        <v>208</v>
-      </c>
-      <c r="M24" s="3" t="s">
-        <v>209</v>
-      </c>
-      <c r="N24" s="3" t="s">
-        <v>208</v>
-      </c>
-      <c r="O24" s="3" t="s">
-        <v>210</v>
-      </c>
-      <c r="P24" s="3" t="s">
-        <v>208</v>
-      </c>
-      <c r="Q24" s="3" t="s">
-        <v>211</v>
       </c>
     </row>
     <row r="25" spans="1:17" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A25" s="3" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="B25" s="3" t="s">
-        <v>373</v>
+        <v>371</v>
       </c>
       <c r="C25" s="3" t="s">
-        <v>212</v>
+        <v>210</v>
       </c>
       <c r="D25" s="3" t="s">
-        <v>213</v>
+        <v>211</v>
       </c>
       <c r="E25" s="3" t="s">
+        <v>202</v>
+      </c>
+      <c r="F25" s="3" t="s">
+        <v>203</v>
+      </c>
+      <c r="G25" s="3" t="s">
         <v>204</v>
       </c>
-      <c r="F25" s="3" t="s">
+      <c r="H25" s="3" t="s">
+        <v>85</v>
+      </c>
+      <c r="I25" s="3" t="s">
         <v>205</v>
       </c>
-      <c r="G25" s="3" t="s">
-        <v>206</v>
-      </c>
-      <c r="H25" s="3" t="s">
-        <v>85</v>
-      </c>
-      <c r="I25" s="3" t="s">
-        <v>207</v>
-      </c>
       <c r="J25" s="3" t="s">
+        <v>206</v>
+      </c>
+      <c r="K25" s="3" t="s">
+        <v>207</v>
+      </c>
+      <c r="L25" s="3" t="s">
+        <v>206</v>
+      </c>
+      <c r="M25" s="3" t="s">
+        <v>207</v>
+      </c>
+      <c r="N25" s="3" t="s">
+        <v>206</v>
+      </c>
+      <c r="O25" s="3" t="s">
         <v>208</v>
       </c>
-      <c r="K25" s="3" t="s">
+      <c r="P25" s="3" t="s">
+        <v>206</v>
+      </c>
+      <c r="Q25" s="3" t="s">
         <v>209</v>
-      </c>
-      <c r="L25" s="3" t="s">
-        <v>208</v>
-      </c>
-      <c r="M25" s="3" t="s">
-        <v>209</v>
-      </c>
-      <c r="N25" s="3" t="s">
-        <v>208</v>
-      </c>
-      <c r="O25" s="3" t="s">
-        <v>210</v>
-      </c>
-      <c r="P25" s="3" t="s">
-        <v>208</v>
-      </c>
-      <c r="Q25" s="3" t="s">
-        <v>211</v>
       </c>
     </row>
     <row r="26" spans="1:17" ht="45" customHeight="1" x14ac:dyDescent="0.25">
@@ -8574,105 +8568,105 @@
         <v>160</v>
       </c>
       <c r="B26" s="3" t="s">
-        <v>374</v>
+        <v>372</v>
       </c>
       <c r="C26" s="3" t="s">
-        <v>212</v>
+        <v>210</v>
       </c>
       <c r="D26" s="3" t="s">
-        <v>213</v>
+        <v>211</v>
       </c>
       <c r="E26" s="3" t="s">
+        <v>202</v>
+      </c>
+      <c r="F26" s="3" t="s">
+        <v>203</v>
+      </c>
+      <c r="G26" s="3" t="s">
         <v>204</v>
       </c>
-      <c r="F26" s="3" t="s">
+      <c r="H26" s="3" t="s">
+        <v>85</v>
+      </c>
+      <c r="I26" s="3" t="s">
         <v>205</v>
       </c>
-      <c r="G26" s="3" t="s">
-        <v>206</v>
-      </c>
-      <c r="H26" s="3" t="s">
-        <v>85</v>
-      </c>
-      <c r="I26" s="3" t="s">
-        <v>207</v>
-      </c>
       <c r="J26" s="3" t="s">
+        <v>206</v>
+      </c>
+      <c r="K26" s="3" t="s">
+        <v>207</v>
+      </c>
+      <c r="L26" s="3" t="s">
+        <v>206</v>
+      </c>
+      <c r="M26" s="3" t="s">
+        <v>207</v>
+      </c>
+      <c r="N26" s="3" t="s">
+        <v>206</v>
+      </c>
+      <c r="O26" s="3" t="s">
         <v>208</v>
       </c>
-      <c r="K26" s="3" t="s">
+      <c r="P26" s="3" t="s">
+        <v>206</v>
+      </c>
+      <c r="Q26" s="3" t="s">
         <v>209</v>
-      </c>
-      <c r="L26" s="3" t="s">
-        <v>208</v>
-      </c>
-      <c r="M26" s="3" t="s">
-        <v>209</v>
-      </c>
-      <c r="N26" s="3" t="s">
-        <v>208</v>
-      </c>
-      <c r="O26" s="3" t="s">
-        <v>210</v>
-      </c>
-      <c r="P26" s="3" t="s">
-        <v>208</v>
-      </c>
-      <c r="Q26" s="3" t="s">
-        <v>211</v>
       </c>
     </row>
     <row r="27" spans="1:17" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A27" s="3" t="s">
-        <v>163</v>
+        <v>161</v>
       </c>
       <c r="B27" s="3" t="s">
-        <v>375</v>
+        <v>373</v>
       </c>
       <c r="C27" s="3" t="s">
-        <v>212</v>
+        <v>210</v>
       </c>
       <c r="D27" s="3" t="s">
-        <v>213</v>
+        <v>211</v>
       </c>
       <c r="E27" s="3" t="s">
+        <v>202</v>
+      </c>
+      <c r="F27" s="3" t="s">
+        <v>203</v>
+      </c>
+      <c r="G27" s="3" t="s">
         <v>204</v>
       </c>
-      <c r="F27" s="3" t="s">
+      <c r="H27" s="3" t="s">
+        <v>85</v>
+      </c>
+      <c r="I27" s="3" t="s">
         <v>205</v>
       </c>
-      <c r="G27" s="3" t="s">
-        <v>206</v>
-      </c>
-      <c r="H27" s="3" t="s">
-        <v>85</v>
-      </c>
-      <c r="I27" s="3" t="s">
-        <v>207</v>
-      </c>
       <c r="J27" s="3" t="s">
+        <v>206</v>
+      </c>
+      <c r="K27" s="3" t="s">
+        <v>207</v>
+      </c>
+      <c r="L27" s="3" t="s">
+        <v>206</v>
+      </c>
+      <c r="M27" s="3" t="s">
+        <v>207</v>
+      </c>
+      <c r="N27" s="3" t="s">
+        <v>206</v>
+      </c>
+      <c r="O27" s="3" t="s">
         <v>208</v>
       </c>
-      <c r="K27" s="3" t="s">
+      <c r="P27" s="3" t="s">
+        <v>206</v>
+      </c>
+      <c r="Q27" s="3" t="s">
         <v>209</v>
-      </c>
-      <c r="L27" s="3" t="s">
-        <v>208</v>
-      </c>
-      <c r="M27" s="3" t="s">
-        <v>209</v>
-      </c>
-      <c r="N27" s="3" t="s">
-        <v>208</v>
-      </c>
-      <c r="O27" s="3" t="s">
-        <v>210</v>
-      </c>
-      <c r="P27" s="3" t="s">
-        <v>208</v>
-      </c>
-      <c r="Q27" s="3" t="s">
-        <v>211</v>
       </c>
     </row>
   </sheetData>
@@ -8698,132 +8692,132 @@
   <sheetData>
     <row r="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
-        <v>255</v>
+        <v>253</v>
       </c>
     </row>
     <row r="2" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>249</v>
+        <v>247</v>
       </c>
     </row>
     <row r="3" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>248</v>
+        <v>246</v>
       </c>
     </row>
     <row r="4" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>239</v>
+        <v>237</v>
       </c>
     </row>
     <row r="5" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>242</v>
+        <v>240</v>
       </c>
     </row>
     <row r="6" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>240</v>
+        <v>238</v>
       </c>
     </row>
     <row r="7" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>204</v>
+        <v>202</v>
       </c>
     </row>
     <row r="8" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>238</v>
+        <v>236</v>
       </c>
     </row>
     <row r="9" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>243</v>
+        <v>241</v>
       </c>
     </row>
     <row r="10" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>245</v>
+        <v>243</v>
       </c>
     </row>
     <row r="11" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>260</v>
+        <v>258</v>
       </c>
     </row>
     <row r="12" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>247</v>
+        <v>245</v>
       </c>
     </row>
     <row r="13" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>376</v>
+        <v>374</v>
       </c>
     </row>
     <row r="14" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>281</v>
+        <v>279</v>
       </c>
     </row>
     <row r="15" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>257</v>
+        <v>255</v>
       </c>
     </row>
     <row r="16" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>252</v>
+        <v>250</v>
       </c>
     </row>
     <row r="17" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>259</v>
+        <v>257</v>
       </c>
     </row>
     <row r="18" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>258</v>
+        <v>256</v>
       </c>
     </row>
     <row r="19" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>244</v>
+        <v>242</v>
       </c>
     </row>
     <row r="20" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>254</v>
+        <v>252</v>
       </c>
     </row>
     <row r="21" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>253</v>
+        <v>251</v>
       </c>
     </row>
     <row r="22" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
-        <v>241</v>
+        <v>239</v>
       </c>
     </row>
     <row r="23" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
-        <v>377</v>
+        <v>375</v>
       </c>
     </row>
     <row r="24" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
-        <v>250</v>
+        <v>248</v>
       </c>
     </row>
     <row r="25" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
-        <v>251</v>
+        <v>249</v>
       </c>
     </row>
     <row r="26" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
-        <v>246</v>
+        <v>244</v>
       </c>
     </row>
   </sheetData>
@@ -8838,207 +8832,207 @@
   <sheetData>
     <row r="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
     </row>
     <row r="2" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>253</v>
+        <v>251</v>
       </c>
     </row>
     <row r="3" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>262</v>
+        <v>260</v>
       </c>
     </row>
     <row r="4" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>263</v>
+        <v>261</v>
       </c>
     </row>
     <row r="5" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>264</v>
+        <v>262</v>
       </c>
     </row>
     <row r="6" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>265</v>
+        <v>263</v>
       </c>
     </row>
     <row r="7" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>207</v>
+        <v>205</v>
       </c>
     </row>
     <row r="8" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>266</v>
+        <v>264</v>
       </c>
     </row>
     <row r="9" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>267</v>
+        <v>265</v>
       </c>
     </row>
     <row r="10" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>268</v>
+        <v>266</v>
       </c>
     </row>
     <row r="11" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>269</v>
+        <v>267</v>
       </c>
     </row>
     <row r="12" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>270</v>
+        <v>268</v>
       </c>
     </row>
     <row r="13" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>271</v>
+        <v>269</v>
       </c>
     </row>
     <row r="14" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>272</v>
+        <v>270</v>
       </c>
     </row>
     <row r="15" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>273</v>
+        <v>271</v>
       </c>
     </row>
     <row r="16" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>274</v>
+        <v>272</v>
       </c>
     </row>
     <row r="17" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>275</v>
+        <v>273</v>
       </c>
     </row>
     <row r="18" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>276</v>
+        <v>274</v>
       </c>
     </row>
     <row r="19" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>277</v>
+        <v>275</v>
       </c>
     </row>
     <row r="20" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>278</v>
+        <v>276</v>
       </c>
     </row>
     <row r="21" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>279</v>
+        <v>277</v>
       </c>
     </row>
     <row r="22" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
-        <v>280</v>
+        <v>278</v>
       </c>
     </row>
     <row r="23" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
-        <v>249</v>
+        <v>247</v>
       </c>
     </row>
     <row r="24" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
-        <v>281</v>
+        <v>279</v>
       </c>
     </row>
     <row r="25" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
-        <v>282</v>
+        <v>280</v>
       </c>
     </row>
     <row r="26" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
-        <v>283</v>
+        <v>281</v>
       </c>
     </row>
     <row r="27" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
-        <v>284</v>
+        <v>282</v>
       </c>
     </row>
     <row r="28" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
-        <v>285</v>
+        <v>283</v>
       </c>
     </row>
     <row r="29" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
-        <v>286</v>
+        <v>284</v>
       </c>
     </row>
     <row r="30" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
-        <v>287</v>
+        <v>285</v>
       </c>
     </row>
     <row r="31" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
-        <v>288</v>
+        <v>286</v>
       </c>
     </row>
     <row r="32" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
-        <v>289</v>
+        <v>287</v>
       </c>
     </row>
     <row r="33" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
-        <v>290</v>
+        <v>288</v>
       </c>
     </row>
     <row r="34" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
-        <v>291</v>
+        <v>289</v>
       </c>
     </row>
     <row r="35" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
-        <v>292</v>
+        <v>290</v>
       </c>
     </row>
     <row r="36" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
-        <v>293</v>
+        <v>291</v>
       </c>
     </row>
     <row r="37" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
-        <v>294</v>
+        <v>292</v>
       </c>
     </row>
     <row r="38" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
-        <v>295</v>
+        <v>293</v>
       </c>
     </row>
     <row r="39" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
-        <v>296</v>
+        <v>294</v>
       </c>
     </row>
     <row r="40" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
-        <v>297</v>
+        <v>295</v>
       </c>
     </row>
     <row r="41" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
-        <v>298</v>
+        <v>296</v>
       </c>
     </row>
   </sheetData>
